--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-09-24 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-09-25 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">80 dòng × 7 chỉ số · 2026-07-05 → 2026-09-22</t>
+    <t xml:space="preserve">81 dòng × 7 chỉ số · 2026-07-05 → 2026-09-23</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">44 dòng × 14 chỉ số · 2026-07-23 → 2026-09-24</t>
+    <t xml:space="preserve">45 dòng × 14 chỉ số · 2026-07-23 → 2026-09-25</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">44 dòng × 14 chỉ số · 2026-06-30 → 2026-09-24</t>
+    <t xml:space="preserve">45 dòng × 14 chỉ số · 2026-06-30 → 2026-09-25</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">41 dòng × 11 chỉ số · 2026-07-27 → 2026-09-24</t>
+    <t xml:space="preserve">42 dòng × 11 chỉ số · 2026-07-27 → 2026-09-25</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 80 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 81 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 44 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 45 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 44 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 45 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 41 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 42 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -978,7 +978,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3130,6 +3130,32 @@
       </c>
       <c r="H85" s="16" t="n">
         <v>29</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="15" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B86" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>187</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="F86" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H86" s="16" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3148,7 +3174,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5330,6 +5356,53 @@
       </c>
       <c r="O49" s="16" t="n">
         <v>634</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B50" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>135</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>4560</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>486</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="I50" s="16" t="n">
+        <v>2422</v>
+      </c>
+      <c r="J50" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K50" s="16" t="n">
+        <v>1328</v>
+      </c>
+      <c r="L50" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="M50" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="N50" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" s="16" t="n">
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -5348,7 +5421,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7434,6 +7507,53 @@
       </c>
       <c r="O49" s="16" t="n">
         <v>328</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B50" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>699</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>663</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>584</v>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>399</v>
+      </c>
+      <c r="I50" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="J50" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K50" s="16" t="n">
+        <v>1034</v>
+      </c>
+      <c r="L50" s="19" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="M50" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="N50" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O50" s="16" t="n">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -7452,7 +7572,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8968,6 +9088,44 @@
       </c>
       <c r="L46" s="16" t="n">
         <v>239199</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H47" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="J47" s="16" t="n">
+        <v>336</v>
+      </c>
+      <c r="K47" s="16" t="n">
+        <v>274</v>
+      </c>
+      <c r="L47" s="16" t="n">
+        <v>239208</v>
       </c>
     </row>
   </sheetData>
@@ -9032,16 +9190,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>111</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9049,16 +9207,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>341</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9066,16 +9224,16 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>3782</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>3969</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9083,16 +9241,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>349</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>380</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9100,16 +9258,16 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>11</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9117,16 +9275,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>140</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>147</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9134,16 +9292,16 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H85,'Social — theo ngày'!$A$6:$A$85,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$85,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2112</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2157</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9178,7 +9336,7 @@
         <v>115</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B49</f>
+        <f aca="false">'Social — 28 ngày'!B50</f>
         <v>116</v>
       </c>
     </row>
@@ -9195,8 +9353,8 @@
         <v>184</v>
       </c>
       <c r="D18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C49</f>
-        <v>137</v>
+        <f aca="false">'Social — 28 ngày'!C50</f>
+        <v>135</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9212,8 +9370,8 @@
         <v>4735</v>
       </c>
       <c r="D19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D49</f>
-        <v>4514</v>
+        <f aca="false">'Social — 28 ngày'!D50</f>
+        <v>4560</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9229,8 +9387,8 @@
         <v>280</v>
       </c>
       <c r="D20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E49</f>
-        <v>455</v>
+        <f aca="false">'Social — 28 ngày'!E50</f>
+        <v>486</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9246,7 +9404,7 @@
         <v>47</v>
       </c>
       <c r="D21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F49</f>
+        <f aca="false">'Social — 28 ngày'!F50</f>
         <v>49</v>
       </c>
     </row>
@@ -9263,8 +9421,8 @@
         <v>68</v>
       </c>
       <c r="D22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G49</f>
-        <v>13</v>
+        <f aca="false">'Social — 28 ngày'!G50</f>
+        <v>15</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9280,7 +9438,7 @@
         <v>275</v>
       </c>
       <c r="D23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H49</f>
+        <f aca="false">'Social — 28 ngày'!H50</f>
         <v>86</v>
       </c>
     </row>
@@ -9297,8 +9455,8 @@
         <v>1039</v>
       </c>
       <c r="D24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I49</f>
-        <v>2485</v>
+        <f aca="false">'Social — 28 ngày'!I50</f>
+        <v>2422</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9314,7 +9472,7 @@
         <v>100</v>
       </c>
       <c r="D25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J49</f>
+        <f aca="false">'Social — 28 ngày'!J50</f>
         <v>102</v>
       </c>
     </row>
@@ -9331,8 +9489,8 @@
         <v>1691</v>
       </c>
       <c r="D26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K49</f>
-        <v>1320</v>
+        <f aca="false">'Social — 28 ngày'!K50</f>
+        <v>1328</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9348,8 +9506,8 @@
         <v>127</v>
       </c>
       <c r="D27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L49</f>
-        <v>36</v>
+        <f aca="false">'Social — 28 ngày'!L50</f>
+        <v>33</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9365,8 +9523,8 @@
         <v>86</v>
       </c>
       <c r="D28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M49</f>
-        <v>58</v>
+        <f aca="false">'Social — 28 ngày'!M50</f>
+        <v>59</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9382,7 +9540,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N49</f>
+        <f aca="false">'Social — 28 ngày'!N50</f>
         <v>4</v>
       </c>
     </row>
@@ -9399,8 +9557,8 @@
         <v>59</v>
       </c>
       <c r="D30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O49</f>
-        <v>634</v>
+        <f aca="false">'Social — 28 ngày'!O50</f>
+        <v>635</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9442,7 +9600,7 @@
         <v>21</v>
       </c>
       <c r="E34" s="24" t="n">
-        <f aca="false">SEO!B49</f>
+        <f aca="false">SEO!B50</f>
         <v>12</v>
       </c>
     </row>
@@ -9463,8 +9621,8 @@
         <v>364</v>
       </c>
       <c r="E35" s="24" t="n">
-        <f aca="false">SEO!C49</f>
-        <v>697</v>
+        <f aca="false">SEO!C50</f>
+        <v>699</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9484,8 +9642,8 @@
         <v>349</v>
       </c>
       <c r="E36" s="24" t="n">
-        <f aca="false">SEO!D49</f>
-        <v>661</v>
+        <f aca="false">SEO!D50</f>
+        <v>663</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9505,8 +9663,8 @@
         <v>42.93</v>
       </c>
       <c r="E37" s="24" t="n">
-        <f aca="false">SEO!E49</f>
-        <v>36.87</v>
+        <f aca="false">SEO!E50</f>
+        <v>33.9</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9526,8 +9684,8 @@
         <v>7</v>
       </c>
       <c r="E38" s="24" t="n">
-        <f aca="false">SEO!F49</f>
-        <v>1</v>
+        <f aca="false">SEO!F50</f>
+        <v>3</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9547,8 +9705,8 @@
         <v>375</v>
       </c>
       <c r="E39" s="24" t="n">
-        <f aca="false">SEO!G49</f>
-        <v>575</v>
+        <f aca="false">SEO!G50</f>
+        <v>584</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9568,8 +9726,8 @@
         <v>204</v>
       </c>
       <c r="E40" s="24" t="n">
-        <f aca="false">SEO!H49</f>
-        <v>383</v>
+        <f aca="false">SEO!H50</f>
+        <v>399</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9589,7 +9747,7 @@
         <v>67</v>
       </c>
       <c r="E41" s="24" t="n">
-        <f aca="false">SEO!I49</f>
+        <f aca="false">SEO!I50</f>
         <v>34</v>
       </c>
     </row>
@@ -9610,8 +9768,8 @@
         <v>3.8</v>
       </c>
       <c r="E42" s="24" t="n">
-        <f aca="false">SEO!J49</f>
-        <v>3.1</v>
+        <f aca="false">SEO!J50</f>
+        <v>3.3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9631,8 +9789,8 @@
         <v>1757</v>
       </c>
       <c r="E43" s="24" t="n">
-        <f aca="false">SEO!K49</f>
-        <v>1087</v>
+        <f aca="false">SEO!K50</f>
+        <v>1034</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9652,8 +9810,8 @@
         <v>29.4</v>
       </c>
       <c r="E44" s="24" t="n">
-        <f aca="false">SEO!L49</f>
-        <v>31.1</v>
+        <f aca="false">SEO!L50</f>
+        <v>29.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9673,8 +9831,8 @@
         <v>151</v>
       </c>
       <c r="E45" s="24" t="n">
-        <f aca="false">SEO!M49</f>
-        <v>95</v>
+        <f aca="false">SEO!M50</f>
+        <v>86</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9694,7 +9852,7 @@
         <v>95</v>
       </c>
       <c r="E46" s="24" t="n">
-        <f aca="false">SEO!N49</f>
+        <f aca="false">SEO!N50</f>
         <v>119</v>
       </c>
     </row>
@@ -9715,8 +9873,8 @@
         <v>1022</v>
       </c>
       <c r="E47" s="24" t="n">
-        <f aca="false">SEO!O49</f>
-        <v>328</v>
+        <f aca="false">SEO!O50</f>
+        <v>336</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9751,7 +9909,7 @@
         <v>88</v>
       </c>
       <c r="D51" s="24" t="n">
-        <f aca="false">Audit!B46</f>
+        <f aca="false">Audit!B47</f>
         <v>92</v>
       </c>
     </row>
@@ -9768,8 +9926,8 @@
         <v>97</v>
       </c>
       <c r="D52" s="24" t="n">
-        <f aca="false">Audit!C46</f>
-        <v>92</v>
+        <f aca="false">Audit!C47</f>
+        <v>93</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9785,7 +9943,7 @@
         <v>92</v>
       </c>
       <c r="D53" s="24" t="n">
-        <f aca="false">Audit!D46</f>
+        <f aca="false">Audit!D47</f>
         <v>93</v>
       </c>
     </row>
@@ -9802,7 +9960,7 @@
         <v>91</v>
       </c>
       <c r="D54" s="24" t="n">
-        <f aca="false">Audit!E46</f>
+        <f aca="false">Audit!E47</f>
         <v>92</v>
       </c>
     </row>
@@ -9819,7 +9977,7 @@
         <v>91</v>
       </c>
       <c r="D55" s="24" t="n">
-        <f aca="false">Audit!F46</f>
+        <f aca="false">Audit!F47</f>
         <v>118</v>
       </c>
     </row>
@@ -9836,8 +9994,8 @@
         <v>88</v>
       </c>
       <c r="D56" s="24" t="n">
-        <f aca="false">Audit!G46</f>
-        <v>99</v>
+        <f aca="false">Audit!G47</f>
+        <v>98</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9853,7 +10011,7 @@
         <v>92</v>
       </c>
       <c r="D57" s="24" t="n">
-        <f aca="false">Audit!H46</f>
+        <f aca="false">Audit!H47</f>
         <v>119</v>
       </c>
     </row>
@@ -9870,7 +10028,7 @@
         <v>96</v>
       </c>
       <c r="D58" s="24" t="n">
-        <f aca="false">Audit!I46</f>
+        <f aca="false">Audit!I47</f>
         <v>88</v>
       </c>
     </row>
@@ -9887,8 +10045,8 @@
         <v>862</v>
       </c>
       <c r="D59" s="24" t="n">
-        <f aca="false">Audit!J46</f>
-        <v>328</v>
+        <f aca="false">Audit!J47</f>
+        <v>336</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9904,8 +10062,8 @@
         <v>0</v>
       </c>
       <c r="D60" s="24" t="n">
-        <f aca="false">Audit!K46</f>
-        <v>267</v>
+        <f aca="false">Audit!K47</f>
+        <v>274</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9921,8 +10079,8 @@
         <v>0</v>
       </c>
       <c r="D61" s="24" t="n">
-        <f aca="false">Audit!L46</f>
-        <v>239199</v>
+        <f aca="false">Audit!L47</f>
+        <v>239208</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-09-25 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-09-26 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">81 dòng × 7 chỉ số · 2026-07-05 → 2026-09-23</t>
+    <t xml:space="preserve">82 dòng × 7 chỉ số · 2026-07-05 → 2026-09-24</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">45 dòng × 14 chỉ số · 2026-07-23 → 2026-09-25</t>
+    <t xml:space="preserve">46 dòng × 14 chỉ số · 2026-07-23 → 2026-09-26</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">45 dòng × 14 chỉ số · 2026-06-30 → 2026-09-25</t>
+    <t xml:space="preserve">46 dòng × 14 chỉ số · 2026-06-30 → 2026-09-26</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">42 dòng × 11 chỉ số · 2026-07-27 → 2026-09-25</t>
+    <t xml:space="preserve">43 dòng × 11 chỉ số · 2026-07-27 → 2026-09-26</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 81 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 82 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 45 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 46 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 45 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 46 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 42 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 43 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -978,7 +978,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3156,6 +3156,32 @@
       </c>
       <c r="H86" s="16" t="n">
         <v>45</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="15" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B87" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" s="16" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3174,7 +3200,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5403,6 +5429,53 @@
       </c>
       <c r="O50" s="16" t="n">
         <v>635</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B51" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>4509</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>433</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="I51" s="16" t="n">
+        <v>2397</v>
+      </c>
+      <c r="J51" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K51" s="16" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L51" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="M51" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -5421,7 +5494,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7554,6 +7627,53 @@
       </c>
       <c r="O50" s="16" t="n">
         <v>336</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B51" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>701</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>665</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>558</v>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>387</v>
+      </c>
+      <c r="I51" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="J51" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K51" s="16" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L51" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="M51" s="16" t="n">
+        <v>81</v>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -7572,7 +7692,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9126,6 +9246,44 @@
       </c>
       <c r="L47" s="16" t="n">
         <v>239208</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B48" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>96</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H48" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I48" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <v>337</v>
+      </c>
+      <c r="K48" s="16" t="n">
+        <v>271</v>
+      </c>
+      <c r="L48" s="16" t="n">
+        <v>239577</v>
       </c>
     </row>
   </sheetData>
@@ -9190,16 +9348,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>118</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>124</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9207,16 +9365,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>345</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>347</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9224,16 +9382,16 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>3969</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>4093</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9241,16 +9399,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>380</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>396</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9258,15 +9416,15 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>13</v>
       </c>
     </row>
@@ -9275,16 +9433,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>147</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>149</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9292,16 +9450,16 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H86,'Social — theo ngày'!$A$6:$A$86,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$86,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2157</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2186</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9336,7 +9494,7 @@
         <v>115</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B50</f>
+        <f aca="false">'Social — 28 ngày'!B51</f>
         <v>116</v>
       </c>
     </row>
@@ -9353,8 +9511,8 @@
         <v>184</v>
       </c>
       <c r="D18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C50</f>
-        <v>135</v>
+        <f aca="false">'Social — 28 ngày'!C51</f>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9370,8 +9528,8 @@
         <v>4735</v>
       </c>
       <c r="D19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D50</f>
-        <v>4560</v>
+        <f aca="false">'Social — 28 ngày'!D51</f>
+        <v>4509</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9387,8 +9545,8 @@
         <v>280</v>
       </c>
       <c r="D20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E50</f>
-        <v>486</v>
+        <f aca="false">'Social — 28 ngày'!E51</f>
+        <v>433</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9404,7 +9562,7 @@
         <v>47</v>
       </c>
       <c r="D21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F50</f>
+        <f aca="false">'Social — 28 ngày'!F51</f>
         <v>49</v>
       </c>
     </row>
@@ -9421,7 +9579,7 @@
         <v>68</v>
       </c>
       <c r="D22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G50</f>
+        <f aca="false">'Social — 28 ngày'!G51</f>
         <v>15</v>
       </c>
     </row>
@@ -9438,7 +9596,7 @@
         <v>275</v>
       </c>
       <c r="D23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H50</f>
+        <f aca="false">'Social — 28 ngày'!H51</f>
         <v>86</v>
       </c>
     </row>
@@ -9455,8 +9613,8 @@
         <v>1039</v>
       </c>
       <c r="D24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I50</f>
-        <v>2422</v>
+        <f aca="false">'Social — 28 ngày'!I51</f>
+        <v>2397</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9472,7 +9630,7 @@
         <v>100</v>
       </c>
       <c r="D25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J50</f>
+        <f aca="false">'Social — 28 ngày'!J51</f>
         <v>102</v>
       </c>
     </row>
@@ -9489,8 +9647,8 @@
         <v>1691</v>
       </c>
       <c r="D26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K50</f>
-        <v>1328</v>
+        <f aca="false">'Social — 28 ngày'!K51</f>
+        <v>1229</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9506,8 +9664,8 @@
         <v>127</v>
       </c>
       <c r="D27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L50</f>
-        <v>33</v>
+        <f aca="false">'Social — 28 ngày'!L51</f>
+        <v>28</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9523,8 +9681,8 @@
         <v>86</v>
       </c>
       <c r="D28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M50</f>
-        <v>59</v>
+        <f aca="false">'Social — 28 ngày'!M51</f>
+        <v>44</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9540,7 +9698,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N50</f>
+        <f aca="false">'Social — 28 ngày'!N51</f>
         <v>4</v>
       </c>
     </row>
@@ -9557,8 +9715,8 @@
         <v>59</v>
       </c>
       <c r="D30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O50</f>
-        <v>635</v>
+        <f aca="false">'Social — 28 ngày'!O51</f>
+        <v>634</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9600,8 +9758,8 @@
         <v>21</v>
       </c>
       <c r="E34" s="24" t="n">
-        <f aca="false">SEO!B50</f>
-        <v>12</v>
+        <f aca="false">SEO!B51</f>
+        <v>14</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9621,8 +9779,8 @@
         <v>364</v>
       </c>
       <c r="E35" s="24" t="n">
-        <f aca="false">SEO!C50</f>
-        <v>699</v>
+        <f aca="false">SEO!C51</f>
+        <v>701</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9642,8 +9800,8 @@
         <v>349</v>
       </c>
       <c r="E36" s="24" t="n">
-        <f aca="false">SEO!D50</f>
-        <v>663</v>
+        <f aca="false">SEO!D51</f>
+        <v>665</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9663,8 +9821,8 @@
         <v>42.93</v>
       </c>
       <c r="E37" s="24" t="n">
-        <f aca="false">SEO!E50</f>
-        <v>33.9</v>
+        <f aca="false">SEO!E51</f>
+        <v>34.59</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9684,7 +9842,7 @@
         <v>7</v>
       </c>
       <c r="E38" s="24" t="n">
-        <f aca="false">SEO!F50</f>
+        <f aca="false">SEO!F51</f>
         <v>3</v>
       </c>
     </row>
@@ -9705,8 +9863,8 @@
         <v>375</v>
       </c>
       <c r="E39" s="24" t="n">
-        <f aca="false">SEO!G50</f>
-        <v>584</v>
+        <f aca="false">SEO!G51</f>
+        <v>558</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9726,8 +9884,8 @@
         <v>204</v>
       </c>
       <c r="E40" s="24" t="n">
-        <f aca="false">SEO!H50</f>
-        <v>399</v>
+        <f aca="false">SEO!H51</f>
+        <v>387</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9747,7 +9905,7 @@
         <v>67</v>
       </c>
       <c r="E41" s="24" t="n">
-        <f aca="false">SEO!I50</f>
+        <f aca="false">SEO!I51</f>
         <v>34</v>
       </c>
     </row>
@@ -9768,8 +9926,8 @@
         <v>3.8</v>
       </c>
       <c r="E42" s="24" t="n">
-        <f aca="false">SEO!J50</f>
-        <v>3.3</v>
+        <f aca="false">SEO!J51</f>
+        <v>3.4</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9789,8 +9947,8 @@
         <v>1757</v>
       </c>
       <c r="E43" s="24" t="n">
-        <f aca="false">SEO!K50</f>
-        <v>1034</v>
+        <f aca="false">SEO!K51</f>
+        <v>1013</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9810,8 +9968,8 @@
         <v>29.4</v>
       </c>
       <c r="E44" s="24" t="n">
-        <f aca="false">SEO!L50</f>
-        <v>29.1</v>
+        <f aca="false">SEO!L51</f>
+        <v>28</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9831,8 +9989,8 @@
         <v>151</v>
       </c>
       <c r="E45" s="24" t="n">
-        <f aca="false">SEO!M50</f>
-        <v>86</v>
+        <f aca="false">SEO!M51</f>
+        <v>81</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9852,7 +10010,7 @@
         <v>95</v>
       </c>
       <c r="E46" s="24" t="n">
-        <f aca="false">SEO!N50</f>
+        <f aca="false">SEO!N51</f>
         <v>119</v>
       </c>
     </row>
@@ -9873,8 +10031,8 @@
         <v>1022</v>
       </c>
       <c r="E47" s="24" t="n">
-        <f aca="false">SEO!O50</f>
-        <v>336</v>
+        <f aca="false">SEO!O51</f>
+        <v>337</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9909,7 +10067,7 @@
         <v>88</v>
       </c>
       <c r="D51" s="24" t="n">
-        <f aca="false">Audit!B47</f>
+        <f aca="false">Audit!B48</f>
         <v>92</v>
       </c>
     </row>
@@ -9926,8 +10084,8 @@
         <v>97</v>
       </c>
       <c r="D52" s="24" t="n">
-        <f aca="false">Audit!C47</f>
-        <v>93</v>
+        <f aca="false">Audit!C48</f>
+        <v>96</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9943,8 +10101,8 @@
         <v>92</v>
       </c>
       <c r="D53" s="24" t="n">
-        <f aca="false">Audit!D47</f>
-        <v>93</v>
+        <f aca="false">Audit!D48</f>
+        <v>95</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9960,7 +10118,7 @@
         <v>91</v>
       </c>
       <c r="D54" s="24" t="n">
-        <f aca="false">Audit!E47</f>
+        <f aca="false">Audit!E48</f>
         <v>92</v>
       </c>
     </row>
@@ -9977,7 +10135,7 @@
         <v>91</v>
       </c>
       <c r="D55" s="24" t="n">
-        <f aca="false">Audit!F47</f>
+        <f aca="false">Audit!F48</f>
         <v>118</v>
       </c>
     </row>
@@ -9994,7 +10152,7 @@
         <v>88</v>
       </c>
       <c r="D56" s="24" t="n">
-        <f aca="false">Audit!G47</f>
+        <f aca="false">Audit!G48</f>
         <v>98</v>
       </c>
     </row>
@@ -10011,7 +10169,7 @@
         <v>92</v>
       </c>
       <c r="D57" s="24" t="n">
-        <f aca="false">Audit!H47</f>
+        <f aca="false">Audit!H48</f>
         <v>119</v>
       </c>
     </row>
@@ -10028,8 +10186,8 @@
         <v>96</v>
       </c>
       <c r="D58" s="24" t="n">
-        <f aca="false">Audit!I47</f>
-        <v>88</v>
+        <f aca="false">Audit!I48</f>
+        <v>92</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10045,8 +10203,8 @@
         <v>862</v>
       </c>
       <c r="D59" s="24" t="n">
-        <f aca="false">Audit!J47</f>
-        <v>336</v>
+        <f aca="false">Audit!J48</f>
+        <v>337</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10062,8 +10220,8 @@
         <v>0</v>
       </c>
       <c r="D60" s="24" t="n">
-        <f aca="false">Audit!K47</f>
-        <v>274</v>
+        <f aca="false">Audit!K48</f>
+        <v>271</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10079,8 +10237,8 @@
         <v>0</v>
       </c>
       <c r="D61" s="24" t="n">
-        <f aca="false">Audit!L47</f>
-        <v>239208</v>
+        <f aca="false">Audit!L48</f>
+        <v>239577</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-09-26 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-09-28 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">82 dòng × 7 chỉ số · 2026-07-05 → 2026-09-24</t>
+    <t xml:space="preserve">84 dòng × 7 chỉ số · 2026-07-05 → 2026-09-26</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">46 dòng × 14 chỉ số · 2026-07-23 → 2026-09-26</t>
+    <t xml:space="preserve">47 dòng × 14 chỉ số · 2026-07-23 → 2026-09-28</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">46 dòng × 14 chỉ số · 2026-06-30 → 2026-09-26</t>
+    <t xml:space="preserve">47 dòng × 14 chỉ số · 2026-06-30 → 2026-09-28</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">43 dòng × 11 chỉ số · 2026-07-27 → 2026-09-26</t>
+    <t xml:space="preserve">44 dòng × 11 chỉ số · 2026-07-27 → 2026-09-28</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 82 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 84 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 46 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 47 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 46 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 47 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 43 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 44 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -978,7 +978,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3182,6 +3182,58 @@
       </c>
       <c r="H87" s="16" t="n">
         <v>29</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B88" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F88" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G88" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H88" s="16" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="15" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B89" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="16" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3200,7 +3252,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5475,6 +5527,53 @@
         <v>4</v>
       </c>
       <c r="O51" s="16" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>144</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>4483</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>445</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>2320</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K52" s="16" t="n">
+        <v>1232</v>
+      </c>
+      <c r="L52" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="M52" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="N52" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O52" s="16" t="n">
         <v>634</v>
       </c>
     </row>
@@ -5494,7 +5593,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7674,6 +7773,53 @@
       </c>
       <c r="O51" s="16" t="n">
         <v>337</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>745</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>709</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>552</v>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>392</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" s="16" t="n">
+        <v>1039</v>
+      </c>
+      <c r="L52" s="19" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="M52" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="N52" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -7692,7 +7838,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9283,6 +9429,44 @@
         <v>271</v>
       </c>
       <c r="L48" s="16" t="n">
+        <v>239577</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B49" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H49" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I49" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="J49" s="16" t="n">
+        <v>334</v>
+      </c>
+      <c r="K49" s="16" t="n">
+        <v>268</v>
+      </c>
+      <c r="L49" s="16" t="n">
         <v>239577</v>
       </c>
     </row>
@@ -9348,16 +9532,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>124</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9365,15 +9549,15 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>347</v>
       </c>
     </row>
@@ -9382,16 +9566,16 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>4093</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>4274</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9399,16 +9583,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>396</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>412</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9416,16 +9600,16 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>13</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9433,16 +9617,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>149</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9450,16 +9634,16 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H87,'Social — theo ngày'!$A$6:$A$87,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$87,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2186</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2220</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9494,7 +9678,7 @@
         <v>115</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B51</f>
+        <f aca="false">'Social — 28 ngày'!B52</f>
         <v>116</v>
       </c>
     </row>
@@ -9511,8 +9695,8 @@
         <v>184</v>
       </c>
       <c r="D18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C51</f>
-        <v>140</v>
+        <f aca="false">'Social — 28 ngày'!C52</f>
+        <v>144</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9528,8 +9712,8 @@
         <v>4735</v>
       </c>
       <c r="D19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D51</f>
-        <v>4509</v>
+        <f aca="false">'Social — 28 ngày'!D52</f>
+        <v>4483</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9545,8 +9729,8 @@
         <v>280</v>
       </c>
       <c r="D20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E51</f>
-        <v>433</v>
+        <f aca="false">'Social — 28 ngày'!E52</f>
+        <v>445</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9562,7 +9746,7 @@
         <v>47</v>
       </c>
       <c r="D21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F51</f>
+        <f aca="false">'Social — 28 ngày'!F52</f>
         <v>49</v>
       </c>
     </row>
@@ -9579,8 +9763,8 @@
         <v>68</v>
       </c>
       <c r="D22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G51</f>
-        <v>15</v>
+        <f aca="false">'Social — 28 ngày'!G52</f>
+        <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9596,8 +9780,8 @@
         <v>275</v>
       </c>
       <c r="D23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H51</f>
-        <v>86</v>
+        <f aca="false">'Social — 28 ngày'!H52</f>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9613,8 +9797,8 @@
         <v>1039</v>
       </c>
       <c r="D24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I51</f>
-        <v>2397</v>
+        <f aca="false">'Social — 28 ngày'!I52</f>
+        <v>2320</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9630,7 +9814,7 @@
         <v>100</v>
       </c>
       <c r="D25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J51</f>
+        <f aca="false">'Social — 28 ngày'!J52</f>
         <v>102</v>
       </c>
     </row>
@@ -9647,8 +9831,8 @@
         <v>1691</v>
       </c>
       <c r="D26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K51</f>
-        <v>1229</v>
+        <f aca="false">'Social — 28 ngày'!K52</f>
+        <v>1232</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9664,8 +9848,8 @@
         <v>127</v>
       </c>
       <c r="D27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L51</f>
-        <v>28</v>
+        <f aca="false">'Social — 28 ngày'!L52</f>
+        <v>27</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9681,8 +9865,8 @@
         <v>86</v>
       </c>
       <c r="D28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M51</f>
-        <v>44</v>
+        <f aca="false">'Social — 28 ngày'!M52</f>
+        <v>43</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9698,7 +9882,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N51</f>
+        <f aca="false">'Social — 28 ngày'!N52</f>
         <v>4</v>
       </c>
     </row>
@@ -9715,7 +9899,7 @@
         <v>59</v>
       </c>
       <c r="D30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O51</f>
+        <f aca="false">'Social — 28 ngày'!O52</f>
         <v>634</v>
       </c>
     </row>
@@ -9758,8 +9942,8 @@
         <v>21</v>
       </c>
       <c r="E34" s="24" t="n">
-        <f aca="false">SEO!B51</f>
-        <v>14</v>
+        <f aca="false">SEO!B52</f>
+        <v>17</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9779,8 +9963,8 @@
         <v>364</v>
       </c>
       <c r="E35" s="24" t="n">
-        <f aca="false">SEO!C51</f>
-        <v>701</v>
+        <f aca="false">SEO!C52</f>
+        <v>745</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9800,8 +9984,8 @@
         <v>349</v>
       </c>
       <c r="E36" s="24" t="n">
-        <f aca="false">SEO!D51</f>
-        <v>665</v>
+        <f aca="false">SEO!D52</f>
+        <v>709</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9821,8 +10005,8 @@
         <v>42.93</v>
       </c>
       <c r="E37" s="24" t="n">
-        <f aca="false">SEO!E51</f>
-        <v>34.59</v>
+        <f aca="false">SEO!E52</f>
+        <v>33.88</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9842,7 +10026,7 @@
         <v>7</v>
       </c>
       <c r="E38" s="24" t="n">
-        <f aca="false">SEO!F51</f>
+        <f aca="false">SEO!F52</f>
         <v>3</v>
       </c>
     </row>
@@ -9863,8 +10047,8 @@
         <v>375</v>
       </c>
       <c r="E39" s="24" t="n">
-        <f aca="false">SEO!G51</f>
-        <v>558</v>
+        <f aca="false">SEO!G52</f>
+        <v>552</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9884,8 +10068,8 @@
         <v>204</v>
       </c>
       <c r="E40" s="24" t="n">
-        <f aca="false">SEO!H51</f>
-        <v>387</v>
+        <f aca="false">SEO!H52</f>
+        <v>392</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9905,8 +10089,8 @@
         <v>67</v>
       </c>
       <c r="E41" s="24" t="n">
-        <f aca="false">SEO!I51</f>
-        <v>34</v>
+        <f aca="false">SEO!I52</f>
+        <v>31</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9926,8 +10110,8 @@
         <v>3.8</v>
       </c>
       <c r="E42" s="24" t="n">
-        <f aca="false">SEO!J51</f>
-        <v>3.4</v>
+        <f aca="false">SEO!J52</f>
+        <v>3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9947,8 +10131,8 @@
         <v>1757</v>
       </c>
       <c r="E43" s="24" t="n">
-        <f aca="false">SEO!K51</f>
-        <v>1013</v>
+        <f aca="false">SEO!K52</f>
+        <v>1039</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9968,8 +10152,8 @@
         <v>29.4</v>
       </c>
       <c r="E44" s="24" t="n">
-        <f aca="false">SEO!L51</f>
-        <v>28</v>
+        <f aca="false">SEO!L52</f>
+        <v>26.6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9989,8 +10173,8 @@
         <v>151</v>
       </c>
       <c r="E45" s="24" t="n">
-        <f aca="false">SEO!M51</f>
-        <v>81</v>
+        <f aca="false">SEO!M52</f>
+        <v>78</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10010,7 +10194,7 @@
         <v>95</v>
       </c>
       <c r="E46" s="24" t="n">
-        <f aca="false">SEO!N51</f>
+        <f aca="false">SEO!N52</f>
         <v>119</v>
       </c>
     </row>
@@ -10031,8 +10215,8 @@
         <v>1022</v>
       </c>
       <c r="E47" s="24" t="n">
-        <f aca="false">SEO!O51</f>
-        <v>337</v>
+        <f aca="false">SEO!O52</f>
+        <v>334</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10067,7 +10251,7 @@
         <v>88</v>
       </c>
       <c r="D51" s="24" t="n">
-        <f aca="false">Audit!B48</f>
+        <f aca="false">Audit!B49</f>
         <v>92</v>
       </c>
     </row>
@@ -10084,8 +10268,8 @@
         <v>97</v>
       </c>
       <c r="D52" s="24" t="n">
-        <f aca="false">Audit!C48</f>
-        <v>96</v>
+        <f aca="false">Audit!C49</f>
+        <v>95</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10101,8 +10285,8 @@
         <v>92</v>
       </c>
       <c r="D53" s="24" t="n">
-        <f aca="false">Audit!D48</f>
-        <v>95</v>
+        <f aca="false">Audit!D49</f>
+        <v>94</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10118,7 +10302,7 @@
         <v>91</v>
       </c>
       <c r="D54" s="24" t="n">
-        <f aca="false">Audit!E48</f>
+        <f aca="false">Audit!E49</f>
         <v>92</v>
       </c>
     </row>
@@ -10135,7 +10319,7 @@
         <v>91</v>
       </c>
       <c r="D55" s="24" t="n">
-        <f aca="false">Audit!F48</f>
+        <f aca="false">Audit!F49</f>
         <v>118</v>
       </c>
     </row>
@@ -10152,7 +10336,7 @@
         <v>88</v>
       </c>
       <c r="D56" s="24" t="n">
-        <f aca="false">Audit!G48</f>
+        <f aca="false">Audit!G49</f>
         <v>98</v>
       </c>
     </row>
@@ -10169,7 +10353,7 @@
         <v>92</v>
       </c>
       <c r="D57" s="24" t="n">
-        <f aca="false">Audit!H48</f>
+        <f aca="false">Audit!H49</f>
         <v>119</v>
       </c>
     </row>
@@ -10186,7 +10370,7 @@
         <v>96</v>
       </c>
       <c r="D58" s="24" t="n">
-        <f aca="false">Audit!I48</f>
+        <f aca="false">Audit!I49</f>
         <v>92</v>
       </c>
     </row>
@@ -10203,8 +10387,8 @@
         <v>862</v>
       </c>
       <c r="D59" s="24" t="n">
-        <f aca="false">Audit!J48</f>
-        <v>337</v>
+        <f aca="false">Audit!J49</f>
+        <v>334</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10220,8 +10404,8 @@
         <v>0</v>
       </c>
       <c r="D60" s="24" t="n">
-        <f aca="false">Audit!K48</f>
-        <v>271</v>
+        <f aca="false">Audit!K49</f>
+        <v>268</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10237,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="24" t="n">
-        <f aca="false">Audit!L48</f>
+        <f aca="false">Audit!L49</f>
         <v>239577</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-09-28 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-09-29 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">84 dòng × 7 chỉ số · 2026-07-05 → 2026-09-26</t>
+    <t xml:space="preserve">85 dòng × 7 chỉ số · 2026-07-05 → 2026-09-27</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">47 dòng × 14 chỉ số · 2026-07-23 → 2026-09-28</t>
+    <t xml:space="preserve">48 dòng × 14 chỉ số · 2026-07-23 → 2026-09-29</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">47 dòng × 14 chỉ số · 2026-06-30 → 2026-09-28</t>
+    <t xml:space="preserve">48 dòng × 14 chỉ số · 2026-06-30 → 2026-09-29</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">44 dòng × 11 chỉ số · 2026-07-27 → 2026-09-28</t>
+    <t xml:space="preserve">45 dòng × 11 chỉ số · 2026-07-27 → 2026-09-29</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 84 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 85 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 47 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 48 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 47 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 48 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 44 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 45 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -978,7 +978,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3234,6 +3234,32 @@
       </c>
       <c r="H89" s="16" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="15" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="16" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3278,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5574,6 +5600,53 @@
         <v>4</v>
       </c>
       <c r="O52" s="16" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>138</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>4496</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>442</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>2287</v>
+      </c>
+      <c r="J53" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K53" s="16" t="n">
+        <v>1210</v>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="M53" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="N53" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" s="16" t="n">
         <v>634</v>
       </c>
     </row>
@@ -5593,7 +5666,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7820,6 +7893,53 @@
       </c>
       <c r="O52" s="16" t="n">
         <v>334</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>850</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>814</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>555</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>393</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="J53" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K53" s="16" t="n">
+        <v>1051</v>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="M53" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="N53" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -7838,7 +7958,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9468,6 +9588,44 @@
       </c>
       <c r="L49" s="16" t="n">
         <v>239577</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B50" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="H50" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I50" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="J50" s="16" t="n">
+        <v>323</v>
+      </c>
+      <c r="K50" s="16" t="n">
+        <v>270</v>
+      </c>
+      <c r="L50" s="16" t="n">
+        <v>241329</v>
       </c>
     </row>
   </sheetData>
@@ -9532,15 +9690,15 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>135</v>
       </c>
     </row>
@@ -9549,16 +9707,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>347</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>350</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9566,16 +9724,16 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>4274</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>4339</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9583,16 +9741,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>412</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>416</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9600,15 +9758,15 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>17</v>
       </c>
     </row>
@@ -9617,16 +9775,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>155</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9634,16 +9792,16 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H89,'Social — theo ngày'!$A$6:$A$89,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$89,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2220</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2228</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9678,7 +9836,7 @@
         <v>115</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B52</f>
+        <f aca="false">'Social — 28 ngày'!B53</f>
         <v>116</v>
       </c>
     </row>
@@ -9695,8 +9853,8 @@
         <v>184</v>
       </c>
       <c r="D18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C52</f>
-        <v>144</v>
+        <f aca="false">'Social — 28 ngày'!C53</f>
+        <v>138</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9712,8 +9870,8 @@
         <v>4735</v>
       </c>
       <c r="D19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D52</f>
-        <v>4483</v>
+        <f aca="false">'Social — 28 ngày'!D53</f>
+        <v>4496</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9729,8 +9887,8 @@
         <v>280</v>
       </c>
       <c r="D20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E52</f>
-        <v>445</v>
+        <f aca="false">'Social — 28 ngày'!E53</f>
+        <v>442</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9746,7 +9904,7 @@
         <v>47</v>
       </c>
       <c r="D21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F52</f>
+        <f aca="false">'Social — 28 ngày'!F53</f>
         <v>49</v>
       </c>
     </row>
@@ -9763,8 +9921,8 @@
         <v>68</v>
       </c>
       <c r="D22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G52</f>
-        <v>18</v>
+        <f aca="false">'Social — 28 ngày'!G53</f>
+        <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9780,7 +9938,7 @@
         <v>275</v>
       </c>
       <c r="D23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H52</f>
+        <f aca="false">'Social — 28 ngày'!H53</f>
         <v>87</v>
       </c>
     </row>
@@ -9797,8 +9955,8 @@
         <v>1039</v>
       </c>
       <c r="D24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I52</f>
-        <v>2320</v>
+        <f aca="false">'Social — 28 ngày'!I53</f>
+        <v>2287</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9814,7 +9972,7 @@
         <v>100</v>
       </c>
       <c r="D25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J52</f>
+        <f aca="false">'Social — 28 ngày'!J53</f>
         <v>102</v>
       </c>
     </row>
@@ -9831,8 +9989,8 @@
         <v>1691</v>
       </c>
       <c r="D26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K52</f>
-        <v>1232</v>
+        <f aca="false">'Social — 28 ngày'!K53</f>
+        <v>1210</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9848,8 +10006,8 @@
         <v>127</v>
       </c>
       <c r="D27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L52</f>
-        <v>27</v>
+        <f aca="false">'Social — 28 ngày'!L53</f>
+        <v>24</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9865,8 +10023,8 @@
         <v>86</v>
       </c>
       <c r="D28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M52</f>
-        <v>43</v>
+        <f aca="false">'Social — 28 ngày'!M53</f>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9882,7 +10040,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N52</f>
+        <f aca="false">'Social — 28 ngày'!N53</f>
         <v>4</v>
       </c>
     </row>
@@ -9899,7 +10057,7 @@
         <v>59</v>
       </c>
       <c r="D30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O52</f>
+        <f aca="false">'Social — 28 ngày'!O53</f>
         <v>634</v>
       </c>
     </row>
@@ -9942,7 +10100,7 @@
         <v>21</v>
       </c>
       <c r="E34" s="24" t="n">
-        <f aca="false">SEO!B52</f>
+        <f aca="false">SEO!B53</f>
         <v>17</v>
       </c>
     </row>
@@ -9963,8 +10121,8 @@
         <v>364</v>
       </c>
       <c r="E35" s="24" t="n">
-        <f aca="false">SEO!C52</f>
-        <v>745</v>
+        <f aca="false">SEO!C53</f>
+        <v>850</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9984,8 +10142,8 @@
         <v>349</v>
       </c>
       <c r="E36" s="24" t="n">
-        <f aca="false">SEO!D52</f>
-        <v>709</v>
+        <f aca="false">SEO!D53</f>
+        <v>814</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10005,8 +10163,8 @@
         <v>42.93</v>
       </c>
       <c r="E37" s="24" t="n">
-        <f aca="false">SEO!E52</f>
-        <v>33.88</v>
+        <f aca="false">SEO!E53</f>
+        <v>34.59</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10026,7 +10184,7 @@
         <v>7</v>
       </c>
       <c r="E38" s="24" t="n">
-        <f aca="false">SEO!F52</f>
+        <f aca="false">SEO!F53</f>
         <v>3</v>
       </c>
     </row>
@@ -10047,8 +10205,8 @@
         <v>375</v>
       </c>
       <c r="E39" s="24" t="n">
-        <f aca="false">SEO!G52</f>
-        <v>552</v>
+        <f aca="false">SEO!G53</f>
+        <v>555</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10068,8 +10226,8 @@
         <v>204</v>
       </c>
       <c r="E40" s="24" t="n">
-        <f aca="false">SEO!H52</f>
-        <v>392</v>
+        <f aca="false">SEO!H53</f>
+        <v>393</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10089,8 +10247,8 @@
         <v>67</v>
       </c>
       <c r="E41" s="24" t="n">
-        <f aca="false">SEO!I52</f>
-        <v>31</v>
+        <f aca="false">SEO!I53</f>
+        <v>32</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10110,7 +10268,7 @@
         <v>3.8</v>
       </c>
       <c r="E42" s="24" t="n">
-        <f aca="false">SEO!J52</f>
+        <f aca="false">SEO!J53</f>
         <v>3</v>
       </c>
     </row>
@@ -10131,8 +10289,8 @@
         <v>1757</v>
       </c>
       <c r="E43" s="24" t="n">
-        <f aca="false">SEO!K52</f>
-        <v>1039</v>
+        <f aca="false">SEO!K53</f>
+        <v>1051</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10152,8 +10310,8 @@
         <v>29.4</v>
       </c>
       <c r="E44" s="24" t="n">
-        <f aca="false">SEO!L52</f>
-        <v>26.6</v>
+        <f aca="false">SEO!L53</f>
+        <v>26</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10173,8 +10331,8 @@
         <v>151</v>
       </c>
       <c r="E45" s="24" t="n">
-        <f aca="false">SEO!M52</f>
-        <v>78</v>
+        <f aca="false">SEO!M53</f>
+        <v>80</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10194,7 +10352,7 @@
         <v>95</v>
       </c>
       <c r="E46" s="24" t="n">
-        <f aca="false">SEO!N52</f>
+        <f aca="false">SEO!N53</f>
         <v>119</v>
       </c>
     </row>
@@ -10215,8 +10373,8 @@
         <v>1022</v>
       </c>
       <c r="E47" s="24" t="n">
-        <f aca="false">SEO!O52</f>
-        <v>334</v>
+        <f aca="false">SEO!O53</f>
+        <v>323</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10251,8 +10409,8 @@
         <v>88</v>
       </c>
       <c r="D51" s="24" t="n">
-        <f aca="false">Audit!B49</f>
-        <v>92</v>
+        <f aca="false">Audit!B50</f>
+        <v>93</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10268,8 +10426,8 @@
         <v>97</v>
       </c>
       <c r="D52" s="24" t="n">
-        <f aca="false">Audit!C49</f>
-        <v>95</v>
+        <f aca="false">Audit!C50</f>
+        <v>98</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10285,8 +10443,8 @@
         <v>92</v>
       </c>
       <c r="D53" s="24" t="n">
-        <f aca="false">Audit!D49</f>
-        <v>94</v>
+        <f aca="false">Audit!D50</f>
+        <v>95</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10302,7 +10460,7 @@
         <v>91</v>
       </c>
       <c r="D54" s="24" t="n">
-        <f aca="false">Audit!E49</f>
+        <f aca="false">Audit!E50</f>
         <v>92</v>
       </c>
     </row>
@@ -10319,7 +10477,7 @@
         <v>91</v>
       </c>
       <c r="D55" s="24" t="n">
-        <f aca="false">Audit!F49</f>
+        <f aca="false">Audit!F50</f>
         <v>118</v>
       </c>
     </row>
@@ -10336,8 +10494,8 @@
         <v>88</v>
       </c>
       <c r="D56" s="24" t="n">
-        <f aca="false">Audit!G49</f>
-        <v>98</v>
+        <f aca="false">Audit!G50</f>
+        <v>99</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10353,7 +10511,7 @@
         <v>92</v>
       </c>
       <c r="D57" s="24" t="n">
-        <f aca="false">Audit!H49</f>
+        <f aca="false">Audit!H50</f>
         <v>119</v>
       </c>
     </row>
@@ -10370,7 +10528,7 @@
         <v>96</v>
       </c>
       <c r="D58" s="24" t="n">
-        <f aca="false">Audit!I49</f>
+        <f aca="false">Audit!I50</f>
         <v>92</v>
       </c>
     </row>
@@ -10387,8 +10545,8 @@
         <v>862</v>
       </c>
       <c r="D59" s="24" t="n">
-        <f aca="false">Audit!J49</f>
-        <v>334</v>
+        <f aca="false">Audit!J50</f>
+        <v>323</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10404,8 +10562,8 @@
         <v>0</v>
       </c>
       <c r="D60" s="24" t="n">
-        <f aca="false">Audit!K49</f>
-        <v>268</v>
+        <f aca="false">Audit!K50</f>
+        <v>270</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10421,8 +10579,8 @@
         <v>0</v>
       </c>
       <c r="D61" s="24" t="n">
-        <f aca="false">Audit!L49</f>
-        <v>239577</v>
+        <f aca="false">Audit!L50</f>
+        <v>241329</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-09-29 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-09-30 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">85 dòng × 7 chỉ số · 2026-07-05 → 2026-09-27</t>
+    <t xml:space="preserve">86 dòng × 7 chỉ số · 2026-07-05 → 2026-09-28</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">48 dòng × 14 chỉ số · 2026-07-23 → 2026-09-29</t>
+    <t xml:space="preserve">49 dòng × 14 chỉ số · 2026-07-23 → 2026-09-30</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">48 dòng × 14 chỉ số · 2026-06-30 → 2026-09-29</t>
+    <t xml:space="preserve">49 dòng × 14 chỉ số · 2026-06-30 → 2026-09-30</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">45 dòng × 11 chỉ số · 2026-07-27 → 2026-09-29</t>
+    <t xml:space="preserve">46 dòng × 11 chỉ số · 2026-07-27 → 2026-09-30</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 85 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 86 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 48 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 49 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 48 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 49 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 45 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 46 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -978,7 +978,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3260,6 +3260,32 @@
       </c>
       <c r="H90" s="16" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="15" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B91" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C91" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F91" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" s="16" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3278,7 +3304,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5647,6 +5673,53 @@
         <v>4</v>
       </c>
       <c r="O53" s="16" t="n">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>4519</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>422</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="I54" s="16" t="n">
+        <v>2258</v>
+      </c>
+      <c r="J54" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K54" s="16" t="n">
+        <v>1193</v>
+      </c>
+      <c r="L54" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="M54" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="N54" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" s="16" t="n">
         <v>634</v>
       </c>
     </row>
@@ -5666,7 +5739,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7940,6 +8013,53 @@
       </c>
       <c r="O53" s="16" t="n">
         <v>323</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>882</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>559</v>
+      </c>
+      <c r="H54" s="16" t="n">
+        <v>394</v>
+      </c>
+      <c r="I54" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="J54" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K54" s="16" t="n">
+        <v>1056</v>
+      </c>
+      <c r="L54" s="19" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="M54" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="N54" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O54" s="16" t="n">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -7958,7 +8078,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9625,6 +9745,44 @@
         <v>270</v>
       </c>
       <c r="L50" s="16" t="n">
+        <v>241329</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B51" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C51" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H51" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I51" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="J51" s="16" t="n">
+        <v>342</v>
+      </c>
+      <c r="K51" s="16" t="n">
+        <v>276</v>
+      </c>
+      <c r="L51" s="16" t="n">
         <v>241329</v>
       </c>
     </row>
@@ -9690,16 +9848,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>135</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9707,16 +9865,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>350</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>353</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9724,16 +9882,16 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>4339</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>4519</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9741,16 +9899,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>416</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>422</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9758,16 +9916,16 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>17</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9775,16 +9933,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>156</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9792,16 +9950,16 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H90,'Social — theo ngày'!$A$6:$A$90,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$90,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2228</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9836,7 +9994,7 @@
         <v>115</v>
       </c>
       <c r="D17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B53</f>
+        <f aca="false">'Social — 28 ngày'!B54</f>
         <v>116</v>
       </c>
     </row>
@@ -9853,8 +10011,8 @@
         <v>184</v>
       </c>
       <c r="D18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C53</f>
-        <v>138</v>
+        <f aca="false">'Social — 28 ngày'!C54</f>
+        <v>141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9870,8 +10028,8 @@
         <v>4735</v>
       </c>
       <c r="D19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D53</f>
-        <v>4496</v>
+        <f aca="false">'Social — 28 ngày'!D54</f>
+        <v>4519</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9887,8 +10045,8 @@
         <v>280</v>
       </c>
       <c r="D20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E53</f>
-        <v>442</v>
+        <f aca="false">'Social — 28 ngày'!E54</f>
+        <v>422</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9904,7 +10062,7 @@
         <v>47</v>
       </c>
       <c r="D21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F53</f>
+        <f aca="false">'Social — 28 ngày'!F54</f>
         <v>49</v>
       </c>
     </row>
@@ -9921,8 +10079,8 @@
         <v>68</v>
       </c>
       <c r="D22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G53</f>
-        <v>17</v>
+        <f aca="false">'Social — 28 ngày'!G54</f>
+        <v>20</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9938,7 +10096,7 @@
         <v>275</v>
       </c>
       <c r="D23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H53</f>
+        <f aca="false">'Social — 28 ngày'!H54</f>
         <v>87</v>
       </c>
     </row>
@@ -9955,8 +10113,8 @@
         <v>1039</v>
       </c>
       <c r="D24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I53</f>
-        <v>2287</v>
+        <f aca="false">'Social — 28 ngày'!I54</f>
+        <v>2258</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9972,7 +10130,7 @@
         <v>100</v>
       </c>
       <c r="D25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J53</f>
+        <f aca="false">'Social — 28 ngày'!J54</f>
         <v>102</v>
       </c>
     </row>
@@ -9989,8 +10147,8 @@
         <v>1691</v>
       </c>
       <c r="D26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K53</f>
-        <v>1210</v>
+        <f aca="false">'Social — 28 ngày'!K54</f>
+        <v>1193</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10006,7 +10164,7 @@
         <v>127</v>
       </c>
       <c r="D27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L53</f>
+        <f aca="false">'Social — 28 ngày'!L54</f>
         <v>24</v>
       </c>
     </row>
@@ -10023,8 +10181,8 @@
         <v>86</v>
       </c>
       <c r="D28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M53</f>
-        <v>38</v>
+        <f aca="false">'Social — 28 ngày'!M54</f>
+        <v>36</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10040,7 +10198,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N53</f>
+        <f aca="false">'Social — 28 ngày'!N54</f>
         <v>4</v>
       </c>
     </row>
@@ -10057,7 +10215,7 @@
         <v>59</v>
       </c>
       <c r="D30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O53</f>
+        <f aca="false">'Social — 28 ngày'!O54</f>
         <v>634</v>
       </c>
     </row>
@@ -10100,8 +10258,8 @@
         <v>21</v>
       </c>
       <c r="E34" s="24" t="n">
-        <f aca="false">SEO!B53</f>
-        <v>17</v>
+        <f aca="false">SEO!B54</f>
+        <v>16</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10121,8 +10279,8 @@
         <v>364</v>
       </c>
       <c r="E35" s="24" t="n">
-        <f aca="false">SEO!C53</f>
-        <v>850</v>
+        <f aca="false">SEO!C54</f>
+        <v>918</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10142,8 +10300,8 @@
         <v>349</v>
       </c>
       <c r="E36" s="24" t="n">
-        <f aca="false">SEO!D53</f>
-        <v>814</v>
+        <f aca="false">SEO!D54</f>
+        <v>882</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10163,8 +10321,8 @@
         <v>42.93</v>
       </c>
       <c r="E37" s="24" t="n">
-        <f aca="false">SEO!E53</f>
-        <v>34.59</v>
+        <f aca="false">SEO!E54</f>
+        <v>33.99</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10184,8 +10342,8 @@
         <v>7</v>
       </c>
       <c r="E38" s="24" t="n">
-        <f aca="false">SEO!F53</f>
-        <v>3</v>
+        <f aca="false">SEO!F54</f>
+        <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10205,8 +10363,8 @@
         <v>375</v>
       </c>
       <c r="E39" s="24" t="n">
-        <f aca="false">SEO!G53</f>
-        <v>555</v>
+        <f aca="false">SEO!G54</f>
+        <v>559</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10226,8 +10384,8 @@
         <v>204</v>
       </c>
       <c r="E40" s="24" t="n">
-        <f aca="false">SEO!H53</f>
-        <v>393</v>
+        <f aca="false">SEO!H54</f>
+        <v>394</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10247,8 +10405,8 @@
         <v>67</v>
       </c>
       <c r="E41" s="24" t="n">
-        <f aca="false">SEO!I53</f>
-        <v>32</v>
+        <f aca="false">SEO!I54</f>
+        <v>30</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10268,8 +10426,8 @@
         <v>3.8</v>
       </c>
       <c r="E42" s="24" t="n">
-        <f aca="false">SEO!J53</f>
-        <v>3</v>
+        <f aca="false">SEO!J54</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10289,8 +10447,8 @@
         <v>1757</v>
       </c>
       <c r="E43" s="24" t="n">
-        <f aca="false">SEO!K53</f>
-        <v>1051</v>
+        <f aca="false">SEO!K54</f>
+        <v>1056</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10310,8 +10468,8 @@
         <v>29.4</v>
       </c>
       <c r="E44" s="24" t="n">
-        <f aca="false">SEO!L53</f>
-        <v>26</v>
+        <f aca="false">SEO!L54</f>
+        <v>25.8</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10331,7 +10489,7 @@
         <v>151</v>
       </c>
       <c r="E45" s="24" t="n">
-        <f aca="false">SEO!M53</f>
+        <f aca="false">SEO!M54</f>
         <v>80</v>
       </c>
     </row>
@@ -10352,7 +10510,7 @@
         <v>95</v>
       </c>
       <c r="E46" s="24" t="n">
-        <f aca="false">SEO!N53</f>
+        <f aca="false">SEO!N54</f>
         <v>119</v>
       </c>
     </row>
@@ -10373,8 +10531,8 @@
         <v>1022</v>
       </c>
       <c r="E47" s="24" t="n">
-        <f aca="false">SEO!O53</f>
-        <v>323</v>
+        <f aca="false">SEO!O54</f>
+        <v>342</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10409,7 +10567,7 @@
         <v>88</v>
       </c>
       <c r="D51" s="24" t="n">
-        <f aca="false">Audit!B50</f>
+        <f aca="false">Audit!B51</f>
         <v>93</v>
       </c>
     </row>
@@ -10426,7 +10584,7 @@
         <v>97</v>
       </c>
       <c r="D52" s="24" t="n">
-        <f aca="false">Audit!C50</f>
+        <f aca="false">Audit!C51</f>
         <v>98</v>
       </c>
     </row>
@@ -10443,7 +10601,7 @@
         <v>92</v>
       </c>
       <c r="D53" s="24" t="n">
-        <f aca="false">Audit!D50</f>
+        <f aca="false">Audit!D51</f>
         <v>95</v>
       </c>
     </row>
@@ -10460,7 +10618,7 @@
         <v>91</v>
       </c>
       <c r="D54" s="24" t="n">
-        <f aca="false">Audit!E50</f>
+        <f aca="false">Audit!E51</f>
         <v>92</v>
       </c>
     </row>
@@ -10477,7 +10635,7 @@
         <v>91</v>
       </c>
       <c r="D55" s="24" t="n">
-        <f aca="false">Audit!F50</f>
+        <f aca="false">Audit!F51</f>
         <v>118</v>
       </c>
     </row>
@@ -10494,8 +10652,8 @@
         <v>88</v>
       </c>
       <c r="D56" s="24" t="n">
-        <f aca="false">Audit!G50</f>
-        <v>99</v>
+        <f aca="false">Audit!G51</f>
+        <v>98</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10511,7 +10669,7 @@
         <v>92</v>
       </c>
       <c r="D57" s="24" t="n">
-        <f aca="false">Audit!H50</f>
+        <f aca="false">Audit!H51</f>
         <v>119</v>
       </c>
     </row>
@@ -10528,7 +10686,7 @@
         <v>96</v>
       </c>
       <c r="D58" s="24" t="n">
-        <f aca="false">Audit!I50</f>
+        <f aca="false">Audit!I51</f>
         <v>92</v>
       </c>
     </row>
@@ -10545,8 +10703,8 @@
         <v>862</v>
       </c>
       <c r="D59" s="24" t="n">
-        <f aca="false">Audit!J50</f>
-        <v>323</v>
+        <f aca="false">Audit!J51</f>
+        <v>342</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10562,8 +10720,8 @@
         <v>0</v>
       </c>
       <c r="D60" s="24" t="n">
-        <f aca="false">Audit!K50</f>
-        <v>270</v>
+        <f aca="false">Audit!K51</f>
+        <v>276</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10579,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="24" t="n">
-        <f aca="false">Audit!L50</f>
+        <f aca="false">Audit!L51</f>
         <v>241329</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="97">
   <si>
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-09-30 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-01 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">86 dòng × 7 chỉ số · 2026-07-05 → 2026-09-28</t>
+    <t xml:space="preserve">87 dòng × 7 chỉ số · 2026-07-05 → 2026-09-29</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">49 dòng × 14 chỉ số · 2026-07-23 → 2026-09-30</t>
+    <t xml:space="preserve">50 dòng × 14 chỉ số · 2026-07-23 → 2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">49 dòng × 14 chỉ số · 2026-06-30 → 2026-09-30</t>
+    <t xml:space="preserve">50 dòng × 14 chỉ số · 2026-06-30 → 2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">46 dòng × 11 chỉ số · 2026-07-27 → 2026-09-30</t>
+    <t xml:space="preserve">47 dòng × 11 chỉ số · 2026-07-27 → 2026-10-01</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 86 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 87 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 49 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 50 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 49 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 50 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 46 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 47 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t xml:space="preserve">KHÔNG CỘNG — Social — 28 ngày (lấy ngày quét cuối tháng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10</t>
   </si>
   <si>
     <t xml:space="preserve">KHÔNG CỘNG — SEO (lấy ngày quét cuối tháng)</t>
@@ -978,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3286,6 +3289,32 @@
       </c>
       <c r="H91" s="16" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="15" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B92" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G92" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H92" s="16" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3333,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5722,6 +5751,49 @@
       <c r="O54" s="16" t="n">
         <v>634</v>
       </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>132</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>4427</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>421</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>2297</v>
+      </c>
+      <c r="J55" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K55" s="16" t="n">
+        <v>1219</v>
+      </c>
+      <c r="L55" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="M55" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5739,7 +5811,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8060,6 +8132,35 @@
       </c>
       <c r="O54" s="16" t="n">
         <v>342</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>882</v>
+      </c>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+      <c r="N55" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -8078,7 +8179,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9784,6 +9885,44 @@
       </c>
       <c r="L51" s="16" t="n">
         <v>241329</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H52" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I52" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <v>331</v>
+      </c>
+      <c r="K52" s="16" t="n">
+        <v>268</v>
+      </c>
+      <c r="L52" s="16" t="n">
+        <v>241211</v>
       </c>
     </row>
   </sheetData>
@@ -9802,7 +9941,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -9848,16 +9987,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>141</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9865,15 +10004,15 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>353</v>
       </c>
     </row>
@@ -9882,16 +10021,16 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>4519</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>4614</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9899,15 +10038,15 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>422</v>
       </c>
     </row>
@@ -9916,16 +10055,16 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>20</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9933,16 +10072,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>160</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>166</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9950,16 +10089,16 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H91,'Social — theo ngày'!$A$6:$A$91,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$91,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2258</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2318</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9980,6 +10119,9 @@
       <c r="D16" s="21" t="s">
         <v>91</v>
       </c>
+      <c r="E16" s="21" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
@@ -9997,6 +10139,10 @@
         <f aca="false">'Social — 28 ngày'!B54</f>
         <v>116</v>
       </c>
+      <c r="E17" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!B55</f>
+        <v>116</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
@@ -10014,6 +10160,10 @@
         <f aca="false">'Social — 28 ngày'!C54</f>
         <v>141</v>
       </c>
+      <c r="E18" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!C55</f>
+        <v>132</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
@@ -10031,6 +10181,10 @@
         <f aca="false">'Social — 28 ngày'!D54</f>
         <v>4519</v>
       </c>
+      <c r="E19" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!D55</f>
+        <v>4427</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
@@ -10048,6 +10202,10 @@
         <f aca="false">'Social — 28 ngày'!E54</f>
         <v>422</v>
       </c>
+      <c r="E20" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!E55</f>
+        <v>421</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
@@ -10065,6 +10223,10 @@
         <f aca="false">'Social — 28 ngày'!F54</f>
         <v>49</v>
       </c>
+      <c r="E21" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!F55</f>
+        <v>49</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
@@ -10082,6 +10244,10 @@
         <f aca="false">'Social — 28 ngày'!G54</f>
         <v>20</v>
       </c>
+      <c r="E22" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!G55</f>
+        <v>23</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
@@ -10099,6 +10265,10 @@
         <f aca="false">'Social — 28 ngày'!H54</f>
         <v>87</v>
       </c>
+      <c r="E23" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!H55</f>
+        <v>87</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
@@ -10116,6 +10286,10 @@
         <f aca="false">'Social — 28 ngày'!I54</f>
         <v>2258</v>
       </c>
+      <c r="E24" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!I55</f>
+        <v>2297</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
@@ -10133,6 +10307,10 @@
         <f aca="false">'Social — 28 ngày'!J54</f>
         <v>102</v>
       </c>
+      <c r="E25" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!J55</f>
+        <v>102</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
@@ -10150,6 +10328,10 @@
         <f aca="false">'Social — 28 ngày'!K54</f>
         <v>1193</v>
       </c>
+      <c r="E26" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!K55</f>
+        <v>1219</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
@@ -10167,6 +10349,10 @@
         <f aca="false">'Social — 28 ngày'!L54</f>
         <v>24</v>
       </c>
+      <c r="E27" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!L55</f>
+        <v>26</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
@@ -10184,6 +10370,10 @@
         <f aca="false">'Social — 28 ngày'!M54</f>
         <v>36</v>
       </c>
+      <c r="E28" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!M55</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
@@ -10201,6 +10391,10 @@
         <f aca="false">'Social — 28 ngày'!N54</f>
         <v>4</v>
       </c>
+      <c r="E29" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!N55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
@@ -10218,10 +10412,14 @@
         <f aca="false">'Social — 28 ngày'!O54</f>
         <v>634</v>
       </c>
+      <c r="E30" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!O55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10229,7 +10427,7 @@
         <v>88</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" s="21" t="s">
         <v>89</v>
@@ -10239,6 +10437,9 @@
       </c>
       <c r="E33" s="21" t="s">
         <v>91</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10261,6 +10462,10 @@
         <f aca="false">SEO!B54</f>
         <v>16</v>
       </c>
+      <c r="F34" s="24" t="n">
+        <f aca="false">SEO!B55</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
@@ -10282,6 +10487,10 @@
         <f aca="false">SEO!C54</f>
         <v>918</v>
       </c>
+      <c r="F35" s="24" t="n">
+        <f aca="false">SEO!C55</f>
+        <v>918</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="22" t="s">
@@ -10303,6 +10512,10 @@
         <f aca="false">SEO!D54</f>
         <v>882</v>
       </c>
+      <c r="F36" s="24" t="n">
+        <f aca="false">SEO!D55</f>
+        <v>882</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
@@ -10324,6 +10537,10 @@
         <f aca="false">SEO!E54</f>
         <v>33.99</v>
       </c>
+      <c r="F37" s="24" t="n">
+        <f aca="false">SEO!E55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
@@ -10345,6 +10562,10 @@
         <f aca="false">SEO!F54</f>
         <v>4</v>
       </c>
+      <c r="F38" s="24" t="n">
+        <f aca="false">SEO!F55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
@@ -10366,6 +10587,10 @@
         <f aca="false">SEO!G54</f>
         <v>559</v>
       </c>
+      <c r="F39" s="24" t="n">
+        <f aca="false">SEO!G55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="22" t="s">
@@ -10387,6 +10612,10 @@
         <f aca="false">SEO!H54</f>
         <v>394</v>
       </c>
+      <c r="F40" s="24" t="n">
+        <f aca="false">SEO!H55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="22" t="s">
@@ -10408,6 +10637,10 @@
         <f aca="false">SEO!I54</f>
         <v>30</v>
       </c>
+      <c r="F41" s="24" t="n">
+        <f aca="false">SEO!I55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
@@ -10429,6 +10662,10 @@
         <f aca="false">SEO!J54</f>
         <v>2.8</v>
       </c>
+      <c r="F42" s="24" t="n">
+        <f aca="false">SEO!J55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="22" t="s">
@@ -10450,6 +10687,10 @@
         <f aca="false">SEO!K54</f>
         <v>1056</v>
       </c>
+      <c r="F43" s="24" t="n">
+        <f aca="false">SEO!K55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="22" t="s">
@@ -10471,6 +10712,10 @@
         <f aca="false">SEO!L54</f>
         <v>25.8</v>
       </c>
+      <c r="F44" s="24" t="n">
+        <f aca="false">SEO!L55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="22" t="s">
@@ -10492,6 +10737,10 @@
         <f aca="false">SEO!M54</f>
         <v>80</v>
       </c>
+      <c r="F45" s="24" t="n">
+        <f aca="false">SEO!M55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="22" t="s">
@@ -10513,6 +10762,10 @@
         <f aca="false">SEO!N54</f>
         <v>119</v>
       </c>
+      <c r="F46" s="24" t="n">
+        <f aca="false">SEO!N55</f>
+        <v>119</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="22" t="s">
@@ -10534,10 +10787,14 @@
         <f aca="false">SEO!O54</f>
         <v>342</v>
       </c>
+      <c r="F47" s="24" t="n">
+        <f aca="false">SEO!O55</f>
+        <v>331</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10553,6 +10810,9 @@
       <c r="D50" s="21" t="s">
         <v>91</v>
       </c>
+      <c r="E50" s="21" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="22" t="s">
@@ -10570,6 +10830,10 @@
         <f aca="false">Audit!B51</f>
         <v>93</v>
       </c>
+      <c r="E51" s="24" t="n">
+        <f aca="false">Audit!B52</f>
+        <v>93</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="22" t="s">
@@ -10587,6 +10851,10 @@
         <f aca="false">Audit!C51</f>
         <v>98</v>
       </c>
+      <c r="E52" s="24" t="n">
+        <f aca="false">Audit!C52</f>
+        <v>98</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="22" t="s">
@@ -10604,6 +10872,10 @@
         <f aca="false">Audit!D51</f>
         <v>95</v>
       </c>
+      <c r="E53" s="24" t="n">
+        <f aca="false">Audit!D52</f>
+        <v>95</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="s">
@@ -10621,6 +10893,10 @@
         <f aca="false">Audit!E51</f>
         <v>92</v>
       </c>
+      <c r="E54" s="24" t="n">
+        <f aca="false">Audit!E52</f>
+        <v>92</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
@@ -10638,6 +10914,10 @@
         <f aca="false">Audit!F51</f>
         <v>118</v>
       </c>
+      <c r="E55" s="24" t="n">
+        <f aca="false">Audit!F52</f>
+        <v>118</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="22" t="s">
@@ -10655,6 +10935,10 @@
         <f aca="false">Audit!G51</f>
         <v>98</v>
       </c>
+      <c r="E56" s="24" t="n">
+        <f aca="false">Audit!G52</f>
+        <v>98</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="22" t="s">
@@ -10672,6 +10956,10 @@
         <f aca="false">Audit!H51</f>
         <v>119</v>
       </c>
+      <c r="E57" s="24" t="n">
+        <f aca="false">Audit!H52</f>
+        <v>119</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="22" t="s">
@@ -10689,6 +10977,10 @@
         <f aca="false">Audit!I51</f>
         <v>92</v>
       </c>
+      <c r="E58" s="24" t="n">
+        <f aca="false">Audit!I52</f>
+        <v>92</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="22" t="s">
@@ -10706,6 +10998,10 @@
         <f aca="false">Audit!J51</f>
         <v>342</v>
       </c>
+      <c r="E59" s="24" t="n">
+        <f aca="false">Audit!J52</f>
+        <v>331</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="22" t="s">
@@ -10723,6 +11019,10 @@
         <f aca="false">Audit!K51</f>
         <v>276</v>
       </c>
+      <c r="E60" s="24" t="n">
+        <f aca="false">Audit!K52</f>
+        <v>268</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="22" t="s">
@@ -10739,6 +11039,10 @@
       <c r="D61" s="24" t="n">
         <f aca="false">Audit!L51</f>
         <v>241329</v>
+      </c>
+      <c r="E61" s="24" t="n">
+        <f aca="false">Audit!L52</f>
+        <v>241211</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-01 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-02 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">87 dòng × 7 chỉ số · 2026-07-05 → 2026-09-29</t>
+    <t xml:space="preserve">88 dòng × 7 chỉ số · 2026-07-05 → 2026-09-30</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">50 dòng × 14 chỉ số · 2026-07-23 → 2026-10-01</t>
+    <t xml:space="preserve">51 dòng × 14 chỉ số · 2026-07-23 → 2026-10-02</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">50 dòng × 14 chỉ số · 2026-06-30 → 2026-10-01</t>
+    <t xml:space="preserve">51 dòng × 14 chỉ số · 2026-06-30 → 2026-10-02</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">47 dòng × 11 chỉ số · 2026-07-27 → 2026-10-01</t>
+    <t xml:space="preserve">48 dòng × 11 chỉ số · 2026-07-27 → 2026-10-02</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 87 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 88 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 50 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 51 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 50 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 51 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 47 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 48 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3315,6 +3315,32 @@
       </c>
       <c r="H92" s="16" t="n">
         <v>60</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="15" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B93" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C93" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="16" t="n">
+        <v>162</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H93" s="16" t="n">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3333,7 +3359,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5794,6 +5820,53 @@
       </c>
       <c r="N55" s="16"/>
       <c r="O55" s="16"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B56" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>4339</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="F56" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="I56" s="16" t="n">
+        <v>2409</v>
+      </c>
+      <c r="J56" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K56" s="16" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L56" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="M56" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="N56" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>633</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5811,7 +5884,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8161,6 +8234,53 @@
       </c>
       <c r="O55" s="16" t="n">
         <v>331</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B56" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>882</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="F56" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>587</v>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>403</v>
+      </c>
+      <c r="I56" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="J56" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K56" s="16" t="n">
+        <v>979</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M56" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="N56" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -8179,7 +8299,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9922,6 +10042,44 @@
         <v>268</v>
       </c>
       <c r="L52" s="16" t="n">
+        <v>241211</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B53" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>96</v>
+      </c>
+      <c r="H53" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I53" s="16" t="n">
+        <v>92</v>
+      </c>
+      <c r="J53" s="16" t="n">
+        <v>531</v>
+      </c>
+      <c r="K53" s="16" t="n">
+        <v>493</v>
+      </c>
+      <c r="L53" s="16" t="n">
         <v>241211</v>
       </c>
     </row>
@@ -9987,16 +10145,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>145</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10004,16 +10162,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>353</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>354</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10021,16 +10179,16 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>4614</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>4776</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10038,16 +10196,16 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>422</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>425</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10055,16 +10213,16 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>23</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10072,16 +10230,16 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>166</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>174</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10089,16 +10247,16 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H92,'Social — theo ngày'!$A$6:$A$92,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$92,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2318</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2465</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10140,7 +10298,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B55</f>
+        <f aca="false">'Social — 28 ngày'!B56</f>
         <v>116</v>
       </c>
     </row>
@@ -10161,8 +10319,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C55</f>
-        <v>132</v>
+        <f aca="false">'Social — 28 ngày'!C56</f>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10182,8 +10340,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D55</f>
-        <v>4427</v>
+        <f aca="false">'Social — 28 ngày'!D56</f>
+        <v>4339</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10203,8 +10361,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E55</f>
-        <v>421</v>
+        <f aca="false">'Social — 28 ngày'!E56</f>
+        <v>401</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10224,7 +10382,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F55</f>
+        <f aca="false">'Social — 28 ngày'!F56</f>
         <v>49</v>
       </c>
     </row>
@@ -10245,8 +10403,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G55</f>
-        <v>23</v>
+        <f aca="false">'Social — 28 ngày'!G56</f>
+        <v>25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10266,8 +10424,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H55</f>
-        <v>87</v>
+        <f aca="false">'Social — 28 ngày'!H56</f>
+        <v>90</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10287,8 +10445,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I55</f>
-        <v>2297</v>
+        <f aca="false">'Social — 28 ngày'!I56</f>
+        <v>2409</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10308,7 +10466,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J55</f>
+        <f aca="false">'Social — 28 ngày'!J56</f>
         <v>102</v>
       </c>
     </row>
@@ -10329,8 +10487,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K55</f>
-        <v>1219</v>
+        <f aca="false">'Social — 28 ngày'!K56</f>
+        <v>1225</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10350,8 +10508,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L55</f>
-        <v>26</v>
+        <f aca="false">'Social — 28 ngày'!L56</f>
+        <v>27</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10371,8 +10529,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M55</f>
-        <v>37</v>
+        <f aca="false">'Social — 28 ngày'!M56</f>
+        <v>35</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10392,8 +10550,8 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N55</f>
-        <v>0</v>
+        <f aca="false">'Social — 28 ngày'!N56</f>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10413,8 +10571,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O55</f>
-        <v>0</v>
+        <f aca="false">'Social — 28 ngày'!O56</f>
+        <v>633</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10463,7 +10621,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B55</f>
+        <f aca="false">SEO!B56</f>
         <v>18</v>
       </c>
     </row>
@@ -10488,7 +10646,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C55</f>
+        <f aca="false">SEO!C56</f>
         <v>918</v>
       </c>
     </row>
@@ -10513,7 +10671,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D55</f>
+        <f aca="false">SEO!D56</f>
         <v>882</v>
       </c>
     </row>
@@ -10538,8 +10696,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E55</f>
-        <v>0</v>
+        <f aca="false">SEO!E56</f>
+        <v>34.92</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10563,8 +10721,8 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F55</f>
-        <v>0</v>
+        <f aca="false">SEO!F56</f>
+        <v>7</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10588,8 +10746,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G55</f>
-        <v>0</v>
+        <f aca="false">SEO!G56</f>
+        <v>587</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10613,8 +10771,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H55</f>
-        <v>0</v>
+        <f aca="false">SEO!H56</f>
+        <v>403</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10638,8 +10796,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I55</f>
-        <v>0</v>
+        <f aca="false">SEO!I56</f>
+        <v>31</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10663,8 +10821,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J55</f>
-        <v>0</v>
+        <f aca="false">SEO!J56</f>
+        <v>3.2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10688,8 +10846,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K55</f>
-        <v>0</v>
+        <f aca="false">SEO!K56</f>
+        <v>979</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10713,8 +10871,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L55</f>
-        <v>0</v>
+        <f aca="false">SEO!L56</f>
+        <v>23.6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10738,8 +10896,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M55</f>
-        <v>0</v>
+        <f aca="false">SEO!M56</f>
+        <v>84</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10763,7 +10921,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N55</f>
+        <f aca="false">SEO!N56</f>
         <v>119</v>
       </c>
     </row>
@@ -10788,8 +10946,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O55</f>
-        <v>331</v>
+        <f aca="false">SEO!O56</f>
+        <v>531</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10831,7 +10989,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B52</f>
+        <f aca="false">Audit!B53</f>
         <v>93</v>
       </c>
     </row>
@@ -10852,8 +11010,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C52</f>
-        <v>98</v>
+        <f aca="false">Audit!C53</f>
+        <v>99</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10873,7 +11031,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D52</f>
+        <f aca="false">Audit!D53</f>
         <v>95</v>
       </c>
     </row>
@@ -10894,7 +11052,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E52</f>
+        <f aca="false">Audit!E53</f>
         <v>92</v>
       </c>
     </row>
@@ -10915,7 +11073,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F52</f>
+        <f aca="false">Audit!F53</f>
         <v>118</v>
       </c>
     </row>
@@ -10936,8 +11094,8 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G52</f>
-        <v>98</v>
+        <f aca="false">Audit!G53</f>
+        <v>96</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10957,7 +11115,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H52</f>
+        <f aca="false">Audit!H53</f>
         <v>119</v>
       </c>
     </row>
@@ -10978,7 +11136,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I52</f>
+        <f aca="false">Audit!I53</f>
         <v>92</v>
       </c>
     </row>
@@ -10999,8 +11157,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J52</f>
-        <v>331</v>
+        <f aca="false">Audit!J53</f>
+        <v>531</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11020,8 +11178,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K52</f>
-        <v>268</v>
+        <f aca="false">Audit!K53</f>
+        <v>493</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11041,7 +11199,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L52</f>
+        <f aca="false">Audit!L53</f>
         <v>241211</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="97">
   <si>
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-02 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-03 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">88 dòng × 7 chỉ số · 2026-07-05 → 2026-09-30</t>
+    <t xml:space="preserve">90 dòng × 7 chỉ số · 2026-07-05 → 2026-10-02</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">51 dòng × 14 chỉ số · 2026-07-23 → 2026-10-02</t>
+    <t xml:space="preserve">52 dòng × 14 chỉ số · 2026-07-23 → 2026-10-03</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">51 dòng × 14 chỉ số · 2026-06-30 → 2026-10-02</t>
+    <t xml:space="preserve">52 dòng × 14 chỉ số · 2026-06-30 → 2026-10-03</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">48 dòng × 11 chỉ số · 2026-07-27 → 2026-10-02</t>
+    <t xml:space="preserve">49 dòng × 11 chỉ số · 2026-07-27 → 2026-10-03</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 88 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 90 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 51 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 52 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 51 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 52 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 48 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 49 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -303,10 +303,10 @@
     <t xml:space="preserve">2026-09</t>
   </si>
   <si>
-    <t xml:space="preserve">KHÔNG CỘNG — Social — 28 ngày (lấy ngày quét cuối tháng)</t>
+    <t xml:space="preserve">2026-10</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10</t>
+    <t xml:space="preserve">KHÔNG CỘNG — Social — 28 ngày (lấy ngày quét cuối tháng)</t>
   </si>
   <si>
     <t xml:space="preserve">KHÔNG CỘNG — SEO (lấy ngày quét cuối tháng)</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3341,6 +3341,58 @@
       </c>
       <c r="H93" s="16" t="n">
         <v>147</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="15" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B94" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C94" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D94" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F94" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G94" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H94" s="16" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="15" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B95" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C95" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="D95" s="16" t="n">
+        <v>194</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H95" s="16" t="n">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3359,7 +3411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5866,6 +5918,53 @@
       </c>
       <c r="O56" s="16" t="n">
         <v>633</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B57" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>157</v>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>4412</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="H57" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="I57" s="16" t="n">
+        <v>2610</v>
+      </c>
+      <c r="J57" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K57" s="16" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L57" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="M57" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="N57" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O57" s="16" t="n">
+        <v>736</v>
       </c>
     </row>
   </sheetData>
@@ -5884,7 +5983,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8281,6 +8380,53 @@
       </c>
       <c r="O56" s="16" t="n">
         <v>531</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B57" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>882</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>584</v>
+      </c>
+      <c r="H57" s="16" t="n">
+        <v>402</v>
+      </c>
+      <c r="I57" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="J57" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" s="16" t="n">
+        <v>923</v>
+      </c>
+      <c r="L57" s="19" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M57" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="N57" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O57" s="19" t="n">
+        <v>326.9</v>
       </c>
     </row>
   </sheetData>
@@ -8299,7 +8445,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10056,10 +10202,10 @@
         <v>99</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F53" s="16" t="n">
         <v>118</v>
@@ -10071,16 +10217,54 @@
         <v>119</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>531</v>
+        <v>564</v>
       </c>
       <c r="K53" s="16" t="n">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="L53" s="16" t="n">
-        <v>241211</v>
+        <v>241675</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B54" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H54" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I54" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J54" s="16" t="n">
+        <v>327</v>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="L54" s="16" t="n">
+        <v>241675</v>
       </c>
     </row>
   </sheetData>
@@ -10103,7 +10287,7 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10139,22 +10323,29 @@
       <c r="D6" s="21" t="s">
         <v>91</v>
       </c>
+      <c r="E6" s="21" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10162,16 +10353,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>90</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10179,16 +10374,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>383</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10196,16 +10395,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10213,16 +10416,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10230,16 +10437,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>174</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>42</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10247,21 +10458,25 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H93,'Social — theo ngày'!$A$6:$A$93,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$93,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>288</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10278,7 +10493,7 @@
         <v>91</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10298,7 +10513,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B56</f>
+        <f aca="false">'Social — 28 ngày'!B57</f>
         <v>116</v>
       </c>
     </row>
@@ -10319,8 +10534,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C56</f>
-        <v>140</v>
+        <f aca="false">'Social — 28 ngày'!C57</f>
+        <v>157</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10340,8 +10555,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D56</f>
-        <v>4339</v>
+        <f aca="false">'Social — 28 ngày'!D57</f>
+        <v>4412</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10361,7 +10576,7 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E56</f>
+        <f aca="false">'Social — 28 ngày'!E57</f>
         <v>401</v>
       </c>
     </row>
@@ -10382,7 +10597,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F56</f>
+        <f aca="false">'Social — 28 ngày'!F57</f>
         <v>49</v>
       </c>
     </row>
@@ -10403,8 +10618,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G56</f>
-        <v>25</v>
+        <f aca="false">'Social — 28 ngày'!G57</f>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10424,8 +10639,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H56</f>
-        <v>90</v>
+        <f aca="false">'Social — 28 ngày'!H57</f>
+        <v>116</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10445,8 +10660,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I56</f>
-        <v>2409</v>
+        <f aca="false">'Social — 28 ngày'!I57</f>
+        <v>2610</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10466,7 +10681,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J56</f>
+        <f aca="false">'Social — 28 ngày'!J57</f>
         <v>102</v>
       </c>
     </row>
@@ -10487,8 +10702,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K56</f>
-        <v>1225</v>
+        <f aca="false">'Social — 28 ngày'!K57</f>
+        <v>1263</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10508,8 +10723,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L56</f>
-        <v>27</v>
+        <f aca="false">'Social — 28 ngày'!L57</f>
+        <v>33</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10529,8 +10744,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M56</f>
-        <v>35</v>
+        <f aca="false">'Social — 28 ngày'!M57</f>
+        <v>34</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10550,8 +10765,8 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N56</f>
-        <v>6</v>
+        <f aca="false">'Social — 28 ngày'!N57</f>
+        <v>7</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10571,8 +10786,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O56</f>
-        <v>633</v>
+        <f aca="false">'Social — 28 ngày'!O57</f>
+        <v>736</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10597,7 +10812,7 @@
         <v>91</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10621,8 +10836,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B56</f>
-        <v>18</v>
+        <f aca="false">SEO!B57</f>
+        <v>16</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10646,7 +10861,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C56</f>
+        <f aca="false">SEO!C57</f>
         <v>918</v>
       </c>
     </row>
@@ -10671,7 +10886,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D56</f>
+        <f aca="false">SEO!D57</f>
         <v>882</v>
       </c>
     </row>
@@ -10696,8 +10911,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E56</f>
-        <v>34.92</v>
+        <f aca="false">SEO!E57</f>
+        <v>35.45</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10721,7 +10936,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F56</f>
+        <f aca="false">SEO!F57</f>
         <v>7</v>
       </c>
     </row>
@@ -10746,8 +10961,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G56</f>
-        <v>587</v>
+        <f aca="false">SEO!G57</f>
+        <v>584</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10771,8 +10986,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H56</f>
-        <v>403</v>
+        <f aca="false">SEO!H57</f>
+        <v>402</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10796,8 +11011,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I56</f>
-        <v>31</v>
+        <f aca="false">SEO!I57</f>
+        <v>28</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10821,8 +11036,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J56</f>
-        <v>3.2</v>
+        <f aca="false">SEO!J57</f>
+        <v>3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10846,8 +11061,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K56</f>
-        <v>979</v>
+        <f aca="false">SEO!K57</f>
+        <v>923</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10871,8 +11086,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L56</f>
-        <v>23.6</v>
+        <f aca="false">SEO!L57</f>
+        <v>22.6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10896,8 +11111,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M56</f>
-        <v>84</v>
+        <f aca="false">SEO!M57</f>
+        <v>86</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10921,7 +11136,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N56</f>
+        <f aca="false">SEO!N57</f>
         <v>119</v>
       </c>
     </row>
@@ -10946,8 +11161,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O56</f>
-        <v>531</v>
+        <f aca="false">SEO!O57</f>
+        <v>326.9</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10969,7 +11184,7 @@
         <v>91</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10989,7 +11204,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B53</f>
+        <f aca="false">Audit!B54</f>
         <v>93</v>
       </c>
     </row>
@@ -11010,8 +11225,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C53</f>
-        <v>99</v>
+        <f aca="false">Audit!C54</f>
+        <v>98</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11031,8 +11246,8 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D53</f>
-        <v>95</v>
+        <f aca="false">Audit!D54</f>
+        <v>97</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11052,8 +11267,8 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E53</f>
-        <v>92</v>
+        <f aca="false">Audit!E54</f>
+        <v>94</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11073,7 +11288,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F53</f>
+        <f aca="false">Audit!F54</f>
         <v>118</v>
       </c>
     </row>
@@ -11094,8 +11309,8 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G53</f>
-        <v>96</v>
+        <f aca="false">Audit!G54</f>
+        <v>98</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11115,7 +11330,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H53</f>
+        <f aca="false">Audit!H54</f>
         <v>119</v>
       </c>
     </row>
@@ -11136,8 +11351,8 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I53</f>
-        <v>92</v>
+        <f aca="false">Audit!I54</f>
+        <v>98</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11157,8 +11372,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J53</f>
-        <v>531</v>
+        <f aca="false">Audit!J54</f>
+        <v>327</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11178,8 +11393,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K53</f>
-        <v>493</v>
+        <f aca="false">Audit!K54</f>
+        <v>274.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11199,8 +11414,8 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L53</f>
-        <v>241211</v>
+        <f aca="false">Audit!L54</f>
+        <v>241675</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-03 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-04 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">90 dòng × 7 chỉ số · 2026-07-05 → 2026-10-02</t>
+    <t xml:space="preserve">91 dòng × 7 chỉ số · 2026-07-05 → 2026-10-03</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">52 dòng × 14 chỉ số · 2026-07-23 → 2026-10-03</t>
+    <t xml:space="preserve">53 dòng × 14 chỉ số · 2026-07-23 → 2026-10-05</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">52 dòng × 14 chỉ số · 2026-06-30 → 2026-10-03</t>
+    <t xml:space="preserve">53 dòng × 14 chỉ số · 2026-06-30 → 2026-10-05</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">49 dòng × 11 chỉ số · 2026-07-27 → 2026-10-03</t>
+    <t xml:space="preserve">50 dòng × 11 chỉ số · 2026-07-27 → 2026-10-05</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 90 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 91 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 52 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 53 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 52 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 53 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 49 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 50 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -2788,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="F72" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G72" s="16" t="n">
         <v>14</v>
@@ -2814,7 +2814,7 @@
         <v>12</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" s="16" t="n">
         <v>6</v>
@@ -2918,7 +2918,7 @@
         <v>7</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>3</v>
@@ -2944,7 +2944,7 @@
         <v>77</v>
       </c>
       <c r="F78" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G78" s="16" t="n">
         <v>39</v>
@@ -3393,6 +3393,32 @@
       </c>
       <c r="H95" s="16" t="n">
         <v>183</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="15" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B96" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D96" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="16" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3411,7 +3437,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5965,6 +5991,53 @@
       </c>
       <c r="O57" s="16" t="n">
         <v>736</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B58" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>158</v>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>4404</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="F58" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G58" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="H58" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="I58" s="16" t="n">
+        <v>2616</v>
+      </c>
+      <c r="J58" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K58" s="16" t="n">
+        <v>1282</v>
+      </c>
+      <c r="L58" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="M58" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="N58" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -5983,7 +6056,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8427,6 +8500,53 @@
       </c>
       <c r="O57" s="19" t="n">
         <v>326.9</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B58" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>882</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="F58" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G58" s="16" t="n">
+        <v>597</v>
+      </c>
+      <c r="H58" s="16" t="n">
+        <v>414</v>
+      </c>
+      <c r="I58" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K58" s="16" t="n">
+        <v>778</v>
+      </c>
+      <c r="L58" s="19" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M58" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="N58" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -8445,7 +8565,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10264,6 +10384,44 @@
         <v>274.5</v>
       </c>
       <c r="L54" s="16" t="n">
+        <v>241675</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H55" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I55" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J55" s="16" t="n">
+        <v>326</v>
+      </c>
+      <c r="K55" s="19" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="L55" s="16" t="n">
         <v>241675</v>
       </c>
     </row>
@@ -10332,20 +10490,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>21</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10353,20 +10511,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>90</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>96</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10374,20 +10532,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>383</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>437</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10395,19 +10553,19 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>6</v>
       </c>
     </row>
@@ -10416,20 +10574,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>10</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10437,20 +10595,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>174</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>42</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10458,20 +10616,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H95,'Social — theo ngày'!$A$6:$A$95,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$95,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>288</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>305</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10513,7 +10671,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B57</f>
+        <f aca="false">'Social — 28 ngày'!B58</f>
         <v>116</v>
       </c>
     </row>
@@ -10534,8 +10692,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C57</f>
-        <v>157</v>
+        <f aca="false">'Social — 28 ngày'!C58</f>
+        <v>158</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10555,8 +10713,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D57</f>
-        <v>4412</v>
+        <f aca="false">'Social — 28 ngày'!D58</f>
+        <v>4404</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10576,7 +10734,7 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E57</f>
+        <f aca="false">'Social — 28 ngày'!E58</f>
         <v>401</v>
       </c>
     </row>
@@ -10597,7 +10755,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F57</f>
+        <f aca="false">'Social — 28 ngày'!F58</f>
         <v>49</v>
       </c>
     </row>
@@ -10618,8 +10776,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G57</f>
-        <v>32</v>
+        <f aca="false">'Social — 28 ngày'!G58</f>
+        <v>33</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10639,8 +10797,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H57</f>
-        <v>116</v>
+        <f aca="false">'Social — 28 ngày'!H58</f>
+        <v>117</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10660,8 +10818,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I57</f>
-        <v>2610</v>
+        <f aca="false">'Social — 28 ngày'!I58</f>
+        <v>2616</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10681,7 +10839,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J57</f>
+        <f aca="false">'Social — 28 ngày'!J58</f>
         <v>102</v>
       </c>
     </row>
@@ -10702,8 +10860,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K57</f>
-        <v>1263</v>
+        <f aca="false">'Social — 28 ngày'!K58</f>
+        <v>1282</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10723,7 +10881,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L57</f>
+        <f aca="false">'Social — 28 ngày'!L58</f>
         <v>33</v>
       </c>
     </row>
@@ -10744,8 +10902,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M57</f>
-        <v>34</v>
+        <f aca="false">'Social — 28 ngày'!M58</f>
+        <v>36</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10765,7 +10923,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N57</f>
+        <f aca="false">'Social — 28 ngày'!N58</f>
         <v>7</v>
       </c>
     </row>
@@ -10786,8 +10944,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O57</f>
-        <v>736</v>
+        <f aca="false">'Social — 28 ngày'!O58</f>
+        <v>938</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10836,8 +10994,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B57</f>
-        <v>16</v>
+        <f aca="false">SEO!B58</f>
+        <v>14</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10861,7 +11019,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C57</f>
+        <f aca="false">SEO!C58</f>
         <v>918</v>
       </c>
     </row>
@@ -10886,7 +11044,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D57</f>
+        <f aca="false">SEO!D58</f>
         <v>882</v>
       </c>
     </row>
@@ -10911,8 +11069,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E57</f>
-        <v>35.45</v>
+        <f aca="false">SEO!E58</f>
+        <v>35.18</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10936,7 +11094,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F57</f>
+        <f aca="false">SEO!F58</f>
         <v>7</v>
       </c>
     </row>
@@ -10961,8 +11119,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G57</f>
-        <v>584</v>
+        <f aca="false">SEO!G58</f>
+        <v>597</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10986,8 +11144,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H57</f>
-        <v>402</v>
+        <f aca="false">SEO!H58</f>
+        <v>414</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11011,8 +11169,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I57</f>
-        <v>28</v>
+        <f aca="false">SEO!I58</f>
+        <v>22</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11036,8 +11194,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J57</f>
-        <v>3</v>
+        <f aca="false">SEO!J58</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11061,8 +11219,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K57</f>
-        <v>923</v>
+        <f aca="false">SEO!K58</f>
+        <v>778</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11086,8 +11244,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L57</f>
-        <v>22.6</v>
+        <f aca="false">SEO!L58</f>
+        <v>19.3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11111,8 +11269,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M57</f>
-        <v>86</v>
+        <f aca="false">SEO!M58</f>
+        <v>83</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11136,7 +11294,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N57</f>
+        <f aca="false">SEO!N58</f>
         <v>119</v>
       </c>
     </row>
@@ -11161,8 +11319,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O57</f>
-        <v>326.9</v>
+        <f aca="false">SEO!O58</f>
+        <v>326</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11204,7 +11362,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B54</f>
+        <f aca="false">Audit!B55</f>
         <v>93</v>
       </c>
     </row>
@@ -11225,7 +11383,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C54</f>
+        <f aca="false">Audit!C55</f>
         <v>98</v>
       </c>
     </row>
@@ -11246,7 +11404,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D54</f>
+        <f aca="false">Audit!D55</f>
         <v>97</v>
       </c>
     </row>
@@ -11267,7 +11425,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E54</f>
+        <f aca="false">Audit!E55</f>
         <v>94</v>
       </c>
     </row>
@@ -11288,7 +11446,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F54</f>
+        <f aca="false">Audit!F55</f>
         <v>118</v>
       </c>
     </row>
@@ -11309,7 +11467,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G54</f>
+        <f aca="false">Audit!G55</f>
         <v>98</v>
       </c>
     </row>
@@ -11330,7 +11488,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H54</f>
+        <f aca="false">Audit!H55</f>
         <v>119</v>
       </c>
     </row>
@@ -11351,7 +11509,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I54</f>
+        <f aca="false">Audit!I55</f>
         <v>98</v>
       </c>
     </row>
@@ -11372,8 +11530,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J54</f>
-        <v>327</v>
+        <f aca="false">Audit!J55</f>
+        <v>326</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11393,8 +11551,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K54</f>
-        <v>274.5</v>
+        <f aca="false">Audit!K55</f>
+        <v>271.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11414,7 +11572,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L54</f>
+        <f aca="false">Audit!L55</f>
         <v>241675</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-04 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-05 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">91 dòng × 7 chỉ số · 2026-07-05 → 2026-10-03</t>
+    <t xml:space="preserve">92 dòng × 7 chỉ số · 2026-07-05 → 2026-10-04</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">53 dòng × 14 chỉ số · 2026-07-23 → 2026-10-05</t>
+    <t xml:space="preserve">54 dòng × 14 chỉ số · 2026-07-23 → 2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">53 dòng × 14 chỉ số · 2026-06-30 → 2026-10-05</t>
+    <t xml:space="preserve">54 dòng × 14 chỉ số · 2026-06-30 → 2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">50 dòng × 11 chỉ số · 2026-07-27 → 2026-10-05</t>
+    <t xml:space="preserve">51 dòng × 11 chỉ số · 2026-07-27 → 2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 91 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 92 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 53 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 54 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 53 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 54 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 50 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 51 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3419,6 +3419,32 @@
       </c>
       <c r="H96" s="16" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="15" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="16" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3437,7 +3463,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6038,6 +6064,53 @@
       </c>
       <c r="O58" s="16" t="n">
         <v>938</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B59" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>158</v>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>4380</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>366</v>
+      </c>
+      <c r="F59" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="H59" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="I59" s="16" t="n">
+        <v>2610</v>
+      </c>
+      <c r="J59" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K59" s="16" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L59" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="M59" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="N59" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>940</v>
       </c>
     </row>
   </sheetData>
@@ -6056,7 +6129,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8547,6 +8620,53 @@
       </c>
       <c r="O58" s="16" t="n">
         <v>326</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B59" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>882</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="F59" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>599</v>
+      </c>
+      <c r="H59" s="16" t="n">
+        <v>417</v>
+      </c>
+      <c r="I59" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J59" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K59" s="16" t="n">
+        <v>763</v>
+      </c>
+      <c r="L59" s="19" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="M59" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="N59" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -8565,7 +8685,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10422,6 +10542,44 @@
         <v>271.5</v>
       </c>
       <c r="L55" s="16" t="n">
+        <v>241675</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F56" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H56" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I56" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J56" s="16" t="n">
+        <v>333</v>
+      </c>
+      <c r="K56" s="19" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="L56" s="16" t="n">
         <v>241675</v>
       </c>
     </row>
@@ -10490,19 +10648,19 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>23</v>
       </c>
     </row>
@@ -10511,20 +10669,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>96</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10532,20 +10690,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>437</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>482</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10553,20 +10711,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>6</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10574,19 +10732,19 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>11</v>
       </c>
     </row>
@@ -10595,20 +10753,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>174</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>45</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10616,20 +10774,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H96,'Social — theo ngày'!$A$6:$A$96,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$96,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>305</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>324</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10671,7 +10829,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B58</f>
+        <f aca="false">'Social — 28 ngày'!B59</f>
         <v>116</v>
       </c>
     </row>
@@ -10692,7 +10850,7 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C58</f>
+        <f aca="false">'Social — 28 ngày'!C59</f>
         <v>158</v>
       </c>
     </row>
@@ -10713,8 +10871,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D58</f>
-        <v>4404</v>
+        <f aca="false">'Social — 28 ngày'!D59</f>
+        <v>4380</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10734,8 +10892,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E58</f>
-        <v>401</v>
+        <f aca="false">'Social — 28 ngày'!E59</f>
+        <v>366</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10755,7 +10913,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F58</f>
+        <f aca="false">'Social — 28 ngày'!F59</f>
         <v>49</v>
       </c>
     </row>
@@ -10776,7 +10934,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G58</f>
+        <f aca="false">'Social — 28 ngày'!G59</f>
         <v>33</v>
       </c>
     </row>
@@ -10797,7 +10955,7 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H58</f>
+        <f aca="false">'Social — 28 ngày'!H59</f>
         <v>117</v>
       </c>
     </row>
@@ -10818,8 +10976,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I58</f>
-        <v>2616</v>
+        <f aca="false">'Social — 28 ngày'!I59</f>
+        <v>2610</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10839,7 +10997,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J58</f>
+        <f aca="false">'Social — 28 ngày'!J59</f>
         <v>102</v>
       </c>
     </row>
@@ -10860,8 +11018,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K58</f>
-        <v>1282</v>
+        <f aca="false">'Social — 28 ngày'!K59</f>
+        <v>1253</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10881,8 +11039,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L58</f>
-        <v>33</v>
+        <f aca="false">'Social — 28 ngày'!L59</f>
+        <v>31</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10902,8 +11060,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M58</f>
-        <v>36</v>
+        <f aca="false">'Social — 28 ngày'!M59</f>
+        <v>37</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10923,7 +11081,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N58</f>
+        <f aca="false">'Social — 28 ngày'!N59</f>
         <v>7</v>
       </c>
     </row>
@@ -10944,8 +11102,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O58</f>
-        <v>938</v>
+        <f aca="false">'Social — 28 ngày'!O59</f>
+        <v>940</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10994,8 +11152,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B58</f>
-        <v>14</v>
+        <f aca="false">SEO!B59</f>
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11019,7 +11177,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C58</f>
+        <f aca="false">SEO!C59</f>
         <v>918</v>
       </c>
     </row>
@@ -11044,7 +11202,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D58</f>
+        <f aca="false">SEO!D59</f>
         <v>882</v>
       </c>
     </row>
@@ -11069,8 +11227,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E58</f>
-        <v>35.18</v>
+        <f aca="false">SEO!E59</f>
+        <v>34.22</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11094,7 +11252,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F58</f>
+        <f aca="false">SEO!F59</f>
         <v>7</v>
       </c>
     </row>
@@ -11119,8 +11277,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G58</f>
-        <v>597</v>
+        <f aca="false">SEO!G59</f>
+        <v>599</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11144,8 +11302,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H58</f>
-        <v>414</v>
+        <f aca="false">SEO!H59</f>
+        <v>417</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11169,7 +11327,7 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I58</f>
+        <f aca="false">SEO!I59</f>
         <v>22</v>
       </c>
     </row>
@@ -11194,8 +11352,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J58</f>
-        <v>2.8</v>
+        <f aca="false">SEO!J59</f>
+        <v>2.9</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11219,8 +11377,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K58</f>
-        <v>778</v>
+        <f aca="false">SEO!K59</f>
+        <v>763</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11244,8 +11402,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L58</f>
-        <v>19.3</v>
+        <f aca="false">SEO!L59</f>
+        <v>19.6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11269,7 +11427,7 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M58</f>
+        <f aca="false">SEO!M59</f>
         <v>83</v>
       </c>
     </row>
@@ -11294,7 +11452,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N58</f>
+        <f aca="false">SEO!N59</f>
         <v>119</v>
       </c>
     </row>
@@ -11319,8 +11477,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O58</f>
-        <v>326</v>
+        <f aca="false">SEO!O59</f>
+        <v>333</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11362,7 +11520,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B55</f>
+        <f aca="false">Audit!B56</f>
         <v>93</v>
       </c>
     </row>
@@ -11383,8 +11541,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C55</f>
-        <v>98</v>
+        <f aca="false">Audit!C56</f>
+        <v>99</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11404,7 +11562,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D55</f>
+        <f aca="false">Audit!D56</f>
         <v>97</v>
       </c>
     </row>
@@ -11425,7 +11583,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E55</f>
+        <f aca="false">Audit!E56</f>
         <v>94</v>
       </c>
     </row>
@@ -11446,7 +11604,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F55</f>
+        <f aca="false">Audit!F56</f>
         <v>118</v>
       </c>
     </row>
@@ -11467,7 +11625,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G55</f>
+        <f aca="false">Audit!G56</f>
         <v>98</v>
       </c>
     </row>
@@ -11488,7 +11646,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H55</f>
+        <f aca="false">Audit!H56</f>
         <v>119</v>
       </c>
     </row>
@@ -11509,7 +11667,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I55</f>
+        <f aca="false">Audit!I56</f>
         <v>98</v>
       </c>
     </row>
@@ -11530,8 +11688,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J55</f>
-        <v>326</v>
+        <f aca="false">Audit!J56</f>
+        <v>333</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11551,8 +11709,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K55</f>
-        <v>271.5</v>
+        <f aca="false">Audit!K56</f>
+        <v>282.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11572,7 +11730,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L55</f>
+        <f aca="false">Audit!L56</f>
         <v>241675</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-05 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-06 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">92 dòng × 7 chỉ số · 2026-07-05 → 2026-10-04</t>
+    <t xml:space="preserve">93 dòng × 7 chỉ số · 2026-07-05 → 2026-10-05</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">54 dòng × 14 chỉ số · 2026-07-23 → 2026-10-06</t>
+    <t xml:space="preserve">55 dòng × 14 chỉ số · 2026-07-23 → 2026-10-07</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">54 dòng × 14 chỉ số · 2026-06-30 → 2026-10-06</t>
+    <t xml:space="preserve">55 dòng × 14 chỉ số · 2026-06-30 → 2026-10-07</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">51 dòng × 11 chỉ số · 2026-07-27 → 2026-10-06</t>
+    <t xml:space="preserve">52 dòng × 11 chỉ số · 2026-07-27 → 2026-10-07</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 92 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 93 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 54 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 55 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 54 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 55 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 51 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 52 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -2788,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="F72" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G72" s="16" t="n">
         <v>14</v>
@@ -2814,7 +2814,7 @@
         <v>12</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G73" s="16" t="n">
         <v>6</v>
@@ -2918,7 +2918,7 @@
         <v>7</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>3</v>
@@ -2944,10 +2944,10 @@
         <v>77</v>
       </c>
       <c r="F78" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H78" s="16" t="n">
         <v>310</v>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H80" s="16" t="n">
         <v>49</v>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H81" s="16" t="n">
         <v>274</v>
@@ -3129,7 +3129,7 @@
         <v>2</v>
       </c>
       <c r="G85" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H85" s="16" t="n">
         <v>29</v>
@@ -3207,7 +3207,7 @@
         <v>4</v>
       </c>
       <c r="G88" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H88" s="16" t="n">
         <v>29</v>
@@ -3285,7 +3285,7 @@
         <v>3</v>
       </c>
       <c r="G91" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H91" s="16" t="n">
         <v>30</v>
@@ -3337,7 +3337,7 @@
         <v>2</v>
       </c>
       <c r="G93" s="16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H93" s="16" t="n">
         <v>147</v>
@@ -3363,7 +3363,7 @@
         <v>7</v>
       </c>
       <c r="G94" s="16" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H94" s="16" t="n">
         <v>105</v>
@@ -3445,6 +3445,32 @@
       </c>
       <c r="H97" s="16" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="15" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B98" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="C98" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="16" t="n">
+        <v>197</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F98" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H98" s="16" t="n">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3463,7 +3489,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6111,6 +6137,53 @@
       </c>
       <c r="O59" s="16" t="n">
         <v>940</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B60" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>201</v>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>4418</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>352</v>
+      </c>
+      <c r="F60" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G60" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="H60" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I60" s="16" t="n">
+        <v>2707</v>
+      </c>
+      <c r="J60" s="16" t="n">
+        <v>102</v>
+      </c>
+      <c r="K60" s="16" t="n">
+        <v>1188</v>
+      </c>
+      <c r="L60" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="M60" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="N60" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -6129,7 +6202,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8667,6 +8740,53 @@
       </c>
       <c r="O59" s="16" t="n">
         <v>333</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B60" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>918</v>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>882</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="F60" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G60" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="H60" s="16" t="n">
+        <v>421</v>
+      </c>
+      <c r="I60" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K60" s="16" t="n">
+        <v>748</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M60" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="N60" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -8685,7 +8805,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10580,6 +10700,44 @@
         <v>282.5</v>
       </c>
       <c r="L56" s="16" t="n">
+        <v>241675</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H57" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I57" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J57" s="16" t="n">
+        <v>338</v>
+      </c>
+      <c r="K57" s="19" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="L57" s="16" t="n">
         <v>241675</v>
       </c>
     </row>
@@ -10648,20 +10806,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>23</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10669,20 +10827,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>100</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10690,20 +10848,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>482</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>679</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10711,20 +10869,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>8</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10732,19 +10890,19 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>11</v>
       </c>
     </row>
@@ -10753,20 +10911,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>174</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>46</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10774,20 +10932,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H97,'Social — theo ngày'!$A$6:$A$97,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$97,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>324</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>467</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10829,7 +10987,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B59</f>
+        <f aca="false">'Social — 28 ngày'!B60</f>
         <v>116</v>
       </c>
     </row>
@@ -10850,8 +11008,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C59</f>
-        <v>158</v>
+        <f aca="false">'Social — 28 ngày'!C60</f>
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10871,8 +11029,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D59</f>
-        <v>4380</v>
+        <f aca="false">'Social — 28 ngày'!D60</f>
+        <v>4418</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10892,8 +11050,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E59</f>
-        <v>366</v>
+        <f aca="false">'Social — 28 ngày'!E60</f>
+        <v>352</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10913,7 +11071,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F59</f>
+        <f aca="false">'Social — 28 ngày'!F60</f>
         <v>49</v>
       </c>
     </row>
@@ -10934,7 +11092,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G59</f>
+        <f aca="false">'Social — 28 ngày'!G60</f>
         <v>33</v>
       </c>
     </row>
@@ -10955,8 +11113,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H59</f>
-        <v>117</v>
+        <f aca="false">'Social — 28 ngày'!H60</f>
+        <v>119</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10976,8 +11134,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I59</f>
-        <v>2610</v>
+        <f aca="false">'Social — 28 ngày'!I60</f>
+        <v>2707</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10997,7 +11155,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J59</f>
+        <f aca="false">'Social — 28 ngày'!J60</f>
         <v>102</v>
       </c>
     </row>
@@ -11018,8 +11176,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K59</f>
-        <v>1253</v>
+        <f aca="false">'Social — 28 ngày'!K60</f>
+        <v>1188</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11039,8 +11197,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L59</f>
-        <v>31</v>
+        <f aca="false">'Social — 28 ngày'!L60</f>
+        <v>29</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11060,8 +11218,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M59</f>
-        <v>37</v>
+        <f aca="false">'Social — 28 ngày'!M60</f>
+        <v>29</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11081,7 +11239,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N59</f>
+        <f aca="false">'Social — 28 ngày'!N60</f>
         <v>7</v>
       </c>
     </row>
@@ -11102,8 +11260,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O59</f>
-        <v>940</v>
+        <f aca="false">'Social — 28 ngày'!O60</f>
+        <v>939</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11152,7 +11310,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B59</f>
+        <f aca="false">SEO!B60</f>
         <v>13</v>
       </c>
     </row>
@@ -11177,7 +11335,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C59</f>
+        <f aca="false">SEO!C60</f>
         <v>918</v>
       </c>
     </row>
@@ -11202,7 +11360,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D59</f>
+        <f aca="false">SEO!D60</f>
         <v>882</v>
       </c>
     </row>
@@ -11227,8 +11385,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E59</f>
-        <v>34.22</v>
+        <f aca="false">SEO!E60</f>
+        <v>32.17</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11252,7 +11410,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F59</f>
+        <f aca="false">SEO!F60</f>
         <v>7</v>
       </c>
     </row>
@@ -11277,8 +11435,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G59</f>
-        <v>599</v>
+        <f aca="false">SEO!G60</f>
+        <v>600</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11302,8 +11460,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H59</f>
-        <v>417</v>
+        <f aca="false">SEO!H60</f>
+        <v>421</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11327,7 +11485,7 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I59</f>
+        <f aca="false">SEO!I60</f>
         <v>22</v>
       </c>
     </row>
@@ -11352,7 +11510,7 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J59</f>
+        <f aca="false">SEO!J60</f>
         <v>2.9</v>
       </c>
     </row>
@@ -11377,8 +11535,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K59</f>
-        <v>763</v>
+        <f aca="false">SEO!K60</f>
+        <v>748</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11402,8 +11560,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L59</f>
-        <v>19.6</v>
+        <f aca="false">SEO!L60</f>
+        <v>19.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11427,8 +11585,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M59</f>
-        <v>83</v>
+        <f aca="false">SEO!M60</f>
+        <v>82</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11452,7 +11610,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N59</f>
+        <f aca="false">SEO!N60</f>
         <v>119</v>
       </c>
     </row>
@@ -11477,8 +11635,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O59</f>
-        <v>333</v>
+        <f aca="false">SEO!O60</f>
+        <v>338</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11520,7 +11678,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B56</f>
+        <f aca="false">Audit!B57</f>
         <v>93</v>
       </c>
     </row>
@@ -11541,8 +11699,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C56</f>
-        <v>99</v>
+        <f aca="false">Audit!C57</f>
+        <v>98</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11562,7 +11720,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D56</f>
+        <f aca="false">Audit!D57</f>
         <v>97</v>
       </c>
     </row>
@@ -11583,7 +11741,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E56</f>
+        <f aca="false">Audit!E57</f>
         <v>94</v>
       </c>
     </row>
@@ -11604,7 +11762,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F56</f>
+        <f aca="false">Audit!F57</f>
         <v>118</v>
       </c>
     </row>
@@ -11625,7 +11783,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G56</f>
+        <f aca="false">Audit!G57</f>
         <v>98</v>
       </c>
     </row>
@@ -11646,7 +11804,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H56</f>
+        <f aca="false">Audit!H57</f>
         <v>119</v>
       </c>
     </row>
@@ -11667,7 +11825,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I56</f>
+        <f aca="false">Audit!I57</f>
         <v>98</v>
       </c>
     </row>
@@ -11688,8 +11846,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J56</f>
-        <v>333</v>
+        <f aca="false">Audit!J57</f>
+        <v>338</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11709,8 +11867,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K56</f>
-        <v>282.5</v>
+        <f aca="false">Audit!K57</f>
+        <v>277.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11730,7 +11888,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L56</f>
+        <f aca="false">Audit!L57</f>
         <v>241675</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-06 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-07 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">93 dòng × 7 chỉ số · 2026-07-05 → 2026-10-05</t>
+    <t xml:space="preserve">94 dòng × 7 chỉ số · 2026-07-05 → 2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">55 dòng × 14 chỉ số · 2026-07-23 → 2026-10-07</t>
+    <t xml:space="preserve">56 dòng × 14 chỉ số · 2026-07-23 → 2026-10-08</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">55 dòng × 14 chỉ số · 2026-06-30 → 2026-10-07</t>
+    <t xml:space="preserve">56 dòng × 14 chỉ số · 2026-06-30 → 2026-10-08</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">52 dòng × 11 chỉ số · 2026-07-27 → 2026-10-07</t>
+    <t xml:space="preserve">53 dòng × 11 chỉ số · 2026-07-27 → 2026-10-08</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 93 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 94 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 55 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 56 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 55 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 56 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 52 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 53 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3471,6 +3471,32 @@
       </c>
       <c r="H98" s="16" t="n">
         <v>143</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="15" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B99" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C99" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="D99" s="16" t="n">
+        <v>521</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="F99" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" s="16" t="n">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3489,7 +3515,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6184,6 +6210,53 @@
       </c>
       <c r="O60" s="16" t="n">
         <v>939</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B61" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>198</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>4680</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>393</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G61" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H61" s="16" t="n">
+        <v>114</v>
+      </c>
+      <c r="I61" s="16" t="n">
+        <v>2794</v>
+      </c>
+      <c r="J61" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="K61" s="16" t="n">
+        <v>1220</v>
+      </c>
+      <c r="L61" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="M61" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="N61" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -6202,7 +6275,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8787,6 +8860,53 @@
       </c>
       <c r="O60" s="16" t="n">
         <v>338</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B61" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>917</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>881</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G61" s="16" t="n">
+        <v>616</v>
+      </c>
+      <c r="H61" s="16" t="n">
+        <v>432</v>
+      </c>
+      <c r="I61" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J61" s="19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K61" s="16" t="n">
+        <v>748</v>
+      </c>
+      <c r="L61" s="19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M61" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="N61" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -8805,7 +8925,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10738,6 +10858,44 @@
         <v>277.5</v>
       </c>
       <c r="L57" s="16" t="n">
+        <v>241675</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C58" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F58" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G58" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H58" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I58" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J58" s="16" t="n">
+        <v>308</v>
+      </c>
+      <c r="K58" s="19" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="L58" s="16" t="n">
         <v>241675</v>
       </c>
     </row>
@@ -10806,20 +10964,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>74</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10827,20 +10985,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>108</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10848,20 +11006,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>679</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10869,20 +11027,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>21</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10890,20 +11048,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>11</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10911,20 +11069,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>48</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10932,20 +11090,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H98,'Social — theo ngày'!$A$6:$A$98,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$98,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>467</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>638</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10987,7 +11145,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B60</f>
+        <f aca="false">'Social — 28 ngày'!B61</f>
         <v>116</v>
       </c>
     </row>
@@ -11008,8 +11166,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C60</f>
-        <v>201</v>
+        <f aca="false">'Social — 28 ngày'!C61</f>
+        <v>198</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11029,8 +11187,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D60</f>
-        <v>4418</v>
+        <f aca="false">'Social — 28 ngày'!D61</f>
+        <v>4680</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11050,8 +11208,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E60</f>
-        <v>352</v>
+        <f aca="false">'Social — 28 ngày'!E61</f>
+        <v>393</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11071,7 +11229,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F60</f>
+        <f aca="false">'Social — 28 ngày'!F61</f>
         <v>49</v>
       </c>
     </row>
@@ -11092,8 +11250,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G60</f>
-        <v>33</v>
+        <f aca="false">'Social — 28 ngày'!G61</f>
+        <v>35</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11113,8 +11271,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H60</f>
-        <v>119</v>
+        <f aca="false">'Social — 28 ngày'!H61</f>
+        <v>114</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11134,8 +11292,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I60</f>
-        <v>2707</v>
+        <f aca="false">'Social — 28 ngày'!I61</f>
+        <v>2794</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11155,8 +11313,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J60</f>
-        <v>102</v>
+        <f aca="false">'Social — 28 ngày'!J61</f>
+        <v>120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11176,8 +11334,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K60</f>
-        <v>1188</v>
+        <f aca="false">'Social — 28 ngày'!K61</f>
+        <v>1220</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11197,7 +11355,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L60</f>
+        <f aca="false">'Social — 28 ngày'!L61</f>
         <v>29</v>
       </c>
     </row>
@@ -11218,7 +11376,7 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M60</f>
+        <f aca="false">'Social — 28 ngày'!M61</f>
         <v>29</v>
       </c>
     </row>
@@ -11239,7 +11397,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N60</f>
+        <f aca="false">'Social — 28 ngày'!N61</f>
         <v>7</v>
       </c>
     </row>
@@ -11260,8 +11418,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O60</f>
-        <v>939</v>
+        <f aca="false">'Social — 28 ngày'!O61</f>
+        <v>681</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11310,8 +11468,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B60</f>
-        <v>13</v>
+        <f aca="false">SEO!B61</f>
+        <v>12</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11335,8 +11493,8 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C60</f>
-        <v>918</v>
+        <f aca="false">SEO!C61</f>
+        <v>917</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11360,8 +11518,8 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D60</f>
-        <v>882</v>
+        <f aca="false">SEO!D61</f>
+        <v>881</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11385,8 +11543,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E60</f>
-        <v>32.17</v>
+        <f aca="false">SEO!E61</f>
+        <v>31.01</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11410,7 +11568,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F60</f>
+        <f aca="false">SEO!F61</f>
         <v>7</v>
       </c>
     </row>
@@ -11435,8 +11593,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G60</f>
-        <v>600</v>
+        <f aca="false">SEO!G61</f>
+        <v>616</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11460,8 +11618,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H60</f>
-        <v>421</v>
+        <f aca="false">SEO!H61</f>
+        <v>432</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11485,7 +11643,7 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I60</f>
+        <f aca="false">SEO!I61</f>
         <v>22</v>
       </c>
     </row>
@@ -11510,7 +11668,7 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J60</f>
+        <f aca="false">SEO!J61</f>
         <v>2.9</v>
       </c>
     </row>
@@ -11535,7 +11693,7 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K60</f>
+        <f aca="false">SEO!K61</f>
         <v>748</v>
       </c>
     </row>
@@ -11560,7 +11718,7 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L60</f>
+        <f aca="false">SEO!L61</f>
         <v>19.1</v>
       </c>
     </row>
@@ -11585,7 +11743,7 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M60</f>
+        <f aca="false">SEO!M61</f>
         <v>82</v>
       </c>
     </row>
@@ -11610,7 +11768,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N60</f>
+        <f aca="false">SEO!N61</f>
         <v>119</v>
       </c>
     </row>
@@ -11635,8 +11793,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O60</f>
-        <v>338</v>
+        <f aca="false">SEO!O61</f>
+        <v>308</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11678,7 +11836,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B57</f>
+        <f aca="false">Audit!B58</f>
         <v>93</v>
       </c>
     </row>
@@ -11699,8 +11857,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C57</f>
-        <v>98</v>
+        <f aca="false">Audit!C58</f>
+        <v>99</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11720,7 +11878,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D57</f>
+        <f aca="false">Audit!D58</f>
         <v>97</v>
       </c>
     </row>
@@ -11741,7 +11899,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E57</f>
+        <f aca="false">Audit!E58</f>
         <v>94</v>
       </c>
     </row>
@@ -11762,7 +11920,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F57</f>
+        <f aca="false">Audit!F58</f>
         <v>118</v>
       </c>
     </row>
@@ -11783,7 +11941,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G57</f>
+        <f aca="false">Audit!G58</f>
         <v>98</v>
       </c>
     </row>
@@ -11804,7 +11962,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H57</f>
+        <f aca="false">Audit!H58</f>
         <v>119</v>
       </c>
     </row>
@@ -11825,7 +11983,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I57</f>
+        <f aca="false">Audit!I58</f>
         <v>98</v>
       </c>
     </row>
@@ -11846,8 +12004,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J57</f>
-        <v>338</v>
+        <f aca="false">Audit!J58</f>
+        <v>308</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11867,8 +12025,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K57</f>
-        <v>277.5</v>
+        <f aca="false">Audit!K58</f>
+        <v>264.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11888,7 +12046,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L57</f>
+        <f aca="false">Audit!L58</f>
         <v>241675</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-07 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-08 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">94 dòng × 7 chỉ số · 2026-07-05 → 2026-10-06</t>
+    <t xml:space="preserve">95 dòng × 7 chỉ số · 2026-07-05 → 2026-10-07</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">56 dòng × 14 chỉ số · 2026-07-23 → 2026-10-08</t>
+    <t xml:space="preserve">57 dòng × 14 chỉ số · 2026-07-23 → 2026-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">56 dòng × 14 chỉ số · 2026-06-30 → 2026-10-08</t>
+    <t xml:space="preserve">57 dòng × 14 chỉ số · 2026-06-30 → 2026-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">53 dòng × 11 chỉ số · 2026-07-27 → 2026-10-08</t>
+    <t xml:space="preserve">54 dòng × 11 chỉ số · 2026-07-27 → 2026-10-09</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 94 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 95 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 56 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 57 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 56 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 57 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 53 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 54 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3497,6 +3497,32 @@
       </c>
       <c r="H99" s="16" t="n">
         <v>171</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="15" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B100" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C100" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="D100" s="16" t="n">
+        <v>307</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="F100" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="H100" s="16" t="n">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -3515,7 +3541,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6257,6 +6283,53 @@
       </c>
       <c r="O61" s="16" t="n">
         <v>681</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B62" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>197</v>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>4362</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>442</v>
+      </c>
+      <c r="F62" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G62" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="H62" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="I62" s="16" t="n">
+        <v>2466</v>
+      </c>
+      <c r="J62" s="16" t="n">
+        <v>124</v>
+      </c>
+      <c r="K62" s="16" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L62" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="M62" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="N62" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -6275,7 +6348,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -8907,6 +8980,53 @@
       </c>
       <c r="O61" s="16" t="n">
         <v>308</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B62" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>917</v>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>881</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="F62" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G62" s="16" t="n">
+        <v>635</v>
+      </c>
+      <c r="H62" s="16" t="n">
+        <v>440</v>
+      </c>
+      <c r="I62" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="J62" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K62" s="16" t="n">
+        <v>673</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M62" s="16" t="n">
+        <v>78</v>
+      </c>
+      <c r="N62" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -8925,7 +9045,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10896,6 +11016,44 @@
         <v>264.5</v>
       </c>
       <c r="L58" s="16" t="n">
+        <v>241675</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F59" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H59" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I59" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J59" s="16" t="n">
+        <v>327</v>
+      </c>
+      <c r="K59" s="16" t="n">
+        <v>270</v>
+      </c>
+      <c r="L59" s="16" t="n">
         <v>241675</v>
       </c>
     </row>
@@ -10964,20 +11122,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>78</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10985,20 +11143,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>146</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>207</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11006,20 +11164,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1200</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1507</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11027,20 +11185,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>92</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11048,20 +11206,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>13</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11069,20 +11227,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>51</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11090,20 +11248,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H99,'Social — theo ngày'!$A$6:$A$99,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$99,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>638</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>750</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11145,7 +11303,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B61</f>
+        <f aca="false">'Social — 28 ngày'!B62</f>
         <v>116</v>
       </c>
     </row>
@@ -11166,8 +11324,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C61</f>
-        <v>198</v>
+        <f aca="false">'Social — 28 ngày'!C62</f>
+        <v>197</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11187,8 +11345,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D61</f>
-        <v>4680</v>
+        <f aca="false">'Social — 28 ngày'!D62</f>
+        <v>4362</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11208,8 +11366,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E61</f>
-        <v>393</v>
+        <f aca="false">'Social — 28 ngày'!E62</f>
+        <v>442</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11229,7 +11387,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F61</f>
+        <f aca="false">'Social — 28 ngày'!F62</f>
         <v>49</v>
       </c>
     </row>
@@ -11250,8 +11408,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G61</f>
-        <v>35</v>
+        <f aca="false">'Social — 28 ngày'!G62</f>
+        <v>37</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11271,8 +11429,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H61</f>
-        <v>114</v>
+        <f aca="false">'Social — 28 ngày'!H62</f>
+        <v>117</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11292,8 +11450,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I61</f>
-        <v>2794</v>
+        <f aca="false">'Social — 28 ngày'!I62</f>
+        <v>2466</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11313,8 +11471,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J61</f>
-        <v>120</v>
+        <f aca="false">'Social — 28 ngày'!J62</f>
+        <v>124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11334,8 +11492,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K61</f>
-        <v>1220</v>
+        <f aca="false">'Social — 28 ngày'!K62</f>
+        <v>1243</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11355,8 +11513,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L61</f>
-        <v>29</v>
+        <f aca="false">'Social — 28 ngày'!L62</f>
+        <v>30</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11376,8 +11534,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M61</f>
-        <v>29</v>
+        <f aca="false">'Social — 28 ngày'!M62</f>
+        <v>30</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11397,7 +11555,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N61</f>
+        <f aca="false">'Social — 28 ngày'!N62</f>
         <v>7</v>
       </c>
     </row>
@@ -11418,8 +11576,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O61</f>
-        <v>681</v>
+        <f aca="false">'Social — 28 ngày'!O62</f>
+        <v>841</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11468,7 +11626,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B61</f>
+        <f aca="false">SEO!B62</f>
         <v>12</v>
       </c>
     </row>
@@ -11493,7 +11651,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C61</f>
+        <f aca="false">SEO!C62</f>
         <v>917</v>
       </c>
     </row>
@@ -11518,7 +11676,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D61</f>
+        <f aca="false">SEO!D62</f>
         <v>881</v>
       </c>
     </row>
@@ -11543,8 +11701,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E61</f>
-        <v>31.01</v>
+        <f aca="false">SEO!E62</f>
+        <v>34.02</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11568,7 +11726,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F61</f>
+        <f aca="false">SEO!F62</f>
         <v>7</v>
       </c>
     </row>
@@ -11593,8 +11751,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G61</f>
-        <v>616</v>
+        <f aca="false">SEO!G62</f>
+        <v>635</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11618,8 +11776,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H61</f>
-        <v>432</v>
+        <f aca="false">SEO!H62</f>
+        <v>440</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11643,8 +11801,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I61</f>
-        <v>22</v>
+        <f aca="false">SEO!I62</f>
+        <v>19</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11668,8 +11826,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J61</f>
-        <v>2.9</v>
+        <f aca="false">SEO!J62</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11693,8 +11851,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K61</f>
-        <v>748</v>
+        <f aca="false">SEO!K62</f>
+        <v>673</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11718,8 +11876,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L61</f>
-        <v>19.1</v>
+        <f aca="false">SEO!L62</f>
+        <v>14.6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11743,8 +11901,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M61</f>
-        <v>82</v>
+        <f aca="false">SEO!M62</f>
+        <v>78</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11768,7 +11926,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N61</f>
+        <f aca="false">SEO!N62</f>
         <v>119</v>
       </c>
     </row>
@@ -11793,8 +11951,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O61</f>
-        <v>308</v>
+        <f aca="false">SEO!O62</f>
+        <v>327</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11836,7 +11994,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B58</f>
+        <f aca="false">Audit!B59</f>
         <v>93</v>
       </c>
     </row>
@@ -11857,8 +12015,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C58</f>
-        <v>99</v>
+        <f aca="false">Audit!C59</f>
+        <v>98</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11878,7 +12036,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D58</f>
+        <f aca="false">Audit!D59</f>
         <v>97</v>
       </c>
     </row>
@@ -11899,7 +12057,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E58</f>
+        <f aca="false">Audit!E59</f>
         <v>94</v>
       </c>
     </row>
@@ -11920,7 +12078,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F58</f>
+        <f aca="false">Audit!F59</f>
         <v>118</v>
       </c>
     </row>
@@ -11941,7 +12099,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G58</f>
+        <f aca="false">Audit!G59</f>
         <v>98</v>
       </c>
     </row>
@@ -11962,7 +12120,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H58</f>
+        <f aca="false">Audit!H59</f>
         <v>119</v>
       </c>
     </row>
@@ -11983,7 +12141,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I58</f>
+        <f aca="false">Audit!I59</f>
         <v>98</v>
       </c>
     </row>
@@ -12004,8 +12162,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J58</f>
-        <v>308</v>
+        <f aca="false">Audit!J59</f>
+        <v>327</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12025,8 +12183,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K58</f>
-        <v>264.5</v>
+        <f aca="false">Audit!K59</f>
+        <v>270</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12046,7 +12204,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L58</f>
+        <f aca="false">Audit!L59</f>
         <v>241675</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-08 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-11 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">95 dòng × 7 chỉ số · 2026-07-05 → 2026-10-07</t>
+    <t xml:space="preserve">98 dòng × 7 chỉ số · 2026-07-05 → 2026-10-10</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">57 dòng × 14 chỉ số · 2026-07-23 → 2026-10-09</t>
+    <t xml:space="preserve">58 dòng × 14 chỉ số · 2026-07-23 → 2026-10-12</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">57 dòng × 14 chỉ số · 2026-06-30 → 2026-10-09</t>
+    <t xml:space="preserve">58 dòng × 14 chỉ số · 2026-06-30 → 2026-10-12</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">54 dòng × 11 chỉ số · 2026-07-27 → 2026-10-09</t>
+    <t xml:space="preserve">55 dòng × 11 chỉ số · 2026-07-27 → 2026-10-12</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 95 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 98 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 57 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 58 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 57 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 58 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 54 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 55 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3523,6 +3523,84 @@
       </c>
       <c r="H100" s="16" t="n">
         <v>112</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="15" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B101" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D101" s="16" t="n">
+        <v>216</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F101" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" s="16" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="15" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B102" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="15" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="16" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3541,7 +3619,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6330,6 +6408,53 @@
       </c>
       <c r="O62" s="16" t="n">
         <v>841</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B63" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>190</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>4238</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>431</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="H63" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I63" s="16" t="n">
+        <v>2250</v>
+      </c>
+      <c r="J63" s="16" t="n">
+        <v>128</v>
+      </c>
+      <c r="K63" s="16" t="n">
+        <v>1404</v>
+      </c>
+      <c r="L63" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="M63" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="N63" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O63" s="16" t="n">
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -6348,7 +6473,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9027,6 +9152,53 @@
       </c>
       <c r="O62" s="16" t="n">
         <v>327</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B63" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>917</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>881</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>644</v>
+      </c>
+      <c r="H63" s="16" t="n">
+        <v>437</v>
+      </c>
+      <c r="I63" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J63" s="19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K63" s="16" t="n">
+        <v>673</v>
+      </c>
+      <c r="L63" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="M63" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="N63" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O63" s="16" t="n">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -9045,7 +9217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11054,6 +11226,44 @@
         <v>270</v>
       </c>
       <c r="L59" s="16" t="n">
+        <v>241675</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B60" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C60" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F60" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G60" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H60" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I60" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>313.2</v>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="L60" s="16" t="n">
         <v>241675</v>
       </c>
     </row>
@@ -11122,20 +11332,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>86</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>92</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11143,20 +11353,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>207</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>216</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11164,20 +11374,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1507</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1852</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11185,20 +11395,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>149</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11206,20 +11416,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>15</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11227,20 +11437,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>70</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11248,20 +11458,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H100,'Social — theo ngày'!$A$6:$A$100,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$100,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>750</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>821</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11303,7 +11513,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B62</f>
+        <f aca="false">'Social — 28 ngày'!B63</f>
         <v>116</v>
       </c>
     </row>
@@ -11324,8 +11534,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C62</f>
-        <v>197</v>
+        <f aca="false">'Social — 28 ngày'!C63</f>
+        <v>190</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11345,8 +11555,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D62</f>
-        <v>4362</v>
+        <f aca="false">'Social — 28 ngày'!D63</f>
+        <v>4238</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11366,8 +11576,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E62</f>
-        <v>442</v>
+        <f aca="false">'Social — 28 ngày'!E63</f>
+        <v>431</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11387,7 +11597,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F62</f>
+        <f aca="false">'Social — 28 ngày'!F63</f>
         <v>49</v>
       </c>
     </row>
@@ -11408,8 +11618,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G62</f>
-        <v>37</v>
+        <f aca="false">'Social — 28 ngày'!G63</f>
+        <v>38</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11429,8 +11639,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H62</f>
-        <v>117</v>
+        <f aca="false">'Social — 28 ngày'!H63</f>
+        <v>119</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11450,8 +11660,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I62</f>
-        <v>2466</v>
+        <f aca="false">'Social — 28 ngày'!I63</f>
+        <v>2250</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11471,8 +11681,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J62</f>
-        <v>124</v>
+        <f aca="false">'Social — 28 ngày'!J63</f>
+        <v>128</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11492,8 +11702,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K62</f>
-        <v>1243</v>
+        <f aca="false">'Social — 28 ngày'!K63</f>
+        <v>1404</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11513,8 +11723,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L62</f>
-        <v>30</v>
+        <f aca="false">'Social — 28 ngày'!L63</f>
+        <v>59</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11534,8 +11744,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M62</f>
-        <v>30</v>
+        <f aca="false">'Social — 28 ngày'!M63</f>
+        <v>44</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11555,7 +11765,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N62</f>
+        <f aca="false">'Social — 28 ngày'!N63</f>
         <v>7</v>
       </c>
     </row>
@@ -11576,8 +11786,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O62</f>
-        <v>841</v>
+        <f aca="false">'Social — 28 ngày'!O63</f>
+        <v>846</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11626,8 +11836,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B62</f>
-        <v>12</v>
+        <f aca="false">SEO!B63</f>
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11651,7 +11861,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C62</f>
+        <f aca="false">SEO!C63</f>
         <v>917</v>
       </c>
     </row>
@@ -11676,7 +11886,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D62</f>
+        <f aca="false">SEO!D63</f>
         <v>881</v>
       </c>
     </row>
@@ -11701,8 +11911,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E62</f>
-        <v>34.02</v>
+        <f aca="false">SEO!E63</f>
+        <v>34.78</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11726,7 +11936,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F62</f>
+        <f aca="false">SEO!F63</f>
         <v>7</v>
       </c>
     </row>
@@ -11751,8 +11961,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G62</f>
-        <v>635</v>
+        <f aca="false">SEO!G63</f>
+        <v>644</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11776,8 +11986,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H62</f>
-        <v>440</v>
+        <f aca="false">SEO!H63</f>
+        <v>437</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11801,8 +12011,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I62</f>
-        <v>19</v>
+        <f aca="false">SEO!I63</f>
+        <v>22</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11826,8 +12036,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J62</f>
-        <v>2.8</v>
+        <f aca="false">SEO!J63</f>
+        <v>3.3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11851,7 +12061,7 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K62</f>
+        <f aca="false">SEO!K63</f>
         <v>673</v>
       </c>
     </row>
@@ -11876,8 +12086,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L62</f>
-        <v>14.6</v>
+        <f aca="false">SEO!L63</f>
+        <v>12</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11901,8 +12111,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M62</f>
-        <v>78</v>
+        <f aca="false">SEO!M63</f>
+        <v>69</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11926,7 +12136,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N62</f>
+        <f aca="false">SEO!N63</f>
         <v>119</v>
       </c>
     </row>
@@ -11951,8 +12161,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O62</f>
-        <v>327</v>
+        <f aca="false">SEO!O63</f>
+        <v>313</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11994,7 +12204,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B59</f>
+        <f aca="false">Audit!B60</f>
         <v>93</v>
       </c>
     </row>
@@ -12015,8 +12225,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C59</f>
-        <v>98</v>
+        <f aca="false">Audit!C60</f>
+        <v>99</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12036,7 +12246,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D59</f>
+        <f aca="false">Audit!D60</f>
         <v>97</v>
       </c>
     </row>
@@ -12057,7 +12267,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E59</f>
+        <f aca="false">Audit!E60</f>
         <v>94</v>
       </c>
     </row>
@@ -12078,7 +12288,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F59</f>
+        <f aca="false">Audit!F60</f>
         <v>118</v>
       </c>
     </row>
@@ -12099,7 +12309,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G59</f>
+        <f aca="false">Audit!G60</f>
         <v>98</v>
       </c>
     </row>
@@ -12120,7 +12330,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H59</f>
+        <f aca="false">Audit!H60</f>
         <v>119</v>
       </c>
     </row>
@@ -12141,7 +12351,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I59</f>
+        <f aca="false">Audit!I60</f>
         <v>98</v>
       </c>
     </row>
@@ -12162,8 +12372,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J59</f>
-        <v>327</v>
+        <f aca="false">Audit!J60</f>
+        <v>313.2</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12183,8 +12393,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K59</f>
-        <v>270</v>
+        <f aca="false">Audit!K60</f>
+        <v>269.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12204,7 +12414,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L59</f>
+        <f aca="false">Audit!L60</f>
         <v>241675</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-11 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-12 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">98 dòng × 7 chỉ số · 2026-07-05 → 2026-10-10</t>
+    <t xml:space="preserve">99 dòng × 7 chỉ số · 2026-07-05 → 2026-10-11</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">58 dòng × 14 chỉ số · 2026-07-23 → 2026-10-12</t>
+    <t xml:space="preserve">59 dòng × 14 chỉ số · 2026-07-23 → 2026-10-13</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">58 dòng × 14 chỉ số · 2026-06-30 → 2026-10-12</t>
+    <t xml:space="preserve">59 dòng × 14 chỉ số · 2026-06-30 → 2026-10-13</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">55 dòng × 11 chỉ số · 2026-07-27 → 2026-10-12</t>
+    <t xml:space="preserve">56 dòng × 11 chỉ số · 2026-07-27 → 2026-10-13</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 98 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 99 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 58 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 59 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 58 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 59 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 55 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 56 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3601,6 +3601,32 @@
       </c>
       <c r="H103" s="16" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" s="16" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3619,7 +3645,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6455,6 +6481,53 @@
       </c>
       <c r="O63" s="16" t="n">
         <v>846</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>190</v>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>4156</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>418</v>
+      </c>
+      <c r="F64" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G64" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="H64" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I64" s="16" t="n">
+        <v>2218</v>
+      </c>
+      <c r="J64" s="16" t="n">
+        <v>131</v>
+      </c>
+      <c r="K64" s="16" t="n">
+        <v>1103</v>
+      </c>
+      <c r="L64" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="M64" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="N64" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -6473,7 +6546,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9199,6 +9272,53 @@
       </c>
       <c r="O63" s="16" t="n">
         <v>313</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B64" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>917</v>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>881</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="F64" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" s="16" t="n">
+        <v>660</v>
+      </c>
+      <c r="H64" s="16" t="n">
+        <v>443</v>
+      </c>
+      <c r="I64" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K64" s="16" t="n">
+        <v>673</v>
+      </c>
+      <c r="L64" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="M64" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="N64" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -9217,7 +9337,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11265,6 +11385,44 @@
       </c>
       <c r="L60" s="16" t="n">
         <v>241675</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B61" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G61" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H61" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I61" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J61" s="19" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="K61" s="16" t="n">
+        <v>261</v>
+      </c>
+      <c r="L61" s="16" t="n">
+        <v>242620</v>
       </c>
     </row>
   </sheetData>
@@ -11332,19 +11490,19 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>92</v>
       </c>
     </row>
@@ -11353,20 +11511,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>216</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>217</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11374,20 +11532,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1852</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1886</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11395,20 +11553,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>159</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>162</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11416,19 +11574,19 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>19</v>
       </c>
     </row>
@@ -11437,20 +11595,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>77</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>79</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11458,20 +11616,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H103,'Social — theo ngày'!$A$6:$A$103,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$103,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>821</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>830</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11513,7 +11671,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B63</f>
+        <f aca="false">'Social — 28 ngày'!B64</f>
         <v>116</v>
       </c>
     </row>
@@ -11534,7 +11692,7 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C63</f>
+        <f aca="false">'Social — 28 ngày'!C64</f>
         <v>190</v>
       </c>
     </row>
@@ -11555,8 +11713,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D63</f>
-        <v>4238</v>
+        <f aca="false">'Social — 28 ngày'!D64</f>
+        <v>4156</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11576,8 +11734,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E63</f>
-        <v>431</v>
+        <f aca="false">'Social — 28 ngày'!E64</f>
+        <v>418</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11597,7 +11755,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F63</f>
+        <f aca="false">'Social — 28 ngày'!F64</f>
         <v>49</v>
       </c>
     </row>
@@ -11618,7 +11776,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G63</f>
+        <f aca="false">'Social — 28 ngày'!G64</f>
         <v>38</v>
       </c>
     </row>
@@ -11639,7 +11797,7 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H63</f>
+        <f aca="false">'Social — 28 ngày'!H64</f>
         <v>119</v>
       </c>
     </row>
@@ -11660,8 +11818,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I63</f>
-        <v>2250</v>
+        <f aca="false">'Social — 28 ngày'!I64</f>
+        <v>2218</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11681,8 +11839,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J63</f>
-        <v>128</v>
+        <f aca="false">'Social — 28 ngày'!J64</f>
+        <v>131</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11702,8 +11860,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K63</f>
-        <v>1404</v>
+        <f aca="false">'Social — 28 ngày'!K64</f>
+        <v>1103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11723,8 +11881,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L63</f>
-        <v>59</v>
+        <f aca="false">'Social — 28 ngày'!L64</f>
+        <v>58</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11744,8 +11902,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M63</f>
-        <v>44</v>
+        <f aca="false">'Social — 28 ngày'!M64</f>
+        <v>41</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11765,7 +11923,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N63</f>
+        <f aca="false">'Social — 28 ngày'!N64</f>
         <v>7</v>
       </c>
     </row>
@@ -11786,8 +11944,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O63</f>
-        <v>846</v>
+        <f aca="false">'Social — 28 ngày'!O64</f>
+        <v>842</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11836,8 +11994,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B63</f>
-        <v>13</v>
+        <f aca="false">SEO!B64</f>
+        <v>14</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11861,7 +12019,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C63</f>
+        <f aca="false">SEO!C64</f>
         <v>917</v>
       </c>
     </row>
@@ -11886,7 +12044,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D63</f>
+        <f aca="false">SEO!D64</f>
         <v>881</v>
       </c>
     </row>
@@ -11911,8 +12069,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E63</f>
-        <v>34.78</v>
+        <f aca="false">SEO!E64</f>
+        <v>35.91</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11936,7 +12094,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F63</f>
+        <f aca="false">SEO!F64</f>
         <v>7</v>
       </c>
     </row>
@@ -11961,8 +12119,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G63</f>
-        <v>644</v>
+        <f aca="false">SEO!G64</f>
+        <v>660</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11986,8 +12144,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H63</f>
-        <v>437</v>
+        <f aca="false">SEO!H64</f>
+        <v>443</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12011,8 +12169,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I63</f>
-        <v>22</v>
+        <f aca="false">SEO!I64</f>
+        <v>24</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12036,8 +12194,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J63</f>
-        <v>3.3</v>
+        <f aca="false">SEO!J64</f>
+        <v>3.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12061,7 +12219,7 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K63</f>
+        <f aca="false">SEO!K64</f>
         <v>673</v>
       </c>
     </row>
@@ -12086,7 +12244,7 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L63</f>
+        <f aca="false">SEO!L64</f>
         <v>12</v>
       </c>
     </row>
@@ -12111,8 +12269,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M63</f>
-        <v>69</v>
+        <f aca="false">SEO!M64</f>
+        <v>68</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12136,7 +12294,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N63</f>
+        <f aca="false">SEO!N64</f>
         <v>119</v>
       </c>
     </row>
@@ -12161,8 +12319,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O63</f>
-        <v>313</v>
+        <f aca="false">SEO!O64</f>
+        <v>316</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12204,7 +12362,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B60</f>
+        <f aca="false">Audit!B61</f>
         <v>93</v>
       </c>
     </row>
@@ -12225,8 +12383,8 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C60</f>
-        <v>99</v>
+        <f aca="false">Audit!C61</f>
+        <v>98</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12246,7 +12404,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D60</f>
+        <f aca="false">Audit!D61</f>
         <v>97</v>
       </c>
     </row>
@@ -12267,7 +12425,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E60</f>
+        <f aca="false">Audit!E61</f>
         <v>94</v>
       </c>
     </row>
@@ -12288,7 +12446,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F60</f>
+        <f aca="false">Audit!F61</f>
         <v>118</v>
       </c>
     </row>
@@ -12309,7 +12467,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G60</f>
+        <f aca="false">Audit!G61</f>
         <v>98</v>
       </c>
     </row>
@@ -12330,7 +12488,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H60</f>
+        <f aca="false">Audit!H61</f>
         <v>119</v>
       </c>
     </row>
@@ -12351,7 +12509,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I60</f>
+        <f aca="false">Audit!I61</f>
         <v>98</v>
       </c>
     </row>
@@ -12372,8 +12530,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J60</f>
-        <v>313.2</v>
+        <f aca="false">Audit!J61</f>
+        <v>315.9</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12393,8 +12551,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K60</f>
-        <v>269.5</v>
+        <f aca="false">Audit!K61</f>
+        <v>261</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12414,8 +12572,8 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L60</f>
-        <v>241675</v>
+        <f aca="false">Audit!L61</f>
+        <v>242620</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-12 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-13 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">99 dòng × 7 chỉ số · 2026-07-05 → 2026-10-11</t>
+    <t xml:space="preserve">100 dòng × 7 chỉ số · 2026-07-05 → 2026-10-12</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">59 dòng × 14 chỉ số · 2026-07-23 → 2026-10-13</t>
+    <t xml:space="preserve">60 dòng × 14 chỉ số · 2026-07-23 → 2026-10-14</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">59 dòng × 14 chỉ số · 2026-06-30 → 2026-10-13</t>
+    <t xml:space="preserve">60 dòng × 14 chỉ số · 2026-06-30 → 2026-10-14</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">56 dòng × 11 chỉ số · 2026-07-27 → 2026-10-13</t>
+    <t xml:space="preserve">57 dòng × 11 chỉ số · 2026-07-27 → 2026-10-14</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 99 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 100 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 59 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 60 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 59 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 60 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 56 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 57 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3627,6 +3627,32 @@
       </c>
       <c r="H104" s="16" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B105" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D105" s="16" t="n">
+        <v>201</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F105" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H105" s="16" t="n">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -3645,7 +3671,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6527,6 +6553,53 @@
         <v>7</v>
       </c>
       <c r="O64" s="16" t="n">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>184</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>4139</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>493</v>
+      </c>
+      <c r="F65" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>2169</v>
+      </c>
+      <c r="J65" s="16" t="n">
+        <v>132</v>
+      </c>
+      <c r="K65" s="16" t="n">
+        <v>1090</v>
+      </c>
+      <c r="L65" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="M65" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="N65" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O65" s="16" t="n">
         <v>842</v>
       </c>
     </row>
@@ -6546,7 +6619,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9319,6 +9392,53 @@
       </c>
       <c r="O64" s="16" t="n">
         <v>316</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>915</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>879</v>
+      </c>
+      <c r="E65" s="19" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="F65" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>672</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>448</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K65" s="16" t="n">
+        <v>672</v>
+      </c>
+      <c r="L65" s="19" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M65" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="N65" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -9337,7 +9457,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11423,6 +11543,44 @@
       </c>
       <c r="L61" s="16" t="n">
         <v>242620</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B62" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C62" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F62" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G62" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H62" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I62" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J62" s="19" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="K62" s="19" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="L62" s="16" t="n">
+        <v>241898</v>
       </c>
     </row>
   </sheetData>
@@ -11490,20 +11648,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>92</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11511,20 +11669,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>217</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11532,20 +11690,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1886</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>2087</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11553,20 +11711,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>162</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>244</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11574,20 +11732,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>19</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11595,20 +11753,20 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>79</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>85</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11616,20 +11774,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H104,'Social — theo ngày'!$A$6:$A$104,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$104,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>830</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>959</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11671,7 +11829,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B64</f>
+        <f aca="false">'Social — 28 ngày'!B65</f>
         <v>116</v>
       </c>
     </row>
@@ -11692,8 +11850,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C64</f>
-        <v>190</v>
+        <f aca="false">'Social — 28 ngày'!C65</f>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11713,8 +11871,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D64</f>
-        <v>4156</v>
+        <f aca="false">'Social — 28 ngày'!D65</f>
+        <v>4139</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11734,8 +11892,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E64</f>
-        <v>418</v>
+        <f aca="false">'Social — 28 ngày'!E65</f>
+        <v>493</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11755,7 +11913,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F64</f>
+        <f aca="false">'Social — 28 ngày'!F65</f>
         <v>49</v>
       </c>
     </row>
@@ -11776,8 +11934,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G64</f>
-        <v>38</v>
+        <f aca="false">'Social — 28 ngày'!G65</f>
+        <v>39</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11797,8 +11955,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H64</f>
-        <v>119</v>
+        <f aca="false">'Social — 28 ngày'!H65</f>
+        <v>120</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11818,8 +11976,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I64</f>
-        <v>2218</v>
+        <f aca="false">'Social — 28 ngày'!I65</f>
+        <v>2169</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11839,8 +11997,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J64</f>
-        <v>131</v>
+        <f aca="false">'Social — 28 ngày'!J65</f>
+        <v>132</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11860,8 +12018,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K64</f>
-        <v>1103</v>
+        <f aca="false">'Social — 28 ngày'!K65</f>
+        <v>1090</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11881,8 +12039,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L64</f>
-        <v>58</v>
+        <f aca="false">'Social — 28 ngày'!L65</f>
+        <v>59</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11902,7 +12060,7 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M64</f>
+        <f aca="false">'Social — 28 ngày'!M65</f>
         <v>41</v>
       </c>
     </row>
@@ -11923,7 +12081,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N64</f>
+        <f aca="false">'Social — 28 ngày'!N65</f>
         <v>7</v>
       </c>
     </row>
@@ -11944,7 +12102,7 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O64</f>
+        <f aca="false">'Social — 28 ngày'!O65</f>
         <v>842</v>
       </c>
     </row>
@@ -11994,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B64</f>
+        <f aca="false">SEO!B65</f>
         <v>14</v>
       </c>
     </row>
@@ -12019,8 +12177,8 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C64</f>
-        <v>917</v>
+        <f aca="false">SEO!C65</f>
+        <v>915</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12044,8 +12202,8 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D64</f>
-        <v>881</v>
+        <f aca="false">SEO!D65</f>
+        <v>879</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12069,8 +12227,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E64</f>
-        <v>35.91</v>
+        <f aca="false">SEO!E65</f>
+        <v>36.76</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12094,7 +12252,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F64</f>
+        <f aca="false">SEO!F65</f>
         <v>7</v>
       </c>
     </row>
@@ -12119,8 +12277,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G64</f>
-        <v>660</v>
+        <f aca="false">SEO!G65</f>
+        <v>672</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12144,8 +12302,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H64</f>
-        <v>443</v>
+        <f aca="false">SEO!H65</f>
+        <v>448</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12169,8 +12327,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I64</f>
-        <v>24</v>
+        <f aca="false">SEO!I65</f>
+        <v>23</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12194,8 +12352,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J64</f>
-        <v>3.6</v>
+        <f aca="false">SEO!J65</f>
+        <v>3.4</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12219,8 +12377,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K64</f>
-        <v>673</v>
+        <f aca="false">SEO!K65</f>
+        <v>672</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12244,8 +12402,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L64</f>
-        <v>12</v>
+        <f aca="false">SEO!L65</f>
+        <v>12.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12269,8 +12427,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M64</f>
-        <v>68</v>
+        <f aca="false">SEO!M65</f>
+        <v>67</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12294,7 +12452,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N64</f>
+        <f aca="false">SEO!N65</f>
         <v>119</v>
       </c>
     </row>
@@ -12319,8 +12477,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O64</f>
-        <v>316</v>
+        <f aca="false">SEO!O65</f>
+        <v>317</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12362,7 +12520,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B61</f>
+        <f aca="false">Audit!B62</f>
         <v>93</v>
       </c>
     </row>
@@ -12383,7 +12541,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C61</f>
+        <f aca="false">Audit!C62</f>
         <v>98</v>
       </c>
     </row>
@@ -12404,7 +12562,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D61</f>
+        <f aca="false">Audit!D62</f>
         <v>97</v>
       </c>
     </row>
@@ -12425,8 +12583,8 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E61</f>
-        <v>94</v>
+        <f aca="false">Audit!E62</f>
+        <v>93</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12446,7 +12604,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F61</f>
+        <f aca="false">Audit!F62</f>
         <v>118</v>
       </c>
     </row>
@@ -12467,7 +12625,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G61</f>
+        <f aca="false">Audit!G62</f>
         <v>98</v>
       </c>
     </row>
@@ -12488,7 +12646,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H61</f>
+        <f aca="false">Audit!H62</f>
         <v>119</v>
       </c>
     </row>
@@ -12509,7 +12667,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I61</f>
+        <f aca="false">Audit!I62</f>
         <v>98</v>
       </c>
     </row>
@@ -12530,8 +12688,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J61</f>
-        <v>315.9</v>
+        <f aca="false">Audit!J62</f>
+        <v>317.4</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12551,8 +12709,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K61</f>
-        <v>261</v>
+        <f aca="false">Audit!K62</f>
+        <v>267.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12572,8 +12730,8 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L61</f>
-        <v>242620</v>
+        <f aca="false">Audit!L62</f>
+        <v>241898</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-13 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-14 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">100 dòng × 7 chỉ số · 2026-07-05 → 2026-10-12</t>
+    <t xml:space="preserve">101 dòng × 7 chỉ số · 2026-07-05 → 2026-10-13</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">60 dòng × 14 chỉ số · 2026-07-23 → 2026-10-14</t>
+    <t xml:space="preserve">61 dòng × 14 chỉ số · 2026-07-23 → 2026-10-15</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">60 dòng × 14 chỉ số · 2026-06-30 → 2026-10-14</t>
+    <t xml:space="preserve">61 dòng × 14 chỉ số · 2026-06-30 → 2026-10-15</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">57 dòng × 11 chỉ số · 2026-07-27 → 2026-10-14</t>
+    <t xml:space="preserve">58 dòng × 11 chỉ số · 2026-07-27 → 2026-10-15</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 100 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 101 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 60 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 61 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 60 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 61 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 57 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 58 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3653,6 +3653,32 @@
       </c>
       <c r="H105" s="16" t="n">
         <v>129</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B106" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C106" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="F106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="16" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3671,7 +3697,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6601,6 +6627,53 @@
       </c>
       <c r="O65" s="16" t="n">
         <v>842</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B66" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>181</v>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>3995</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>432</v>
+      </c>
+      <c r="F66" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G66" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>85</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>1868</v>
+      </c>
+      <c r="J66" s="16" t="n">
+        <v>133</v>
+      </c>
+      <c r="K66" s="16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="L66" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="M66" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="N66" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -6619,7 +6692,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9439,6 +9512,53 @@
       </c>
       <c r="O65" s="16" t="n">
         <v>317</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B66" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>913</v>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>877</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="F66" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G66" s="16" t="n">
+        <v>683</v>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>454</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K66" s="16" t="n">
+        <v>730</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M66" s="16" t="n">
+        <v>76</v>
+      </c>
+      <c r="N66" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -9457,7 +9577,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11581,6 +11701,44 @@
       </c>
       <c r="L62" s="16" t="n">
         <v>241898</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B63" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>96</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G63" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="H63" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I63" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J63" s="19" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="K63" s="16" t="n">
+        <v>269</v>
+      </c>
+      <c r="L63" s="16" t="n">
+        <v>242263</v>
       </c>
     </row>
   </sheetData>
@@ -11648,20 +11806,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>94</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11669,20 +11827,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>243</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11690,20 +11848,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>2087</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>2158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11711,20 +11869,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>244</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>260</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11732,19 +11890,19 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>20</v>
       </c>
     </row>
@@ -11753,19 +11911,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -11774,20 +11932,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H105,'Social — theo ngày'!$A$6:$A$105,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$105,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>959</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>968</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11829,7 +11987,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B65</f>
+        <f aca="false">'Social — 28 ngày'!B66</f>
         <v>116</v>
       </c>
     </row>
@@ -11850,8 +12008,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C65</f>
-        <v>184</v>
+        <f aca="false">'Social — 28 ngày'!C66</f>
+        <v>181</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11871,8 +12029,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D65</f>
-        <v>4139</v>
+        <f aca="false">'Social — 28 ngày'!D66</f>
+        <v>3995</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11892,8 +12050,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E65</f>
-        <v>493</v>
+        <f aca="false">'Social — 28 ngày'!E66</f>
+        <v>432</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11913,7 +12071,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F65</f>
+        <f aca="false">'Social — 28 ngày'!F66</f>
         <v>49</v>
       </c>
     </row>
@@ -11934,8 +12092,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G65</f>
-        <v>39</v>
+        <f aca="false">'Social — 28 ngày'!G66</f>
+        <v>36</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11955,8 +12113,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H65</f>
-        <v>120</v>
+        <f aca="false">'Social — 28 ngày'!H66</f>
+        <v>85</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11976,8 +12134,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I65</f>
-        <v>2169</v>
+        <f aca="false">'Social — 28 ngày'!I66</f>
+        <v>1868</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11997,8 +12155,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J65</f>
-        <v>132</v>
+        <f aca="false">'Social — 28 ngày'!J66</f>
+        <v>133</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12018,8 +12176,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K65</f>
-        <v>1090</v>
+        <f aca="false">'Social — 28 ngày'!K66</f>
+        <v>1108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12039,8 +12197,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L65</f>
-        <v>59</v>
+        <f aca="false">'Social — 28 ngày'!L66</f>
+        <v>60</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12060,8 +12218,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M65</f>
-        <v>41</v>
+        <f aca="false">'Social — 28 ngày'!M66</f>
+        <v>37</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12081,7 +12239,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N65</f>
+        <f aca="false">'Social — 28 ngày'!N66</f>
         <v>7</v>
       </c>
     </row>
@@ -12102,8 +12260,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O65</f>
-        <v>842</v>
+        <f aca="false">'Social — 28 ngày'!O66</f>
+        <v>721</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12152,7 +12310,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B65</f>
+        <f aca="false">SEO!B66</f>
         <v>14</v>
       </c>
     </row>
@@ -12177,8 +12335,8 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C65</f>
-        <v>915</v>
+        <f aca="false">SEO!C66</f>
+        <v>913</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12202,8 +12360,8 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D65</f>
-        <v>879</v>
+        <f aca="false">SEO!D66</f>
+        <v>877</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12227,8 +12385,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E65</f>
-        <v>36.76</v>
+        <f aca="false">SEO!E66</f>
+        <v>37.77</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12252,8 +12410,8 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F65</f>
-        <v>7</v>
+        <f aca="false">SEO!F66</f>
+        <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12277,8 +12435,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G65</f>
-        <v>672</v>
+        <f aca="false">SEO!G66</f>
+        <v>683</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12302,8 +12460,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H65</f>
-        <v>448</v>
+        <f aca="false">SEO!H66</f>
+        <v>454</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12327,8 +12485,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I65</f>
-        <v>23</v>
+        <f aca="false">SEO!I66</f>
+        <v>25</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12352,7 +12510,7 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J65</f>
+        <f aca="false">SEO!J66</f>
         <v>3.4</v>
       </c>
     </row>
@@ -12377,8 +12535,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K65</f>
-        <v>672</v>
+        <f aca="false">SEO!K66</f>
+        <v>730</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12402,8 +12560,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L65</f>
-        <v>12.1</v>
+        <f aca="false">SEO!L66</f>
+        <v>12.3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12427,8 +12585,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M65</f>
-        <v>67</v>
+        <f aca="false">SEO!M66</f>
+        <v>76</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12452,7 +12610,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N65</f>
+        <f aca="false">SEO!N66</f>
         <v>119</v>
       </c>
     </row>
@@ -12477,8 +12635,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O65</f>
-        <v>317</v>
+        <f aca="false">SEO!O66</f>
+        <v>325</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12520,7 +12678,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B62</f>
+        <f aca="false">Audit!B63</f>
         <v>93</v>
       </c>
     </row>
@@ -12541,7 +12699,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C62</f>
+        <f aca="false">Audit!C63</f>
         <v>98</v>
       </c>
     </row>
@@ -12562,8 +12720,8 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D62</f>
-        <v>97</v>
+        <f aca="false">Audit!D63</f>
+        <v>96</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12583,7 +12741,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E62</f>
+        <f aca="false">Audit!E63</f>
         <v>93</v>
       </c>
     </row>
@@ -12604,7 +12762,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F62</f>
+        <f aca="false">Audit!F63</f>
         <v>118</v>
       </c>
     </row>
@@ -12625,8 +12783,8 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G62</f>
-        <v>98</v>
+        <f aca="false">Audit!G63</f>
+        <v>97</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12646,7 +12804,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H62</f>
+        <f aca="false">Audit!H63</f>
         <v>119</v>
       </c>
     </row>
@@ -12667,7 +12825,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I62</f>
+        <f aca="false">Audit!I63</f>
         <v>98</v>
       </c>
     </row>
@@ -12688,8 +12846,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J62</f>
-        <v>317.4</v>
+        <f aca="false">Audit!J63</f>
+        <v>324.9</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12709,8 +12867,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K62</f>
-        <v>267.5</v>
+        <f aca="false">Audit!K63</f>
+        <v>269</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12730,8 +12888,8 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L62</f>
-        <v>241898</v>
+        <f aca="false">Audit!L63</f>
+        <v>242263</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-14 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-15 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">101 dòng × 7 chỉ số · 2026-07-05 → 2026-10-13</t>
+    <t xml:space="preserve">102 dòng × 7 chỉ số · 2026-07-05 → 2026-10-14</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">61 dòng × 14 chỉ số · 2026-07-23 → 2026-10-15</t>
+    <t xml:space="preserve">62 dòng × 14 chỉ số · 2026-07-23 → 2026-10-16</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">61 dòng × 14 chỉ số · 2026-06-30 → 2026-10-15</t>
+    <t xml:space="preserve">62 dòng × 14 chỉ số · 2026-06-30 → 2026-10-16</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">58 dòng × 11 chỉ số · 2026-07-27 → 2026-10-15</t>
+    <t xml:space="preserve">59 dòng × 11 chỉ số · 2026-07-27 → 2026-10-16</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 101 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 102 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 61 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 62 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 61 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 62 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 58 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 59 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3679,6 +3679,30 @@
       </c>
       <c r="H106" s="16" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B107" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="16" t="n">
+        <v>176</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>56</v>
+      </c>
+      <c r="F107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="16"/>
+      <c r="H107" s="16" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3697,7 +3721,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6674,6 +6698,45 @@
       </c>
       <c r="O66" s="16" t="n">
         <v>721</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B67" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>176</v>
+      </c>
+      <c r="D67" s="16" t="n">
+        <v>4074</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>475</v>
+      </c>
+      <c r="F67" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="I67" s="16" t="n">
+        <v>1823</v>
+      </c>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O67" s="16" t="n">
+        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -6692,7 +6755,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9559,6 +9622,53 @@
       </c>
       <c r="O66" s="16" t="n">
         <v>325</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B67" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>912</v>
+      </c>
+      <c r="D67" s="16" t="n">
+        <v>876</v>
+      </c>
+      <c r="E67" s="19" t="n">
+        <v>37.82</v>
+      </c>
+      <c r="F67" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>706</v>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>461</v>
+      </c>
+      <c r="I67" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K67" s="16" t="n">
+        <v>707</v>
+      </c>
+      <c r="L67" s="19" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M67" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="N67" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O67" s="16" t="n">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -9577,7 +9687,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11738,6 +11848,44 @@
         <v>269</v>
       </c>
       <c r="L63" s="16" t="n">
+        <v>242263</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B64" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>96</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F64" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G64" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="H64" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I64" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="K64" s="16" t="n">
+        <v>266</v>
+      </c>
+      <c r="L64" s="16" t="n">
         <v>242263</v>
       </c>
     </row>
@@ -11806,20 +11954,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>97</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11827,19 +11975,19 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>244</v>
       </c>
     </row>
@@ -11848,20 +11996,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>2158</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>2334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11869,20 +12017,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>260</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>316</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11890,19 +12038,19 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>20</v>
       </c>
     </row>
@@ -11911,19 +12059,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -11932,20 +12080,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H106,'Social — theo ngày'!$A$6:$A$106,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$106,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>968</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1025</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11987,7 +12135,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B66</f>
+        <f aca="false">'Social — 28 ngày'!B67</f>
         <v>116</v>
       </c>
     </row>
@@ -12008,8 +12156,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C66</f>
-        <v>181</v>
+        <f aca="false">'Social — 28 ngày'!C67</f>
+        <v>176</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12029,8 +12177,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D66</f>
-        <v>3995</v>
+        <f aca="false">'Social — 28 ngày'!D67</f>
+        <v>4074</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12050,8 +12198,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E66</f>
-        <v>432</v>
+        <f aca="false">'Social — 28 ngày'!E67</f>
+        <v>475</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12071,7 +12219,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F66</f>
+        <f aca="false">'Social — 28 ngày'!F67</f>
         <v>49</v>
       </c>
     </row>
@@ -12092,7 +12240,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G66</f>
+        <f aca="false">'Social — 28 ngày'!G67</f>
         <v>36</v>
       </c>
     </row>
@@ -12113,8 +12261,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H66</f>
-        <v>85</v>
+        <f aca="false">'Social — 28 ngày'!H67</f>
+        <v>82</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12134,8 +12282,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I66</f>
-        <v>1868</v>
+        <f aca="false">'Social — 28 ngày'!I67</f>
+        <v>1823</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12155,8 +12303,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J66</f>
-        <v>133</v>
+        <f aca="false">'Social — 28 ngày'!J67</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12176,8 +12324,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K66</f>
-        <v>1108</v>
+        <f aca="false">'Social — 28 ngày'!K67</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12197,8 +12345,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L66</f>
-        <v>60</v>
+        <f aca="false">'Social — 28 ngày'!L67</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12218,8 +12366,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M66</f>
-        <v>37</v>
+        <f aca="false">'Social — 28 ngày'!M67</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12239,7 +12387,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N66</f>
+        <f aca="false">'Social — 28 ngày'!N67</f>
         <v>7</v>
       </c>
     </row>
@@ -12260,8 +12408,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O66</f>
-        <v>721</v>
+        <f aca="false">'Social — 28 ngày'!O67</f>
+        <v>718</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12310,8 +12458,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B66</f>
-        <v>14</v>
+        <f aca="false">SEO!B67</f>
+        <v>15</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12335,8 +12483,8 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C66</f>
-        <v>913</v>
+        <f aca="false">SEO!C67</f>
+        <v>912</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12360,8 +12508,8 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D66</f>
-        <v>877</v>
+        <f aca="false">SEO!D67</f>
+        <v>876</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12385,8 +12533,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E66</f>
-        <v>37.77</v>
+        <f aca="false">SEO!E67</f>
+        <v>37.82</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12410,7 +12558,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F66</f>
+        <f aca="false">SEO!F67</f>
         <v>9</v>
       </c>
     </row>
@@ -12435,8 +12583,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G66</f>
-        <v>683</v>
+        <f aca="false">SEO!G67</f>
+        <v>706</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12460,8 +12608,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H66</f>
-        <v>454</v>
+        <f aca="false">SEO!H67</f>
+        <v>461</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12485,7 +12633,7 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I66</f>
+        <f aca="false">SEO!I67</f>
         <v>25</v>
       </c>
     </row>
@@ -12510,8 +12658,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J66</f>
-        <v>3.4</v>
+        <f aca="false">SEO!J67</f>
+        <v>3.5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12535,8 +12683,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K66</f>
-        <v>730</v>
+        <f aca="false">SEO!K67</f>
+        <v>707</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12560,8 +12708,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L66</f>
-        <v>12.3</v>
+        <f aca="false">SEO!L67</f>
+        <v>12.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12585,8 +12733,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M66</f>
-        <v>76</v>
+        <f aca="false">SEO!M67</f>
+        <v>75</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12610,7 +12758,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N66</f>
+        <f aca="false">SEO!N67</f>
         <v>119</v>
       </c>
     </row>
@@ -12635,8 +12783,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O66</f>
-        <v>325</v>
+        <f aca="false">SEO!O67</f>
+        <v>335</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12678,7 +12826,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B63</f>
+        <f aca="false">Audit!B64</f>
         <v>93</v>
       </c>
     </row>
@@ -12699,7 +12847,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C63</f>
+        <f aca="false">Audit!C64</f>
         <v>98</v>
       </c>
     </row>
@@ -12720,7 +12868,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D63</f>
+        <f aca="false">Audit!D64</f>
         <v>96</v>
       </c>
     </row>
@@ -12741,7 +12889,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E63</f>
+        <f aca="false">Audit!E64</f>
         <v>93</v>
       </c>
     </row>
@@ -12762,7 +12910,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F63</f>
+        <f aca="false">Audit!F64</f>
         <v>118</v>
       </c>
     </row>
@@ -12783,7 +12931,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G63</f>
+        <f aca="false">Audit!G64</f>
         <v>97</v>
       </c>
     </row>
@@ -12804,7 +12952,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H63</f>
+        <f aca="false">Audit!H64</f>
         <v>119</v>
       </c>
     </row>
@@ -12825,7 +12973,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I63</f>
+        <f aca="false">Audit!I64</f>
         <v>98</v>
       </c>
     </row>
@@ -12846,8 +12994,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J63</f>
-        <v>324.9</v>
+        <f aca="false">Audit!J64</f>
+        <v>335.3</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12867,8 +13015,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K63</f>
-        <v>269</v>
+        <f aca="false">Audit!K64</f>
+        <v>266</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12888,7 +13036,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L63</f>
+        <f aca="false">Audit!L64</f>
         <v>242263</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-15 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-17 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">102 dòng × 7 chỉ số · 2026-07-05 → 2026-10-14</t>
+    <t xml:space="preserve">104 dòng × 7 chỉ số · 2026-07-05 → 2026-10-16</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">62 dòng × 14 chỉ số · 2026-07-23 → 2026-10-16</t>
+    <t xml:space="preserve">63 dòng × 14 chỉ số · 2026-07-23 → 2026-10-18</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">62 dòng × 14 chỉ số · 2026-06-30 → 2026-10-16</t>
+    <t xml:space="preserve">63 dòng × 14 chỉ số · 2026-06-30 → 2026-10-18</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">59 dòng × 11 chỉ số · 2026-07-27 → 2026-10-16</t>
+    <t xml:space="preserve">60 dòng × 11 chỉ số · 2026-07-27 → 2026-10-18</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 102 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 104 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 62 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 63 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 62 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 63 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 59 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 60 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3703,6 +3703,54 @@
       <c r="G107" s="16"/>
       <c r="H107" s="16" t="n">
         <v>57</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B108" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="F108" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" s="16"/>
+      <c r="H108" s="16" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B109" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D109" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F109" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="16"/>
+      <c r="H109" s="16" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3721,7 +3769,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6737,6 +6785,53 @@
       </c>
       <c r="O67" s="16" t="n">
         <v>718</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>171</v>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>3891</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>462</v>
+      </c>
+      <c r="F68" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="H68" s="16" t="n">
+        <v>175</v>
+      </c>
+      <c r="I68" s="16" t="n">
+        <v>1665</v>
+      </c>
+      <c r="J68" s="16" t="n">
+        <v>136</v>
+      </c>
+      <c r="K68" s="16" t="n">
+        <v>1299</v>
+      </c>
+      <c r="L68" s="16" t="n">
+        <v>79</v>
+      </c>
+      <c r="M68" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="N68" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O68" s="16" t="n">
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -6755,7 +6850,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9669,6 +9764,53 @@
       </c>
       <c r="O67" s="16" t="n">
         <v>335</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>912</v>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>876</v>
+      </c>
+      <c r="E68" s="19" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="F68" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <v>679</v>
+      </c>
+      <c r="H68" s="16" t="n">
+        <v>433</v>
+      </c>
+      <c r="I68" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J68" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K68" s="16" t="n">
+        <v>816</v>
+      </c>
+      <c r="L68" s="19" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M68" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="N68" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O68" s="16" t="n">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -9687,7 +9829,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -11886,6 +12028,44 @@
         <v>266</v>
       </c>
       <c r="L64" s="16" t="n">
+        <v>242263</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F65" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G65" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="L65" s="16" t="n">
         <v>242263</v>
       </c>
     </row>
@@ -11954,20 +12134,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>102</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11975,20 +12155,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>244</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>282</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11996,20 +12176,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>2334</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>2543</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12017,20 +12197,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>316</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>355</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12038,20 +12218,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>20</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12059,19 +12239,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -12080,20 +12260,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H107,'Social — theo ngày'!$A$6:$A$107,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$107,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1025</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12135,7 +12315,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B67</f>
+        <f aca="false">'Social — 28 ngày'!B68</f>
         <v>116</v>
       </c>
     </row>
@@ -12156,8 +12336,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C67</f>
-        <v>176</v>
+        <f aca="false">'Social — 28 ngày'!C68</f>
+        <v>171</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12177,8 +12357,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D67</f>
-        <v>4074</v>
+        <f aca="false">'Social — 28 ngày'!D68</f>
+        <v>3891</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12198,8 +12378,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E67</f>
-        <v>475</v>
+        <f aca="false">'Social — 28 ngày'!E68</f>
+        <v>462</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12219,7 +12399,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F67</f>
+        <f aca="false">'Social — 28 ngày'!F68</f>
         <v>49</v>
       </c>
     </row>
@@ -12240,8 +12420,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G67</f>
-        <v>36</v>
+        <f aca="false">'Social — 28 ngày'!G68</f>
+        <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12261,8 +12441,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H67</f>
-        <v>82</v>
+        <f aca="false">'Social — 28 ngày'!H68</f>
+        <v>175</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12282,8 +12462,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I67</f>
-        <v>1823</v>
+        <f aca="false">'Social — 28 ngày'!I68</f>
+        <v>1665</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12303,8 +12483,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J67</f>
-        <v>0</v>
+        <f aca="false">'Social — 28 ngày'!J68</f>
+        <v>136</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12324,8 +12504,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K67</f>
-        <v>0</v>
+        <f aca="false">'Social — 28 ngày'!K68</f>
+        <v>1299</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12345,8 +12525,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L67</f>
-        <v>0</v>
+        <f aca="false">'Social — 28 ngày'!L68</f>
+        <v>79</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12366,8 +12546,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M67</f>
-        <v>0</v>
+        <f aca="false">'Social — 28 ngày'!M68</f>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12387,7 +12567,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N67</f>
+        <f aca="false">'Social — 28 ngày'!N68</f>
         <v>7</v>
       </c>
     </row>
@@ -12408,8 +12588,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O67</f>
-        <v>718</v>
+        <f aca="false">'Social — 28 ngày'!O68</f>
+        <v>586</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12458,8 +12638,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B67</f>
-        <v>15</v>
+        <f aca="false">SEO!B68</f>
+        <v>17</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12483,7 +12663,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C67</f>
+        <f aca="false">SEO!C68</f>
         <v>912</v>
       </c>
     </row>
@@ -12508,7 +12688,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D67</f>
+        <f aca="false">SEO!D68</f>
         <v>876</v>
       </c>
     </row>
@@ -12533,8 +12713,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E67</f>
-        <v>37.82</v>
+        <f aca="false">SEO!E68</f>
+        <v>39.18</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12558,7 +12738,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F67</f>
+        <f aca="false">SEO!F68</f>
         <v>9</v>
       </c>
     </row>
@@ -12583,8 +12763,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G67</f>
-        <v>706</v>
+        <f aca="false">SEO!G68</f>
+        <v>679</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12608,8 +12788,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H67</f>
-        <v>461</v>
+        <f aca="false">SEO!H68</f>
+        <v>433</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12633,8 +12813,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I67</f>
-        <v>25</v>
+        <f aca="false">SEO!I68</f>
+        <v>26</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12658,8 +12838,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J67</f>
-        <v>3.5</v>
+        <f aca="false">SEO!J68</f>
+        <v>3.2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12683,8 +12863,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K67</f>
-        <v>707</v>
+        <f aca="false">SEO!K68</f>
+        <v>816</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12708,8 +12888,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L67</f>
-        <v>12.1</v>
+        <f aca="false">SEO!L68</f>
+        <v>15.2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12733,8 +12913,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M67</f>
-        <v>75</v>
+        <f aca="false">SEO!M68</f>
+        <v>83</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12758,7 +12938,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N67</f>
+        <f aca="false">SEO!N68</f>
         <v>119</v>
       </c>
     </row>
@@ -12783,8 +12963,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O67</f>
-        <v>335</v>
+        <f aca="false">SEO!O68</f>
+        <v>325</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12826,7 +13006,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B64</f>
+        <f aca="false">Audit!B65</f>
         <v>93</v>
       </c>
     </row>
@@ -12847,7 +13027,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C64</f>
+        <f aca="false">Audit!C65</f>
         <v>98</v>
       </c>
     </row>
@@ -12868,8 +13048,8 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D64</f>
-        <v>96</v>
+        <f aca="false">Audit!D65</f>
+        <v>97</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12889,7 +13069,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E64</f>
+        <f aca="false">Audit!E65</f>
         <v>93</v>
       </c>
     </row>
@@ -12910,7 +13090,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F64</f>
+        <f aca="false">Audit!F65</f>
         <v>118</v>
       </c>
     </row>
@@ -12931,8 +13111,8 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G64</f>
-        <v>97</v>
+        <f aca="false">Audit!G65</f>
+        <v>98</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12952,7 +13132,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H64</f>
+        <f aca="false">Audit!H65</f>
         <v>119</v>
       </c>
     </row>
@@ -12973,7 +13153,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I64</f>
+        <f aca="false">Audit!I65</f>
         <v>98</v>
       </c>
     </row>
@@ -12994,8 +13174,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J64</f>
-        <v>335.3</v>
+        <f aca="false">Audit!J65</f>
+        <v>324.9</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13015,8 +13195,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K64</f>
-        <v>266</v>
+        <f aca="false">Audit!K65</f>
+        <v>266.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13036,7 +13216,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L64</f>
+        <f aca="false">Audit!L65</f>
         <v>242263</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-17 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-19 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">104 dòng × 7 chỉ số · 2026-07-05 → 2026-10-16</t>
+    <t xml:space="preserve">106 dòng × 7 chỉ số · 2026-07-05 → 2026-10-18</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">63 dòng × 14 chỉ số · 2026-07-23 → 2026-10-18</t>
+    <t xml:space="preserve">64 dòng × 14 chỉ số · 2026-07-23 → 2026-10-20</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">63 dòng × 14 chỉ số · 2026-06-30 → 2026-10-18</t>
+    <t xml:space="preserve">64 dòng × 14 chỉ số · 2026-06-30 → 2026-10-20</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">60 dòng × 11 chỉ số · 2026-07-27 → 2026-10-18</t>
+    <t xml:space="preserve">61 dòng × 11 chỉ số · 2026-07-27 → 2026-10-20</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 104 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 106 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 63 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 64 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 63 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 64 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 60 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 61 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3751,6 +3751,54 @@
       <c r="G109" s="16"/>
       <c r="H109" s="16" t="n">
         <v>24</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B110" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D110" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="E110" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F110" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="16"/>
+      <c r="H110" s="16" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="15" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B111" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D111" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="F111" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3769,7 +3817,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6832,6 +6880,53 @@
       </c>
       <c r="O68" s="16" t="n">
         <v>586</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B69" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>173</v>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>3981</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>490</v>
+      </c>
+      <c r="F69" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="H69" s="16" t="n">
+        <v>285</v>
+      </c>
+      <c r="I69" s="16" t="n">
+        <v>1775</v>
+      </c>
+      <c r="J69" s="16" t="n">
+        <v>138</v>
+      </c>
+      <c r="K69" s="16" t="n">
+        <v>1278</v>
+      </c>
+      <c r="L69" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="M69" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="N69" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O69" s="16" t="n">
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -6850,7 +6945,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9811,6 +9906,53 @@
       </c>
       <c r="O68" s="16" t="n">
         <v>325</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B69" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>912</v>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>876</v>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="F69" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>673</v>
+      </c>
+      <c r="H69" s="16" t="n">
+        <v>425</v>
+      </c>
+      <c r="I69" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K69" s="16" t="n">
+        <v>951</v>
+      </c>
+      <c r="L69" s="19" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M69" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="N69" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O69" s="16" t="n">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -9829,7 +9971,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -12066,6 +12208,44 @@
         <v>266.5</v>
       </c>
       <c r="L65" s="16" t="n">
+        <v>242263</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B66" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C66" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F66" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G66" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>301.8</v>
+      </c>
+      <c r="K66" s="16" t="n">
+        <v>247</v>
+      </c>
+      <c r="L66" s="16" t="n">
         <v>242263</v>
       </c>
     </row>
@@ -12134,20 +12314,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>108</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12155,20 +12335,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>282</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>326</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12176,20 +12356,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>2543</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>2704</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12197,20 +12377,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>355</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>398</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12218,20 +12398,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>27</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12239,19 +12419,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -12260,20 +12440,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H109,'Social — theo ngày'!$A$6:$A$109,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$109,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1190</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1336</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12315,8 +12495,8 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B68</f>
-        <v>116</v>
+        <f aca="false">'Social — 28 ngày'!B69</f>
+        <v>117</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12336,8 +12516,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C68</f>
-        <v>171</v>
+        <f aca="false">'Social — 28 ngày'!C69</f>
+        <v>173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12357,8 +12537,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D68</f>
-        <v>3891</v>
+        <f aca="false">'Social — 28 ngày'!D69</f>
+        <v>3981</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12378,8 +12558,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E68</f>
-        <v>462</v>
+        <f aca="false">'Social — 28 ngày'!E69</f>
+        <v>490</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12399,7 +12579,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F68</f>
+        <f aca="false">'Social — 28 ngày'!F69</f>
         <v>49</v>
       </c>
     </row>
@@ -12420,8 +12600,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G68</f>
-        <v>43</v>
+        <f aca="false">'Social — 28 ngày'!G69</f>
+        <v>44</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12441,8 +12621,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H68</f>
-        <v>175</v>
+        <f aca="false">'Social — 28 ngày'!H69</f>
+        <v>285</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12462,8 +12642,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I68</f>
-        <v>1665</v>
+        <f aca="false">'Social — 28 ngày'!I69</f>
+        <v>1775</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12483,8 +12663,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J68</f>
-        <v>136</v>
+        <f aca="false">'Social — 28 ngày'!J69</f>
+        <v>138</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12504,8 +12684,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K68</f>
-        <v>1299</v>
+        <f aca="false">'Social — 28 ngày'!K69</f>
+        <v>1278</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12525,8 +12705,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L68</f>
-        <v>79</v>
+        <f aca="false">'Social — 28 ngày'!L69</f>
+        <v>82</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12546,8 +12726,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M68</f>
-        <v>38</v>
+        <f aca="false">'Social — 28 ngày'!M69</f>
+        <v>37</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12567,7 +12747,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N68</f>
+        <f aca="false">'Social — 28 ngày'!N69</f>
         <v>7</v>
       </c>
     </row>
@@ -12588,8 +12768,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O68</f>
-        <v>586</v>
+        <f aca="false">'Social — 28 ngày'!O69</f>
+        <v>780</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12638,8 +12818,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B68</f>
-        <v>17</v>
+        <f aca="false">SEO!B69</f>
+        <v>18</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12663,7 +12843,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C68</f>
+        <f aca="false">SEO!C69</f>
         <v>912</v>
       </c>
     </row>
@@ -12688,7 +12868,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D68</f>
+        <f aca="false">SEO!D69</f>
         <v>876</v>
       </c>
     </row>
@@ -12713,8 +12893,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E68</f>
-        <v>39.18</v>
+        <f aca="false">SEO!E69</f>
+        <v>40.27</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12738,7 +12918,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F68</f>
+        <f aca="false">SEO!F69</f>
         <v>9</v>
       </c>
     </row>
@@ -12763,8 +12943,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G68</f>
-        <v>679</v>
+        <f aca="false">SEO!G69</f>
+        <v>673</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12788,8 +12968,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H68</f>
-        <v>433</v>
+        <f aca="false">SEO!H69</f>
+        <v>425</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12813,7 +12993,7 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I68</f>
+        <f aca="false">SEO!I69</f>
         <v>26</v>
       </c>
     </row>
@@ -12838,8 +13018,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J68</f>
-        <v>3.2</v>
+        <f aca="false">SEO!J69</f>
+        <v>2.7</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12863,8 +13043,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K68</f>
-        <v>816</v>
+        <f aca="false">SEO!K69</f>
+        <v>951</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12888,8 +13068,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L68</f>
-        <v>15.2</v>
+        <f aca="false">SEO!L69</f>
+        <v>17.6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12913,8 +13093,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M68</f>
-        <v>83</v>
+        <f aca="false">SEO!M69</f>
+        <v>90</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12938,7 +13118,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N68</f>
+        <f aca="false">SEO!N69</f>
         <v>119</v>
       </c>
     </row>
@@ -12963,8 +13143,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O68</f>
-        <v>325</v>
+        <f aca="false">SEO!O69</f>
+        <v>302</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13006,7 +13186,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B65</f>
+        <f aca="false">Audit!B66</f>
         <v>93</v>
       </c>
     </row>
@@ -13027,7 +13207,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C65</f>
+        <f aca="false">Audit!C66</f>
         <v>98</v>
       </c>
     </row>
@@ -13048,7 +13228,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D65</f>
+        <f aca="false">Audit!D66</f>
         <v>97</v>
       </c>
     </row>
@@ -13069,7 +13249,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E65</f>
+        <f aca="false">Audit!E66</f>
         <v>93</v>
       </c>
     </row>
@@ -13090,7 +13270,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F65</f>
+        <f aca="false">Audit!F66</f>
         <v>118</v>
       </c>
     </row>
@@ -13111,7 +13291,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G65</f>
+        <f aca="false">Audit!G66</f>
         <v>98</v>
       </c>
     </row>
@@ -13132,7 +13312,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H65</f>
+        <f aca="false">Audit!H66</f>
         <v>119</v>
       </c>
     </row>
@@ -13153,7 +13333,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I65</f>
+        <f aca="false">Audit!I66</f>
         <v>98</v>
       </c>
     </row>
@@ -13174,8 +13354,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J65</f>
-        <v>324.9</v>
+        <f aca="false">Audit!J66</f>
+        <v>301.8</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13195,8 +13375,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K65</f>
-        <v>266.5</v>
+        <f aca="false">Audit!K66</f>
+        <v>247</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13216,7 +13396,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L65</f>
+        <f aca="false">Audit!L66</f>
         <v>242263</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-19 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-20 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">106 dòng × 7 chỉ số · 2026-07-05 → 2026-10-18</t>
+    <t xml:space="preserve">107 dòng × 7 chỉ số · 2026-07-05 → 2026-10-19</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">64 dòng × 14 chỉ số · 2026-07-23 → 2026-10-20</t>
+    <t xml:space="preserve">65 dòng × 14 chỉ số · 2026-07-23 → 2026-10-21</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">64 dòng × 14 chỉ số · 2026-06-30 → 2026-10-20</t>
+    <t xml:space="preserve">65 dòng × 14 chỉ số · 2026-06-30 → 2026-10-21</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">61 dòng × 11 chỉ số · 2026-07-27 → 2026-10-20</t>
+    <t xml:space="preserve">62 dòng × 11 chỉ số · 2026-07-27 → 2026-10-21</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 106 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 107 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 64 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 65 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 64 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 65 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 61 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 62 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3799,6 +3799,30 @@
       <c r="G111" s="16"/>
       <c r="H111" s="16" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B112" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" s="16" t="n">
+        <v>125</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="F112" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3817,7 +3841,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6927,6 +6951,53 @@
       </c>
       <c r="O69" s="16" t="n">
         <v>780</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B70" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>171</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>3957</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>499</v>
+      </c>
+      <c r="F70" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>286</v>
+      </c>
+      <c r="I70" s="16" t="n">
+        <v>1767</v>
+      </c>
+      <c r="J70" s="16" t="n">
+        <v>139</v>
+      </c>
+      <c r="K70" s="16" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L70" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="M70" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="N70" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O70" s="16" t="n">
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -6945,7 +7016,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -9953,6 +10024,53 @@
       </c>
       <c r="O69" s="16" t="n">
         <v>302</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B70" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>911</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>875</v>
+      </c>
+      <c r="E70" s="19" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="F70" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>669</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>419</v>
+      </c>
+      <c r="I70" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="J70" s="19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K70" s="16" t="n">
+        <v>1017</v>
+      </c>
+      <c r="L70" s="19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M70" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="N70" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O70" s="16" t="n">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -9971,7 +10089,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -12246,6 +12364,44 @@
         <v>247</v>
       </c>
       <c r="L66" s="16" t="n">
+        <v>242263</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B67" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D67" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F67" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H67" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I67" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J67" s="16" t="n">
+        <v>308</v>
+      </c>
+      <c r="K67" s="16" t="n">
+        <v>253</v>
+      </c>
+      <c r="L67" s="16" t="n">
         <v>242263</v>
       </c>
     </row>
@@ -12314,20 +12470,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>112</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12335,20 +12491,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>326</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>328</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12356,20 +12512,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>2704</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>2829</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12377,20 +12533,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>398</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>419</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12398,20 +12554,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>28</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>32</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12419,19 +12575,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -12440,20 +12596,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H111,'Social — theo ngày'!$A$6:$A$111,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$111,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1336</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1385</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12495,8 +12651,8 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B69</f>
-        <v>117</v>
+        <f aca="false">'Social — 28 ngày'!B70</f>
+        <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12516,8 +12672,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C69</f>
-        <v>173</v>
+        <f aca="false">'Social — 28 ngày'!C70</f>
+        <v>171</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12537,8 +12693,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D69</f>
-        <v>3981</v>
+        <f aca="false">'Social — 28 ngày'!D70</f>
+        <v>3957</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12558,8 +12714,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E69</f>
-        <v>490</v>
+        <f aca="false">'Social — 28 ngày'!E70</f>
+        <v>499</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12579,7 +12735,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F69</f>
+        <f aca="false">'Social — 28 ngày'!F70</f>
         <v>49</v>
       </c>
     </row>
@@ -12600,8 +12756,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G69</f>
-        <v>44</v>
+        <f aca="false">'Social — 28 ngày'!G70</f>
+        <v>48</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12621,8 +12777,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H69</f>
-        <v>285</v>
+        <f aca="false">'Social — 28 ngày'!H70</f>
+        <v>286</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12642,8 +12798,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I69</f>
-        <v>1775</v>
+        <f aca="false">'Social — 28 ngày'!I70</f>
+        <v>1767</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12663,8 +12819,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J69</f>
-        <v>138</v>
+        <f aca="false">'Social — 28 ngày'!J70</f>
+        <v>139</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12684,8 +12840,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K69</f>
-        <v>1278</v>
+        <f aca="false">'Social — 28 ngày'!K70</f>
+        <v>1263</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12705,8 +12861,8 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L69</f>
-        <v>82</v>
+        <f aca="false">'Social — 28 ngày'!L70</f>
+        <v>80</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12726,8 +12882,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M69</f>
-        <v>37</v>
+        <f aca="false">'Social — 28 ngày'!M70</f>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12747,7 +12903,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N69</f>
+        <f aca="false">'Social — 28 ngày'!N70</f>
         <v>7</v>
       </c>
     </row>
@@ -12768,8 +12924,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O69</f>
-        <v>780</v>
+        <f aca="false">'Social — 28 ngày'!O70</f>
+        <v>782</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12818,8 +12974,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B69</f>
-        <v>18</v>
+        <f aca="false">SEO!B70</f>
+        <v>19</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12843,8 +12999,8 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C69</f>
-        <v>912</v>
+        <f aca="false">SEO!C70</f>
+        <v>911</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12868,8 +13024,8 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D69</f>
-        <v>876</v>
+        <f aca="false">SEO!D70</f>
+        <v>875</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12893,8 +13049,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E69</f>
-        <v>40.27</v>
+        <f aca="false">SEO!E70</f>
+        <v>40.36</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12918,7 +13074,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F69</f>
+        <f aca="false">SEO!F70</f>
         <v>9</v>
       </c>
     </row>
@@ -12943,8 +13099,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G69</f>
-        <v>673</v>
+        <f aca="false">SEO!G70</f>
+        <v>669</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12968,8 +13124,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H69</f>
-        <v>425</v>
+        <f aca="false">SEO!H70</f>
+        <v>419</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12993,8 +13149,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I69</f>
-        <v>26</v>
+        <f aca="false">SEO!I70</f>
+        <v>28</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13018,8 +13174,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J69</f>
-        <v>2.7</v>
+        <f aca="false">SEO!J70</f>
+        <v>2.8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13043,8 +13199,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K69</f>
-        <v>951</v>
+        <f aca="false">SEO!K70</f>
+        <v>1017</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13068,8 +13224,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L69</f>
-        <v>17.6</v>
+        <f aca="false">SEO!L70</f>
+        <v>19.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13093,8 +13249,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M69</f>
-        <v>90</v>
+        <f aca="false">SEO!M70</f>
+        <v>110</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13118,7 +13274,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N69</f>
+        <f aca="false">SEO!N70</f>
         <v>119</v>
       </c>
     </row>
@@ -13143,8 +13299,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O69</f>
-        <v>302</v>
+        <f aca="false">SEO!O70</f>
+        <v>308</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13186,7 +13342,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B66</f>
+        <f aca="false">Audit!B67</f>
         <v>93</v>
       </c>
     </row>
@@ -13207,7 +13363,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C66</f>
+        <f aca="false">Audit!C67</f>
         <v>98</v>
       </c>
     </row>
@@ -13228,7 +13384,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D66</f>
+        <f aca="false">Audit!D67</f>
         <v>97</v>
       </c>
     </row>
@@ -13249,7 +13405,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E66</f>
+        <f aca="false">Audit!E67</f>
         <v>93</v>
       </c>
     </row>
@@ -13270,7 +13426,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F66</f>
+        <f aca="false">Audit!F67</f>
         <v>118</v>
       </c>
     </row>
@@ -13291,7 +13447,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G66</f>
+        <f aca="false">Audit!G67</f>
         <v>98</v>
       </c>
     </row>
@@ -13312,7 +13468,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H66</f>
+        <f aca="false">Audit!H67</f>
         <v>119</v>
       </c>
     </row>
@@ -13333,7 +13489,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I66</f>
+        <f aca="false">Audit!I67</f>
         <v>98</v>
       </c>
     </row>
@@ -13354,8 +13510,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J66</f>
-        <v>301.8</v>
+        <f aca="false">Audit!J67</f>
+        <v>308</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13375,8 +13531,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K66</f>
-        <v>247</v>
+        <f aca="false">Audit!K67</f>
+        <v>253</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13396,7 +13552,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L66</f>
+        <f aca="false">Audit!L67</f>
         <v>242263</v>
       </c>
     </row>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-20 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-21 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">107 dòng × 7 chỉ số · 2026-07-05 → 2026-10-19</t>
+    <t xml:space="preserve">108 dòng × 7 chỉ số · 2026-07-05 → 2026-10-20</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">65 dòng × 14 chỉ số · 2026-07-23 → 2026-10-21</t>
+    <t xml:space="preserve">66 dòng × 14 chỉ số · 2026-07-23 → 2026-10-22</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">65 dòng × 14 chỉ số · 2026-06-30 → 2026-10-21</t>
+    <t xml:space="preserve">66 dòng × 14 chỉ số · 2026-06-30 → 2026-10-22</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">62 dòng × 11 chỉ số · 2026-07-27 → 2026-10-21</t>
+    <t xml:space="preserve">63 dòng × 11 chỉ số · 2026-07-27 → 2026-10-22</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 107 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 108 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 65 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 66 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 65 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 66 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 62 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 63 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3823,6 +3823,30 @@
       <c r="G112" s="16"/>
       <c r="H112" s="16" t="n">
         <v>49</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B113" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C113" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" s="16" t="n">
+        <v>203</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F113" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3841,7 +3865,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6998,6 +7022,53 @@
       </c>
       <c r="O70" s="16" t="n">
         <v>782</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="15" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B71" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>177</v>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>4026</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>517</v>
+      </c>
+      <c r="F71" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="H71" s="16" t="n">
+        <v>286</v>
+      </c>
+      <c r="I71" s="16" t="n">
+        <v>1790</v>
+      </c>
+      <c r="J71" s="16" t="n">
+        <v>138</v>
+      </c>
+      <c r="K71" s="16" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L71" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="M71" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="N71" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -7016,7 +7087,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10071,6 +10142,53 @@
       </c>
       <c r="O70" s="16" t="n">
         <v>308</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="15" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B71" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>911</v>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>875</v>
+      </c>
+      <c r="E71" s="19" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="F71" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>672</v>
+      </c>
+      <c r="H71" s="16" t="n">
+        <v>422</v>
+      </c>
+      <c r="I71" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K71" s="16" t="n">
+        <v>1174</v>
+      </c>
+      <c r="L71" s="19" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M71" s="16" t="n">
+        <v>114</v>
+      </c>
+      <c r="N71" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O71" s="19" t="n">
+        <v>311.2</v>
       </c>
     </row>
   </sheetData>
@@ -10089,7 +10207,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -12403,6 +12521,44 @@
       </c>
       <c r="L67" s="16" t="n">
         <v>242263</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B68" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F68" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H68" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I68" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J68" s="19" t="n">
+        <v>311.2</v>
+      </c>
+      <c r="K68" s="16" t="n">
+        <v>255</v>
+      </c>
+      <c r="L68" s="16" t="n">
+        <v>243021</v>
       </c>
     </row>
   </sheetData>
@@ -12470,20 +12626,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>116</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12491,20 +12647,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>328</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12512,20 +12668,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>2829</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>3032</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12533,20 +12689,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>419</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>441</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12554,20 +12710,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>32</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12575,19 +12731,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -12596,20 +12752,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H112,'Social — theo ngày'!$A$6:$A$112,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$112,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1385</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1437</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12651,7 +12807,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B70</f>
+        <f aca="false">'Social — 28 ngày'!B71</f>
         <v>116</v>
       </c>
     </row>
@@ -12672,8 +12828,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C70</f>
-        <v>171</v>
+        <f aca="false">'Social — 28 ngày'!C71</f>
+        <v>177</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12693,8 +12849,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D70</f>
-        <v>3957</v>
+        <f aca="false">'Social — 28 ngày'!D71</f>
+        <v>4026</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12714,8 +12870,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E70</f>
-        <v>499</v>
+        <f aca="false">'Social — 28 ngày'!E71</f>
+        <v>517</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12735,7 +12891,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F70</f>
+        <f aca="false">'Social — 28 ngày'!F71</f>
         <v>49</v>
       </c>
     </row>
@@ -12756,8 +12912,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G70</f>
-        <v>48</v>
+        <f aca="false">'Social — 28 ngày'!G71</f>
+        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12777,7 +12933,7 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H70</f>
+        <f aca="false">'Social — 28 ngày'!H71</f>
         <v>286</v>
       </c>
     </row>
@@ -12798,8 +12954,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I70</f>
-        <v>1767</v>
+        <f aca="false">'Social — 28 ngày'!I71</f>
+        <v>1790</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12819,8 +12975,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J70</f>
-        <v>139</v>
+        <f aca="false">'Social — 28 ngày'!J71</f>
+        <v>138</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12840,8 +12996,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K70</f>
-        <v>1263</v>
+        <f aca="false">'Social — 28 ngày'!K71</f>
+        <v>1250</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12861,7 +13017,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L70</f>
+        <f aca="false">'Social — 28 ngày'!L71</f>
         <v>80</v>
       </c>
     </row>
@@ -12882,8 +13038,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M70</f>
-        <v>38</v>
+        <f aca="false">'Social — 28 ngày'!M71</f>
+        <v>35</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12903,7 +13059,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N70</f>
+        <f aca="false">'Social — 28 ngày'!N71</f>
         <v>7</v>
       </c>
     </row>
@@ -12924,8 +13080,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O70</f>
-        <v>782</v>
+        <f aca="false">'Social — 28 ngày'!O71</f>
+        <v>783</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12974,8 +13130,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B70</f>
-        <v>19</v>
+        <f aca="false">SEO!B71</f>
+        <v>21</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12999,7 +13155,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C70</f>
+        <f aca="false">SEO!C71</f>
         <v>911</v>
       </c>
     </row>
@@ -13024,7 +13180,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D70</f>
+        <f aca="false">SEO!D71</f>
         <v>875</v>
       </c>
     </row>
@@ -13049,8 +13205,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E70</f>
-        <v>40.36</v>
+        <f aca="false">SEO!E71</f>
+        <v>39.58</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13074,8 +13230,8 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F70</f>
-        <v>9</v>
+        <f aca="false">SEO!F71</f>
+        <v>8</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13099,8 +13255,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G70</f>
-        <v>669</v>
+        <f aca="false">SEO!G71</f>
+        <v>672</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13124,8 +13280,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H70</f>
-        <v>419</v>
+        <f aca="false">SEO!H71</f>
+        <v>422</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13149,8 +13305,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I70</f>
-        <v>28</v>
+        <f aca="false">SEO!I71</f>
+        <v>29</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13174,8 +13330,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J70</f>
-        <v>2.8</v>
+        <f aca="false">SEO!J71</f>
+        <v>2.5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13199,8 +13355,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K70</f>
-        <v>1017</v>
+        <f aca="false">SEO!K71</f>
+        <v>1174</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13224,8 +13380,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L70</f>
-        <v>19.1</v>
+        <f aca="false">SEO!L71</f>
+        <v>18.3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13249,8 +13405,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M70</f>
-        <v>110</v>
+        <f aca="false">SEO!M71</f>
+        <v>114</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13274,7 +13430,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N70</f>
+        <f aca="false">SEO!N71</f>
         <v>119</v>
       </c>
     </row>
@@ -13299,8 +13455,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O70</f>
-        <v>308</v>
+        <f aca="false">SEO!O71</f>
+        <v>311.2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13342,7 +13498,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B67</f>
+        <f aca="false">Audit!B68</f>
         <v>93</v>
       </c>
     </row>
@@ -13363,7 +13519,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C67</f>
+        <f aca="false">Audit!C68</f>
         <v>98</v>
       </c>
     </row>
@@ -13384,7 +13540,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D67</f>
+        <f aca="false">Audit!D68</f>
         <v>97</v>
       </c>
     </row>
@@ -13405,7 +13561,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E67</f>
+        <f aca="false">Audit!E68</f>
         <v>93</v>
       </c>
     </row>
@@ -13426,7 +13582,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F67</f>
+        <f aca="false">Audit!F68</f>
         <v>118</v>
       </c>
     </row>
@@ -13447,7 +13603,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G67</f>
+        <f aca="false">Audit!G68</f>
         <v>98</v>
       </c>
     </row>
@@ -13468,7 +13624,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H67</f>
+        <f aca="false">Audit!H68</f>
         <v>119</v>
       </c>
     </row>
@@ -13489,7 +13645,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I67</f>
+        <f aca="false">Audit!I68</f>
         <v>98</v>
       </c>
     </row>
@@ -13510,8 +13666,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J67</f>
-        <v>308</v>
+        <f aca="false">Audit!J68</f>
+        <v>311.2</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13531,8 +13687,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K67</f>
-        <v>253</v>
+        <f aca="false">Audit!K68</f>
+        <v>255</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13552,8 +13708,8 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L67</f>
-        <v>242263</v>
+        <f aca="false">Audit!L68</f>
+        <v>243021</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -1,694 +1,286 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Đọc trước" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Social — theo ngày" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Social — 28 ngày" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="SEO" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Audit" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Tổng hợp tháng" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Social — theo ngày" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Social — 28 ngày" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng hợp tháng" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="97">
-  <si>
-    <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-21 · nguồn: data/rollup.json của ba repo báo cáo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File này là gì</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bản xuất phẳng của dữ liệu đã lưu trong ba báo cáo DX Living, để đọc bằng tay và dựng báo cáo tháng. KHÔNG phải nguồn sự thật.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguồn sự thật</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/YYYY-MM-DD.json trong mỗi repo — bất biến, mỗi ngày một file, không bao giờ sửa. File Excel này và dashboard cùng đọc từ data/rollup.json, nên không bao giờ lệch nhau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sửa file này thì sao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không ảnh hưởng gì tới báo cáo. Lần xuất sau sẽ ghi đè.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BA LOẠI CHỈ SỐ — đọc kỹ trước khi cộng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số đo của đúng ngày đó. CỘNG DỒN ĐƯỢC. Hiện chỉ Social có (Facebook và Instagram), dựng lại từ chuỗi 28 giá trị lưu sẵn trong mỗi file ngày.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">window28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã là tổng của 28 ngày trước đó. KHÔNG ĐƯỢC CỘNG — hai ngày liền nhau chồng nhau 27 ngày, cộng lại là đếm trùng nhiều lần. Chỉ so đầu kỳ với cuối kỳ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giá trị tại thời điểm quét (điểm số, tốc độ, số follower). Không cộng — lấy giá trị cuối kỳ hoặc trung bình.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ô trống</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngày đó không đo chỉ số này. Không suy ra, không điền 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngày không quét</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không bao giờ được nội suy. Ví dụ không có bản quét 20/09/2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta điều chỉnh số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Với chuỗi day của Social, mỗi ngày giữ lần đọc MỚI NHẤT — Meta có sửa số về sau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CÁC SHEET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social — theo ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108 dòng × 7 chỉ số · 2026-07-05 → 2026-10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social — 28 ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66 dòng × 14 chỉ số · 2026-07-23 → 2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66 dòng × 14 chỉ số · 2026-06-30 → 2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63 dòng × 11 chỉ số · 2026-07-27 → 2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 108 ngày · 7 chỉ số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grain →</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — tương tác/ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — view 3 giây/ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — views/ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — lượt ghé/ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG — tương tác/ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG — reach/ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG — views/ngày</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 66 ngày · 14 chỉ số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — followers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — tương tác (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — views (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FB — lượt ghé (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG — followers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG — tương tác (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG — reach (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IG — views (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn — followers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn — impressions (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn — lượt xem trang (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LinkedIn — reactions (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouTube — subscribers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouTube — views (28n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 66 ngày · 14 chỉ số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahrefs — backlinks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ahrefs — referring domains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA4 — engagement %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA4 — key events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA4 — sessions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GA4 — users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSC — clicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSC — CTR %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSC — impressions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSC — vị trí TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSC — số truy vấn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sitemap — số URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTFB trung bình (ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 63 ngày · 11 chỉ số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crawlability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-page / Meta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số trang crawl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performance / TTFB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structured data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTFB trung vị (ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng số từ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng hợp theo tháng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mọi ô dưới đây là CÔNG THỨC trỏ về các sheet dữ liệu — sửa dữ liệu thì số này tự đổi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chỉ chuỗi grain "day" mới được CỘNG (SUMIFS). window28 và state lấy GIÁ TRỊ NGÀY QUÉT CUỐI CÙNG của tháng (INDEX).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CỘNG ĐƯỢC — số theo ngày thật (Social)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chỉ số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KHÔNG CỘNG — Social — 28 ngày (lấy ngày quét cuối tháng)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KHÔNG CỘNG — SEO (lấy ngày quét cuối tháng)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KHÔNG CỘNG — Audit (lấy ngày quét cuối tháng)</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.00"/>
-    <numFmt numFmtId="168" formatCode="#,##0.##"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="0012161C"/>
+      <sz val="14"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <i val="1"/>
+      <color rgb="006B727C"/>
+      <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF12161C"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF6B727C"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b val="1"/>
+      <color rgb="004A5260"/>
       <sz val="8"/>
-      <color rgb="FF4A5260"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6F5ED"/>
-        <bgColor rgb="FFEEF1F5"/>
+        <fgColor rgb="00E6F5ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF1E3"/>
-        <bgColor rgb="FFEEF1F5"/>
+        <fgColor rgb="00FDF1E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF1F5"/>
-        <bgColor rgb="FFE6F5ED"/>
+        <fgColor rgb="00EEF1F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2C3440"/>
-        <bgColor rgb="FF333300"/>
+        <fgColor rgb="002C3440"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
+    <border>
       <bottom style="thin">
-        <color rgb="FFE6E9EE"/>
+        <color rgb="00E6E9EE"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFDF1E3"/>
-      <rgbColor rgb="FFE6F5ED"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEEF1F5"/>
-      <rgbColor rgb="FFE6E9EE"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF6B727C"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF12161C"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF4A5260"/>
-      <rgbColor rgb="FF2C3440"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -696,366 +288,574 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="104"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="104" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>29</v>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>DX Living — dữ liệu báo cáo theo ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Xuất ngày 2026-10-22 · nguồn: data/rollup.json của ba repo báo cáo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>File này là gì</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Bản xuất phẳng của dữ liệu đã lưu trong ba báo cáo DX Living, để đọc bằng tay và dựng báo cáo tháng. KHÔNG phải nguồn sự thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Nguồn sự thật</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>data/YYYY-MM-DD.json trong mỗi repo — bất biến, mỗi ngày một file, không bao giờ sửa. File Excel này và dashboard cùng đọc từ data/rollup.json, nên không bao giờ lệch nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Sửa file này thì sao</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Không ảnh hưởng gì tới báo cáo. Lần xuất sau sẽ ghi đè.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>BA LOẠI CHỈ SỐ — đọc kỹ trước khi cộng</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Số đo của đúng ngày đó. CỘNG DỒN ĐƯỢC. Hiện chỉ Social có (Facebook và Instagram), dựng lại từ chuỗi 28 giá trị lưu sẵn trong mỗi file ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Đã là tổng của 28 ngày trước đó. KHÔNG ĐƯỢC CỘNG — hai ngày liền nhau chồng nhau 27 ngày, cộng lại là đếm trùng nhiều lần. Chỉ so đầu kỳ với cuối kỳ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Giá trị tại thời điểm quét (điểm số, tốc độ, số follower). Không cộng — lấy giá trị cuối kỳ hoặc trung bình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ô trống</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Ngày đó không đo chỉ số này. Không suy ra, không điền 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Ngày không quét</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Không bao giờ được nội suy. Ví dụ không có bản quét 20/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Meta điều chỉnh số</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Với chuỗi day của Social, mỗi ngày giữ lần đọc MỚI NHẤT — Meta có sửa số về sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CÁC SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Social — theo ngày</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>109 dòng × 7 chỉ số · 2026-07-05 → 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Social — 28 ngày</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>67 dòng × 14 chỉ số · 2026-07-23 → 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>67 dòng × 14 chỉ số · 2026-06-30 → 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>64 dòng × 11 chỉ số · 2026-07-27 → 2026-10-23</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H114"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="15"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Social — theo ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn: Social/data/rollup.json · 109 ngày · 7 chỉ số</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>grain →</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>FB — tương tác/ngày</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>FB — view 3 giây/ngày</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>FB — views/ngày</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>FB — lượt ghé/ngày</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>IG — tương tác/ngày</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>IG — reach/ngày</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>IG — views/ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="15" t="n">
         <v>46208</v>
       </c>
@@ -1081,7 +881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7">
       <c r="A7" s="15" t="n">
         <v>46209</v>
       </c>
@@ -1107,7 +907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8">
       <c r="A8" s="15" t="n">
         <v>46210</v>
       </c>
@@ -1133,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9">
       <c r="A9" s="15" t="n">
         <v>46211</v>
       </c>
@@ -1159,7 +959,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10">
       <c r="A10" s="15" t="n">
         <v>46212</v>
       </c>
@@ -1185,7 +985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11">
       <c r="A11" s="15" t="n">
         <v>46213</v>
       </c>
@@ -1211,7 +1011,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12">
       <c r="A12" s="15" t="n">
         <v>46214</v>
       </c>
@@ -1237,7 +1037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13">
       <c r="A13" s="15" t="n">
         <v>46215</v>
       </c>
@@ -1263,7 +1063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14">
       <c r="A14" s="15" t="n">
         <v>46216</v>
       </c>
@@ -1289,7 +1089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15">
       <c r="A15" s="15" t="n">
         <v>46217</v>
       </c>
@@ -1315,7 +1115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16">
       <c r="A16" s="15" t="n">
         <v>46218</v>
       </c>
@@ -1341,7 +1141,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17">
       <c r="A17" s="15" t="n">
         <v>46219</v>
       </c>
@@ -1367,7 +1167,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18">
       <c r="A18" s="15" t="n">
         <v>46220</v>
       </c>
@@ -1393,7 +1193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19">
       <c r="A19" s="15" t="n">
         <v>46221</v>
       </c>
@@ -1419,7 +1219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20">
       <c r="A20" s="15" t="n">
         <v>46222</v>
       </c>
@@ -1445,7 +1245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21">
       <c r="A21" s="15" t="n">
         <v>46223</v>
       </c>
@@ -1471,7 +1271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22">
       <c r="A22" s="15" t="n">
         <v>46224</v>
       </c>
@@ -1497,7 +1297,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23">
       <c r="A23" s="15" t="n">
         <v>46225</v>
       </c>
@@ -1523,7 +1323,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24">
       <c r="A24" s="15" t="n">
         <v>46226</v>
       </c>
@@ -1549,7 +1349,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25">
       <c r="A25" s="15" t="n">
         <v>46227</v>
       </c>
@@ -1575,7 +1375,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26">
       <c r="A26" s="15" t="n">
         <v>46228</v>
       </c>
@@ -1601,7 +1401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27">
       <c r="A27" s="15" t="n">
         <v>46229</v>
       </c>
@@ -1627,7 +1427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28">
       <c r="A28" s="15" t="n">
         <v>46230</v>
       </c>
@@ -1653,7 +1453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29">
       <c r="A29" s="15" t="n">
         <v>46231</v>
       </c>
@@ -1679,7 +1479,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30">
       <c r="A30" s="15" t="n">
         <v>46232</v>
       </c>
@@ -1705,7 +1505,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31">
       <c r="A31" s="15" t="n">
         <v>46233</v>
       </c>
@@ -1731,7 +1531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32">
       <c r="A32" s="15" t="n">
         <v>46234</v>
       </c>
@@ -1757,7 +1557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33">
       <c r="A33" s="15" t="n">
         <v>46235</v>
       </c>
@@ -1783,7 +1583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34">
       <c r="A34" s="15" t="n">
         <v>46236</v>
       </c>
@@ -1809,7 +1609,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35">
       <c r="A35" s="15" t="n">
         <v>46237</v>
       </c>
@@ -1835,7 +1635,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36">
       <c r="A36" s="15" t="n">
         <v>46238</v>
       </c>
@@ -1861,7 +1661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37">
       <c r="A37" s="15" t="n">
         <v>46239</v>
       </c>
@@ -1887,7 +1687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38">
       <c r="A38" s="15" t="n">
         <v>46240</v>
       </c>
@@ -1913,7 +1713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39">
       <c r="A39" s="15" t="n">
         <v>46241</v>
       </c>
@@ -1939,7 +1739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40">
       <c r="A40" s="15" t="n">
         <v>46242</v>
       </c>
@@ -1965,7 +1765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41">
       <c r="A41" s="15" t="n">
         <v>46243</v>
       </c>
@@ -1991,7 +1791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42">
       <c r="A42" s="15" t="n">
         <v>46244</v>
       </c>
@@ -2017,7 +1817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43">
       <c r="A43" s="15" t="n">
         <v>46245</v>
       </c>
@@ -2043,7 +1843,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44">
       <c r="A44" s="15" t="n">
         <v>46246</v>
       </c>
@@ -2069,7 +1869,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45">
       <c r="A45" s="15" t="n">
         <v>46247</v>
       </c>
@@ -2095,7 +1895,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46">
       <c r="A46" s="15" t="n">
         <v>46248</v>
       </c>
@@ -2121,7 +1921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47">
       <c r="A47" s="15" t="n">
         <v>46249</v>
       </c>
@@ -2147,7 +1947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48">
       <c r="A48" s="15" t="n">
         <v>46250</v>
       </c>
@@ -2173,7 +1973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49">
       <c r="A49" s="15" t="n">
         <v>46251</v>
       </c>
@@ -2199,7 +1999,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50">
       <c r="A50" s="15" t="n">
         <v>46252</v>
       </c>
@@ -2225,7 +2025,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51">
       <c r="A51" s="15" t="n">
         <v>46253</v>
       </c>
@@ -2251,7 +2051,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52">
       <c r="A52" s="15" t="n">
         <v>46254</v>
       </c>
@@ -2277,7 +2077,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53">
       <c r="A53" s="15" t="n">
         <v>46255</v>
       </c>
@@ -2303,7 +2103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54">
       <c r="A54" s="15" t="n">
         <v>46256</v>
       </c>
@@ -2329,7 +2129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55">
       <c r="A55" s="15" t="n">
         <v>46257</v>
       </c>
@@ -2355,7 +2155,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56">
       <c r="A56" s="15" t="n">
         <v>46258</v>
       </c>
@@ -2381,7 +2181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57">
       <c r="A57" s="15" t="n">
         <v>46259</v>
       </c>
@@ -2407,7 +2207,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58">
       <c r="A58" s="15" t="n">
         <v>46260</v>
       </c>
@@ -2433,7 +2233,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59">
       <c r="A59" s="15" t="n">
         <v>46261</v>
       </c>
@@ -2459,7 +2259,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60">
       <c r="A60" s="15" t="n">
         <v>46262</v>
       </c>
@@ -2485,7 +2285,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61">
       <c r="A61" s="15" t="n">
         <v>46263</v>
       </c>
@@ -2511,7 +2311,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62">
       <c r="A62" s="15" t="n">
         <v>46264</v>
       </c>
@@ -2537,7 +2337,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63">
       <c r="A63" s="15" t="n">
         <v>46265</v>
       </c>
@@ -2563,7 +2363,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64">
       <c r="A64" s="15" t="n">
         <v>46266</v>
       </c>
@@ -2589,7 +2389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65">
       <c r="A65" s="15" t="n">
         <v>46267</v>
       </c>
@@ -2615,7 +2415,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66">
       <c r="A66" s="15" t="n">
         <v>46268</v>
       </c>
@@ -2641,7 +2441,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67">
       <c r="A67" s="15" t="n">
         <v>46269</v>
       </c>
@@ -2667,7 +2467,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68">
       <c r="A68" s="15" t="n">
         <v>46270</v>
       </c>
@@ -2693,7 +2493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69">
       <c r="A69" s="15" t="n">
         <v>46271</v>
       </c>
@@ -2719,7 +2519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70">
       <c r="A70" s="15" t="n">
         <v>46272</v>
       </c>
@@ -2745,7 +2545,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71">
       <c r="A71" s="15" t="n">
         <v>46273</v>
       </c>
@@ -2771,7 +2571,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72">
       <c r="A72" s="15" t="n">
         <v>46274</v>
       </c>
@@ -2797,7 +2597,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73">
       <c r="A73" s="15" t="n">
         <v>46275</v>
       </c>
@@ -2823,7 +2623,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74">
       <c r="A74" s="15" t="n">
         <v>46276</v>
       </c>
@@ -2849,7 +2649,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75">
       <c r="A75" s="15" t="n">
         <v>46277</v>
       </c>
@@ -2875,7 +2675,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76">
       <c r="A76" s="15" t="n">
         <v>46278</v>
       </c>
@@ -2901,7 +2701,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77">
       <c r="A77" s="15" t="n">
         <v>46279</v>
       </c>
@@ -2927,7 +2727,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78">
       <c r="A78" s="15" t="n">
         <v>46280</v>
       </c>
@@ -2953,7 +2753,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79">
       <c r="A79" s="15" t="n">
         <v>46281</v>
       </c>
@@ -2979,7 +2779,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80">
       <c r="A80" s="15" t="n">
         <v>46282</v>
       </c>
@@ -3005,7 +2805,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81">
       <c r="A81" s="15" t="n">
         <v>46283</v>
       </c>
@@ -3031,7 +2831,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82">
       <c r="A82" s="15" t="n">
         <v>46284</v>
       </c>
@@ -3057,7 +2857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83">
       <c r="A83" s="15" t="n">
         <v>46285</v>
       </c>
@@ -3083,7 +2883,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84">
       <c r="A84" s="15" t="n">
         <v>46286</v>
       </c>
@@ -3109,7 +2909,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85">
       <c r="A85" s="15" t="n">
         <v>46287</v>
       </c>
@@ -3135,7 +2935,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86">
       <c r="A86" s="15" t="n">
         <v>46288</v>
       </c>
@@ -3161,7 +2961,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87">
       <c r="A87" s="15" t="n">
         <v>46289</v>
       </c>
@@ -3187,7 +2987,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88">
       <c r="A88" s="15" t="n">
         <v>46290</v>
       </c>
@@ -3213,7 +3013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89">
       <c r="A89" s="15" t="n">
         <v>46291</v>
       </c>
@@ -3239,7 +3039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90">
       <c r="A90" s="15" t="n">
         <v>46292</v>
       </c>
@@ -3265,7 +3065,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91">
       <c r="A91" s="15" t="n">
         <v>46293</v>
       </c>
@@ -3291,7 +3091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92">
       <c r="A92" s="15" t="n">
         <v>46294</v>
       </c>
@@ -3317,7 +3117,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93">
       <c r="A93" s="15" t="n">
         <v>46295</v>
       </c>
@@ -3343,7 +3143,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94">
       <c r="A94" s="15" t="n">
         <v>46296</v>
       </c>
@@ -3369,7 +3169,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95">
       <c r="A95" s="15" t="n">
         <v>46297</v>
       </c>
@@ -3395,7 +3195,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96">
       <c r="A96" s="15" t="n">
         <v>46298</v>
       </c>
@@ -3421,7 +3221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97">
       <c r="A97" s="15" t="n">
         <v>46299</v>
       </c>
@@ -3447,7 +3247,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98">
       <c r="A98" s="15" t="n">
         <v>46300</v>
       </c>
@@ -3473,7 +3273,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99">
       <c r="A99" s="15" t="n">
         <v>46301</v>
       </c>
@@ -3499,7 +3299,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100">
       <c r="A100" s="15" t="n">
         <v>46302</v>
       </c>
@@ -3525,7 +3325,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101">
       <c r="A101" s="15" t="n">
         <v>46303</v>
       </c>
@@ -3551,7 +3351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102">
       <c r="A102" s="15" t="n">
         <v>46304</v>
       </c>
@@ -3577,7 +3377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103">
       <c r="A103" s="15" t="n">
         <v>46305</v>
       </c>
@@ -3603,7 +3403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104">
       <c r="A104" s="15" t="n">
         <v>46306</v>
       </c>
@@ -3629,7 +3429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105">
       <c r="A105" s="15" t="n">
         <v>46307</v>
       </c>
@@ -3655,7 +3455,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106">
       <c r="A106" s="15" t="n">
         <v>46308</v>
       </c>
@@ -3681,7 +3481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107">
       <c r="A107" s="15" t="n">
         <v>46309</v>
       </c>
@@ -3700,12 +3500,12 @@
       <c r="F107" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="16"/>
+      <c r="G107" s="16" t="n"/>
       <c r="H107" s="16" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108">
       <c r="A108" s="15" t="n">
         <v>46310</v>
       </c>
@@ -3724,12 +3524,12 @@
       <c r="F108" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="G108" s="16"/>
+      <c r="G108" s="16" t="n"/>
       <c r="H108" s="16" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109">
       <c r="A109" s="15" t="n">
         <v>46311</v>
       </c>
@@ -3748,12 +3548,12 @@
       <c r="F109" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="G109" s="16"/>
+      <c r="G109" s="16" t="n"/>
       <c r="H109" s="16" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110">
       <c r="A110" s="15" t="n">
         <v>46312</v>
       </c>
@@ -3772,12 +3572,12 @@
       <c r="F110" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="16"/>
+      <c r="G110" s="16" t="n"/>
       <c r="H110" s="16" t="n">
         <v>128</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111">
       <c r="A111" s="15" t="n">
         <v>46313</v>
       </c>
@@ -3796,12 +3596,12 @@
       <c r="F111" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G111" s="16"/>
+      <c r="G111" s="16" t="n"/>
       <c r="H111" s="16" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112">
       <c r="A112" s="15" t="n">
         <v>46314</v>
       </c>
@@ -3820,12 +3620,12 @@
       <c r="F112" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="G112" s="16"/>
+      <c r="G112" s="16" t="n"/>
       <c r="H112" s="16" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113">
       <c r="A113" s="15" t="n">
         <v>46315</v>
       </c>
@@ -3844,144 +3644,242 @@
       <c r="F113" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="G113" s="16"/>
+      <c r="G113" s="16" t="n"/>
       <c r="H113" s="16" t="n">
         <v>52</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="15" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B114" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C114" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="D114" s="16" t="n">
+        <v>285</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="F114" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G114" s="16" t="n"/>
+      <c r="H114" s="16" t="n">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="2" style="0" width="15"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Social — 28 ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn: Social/data/rollup.json · 67 ngày · 14 chỉ số</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>grain →</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>FB — followers</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>FB — tương tác (28n)</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>FB — views (28n)</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>FB — lượt ghé (28n)</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>IG — followers</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>IG — tương tác (28n)</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>IG — reach (28n)</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>IG — views (28n)</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn — followers</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn — impressions (28n)</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn — lượt xem trang (28n)</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>LinkedIn — reactions (28n)</t>
+        </is>
+      </c>
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t>YouTube — subscribers</t>
+        </is>
+      </c>
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>YouTube — views (28n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="15" t="n">
         <v>46226</v>
       </c>
@@ -4028,7 +3926,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7">
       <c r="A7" s="15" t="n">
         <v>46230</v>
       </c>
@@ -4075,7 +3973,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8">
       <c r="A8" s="15" t="n">
         <v>46231</v>
       </c>
@@ -4122,7 +4020,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9">
       <c r="A9" s="15" t="n">
         <v>46232</v>
       </c>
@@ -4169,7 +4067,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10">
       <c r="A10" s="15" t="n">
         <v>46233</v>
       </c>
@@ -4216,7 +4114,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11">
       <c r="A11" s="15" t="n">
         <v>46234</v>
       </c>
@@ -4263,7 +4161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12">
       <c r="A12" s="15" t="n">
         <v>46237</v>
       </c>
@@ -4310,7 +4208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13">
       <c r="A13" s="15" t="n">
         <v>46238</v>
       </c>
@@ -4357,7 +4255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14">
       <c r="A14" s="15" t="n">
         <v>46239</v>
       </c>
@@ -4404,7 +4302,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15">
       <c r="A15" s="15" t="n">
         <v>46240</v>
       </c>
@@ -4451,7 +4349,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16">
       <c r="A16" s="15" t="n">
         <v>46241</v>
       </c>
@@ -4498,7 +4396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17">
       <c r="A17" s="15" t="n">
         <v>46244</v>
       </c>
@@ -4545,7 +4443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18">
       <c r="A18" s="15" t="n">
         <v>46245</v>
       </c>
@@ -4592,7 +4490,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19">
       <c r="A19" s="15" t="n">
         <v>46246</v>
       </c>
@@ -4639,7 +4537,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20">
       <c r="A20" s="15" t="n">
         <v>46247</v>
       </c>
@@ -4686,7 +4584,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21">
       <c r="A21" s="15" t="n">
         <v>46248</v>
       </c>
@@ -4733,7 +4631,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22">
       <c r="A22" s="15" t="n">
         <v>46251</v>
       </c>
@@ -4780,7 +4678,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23">
       <c r="A23" s="15" t="n">
         <v>46252</v>
       </c>
@@ -4827,7 +4725,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24">
       <c r="A24" s="15" t="n">
         <v>46253</v>
       </c>
@@ -4874,7 +4772,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25">
       <c r="A25" s="15" t="n">
         <v>46254</v>
       </c>
@@ -4921,7 +4819,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26">
       <c r="A26" s="15" t="n">
         <v>46255</v>
       </c>
@@ -4968,7 +4866,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27">
       <c r="A27" s="15" t="n">
         <v>46258</v>
       </c>
@@ -5015,7 +4913,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28">
       <c r="A28" s="15" t="n">
         <v>46259</v>
       </c>
@@ -5062,7 +4960,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29">
       <c r="A29" s="15" t="n">
         <v>46260</v>
       </c>
@@ -5109,7 +5007,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30">
       <c r="A30" s="15" t="n">
         <v>46261</v>
       </c>
@@ -5156,7 +5054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31">
       <c r="A31" s="15" t="n">
         <v>46262</v>
       </c>
@@ -5203,7 +5101,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32">
       <c r="A32" s="15" t="n">
         <v>46263</v>
       </c>
@@ -5250,7 +5148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33">
       <c r="A33" s="15" t="n">
         <v>46268</v>
       </c>
@@ -5297,7 +5195,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34">
       <c r="A34" s="15" t="n">
         <v>46269</v>
       </c>
@@ -5344,7 +5242,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35">
       <c r="A35" s="15" t="n">
         <v>46272</v>
       </c>
@@ -5391,7 +5289,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36">
       <c r="A36" s="15" t="n">
         <v>46273</v>
       </c>
@@ -5438,7 +5336,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37">
       <c r="A37" s="15" t="n">
         <v>46274</v>
       </c>
@@ -5485,7 +5383,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38">
       <c r="A38" s="15" t="n">
         <v>46275</v>
       </c>
@@ -5532,7 +5430,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39">
       <c r="A39" s="15" t="n">
         <v>46276</v>
       </c>
@@ -5579,7 +5477,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40">
       <c r="A40" s="15" t="n">
         <v>46279</v>
       </c>
@@ -5626,7 +5524,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41">
       <c r="A41" s="15" t="n">
         <v>46280</v>
       </c>
@@ -5673,7 +5571,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42">
       <c r="A42" s="15" t="n">
         <v>46281</v>
       </c>
@@ -5720,7 +5618,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43">
       <c r="A43" s="15" t="n">
         <v>46282</v>
       </c>
@@ -5767,7 +5665,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44">
       <c r="A44" s="15" t="n">
         <v>46283</v>
       </c>
@@ -5814,7 +5712,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45">
       <c r="A45" s="15" t="n">
         <v>46284</v>
       </c>
@@ -5861,7 +5759,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46">
       <c r="A46" s="15" t="n">
         <v>46286</v>
       </c>
@@ -5908,7 +5806,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47">
       <c r="A47" s="15" t="n">
         <v>46287</v>
       </c>
@@ -5955,7 +5853,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48">
       <c r="A48" s="15" t="n">
         <v>46288</v>
       </c>
@@ -6002,7 +5900,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49">
       <c r="A49" s="15" t="n">
         <v>46289</v>
       </c>
@@ -6049,7 +5947,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50">
       <c r="A50" s="15" t="n">
         <v>46290</v>
       </c>
@@ -6096,7 +5994,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51">
       <c r="A51" s="15" t="n">
         <v>46291</v>
       </c>
@@ -6143,7 +6041,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52">
       <c r="A52" s="15" t="n">
         <v>46293</v>
       </c>
@@ -6190,7 +6088,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53">
       <c r="A53" s="15" t="n">
         <v>46294</v>
       </c>
@@ -6237,7 +6135,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54">
       <c r="A54" s="15" t="n">
         <v>46295</v>
       </c>
@@ -6284,7 +6182,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55">
       <c r="A55" s="15" t="n">
         <v>46296</v>
       </c>
@@ -6324,10 +6222,10 @@
       <c r="M55" s="16" t="n">
         <v>37</v>
       </c>
-      <c r="N55" s="16"/>
-      <c r="O55" s="16"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N55" s="16" t="n"/>
+      <c r="O55" s="16" t="n"/>
+    </row>
+    <row r="56">
       <c r="A56" s="15" t="n">
         <v>46297</v>
       </c>
@@ -6374,7 +6272,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57">
       <c r="A57" s="15" t="n">
         <v>46298</v>
       </c>
@@ -6421,7 +6319,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58">
       <c r="A58" s="15" t="n">
         <v>46300</v>
       </c>
@@ -6468,7 +6366,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59">
       <c r="A59" s="15" t="n">
         <v>46301</v>
       </c>
@@ -6515,7 +6413,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60">
       <c r="A60" s="15" t="n">
         <v>46302</v>
       </c>
@@ -6562,7 +6460,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61">
       <c r="A61" s="15" t="n">
         <v>46303</v>
       </c>
@@ -6609,7 +6507,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62">
       <c r="A62" s="15" t="n">
         <v>46304</v>
       </c>
@@ -6656,7 +6554,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63">
       <c r="A63" s="15" t="n">
         <v>46307</v>
       </c>
@@ -6703,7 +6601,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64">
       <c r="A64" s="15" t="n">
         <v>46308</v>
       </c>
@@ -6750,7 +6648,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65">
       <c r="A65" s="15" t="n">
         <v>46309</v>
       </c>
@@ -6797,7 +6695,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66">
       <c r="A66" s="15" t="n">
         <v>46310</v>
       </c>
@@ -6844,7 +6742,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67">
       <c r="A67" s="15" t="n">
         <v>46311</v>
       </c>
@@ -6872,10 +6770,10 @@
       <c r="I67" s="16" t="n">
         <v>1823</v>
       </c>
-      <c r="J67" s="16"/>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+      <c r="J67" s="16" t="n"/>
+      <c r="K67" s="16" t="n"/>
+      <c r="L67" s="16" t="n"/>
+      <c r="M67" s="16" t="n"/>
       <c r="N67" s="16" t="n">
         <v>7</v>
       </c>
@@ -6883,7 +6781,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68">
       <c r="A68" s="15" t="n">
         <v>46313</v>
       </c>
@@ -6930,7 +6828,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69">
       <c r="A69" s="15" t="n">
         <v>46315</v>
       </c>
@@ -6977,7 +6875,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70">
       <c r="A70" s="15" t="n">
         <v>46316</v>
       </c>
@@ -7024,7 +6922,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71">
       <c r="A71" s="15" t="n">
         <v>46317</v>
       </c>
@@ -7071,151 +6969,264 @@
         <v>783</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>175</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>4124</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>531</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G72" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H72" s="16" t="n">
+        <v>334</v>
+      </c>
+      <c r="I72" s="16" t="n">
+        <v>1875</v>
+      </c>
+      <c r="J72" s="16" t="n"/>
+      <c r="K72" s="16" t="n"/>
+      <c r="L72" s="16" t="n"/>
+      <c r="M72" s="16" t="n"/>
+      <c r="N72" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>860</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="2" style="0" width="15"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn: SEO/data/rollup.json · 67 ngày · 14 chỉ số</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>grain →</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>window28</t>
+        </is>
+      </c>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="O4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Ahrefs — trích dẫn AI</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Ahrefs — backlinks</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Ahrefs — referring domains</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>GA4 — engagement %</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>GA4 — key events</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>GA4 — sessions</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>GA4 — users</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>GSC — clicks</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>GSC — CTR %</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>GSC — impressions</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>GSC — vị trí TB</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>GSC — số truy vấn</t>
+        </is>
+      </c>
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t>Sitemap — số URL</t>
+        </is>
+      </c>
+      <c r="O5" s="14" t="inlineStr">
+        <is>
+          <t>TTFB trung bình (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="15" t="n">
         <v>46203</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
       <c r="D6" s="16" t="n">
         <v>244</v>
       </c>
       <c r="E6" s="19" t="n">
         <v>18.9</v>
       </c>
-      <c r="F6" s="16"/>
+      <c r="F6" s="16" t="n"/>
       <c r="G6" s="16" t="n">
         <v>322</v>
       </c>
@@ -7234,16 +7245,16 @@
       <c r="L6" s="19" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+    </row>
+    <row r="7">
       <c r="A7" s="15" t="n">
         <v>46230</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n">
         <v>244</v>
       </c>
@@ -7256,7 +7267,7 @@
       <c r="G7" s="16" t="n">
         <v>442</v>
       </c>
-      <c r="H7" s="16"/>
+      <c r="H7" s="16" t="n"/>
       <c r="I7" s="16" t="n">
         <v>65</v>
       </c>
@@ -7269,11 +7280,11 @@
       <c r="L7" s="19" t="n">
         <v>23.2</v>
       </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n"/>
+    </row>
+    <row r="8">
       <c r="A8" s="15" t="n">
         <v>46231</v>
       </c>
@@ -7295,7 +7306,7 @@
       <c r="G8" s="16" t="n">
         <v>435</v>
       </c>
-      <c r="H8" s="16"/>
+      <c r="H8" s="16" t="n"/>
       <c r="I8" s="16" t="n">
         <v>65</v>
       </c>
@@ -7308,11 +7319,11 @@
       <c r="L8" s="19" t="n">
         <v>23.7</v>
       </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
+    </row>
+    <row r="9">
       <c r="A9" s="15" t="n">
         <v>46232</v>
       </c>
@@ -7326,7 +7337,7 @@
         <v>339</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>64.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>42</v>
@@ -7334,7 +7345,7 @@
       <c r="G9" s="16" t="n">
         <v>421</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="16" t="n"/>
       <c r="I9" s="16" t="n">
         <v>63</v>
       </c>
@@ -7350,10 +7361,10 @@
       <c r="M9" s="16" t="n">
         <v>113</v>
       </c>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n"/>
+    </row>
+    <row r="10">
       <c r="A10" s="15" t="n">
         <v>46233</v>
       </c>
@@ -7367,7 +7378,7 @@
         <v>339</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>64.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F10" s="16" t="n">
         <v>42</v>
@@ -7375,7 +7386,7 @@
       <c r="G10" s="16" t="n">
         <v>421</v>
       </c>
-      <c r="H10" s="16"/>
+      <c r="H10" s="16" t="n"/>
       <c r="I10" s="16" t="n">
         <v>65</v>
       </c>
@@ -7391,10 +7402,10 @@
       <c r="M10" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="16" t="n"/>
+    </row>
+    <row r="11">
       <c r="A11" s="15" t="n">
         <v>46234</v>
       </c>
@@ -7416,7 +7427,7 @@
       <c r="G11" s="16" t="n">
         <v>405</v>
       </c>
-      <c r="H11" s="16"/>
+      <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="n">
         <v>67</v>
       </c>
@@ -7432,10 +7443,10 @@
       <c r="M11" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+    </row>
+    <row r="12">
       <c r="A12" s="15" t="n">
         <v>46237</v>
       </c>
@@ -7457,7 +7468,7 @@
       <c r="G12" s="16" t="n">
         <v>381</v>
       </c>
-      <c r="H12" s="16"/>
+      <c r="H12" s="16" t="n"/>
       <c r="I12" s="16" t="n">
         <v>68</v>
       </c>
@@ -7473,10 +7484,10 @@
       <c r="M12" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+    </row>
+    <row r="13">
       <c r="A13" s="15" t="n">
         <v>46241</v>
       </c>
@@ -7490,7 +7501,7 @@
         <v>366</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>67.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F13" s="16" t="n">
         <v>23</v>
@@ -7519,9 +7530,9 @@
       <c r="N13" s="16" t="n">
         <v>75</v>
       </c>
-      <c r="O13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O13" s="16" t="n"/>
+    </row>
+    <row r="14">
       <c r="A14" s="15" t="n">
         <v>46244</v>
       </c>
@@ -7564,9 +7575,9 @@
       <c r="N14" s="16" t="n">
         <v>76</v>
       </c>
-      <c r="O14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O14" s="16" t="n"/>
+    </row>
+    <row r="15">
       <c r="A15" s="15" t="n">
         <v>46245</v>
       </c>
@@ -7580,7 +7591,7 @@
         <v>397</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>65.04</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>15</v>
@@ -7609,9 +7620,9 @@
       <c r="N15" s="16" t="n">
         <v>77</v>
       </c>
-      <c r="O15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O15" s="16" t="n"/>
+    </row>
+    <row r="16">
       <c r="A16" s="15" t="n">
         <v>46246</v>
       </c>
@@ -7654,9 +7665,9 @@
       <c r="N16" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="O16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O16" s="16" t="n"/>
+    </row>
+    <row r="17">
       <c r="A17" s="15" t="n">
         <v>46247</v>
       </c>
@@ -7699,9 +7710,9 @@
       <c r="N17" s="16" t="n">
         <v>79</v>
       </c>
-      <c r="O17" s="16"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O17" s="16" t="n"/>
+    </row>
+    <row r="18">
       <c r="A18" s="15" t="n">
         <v>46248</v>
       </c>
@@ -7715,7 +7726,7 @@
         <v>410</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>67.82</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="F18" s="16" t="n">
         <v>13</v>
@@ -7744,9 +7755,9 @@
       <c r="N18" s="16" t="n">
         <v>79</v>
       </c>
-      <c r="O18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O18" s="16" t="n"/>
+    </row>
+    <row r="19">
       <c r="A19" s="15" t="n">
         <v>46251</v>
       </c>
@@ -7789,9 +7800,9 @@
       <c r="N19" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="O19" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O19" s="16" t="n"/>
+    </row>
+    <row r="20">
       <c r="A20" s="15" t="n">
         <v>46252</v>
       </c>
@@ -7834,9 +7845,9 @@
       <c r="N20" s="16" t="n">
         <v>82</v>
       </c>
-      <c r="O20" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O20" s="16" t="n"/>
+    </row>
+    <row r="21">
       <c r="A21" s="15" t="n">
         <v>46253</v>
       </c>
@@ -7861,17 +7872,17 @@
       <c r="H21" s="16" t="n">
         <v>56</v>
       </c>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="n"/>
+      <c r="K21" s="16" t="n"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="16" t="n"/>
       <c r="N21" s="16" t="n">
         <v>81</v>
       </c>
-      <c r="O21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O21" s="16" t="n"/>
+    </row>
+    <row r="22">
       <c r="A22" s="15" t="n">
         <v>46254</v>
       </c>
@@ -7914,9 +7925,9 @@
       <c r="N22" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="O22" s="16"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O22" s="16" t="n"/>
+    </row>
+    <row r="23">
       <c r="A23" s="15" t="n">
         <v>46255</v>
       </c>
@@ -7959,9 +7970,9 @@
       <c r="N23" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="O23" s="16"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O23" s="16" t="n"/>
+    </row>
+    <row r="24">
       <c r="A24" s="15" t="n">
         <v>46258</v>
       </c>
@@ -8004,9 +8015,9 @@
       <c r="N24" s="16" t="n">
         <v>86</v>
       </c>
-      <c r="O24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O24" s="16" t="n"/>
+    </row>
+    <row r="25">
       <c r="A25" s="15" t="n">
         <v>46259</v>
       </c>
@@ -8049,9 +8060,9 @@
       <c r="N25" s="16" t="n">
         <v>86</v>
       </c>
-      <c r="O25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O25" s="16" t="n"/>
+    </row>
+    <row r="26">
       <c r="A26" s="15" t="n">
         <v>46260</v>
       </c>
@@ -8094,9 +8105,9 @@
       <c r="N26" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="O26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O26" s="16" t="n"/>
+    </row>
+    <row r="27">
       <c r="A27" s="15" t="n">
         <v>46261</v>
       </c>
@@ -8139,9 +8150,9 @@
       <c r="N27" s="16" t="n">
         <v>91</v>
       </c>
-      <c r="O27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O27" s="16" t="n"/>
+    </row>
+    <row r="28">
       <c r="A28" s="15" t="n">
         <v>46262</v>
       </c>
@@ -8188,7 +8199,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29">
       <c r="A29" s="15" t="n">
         <v>46263</v>
       </c>
@@ -8235,7 +8246,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30">
       <c r="A30" s="15" t="n">
         <v>46265</v>
       </c>
@@ -8282,7 +8293,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31">
       <c r="A31" s="15" t="n">
         <v>46266</v>
       </c>
@@ -8329,7 +8340,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32">
       <c r="A32" s="15" t="n">
         <v>46268</v>
       </c>
@@ -8376,7 +8387,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33">
       <c r="A33" s="15" t="n">
         <v>46269</v>
       </c>
@@ -8423,7 +8434,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34">
       <c r="A34" s="15" t="n">
         <v>46270</v>
       </c>
@@ -8470,7 +8481,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35">
       <c r="A35" s="15" t="n">
         <v>46272</v>
       </c>
@@ -8517,7 +8528,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36">
       <c r="A36" s="15" t="n">
         <v>46273</v>
       </c>
@@ -8564,7 +8575,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37">
       <c r="A37" s="15" t="n">
         <v>46274</v>
       </c>
@@ -8611,7 +8622,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38">
       <c r="A38" s="15" t="n">
         <v>46275</v>
       </c>
@@ -8658,7 +8669,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39">
       <c r="A39" s="15" t="n">
         <v>46276</v>
       </c>
@@ -8705,7 +8716,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40">
       <c r="A40" s="15" t="n">
         <v>46279</v>
       </c>
@@ -8752,7 +8763,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41">
       <c r="A41" s="15" t="n">
         <v>46280</v>
       </c>
@@ -8799,7 +8810,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42">
       <c r="A42" s="15" t="n">
         <v>46281</v>
       </c>
@@ -8846,7 +8857,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43">
       <c r="A43" s="15" t="n">
         <v>46282</v>
       </c>
@@ -8893,7 +8904,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44">
       <c r="A44" s="15" t="n">
         <v>46283</v>
       </c>
@@ -8940,7 +8951,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45">
       <c r="A45" s="15" t="n">
         <v>46284</v>
       </c>
@@ -8987,7 +8998,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46">
       <c r="A46" s="15" t="n">
         <v>46286</v>
       </c>
@@ -9034,7 +9045,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47">
       <c r="A47" s="15" t="n">
         <v>46287</v>
       </c>
@@ -9081,7 +9092,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48">
       <c r="A48" s="15" t="n">
         <v>46288</v>
       </c>
@@ -9128,7 +9139,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49">
       <c r="A49" s="15" t="n">
         <v>46289</v>
       </c>
@@ -9175,7 +9186,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50">
       <c r="A50" s="15" t="n">
         <v>46290</v>
       </c>
@@ -9222,7 +9233,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51">
       <c r="A51" s="15" t="n">
         <v>46291</v>
       </c>
@@ -9269,7 +9280,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52">
       <c r="A52" s="15" t="n">
         <v>46293</v>
       </c>
@@ -9316,7 +9327,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53">
       <c r="A53" s="15" t="n">
         <v>46294</v>
       </c>
@@ -9363,7 +9374,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54">
       <c r="A54" s="15" t="n">
         <v>46295</v>
       </c>
@@ -9410,7 +9421,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55">
       <c r="A55" s="15" t="n">
         <v>46296</v>
       </c>
@@ -9423,15 +9434,15 @@
       <c r="D55" s="16" t="n">
         <v>882</v>
       </c>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="16" t="n"/>
+      <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
+      <c r="K55" s="16" t="n"/>
+      <c r="L55" s="16" t="n"/>
+      <c r="M55" s="16" t="n"/>
       <c r="N55" s="16" t="n">
         <v>119</v>
       </c>
@@ -9439,7 +9450,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56">
       <c r="A56" s="15" t="n">
         <v>46297</v>
       </c>
@@ -9486,7 +9497,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57">
       <c r="A57" s="15" t="n">
         <v>46298</v>
       </c>
@@ -9533,7 +9544,7 @@
         <v>326.9</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58">
       <c r="A58" s="15" t="n">
         <v>46300</v>
       </c>
@@ -9580,7 +9591,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59">
       <c r="A59" s="15" t="n">
         <v>46301</v>
       </c>
@@ -9627,7 +9638,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60">
       <c r="A60" s="15" t="n">
         <v>46302</v>
       </c>
@@ -9674,7 +9685,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61">
       <c r="A61" s="15" t="n">
         <v>46303</v>
       </c>
@@ -9721,7 +9732,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62">
       <c r="A62" s="15" t="n">
         <v>46304</v>
       </c>
@@ -9768,7 +9779,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63">
       <c r="A63" s="15" t="n">
         <v>46307</v>
       </c>
@@ -9815,7 +9826,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64">
       <c r="A64" s="15" t="n">
         <v>46308</v>
       </c>
@@ -9862,7 +9873,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65">
       <c r="A65" s="15" t="n">
         <v>46309</v>
       </c>
@@ -9909,7 +9920,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66">
       <c r="A66" s="15" t="n">
         <v>46310</v>
       </c>
@@ -9956,7 +9967,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67">
       <c r="A67" s="15" t="n">
         <v>46311</v>
       </c>
@@ -10003,7 +10014,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68">
       <c r="A68" s="15" t="n">
         <v>46313</v>
       </c>
@@ -10050,7 +10061,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69">
       <c r="A69" s="15" t="n">
         <v>46315</v>
       </c>
@@ -10097,7 +10108,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70">
       <c r="A70" s="15" t="n">
         <v>46316</v>
       </c>
@@ -10144,7 +10155,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71">
       <c r="A71" s="15" t="n">
         <v>46317</v>
       </c>
@@ -10191,121 +10202,227 @@
         <v>311.2</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>910</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>874</v>
+      </c>
+      <c r="E72" s="19" t="n">
+        <v>39.67</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G72" s="16" t="n">
+        <v>668</v>
+      </c>
+      <c r="H72" s="16" t="n">
+        <v>417</v>
+      </c>
+      <c r="I72" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="J72" s="19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K72" s="16" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L72" s="19" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M72" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="N72" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O72" s="19" t="n">
+        <v>310.4</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="15"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Nguồn: Audit/data/rollup.json · 64 ngày · 11 chỉ số</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>grain →</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Health score</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>On-page / Meta</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Số trang crawl</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Performance / TTFB</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Sitemap — số URL</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Structured data</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>TTFB trung bình (ms)</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>TTFB trung vị (ms)</t>
+        </is>
+      </c>
+      <c r="L5" s="14" t="inlineStr">
+        <is>
+          <t>Tổng số từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="15" t="n">
         <v>46230</v>
       </c>
@@ -10333,11 +10450,11 @@
       <c r="I6" s="16" t="n">
         <v>72</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+    </row>
+    <row r="7">
       <c r="A7" s="15" t="n">
         <v>46231</v>
       </c>
@@ -10365,11 +10482,11 @@
       <c r="I7" s="16" t="n">
         <v>74</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
+    </row>
+    <row r="8">
       <c r="A8" s="15" t="n">
         <v>46232</v>
       </c>
@@ -10397,11 +10514,11 @@
       <c r="I8" s="16" t="n">
         <v>74</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+    </row>
+    <row r="9">
       <c r="A9" s="15" t="n">
         <v>46233</v>
       </c>
@@ -10429,11 +10546,11 @@
       <c r="I9" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="n"/>
+      <c r="L9" s="16" t="n"/>
+    </row>
+    <row r="10">
       <c r="A10" s="15" t="n">
         <v>46234</v>
       </c>
@@ -10461,11 +10578,11 @@
       <c r="I10" s="16" t="n">
         <v>82</v>
       </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="16" t="n"/>
+    </row>
+    <row r="11">
       <c r="A11" s="15" t="n">
         <v>46237</v>
       </c>
@@ -10493,11 +10610,11 @@
       <c r="I11" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+    </row>
+    <row r="12">
       <c r="A12" s="15" t="n">
         <v>46238</v>
       </c>
@@ -10525,11 +10642,11 @@
       <c r="I12" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+    </row>
+    <row r="13">
       <c r="A13" s="15" t="n">
         <v>46239</v>
       </c>
@@ -10557,11 +10674,11 @@
       <c r="I13" s="16" t="n">
         <v>81</v>
       </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+    </row>
+    <row r="14">
       <c r="A14" s="15" t="n">
         <v>46241</v>
       </c>
@@ -10589,11 +10706,11 @@
       <c r="I14" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+    </row>
+    <row r="15">
       <c r="A15" s="15" t="n">
         <v>46244</v>
       </c>
@@ -10621,11 +10738,11 @@
       <c r="I15" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+    </row>
+    <row r="16">
       <c r="A16" s="15" t="n">
         <v>46245</v>
       </c>
@@ -10653,11 +10770,11 @@
       <c r="I16" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+    </row>
+    <row r="17">
       <c r="A17" s="15" t="n">
         <v>46246</v>
       </c>
@@ -10688,10 +10805,10 @@
       <c r="J17" s="16" t="n">
         <v>697</v>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+    </row>
+    <row r="18">
       <c r="A18" s="15" t="n">
         <v>46247</v>
       </c>
@@ -10722,10 +10839,10 @@
       <c r="J18" s="16" t="n">
         <v>674</v>
       </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="16" t="n"/>
+    </row>
+    <row r="19">
       <c r="A19" s="15" t="n">
         <v>46248</v>
       </c>
@@ -10756,10 +10873,10 @@
       <c r="J19" s="16" t="n">
         <v>618</v>
       </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K19" s="16" t="n"/>
+      <c r="L19" s="16" t="n"/>
+    </row>
+    <row r="20">
       <c r="A20" s="15" t="n">
         <v>46251</v>
       </c>
@@ -10790,10 +10907,10 @@
       <c r="J20" s="16" t="n">
         <v>671</v>
       </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+    </row>
+    <row r="21">
       <c r="A21" s="15" t="n">
         <v>46252</v>
       </c>
@@ -10824,10 +10941,10 @@
       <c r="J21" s="16" t="n">
         <v>761</v>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K21" s="16" t="n"/>
+      <c r="L21" s="16" t="n"/>
+    </row>
+    <row r="22">
       <c r="A22" s="15" t="n">
         <v>46253</v>
       </c>
@@ -10858,10 +10975,10 @@
       <c r="J22" s="16" t="n">
         <v>755</v>
       </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K22" s="16" t="n"/>
+      <c r="L22" s="16" t="n"/>
+    </row>
+    <row r="23">
       <c r="A23" s="15" t="n">
         <v>46254</v>
       </c>
@@ -10892,10 +11009,10 @@
       <c r="J23" s="16" t="n">
         <v>821</v>
       </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K23" s="16" t="n"/>
+      <c r="L23" s="16" t="n"/>
+    </row>
+    <row r="24">
       <c r="A24" s="15" t="n">
         <v>46255</v>
       </c>
@@ -10926,10 +11043,10 @@
       <c r="J24" s="16" t="n">
         <v>757</v>
       </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K24" s="16" t="n"/>
+      <c r="L24" s="16" t="n"/>
+    </row>
+    <row r="25">
       <c r="A25" s="15" t="n">
         <v>46258</v>
       </c>
@@ -10960,10 +11077,10 @@
       <c r="J25" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
+    </row>
+    <row r="26">
       <c r="A26" s="15" t="n">
         <v>46259</v>
       </c>
@@ -10994,10 +11111,10 @@
       <c r="J26" s="16" t="n">
         <v>656</v>
       </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="16" t="n"/>
+      <c r="L26" s="16" t="n"/>
+    </row>
+    <row r="27">
       <c r="A27" s="15" t="n">
         <v>46260</v>
       </c>
@@ -11028,10 +11145,10 @@
       <c r="J27" s="16" t="n">
         <v>720</v>
       </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" s="16" t="n"/>
+      <c r="L27" s="16" t="n"/>
+    </row>
+    <row r="28">
       <c r="A28" s="15" t="n">
         <v>46261</v>
       </c>
@@ -11062,10 +11179,10 @@
       <c r="J28" s="16" t="n">
         <v>888</v>
       </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="16" t="n"/>
+    </row>
+    <row r="29">
       <c r="A29" s="15" t="n">
         <v>46262</v>
       </c>
@@ -11096,10 +11213,10 @@
       <c r="J29" s="16" t="n">
         <v>862</v>
       </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" s="16" t="n"/>
+      <c r="L29" s="16" t="n"/>
+    </row>
+    <row r="30">
       <c r="A30" s="15" t="n">
         <v>46268</v>
       </c>
@@ -11130,10 +11247,10 @@
       <c r="J30" s="16" t="n">
         <v>924</v>
       </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n"/>
+    </row>
+    <row r="31">
       <c r="A31" s="15" t="n">
         <v>46269</v>
       </c>
@@ -11149,23 +11266,23 @@
       <c r="E31" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="F31" s="16"/>
+      <c r="F31" s="16" t="n"/>
       <c r="G31" s="16" t="n">
         <v>85</v>
       </c>
-      <c r="H31" s="16"/>
+      <c r="H31" s="16" t="n"/>
       <c r="I31" s="16" t="n">
         <v>96</v>
       </c>
       <c r="J31" s="16" t="n">
         <v>932</v>
       </c>
-      <c r="K31" s="16"/>
+      <c r="K31" s="16" t="n"/>
       <c r="L31" s="16" t="n">
         <v>204862</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32">
       <c r="A32" s="15" t="n">
         <v>46272</v>
       </c>
@@ -11187,19 +11304,19 @@
       <c r="G32" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="H32" s="16"/>
+      <c r="H32" s="16" t="n"/>
       <c r="I32" s="16" t="n">
         <v>96</v>
       </c>
       <c r="J32" s="16" t="n">
         <v>785</v>
       </c>
-      <c r="K32" s="16"/>
+      <c r="K32" s="16" t="n"/>
       <c r="L32" s="16" t="n">
         <v>210673</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33">
       <c r="A33" s="15" t="n">
         <v>46273</v>
       </c>
@@ -11221,19 +11338,19 @@
       <c r="G33" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="H33" s="16"/>
+      <c r="H33" s="16" t="n"/>
       <c r="I33" s="16" t="n">
         <v>95</v>
       </c>
       <c r="J33" s="16" t="n">
         <v>877</v>
       </c>
-      <c r="K33" s="16"/>
+      <c r="K33" s="16" t="n"/>
       <c r="L33" s="16" t="n">
         <v>213007</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34">
       <c r="A34" s="15" t="n">
         <v>46274</v>
       </c>
@@ -11255,7 +11372,7 @@
       <c r="G34" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="H34" s="16"/>
+      <c r="H34" s="16" t="n"/>
       <c r="I34" s="16" t="n">
         <v>94</v>
       </c>
@@ -11269,7 +11386,7 @@
         <v>215236</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35">
       <c r="A35" s="15" t="n">
         <v>46275</v>
       </c>
@@ -11307,7 +11424,7 @@
         <v>216434</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36">
       <c r="A36" s="15" t="n">
         <v>46276</v>
       </c>
@@ -11345,7 +11462,7 @@
         <v>219115</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37">
       <c r="A37" s="15" t="n">
         <v>46279</v>
       </c>
@@ -11383,7 +11500,7 @@
         <v>224048</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38">
       <c r="A38" s="15" t="n">
         <v>46280</v>
       </c>
@@ -11421,7 +11538,7 @@
         <v>218216</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39">
       <c r="A39" s="15" t="n">
         <v>46281</v>
       </c>
@@ -11459,7 +11576,7 @@
         <v>222873</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40">
       <c r="A40" s="15" t="n">
         <v>46282</v>
       </c>
@@ -11497,7 +11614,7 @@
         <v>222873</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41">
       <c r="A41" s="15" t="n">
         <v>46283</v>
       </c>
@@ -11535,7 +11652,7 @@
         <v>224773</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42">
       <c r="A42" s="15" t="n">
         <v>46284</v>
       </c>
@@ -11573,7 +11690,7 @@
         <v>229319</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43">
       <c r="A43" s="15" t="n">
         <v>46286</v>
       </c>
@@ -11611,7 +11728,7 @@
         <v>231563</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44">
       <c r="A44" s="15" t="n">
         <v>46287</v>
       </c>
@@ -11649,7 +11766,7 @@
         <v>234251</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45">
       <c r="A45" s="15" t="n">
         <v>46288</v>
       </c>
@@ -11687,7 +11804,7 @@
         <v>236840</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46">
       <c r="A46" s="15" t="n">
         <v>46289</v>
       </c>
@@ -11725,7 +11842,7 @@
         <v>239199</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47">
       <c r="A47" s="15" t="n">
         <v>46290</v>
       </c>
@@ -11763,7 +11880,7 @@
         <v>239208</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48">
       <c r="A48" s="15" t="n">
         <v>46291</v>
       </c>
@@ -11801,7 +11918,7 @@
         <v>239577</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49">
       <c r="A49" s="15" t="n">
         <v>46293</v>
       </c>
@@ -11839,7 +11956,7 @@
         <v>239577</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50">
       <c r="A50" s="15" t="n">
         <v>46294</v>
       </c>
@@ -11877,7 +11994,7 @@
         <v>241329</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51">
       <c r="A51" s="15" t="n">
         <v>46295</v>
       </c>
@@ -11915,7 +12032,7 @@
         <v>241329</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52">
       <c r="A52" s="15" t="n">
         <v>46296</v>
       </c>
@@ -11953,7 +12070,7 @@
         <v>241211</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53">
       <c r="A53" s="15" t="n">
         <v>46297</v>
       </c>
@@ -11991,7 +12108,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54">
       <c r="A54" s="15" t="n">
         <v>46298</v>
       </c>
@@ -12029,7 +12146,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55">
       <c r="A55" s="15" t="n">
         <v>46300</v>
       </c>
@@ -12067,7 +12184,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56">
       <c r="A56" s="15" t="n">
         <v>46301</v>
       </c>
@@ -12105,7 +12222,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57">
       <c r="A57" s="15" t="n">
         <v>46302</v>
       </c>
@@ -12143,7 +12260,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58">
       <c r="A58" s="15" t="n">
         <v>46303</v>
       </c>
@@ -12181,7 +12298,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59">
       <c r="A59" s="15" t="n">
         <v>46304</v>
       </c>
@@ -12219,7 +12336,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60">
       <c r="A60" s="15" t="n">
         <v>46307</v>
       </c>
@@ -12257,7 +12374,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61">
       <c r="A61" s="15" t="n">
         <v>46308</v>
       </c>
@@ -12295,7 +12412,7 @@
         <v>242620</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62">
       <c r="A62" s="15" t="n">
         <v>46309</v>
       </c>
@@ -12333,7 +12450,7 @@
         <v>241898</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63">
       <c r="A63" s="15" t="n">
         <v>46310</v>
       </c>
@@ -12371,7 +12488,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64">
       <c r="A64" s="15" t="n">
         <v>46311</v>
       </c>
@@ -12409,7 +12526,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65">
       <c r="A65" s="15" t="n">
         <v>46313</v>
       </c>
@@ -12447,7 +12564,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66">
       <c r="A66" s="15" t="n">
         <v>46315</v>
       </c>
@@ -12485,7 +12602,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67">
       <c r="A67" s="15" t="n">
         <v>46316</v>
       </c>
@@ -12523,7 +12640,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68">
       <c r="A68" s="15" t="n">
         <v>46317</v>
       </c>
@@ -12561,1164 +12678,1342 @@
         <v>243021</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="15" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B69" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F69" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H69" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I69" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v>310.4</v>
+      </c>
+      <c r="K69" s="16" t="n">
+        <v>256</v>
+      </c>
+      <c r="L69" s="16" t="n">
+        <v>243401</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="13"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v>125</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v>195</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>160</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v>106</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v>147</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>354</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>333</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v>3579</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v>4978</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>4776</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>3032</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v>189</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v>314</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>425</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>441</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v>51</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v>69</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>25</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v>275</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v>387</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>177</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v>869</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v>1161</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v>2465</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H113,'Social — theo ngày'!$A$6:$A$113,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$113,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B11</f>
-        <v>115</v>
-      </c>
-      <c r="C17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B32</f>
-        <v>115</v>
-      </c>
-      <c r="D17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B54</f>
-        <v>116</v>
-      </c>
-      <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B71</f>
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C11</f>
-        <v>130</v>
-      </c>
-      <c r="C18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C32</f>
-        <v>184</v>
-      </c>
-      <c r="D18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C54</f>
-        <v>141</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C71</f>
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D11</f>
-        <v>3635</v>
-      </c>
-      <c r="C19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D32</f>
-        <v>4735</v>
-      </c>
-      <c r="D19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D54</f>
-        <v>4519</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D71</f>
-        <v>4026</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E11</f>
-        <v>171</v>
-      </c>
-      <c r="C20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E32</f>
-        <v>280</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E54</f>
-        <v>422</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E71</f>
-        <v>517</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F11</f>
-        <v>33</v>
-      </c>
-      <c r="C21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F32</f>
-        <v>47</v>
-      </c>
-      <c r="D21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F54</f>
-        <v>49</v>
-      </c>
-      <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F71</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G11</f>
-        <v>49</v>
-      </c>
-      <c r="C22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G32</f>
-        <v>68</v>
-      </c>
-      <c r="D22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G54</f>
-        <v>20</v>
-      </c>
-      <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G71</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H11</f>
-        <v>192</v>
-      </c>
-      <c r="C23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H32</f>
-        <v>275</v>
-      </c>
-      <c r="D23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H54</f>
-        <v>87</v>
-      </c>
-      <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H71</f>
-        <v>286</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I11</f>
-        <v>855</v>
-      </c>
-      <c r="C24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I32</f>
-        <v>1039</v>
-      </c>
-      <c r="D24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I54</f>
-        <v>2258</v>
-      </c>
-      <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I71</f>
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J11</f>
-        <v>55</v>
-      </c>
-      <c r="C25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J32</f>
-        <v>100</v>
-      </c>
-      <c r="D25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J54</f>
-        <v>102</v>
-      </c>
-      <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J71</f>
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K11</f>
-        <v>1351</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K32</f>
-        <v>1691</v>
-      </c>
-      <c r="D26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K54</f>
-        <v>1193</v>
-      </c>
-      <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K71</f>
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L11</f>
-        <v>39</v>
-      </c>
-      <c r="C27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L32</f>
-        <v>127</v>
-      </c>
-      <c r="D27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L54</f>
-        <v>24</v>
-      </c>
-      <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L71</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M11</f>
-        <v>56</v>
-      </c>
-      <c r="C28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M32</f>
-        <v>86</v>
-      </c>
-      <c r="D28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M54</f>
-        <v>36</v>
-      </c>
-      <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M71</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N11</f>
-        <v>4</v>
-      </c>
-      <c r="C29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N32</f>
-        <v>4</v>
-      </c>
-      <c r="D29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N54</f>
-        <v>4</v>
-      </c>
-      <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N71</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O11</f>
-        <v>28</v>
-      </c>
-      <c r="C30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O32</f>
-        <v>59</v>
-      </c>
-      <c r="D30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O54</f>
-        <v>634</v>
-      </c>
-      <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O71</f>
-        <v>783</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="24" t="n">
-        <f aca="false">SEO!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="24" t="n">
-        <f aca="false">SEO!B11</f>
-        <v>14</v>
-      </c>
-      <c r="D34" s="24" t="n">
-        <f aca="false">SEO!B30</f>
-        <v>21</v>
-      </c>
-      <c r="E34" s="24" t="n">
-        <f aca="false">SEO!B54</f>
-        <v>16</v>
-      </c>
-      <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B71</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" s="24" t="n">
-        <f aca="false">SEO!C6</f>
-        <v>0</v>
-      </c>
-      <c r="C35" s="24" t="n">
-        <f aca="false">SEO!C11</f>
-        <v>346</v>
-      </c>
-      <c r="D35" s="24" t="n">
-        <f aca="false">SEO!C30</f>
-        <v>364</v>
-      </c>
-      <c r="E35" s="24" t="n">
-        <f aca="false">SEO!C54</f>
-        <v>918</v>
-      </c>
-      <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C71</f>
-        <v>911</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36" s="24" t="n">
-        <f aca="false">SEO!D6</f>
-        <v>244</v>
-      </c>
-      <c r="C36" s="24" t="n">
-        <f aca="false">SEO!D11</f>
-        <v>341</v>
-      </c>
-      <c r="D36" s="24" t="n">
-        <f aca="false">SEO!D30</f>
-        <v>349</v>
-      </c>
-      <c r="E36" s="24" t="n">
-        <f aca="false">SEO!D54</f>
-        <v>882</v>
-      </c>
-      <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D71</f>
-        <v>875</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="24" t="n">
-        <f aca="false">SEO!E6</f>
-        <v>18.9</v>
-      </c>
-      <c r="C37" s="24" t="n">
-        <f aca="false">SEO!E11</f>
-        <v>66.7</v>
-      </c>
-      <c r="D37" s="24" t="n">
-        <f aca="false">SEO!E30</f>
-        <v>42.93</v>
-      </c>
-      <c r="E37" s="24" t="n">
-        <f aca="false">SEO!E54</f>
-        <v>33.99</v>
-      </c>
-      <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E71</f>
-        <v>39.58</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="24" t="n">
-        <f aca="false">SEO!F6</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="24" t="n">
-        <f aca="false">SEO!F11</f>
-        <v>42</v>
-      </c>
-      <c r="D38" s="24" t="n">
-        <f aca="false">SEO!F30</f>
-        <v>7</v>
-      </c>
-      <c r="E38" s="24" t="n">
-        <f aca="false">SEO!F54</f>
-        <v>4</v>
-      </c>
-      <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F71</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="24" t="n">
-        <f aca="false">SEO!G6</f>
-        <v>322</v>
-      </c>
-      <c r="C39" s="24" t="n">
-        <f aca="false">SEO!G11</f>
-        <v>405</v>
-      </c>
-      <c r="D39" s="24" t="n">
-        <f aca="false">SEO!G30</f>
-        <v>375</v>
-      </c>
-      <c r="E39" s="24" t="n">
-        <f aca="false">SEO!G54</f>
-        <v>559</v>
-      </c>
-      <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G71</f>
-        <v>672</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="24" t="n">
-        <f aca="false">SEO!H6</f>
-        <v>205</v>
-      </c>
-      <c r="C40" s="24" t="n">
-        <f aca="false">SEO!H11</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="24" t="n">
-        <f aca="false">SEO!H30</f>
-        <v>204</v>
-      </c>
-      <c r="E40" s="24" t="n">
-        <f aca="false">SEO!H54</f>
-        <v>394</v>
-      </c>
-      <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H71</f>
-        <v>422</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="24" t="n">
-        <f aca="false">SEO!I6</f>
-        <v>47</v>
-      </c>
-      <c r="C41" s="24" t="n">
-        <f aca="false">SEO!I11</f>
-        <v>67</v>
-      </c>
-      <c r="D41" s="24" t="n">
-        <f aca="false">SEO!I30</f>
-        <v>67</v>
-      </c>
-      <c r="E41" s="24" t="n">
-        <f aca="false">SEO!I54</f>
-        <v>30</v>
-      </c>
-      <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I71</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" s="24" t="n">
-        <f aca="false">SEO!J6</f>
-        <v>8</v>
-      </c>
-      <c r="C42" s="24" t="n">
-        <f aca="false">SEO!J11</f>
-        <v>6.5</v>
-      </c>
-      <c r="D42" s="24" t="n">
-        <f aca="false">SEO!J30</f>
-        <v>3.8</v>
-      </c>
-      <c r="E42" s="24" t="n">
-        <f aca="false">SEO!J54</f>
-        <v>2.8</v>
-      </c>
-      <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J71</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="24" t="n">
-        <f aca="false">SEO!K6</f>
-        <v>587</v>
-      </c>
-      <c r="C43" s="24" t="n">
-        <f aca="false">SEO!K11</f>
-        <v>1032</v>
-      </c>
-      <c r="D43" s="24" t="n">
-        <f aca="false">SEO!K30</f>
-        <v>1757</v>
-      </c>
-      <c r="E43" s="24" t="n">
-        <f aca="false">SEO!K54</f>
-        <v>1056</v>
-      </c>
-      <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K71</f>
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="24" t="n">
-        <f aca="false">SEO!L6</f>
-        <v>13.8</v>
-      </c>
-      <c r="C44" s="24" t="n">
-        <f aca="false">SEO!L11</f>
-        <v>24.1</v>
-      </c>
-      <c r="D44" s="24" t="n">
-        <f aca="false">SEO!L30</f>
-        <v>29.4</v>
-      </c>
-      <c r="E44" s="24" t="n">
-        <f aca="false">SEO!L54</f>
-        <v>25.8</v>
-      </c>
-      <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L71</f>
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B45" s="24" t="n">
-        <f aca="false">SEO!M6</f>
-        <v>0</v>
-      </c>
-      <c r="C45" s="24" t="n">
-        <f aca="false">SEO!M11</f>
-        <v>92</v>
-      </c>
-      <c r="D45" s="24" t="n">
-        <f aca="false">SEO!M30</f>
-        <v>151</v>
-      </c>
-      <c r="E45" s="24" t="n">
-        <f aca="false">SEO!M54</f>
-        <v>80</v>
-      </c>
-      <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M71</f>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="24" t="n">
-        <f aca="false">SEO!N6</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="24" t="n">
-        <f aca="false">SEO!N11</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="24" t="n">
-        <f aca="false">SEO!N30</f>
-        <v>95</v>
-      </c>
-      <c r="E46" s="24" t="n">
-        <f aca="false">SEO!N54</f>
-        <v>119</v>
-      </c>
-      <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N71</f>
-        <v>119</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B47" s="24" t="n">
-        <f aca="false">SEO!O6</f>
-        <v>0</v>
-      </c>
-      <c r="C47" s="24" t="n">
-        <f aca="false">SEO!O11</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="24" t="n">
-        <f aca="false">SEO!O30</f>
-        <v>1022</v>
-      </c>
-      <c r="E47" s="24" t="n">
-        <f aca="false">SEO!O54</f>
-        <v>342</v>
-      </c>
-      <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O71</f>
-        <v>311.2</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="24" t="n">
-        <f aca="false">Audit!B10</f>
-        <v>77</v>
-      </c>
-      <c r="C51" s="24" t="n">
-        <f aca="false">Audit!B29</f>
-        <v>88</v>
-      </c>
-      <c r="D51" s="24" t="n">
-        <f aca="false">Audit!B51</f>
-        <v>93</v>
-      </c>
-      <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B68</f>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" s="24" t="n">
-        <f aca="false">Audit!C10</f>
-        <v>89</v>
-      </c>
-      <c r="C52" s="24" t="n">
-        <f aca="false">Audit!C29</f>
-        <v>97</v>
-      </c>
-      <c r="D52" s="24" t="n">
-        <f aca="false">Audit!C51</f>
-        <v>98</v>
-      </c>
-      <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C68</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="24" t="n">
-        <f aca="false">Audit!D10</f>
-        <v>84</v>
-      </c>
-      <c r="C53" s="24" t="n">
-        <f aca="false">Audit!D29</f>
-        <v>92</v>
-      </c>
-      <c r="D53" s="24" t="n">
-        <f aca="false">Audit!D51</f>
-        <v>95</v>
-      </c>
-      <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D68</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="24" t="n">
-        <f aca="false">Audit!E10</f>
-        <v>76</v>
-      </c>
-      <c r="C54" s="24" t="n">
-        <f aca="false">Audit!E29</f>
-        <v>91</v>
-      </c>
-      <c r="D54" s="24" t="n">
-        <f aca="false">Audit!E51</f>
-        <v>92</v>
-      </c>
-      <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E68</f>
-        <v>93</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="24" t="n">
-        <f aca="false">Audit!F10</f>
-        <v>68</v>
-      </c>
-      <c r="C55" s="24" t="n">
-        <f aca="false">Audit!F29</f>
-        <v>91</v>
-      </c>
-      <c r="D55" s="24" t="n">
-        <f aca="false">Audit!F51</f>
-        <v>118</v>
-      </c>
-      <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F68</f>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B56" s="24" t="n">
-        <f aca="false">Audit!G10</f>
-        <v>91</v>
-      </c>
-      <c r="C56" s="24" t="n">
-        <f aca="false">Audit!G29</f>
-        <v>88</v>
-      </c>
-      <c r="D56" s="24" t="n">
-        <f aca="false">Audit!G51</f>
-        <v>98</v>
-      </c>
-      <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G68</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57" s="24" t="n">
-        <f aca="false">Audit!H10</f>
-        <v>67</v>
-      </c>
-      <c r="C57" s="24" t="n">
-        <f aca="false">Audit!H29</f>
-        <v>92</v>
-      </c>
-      <c r="D57" s="24" t="n">
-        <f aca="false">Audit!H51</f>
-        <v>119</v>
-      </c>
-      <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H68</f>
-        <v>119</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58" s="24" t="n">
-        <f aca="false">Audit!I10</f>
-        <v>82</v>
-      </c>
-      <c r="C58" s="24" t="n">
-        <f aca="false">Audit!I29</f>
-        <v>96</v>
-      </c>
-      <c r="D58" s="24" t="n">
-        <f aca="false">Audit!I51</f>
-        <v>92</v>
-      </c>
-      <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I68</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" s="24" t="n">
-        <f aca="false">Audit!J10</f>
-        <v>0</v>
-      </c>
-      <c r="C59" s="24" t="n">
-        <f aca="false">Audit!J29</f>
-        <v>862</v>
-      </c>
-      <c r="D59" s="24" t="n">
-        <f aca="false">Audit!J51</f>
-        <v>342</v>
-      </c>
-      <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J68</f>
-        <v>311.2</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B60" s="24" t="n">
-        <f aca="false">Audit!K10</f>
-        <v>0</v>
-      </c>
-      <c r="C60" s="24" t="n">
-        <f aca="false">Audit!K29</f>
-        <v>0</v>
-      </c>
-      <c r="D60" s="24" t="n">
-        <f aca="false">Audit!K51</f>
-        <v>276</v>
-      </c>
-      <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K68</f>
-        <v>255</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="B61" s="24" t="n">
-        <f aca="false">Audit!L10</f>
-        <v>0</v>
-      </c>
-      <c r="C61" s="24" t="n">
-        <f aca="false">Audit!L29</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="24" t="n">
-        <f aca="false">Audit!L51</f>
-        <v>241329</v>
-      </c>
-      <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L68</f>
-        <v>243021</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tổng hợp theo tháng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Mọi ô dưới đây là CÔNG THỨC trỏ về các sheet dữ liệu — sửa dữ liệu thì số này tự đổi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ chuỗi grain "day" mới được CỘNG (SUMIFS). window28 và state lấy GIÁ TRỊ NGÀY QUÉT CUỐI CÙNG của tháng (INDEX).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>CỘNG ĐƯỢC — số theo ngày thật (Social)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>FB — tương tác/ngày</t>
+        </is>
+      </c>
+      <c r="B7" s="16">
+        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v/>
+      </c>
+      <c r="C7" s="16">
+        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>FB — view 3 giây/ngày</t>
+        </is>
+      </c>
+      <c r="B8" s="16">
+        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v/>
+      </c>
+      <c r="C8" s="16">
+        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>FB — views/ngày</t>
+        </is>
+      </c>
+      <c r="B9" s="16">
+        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v/>
+      </c>
+      <c r="C9" s="16">
+        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>FB — lượt ghé/ngày</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v/>
+      </c>
+      <c r="C10" s="16">
+        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>IG — tương tác/ngày</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v/>
+      </c>
+      <c r="C11" s="16">
+        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>IG — reach/ngày</t>
+        </is>
+      </c>
+      <c r="B12" s="16">
+        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v/>
+      </c>
+      <c r="C12" s="16">
+        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>IG — views/ngày</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>KHÔNG CỘNG — Social — 28 ngày (lấy ngày quét cuối tháng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>FB — followers</t>
+        </is>
+      </c>
+      <c r="B17" s="24">
+        <f>'Social — 28 ngày'!B11</f>
+        <v/>
+      </c>
+      <c r="C17" s="24">
+        <f>'Social — 28 ngày'!B32</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>'Social — 28 ngày'!B54</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>'Social — 28 ngày'!B72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>FB — tương tác (28n)</t>
+        </is>
+      </c>
+      <c r="B18" s="24">
+        <f>'Social — 28 ngày'!C11</f>
+        <v/>
+      </c>
+      <c r="C18" s="24">
+        <f>'Social — 28 ngày'!C32</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>'Social — 28 ngày'!C54</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>'Social — 28 ngày'!C72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>FB — views (28n)</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>'Social — 28 ngày'!D11</f>
+        <v/>
+      </c>
+      <c r="C19" s="24">
+        <f>'Social — 28 ngày'!D32</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>'Social — 28 ngày'!D54</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>'Social — 28 ngày'!D72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>FB — lượt ghé (28n)</t>
+        </is>
+      </c>
+      <c r="B20" s="24">
+        <f>'Social — 28 ngày'!E11</f>
+        <v/>
+      </c>
+      <c r="C20" s="24">
+        <f>'Social — 28 ngày'!E32</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>'Social — 28 ngày'!E54</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>'Social — 28 ngày'!E72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>IG — followers</t>
+        </is>
+      </c>
+      <c r="B21" s="24">
+        <f>'Social — 28 ngày'!F11</f>
+        <v/>
+      </c>
+      <c r="C21" s="24">
+        <f>'Social — 28 ngày'!F32</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>'Social — 28 ngày'!F54</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>'Social — 28 ngày'!F72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>IG — tương tác (28n)</t>
+        </is>
+      </c>
+      <c r="B22" s="24">
+        <f>'Social — 28 ngày'!G11</f>
+        <v/>
+      </c>
+      <c r="C22" s="24">
+        <f>'Social — 28 ngày'!G32</f>
+        <v/>
+      </c>
+      <c r="D22" s="24">
+        <f>'Social — 28 ngày'!G54</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>'Social — 28 ngày'!G72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>IG — reach (28n)</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>'Social — 28 ngày'!H11</f>
+        <v/>
+      </c>
+      <c r="C23" s="24">
+        <f>'Social — 28 ngày'!H32</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>'Social — 28 ngày'!H54</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>'Social — 28 ngày'!H72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>IG — views (28n)</t>
+        </is>
+      </c>
+      <c r="B24" s="24">
+        <f>'Social — 28 ngày'!I11</f>
+        <v/>
+      </c>
+      <c r="C24" s="24">
+        <f>'Social — 28 ngày'!I32</f>
+        <v/>
+      </c>
+      <c r="D24" s="24">
+        <f>'Social — 28 ngày'!I54</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>'Social — 28 ngày'!I72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>LinkedIn — followers</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>'Social — 28 ngày'!J11</f>
+        <v/>
+      </c>
+      <c r="C25" s="24">
+        <f>'Social — 28 ngày'!J32</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>'Social — 28 ngày'!J54</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>'Social — 28 ngày'!J72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>LinkedIn — impressions (28n)</t>
+        </is>
+      </c>
+      <c r="B26" s="24">
+        <f>'Social — 28 ngày'!K11</f>
+        <v/>
+      </c>
+      <c r="C26" s="24">
+        <f>'Social — 28 ngày'!K32</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>'Social — 28 ngày'!K54</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>'Social — 28 ngày'!K72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>LinkedIn — lượt xem trang (28n)</t>
+        </is>
+      </c>
+      <c r="B27" s="24">
+        <f>'Social — 28 ngày'!L11</f>
+        <v/>
+      </c>
+      <c r="C27" s="24">
+        <f>'Social — 28 ngày'!L32</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>'Social — 28 ngày'!L54</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>'Social — 28 ngày'!L72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>LinkedIn — reactions (28n)</t>
+        </is>
+      </c>
+      <c r="B28" s="24">
+        <f>'Social — 28 ngày'!M11</f>
+        <v/>
+      </c>
+      <c r="C28" s="24">
+        <f>'Social — 28 ngày'!M32</f>
+        <v/>
+      </c>
+      <c r="D28" s="24">
+        <f>'Social — 28 ngày'!M54</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>'Social — 28 ngày'!M72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>YouTube — subscribers</t>
+        </is>
+      </c>
+      <c r="B29" s="24">
+        <f>'Social — 28 ngày'!N11</f>
+        <v/>
+      </c>
+      <c r="C29" s="24">
+        <f>'Social — 28 ngày'!N32</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>'Social — 28 ngày'!N54</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>'Social — 28 ngày'!N72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>YouTube — views (28n)</t>
+        </is>
+      </c>
+      <c r="B30" s="24">
+        <f>'Social — 28 ngày'!O11</f>
+        <v/>
+      </c>
+      <c r="C30" s="24">
+        <f>'Social — 28 ngày'!O32</f>
+        <v/>
+      </c>
+      <c r="D30" s="24">
+        <f>'Social — 28 ngày'!O54</f>
+        <v/>
+      </c>
+      <c r="E30" s="24">
+        <f>'Social — 28 ngày'!O72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>KHÔNG CỘNG — SEO (lấy ngày quét cuối tháng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Ahrefs — trích dẫn AI</t>
+        </is>
+      </c>
+      <c r="B34" s="24">
+        <f>'SEO'!B6</f>
+        <v/>
+      </c>
+      <c r="C34" s="24">
+        <f>'SEO'!B11</f>
+        <v/>
+      </c>
+      <c r="D34" s="24">
+        <f>'SEO'!B30</f>
+        <v/>
+      </c>
+      <c r="E34" s="24">
+        <f>'SEO'!B54</f>
+        <v/>
+      </c>
+      <c r="F34" s="24">
+        <f>'SEO'!B72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Ahrefs — backlinks</t>
+        </is>
+      </c>
+      <c r="B35" s="24">
+        <f>'SEO'!C6</f>
+        <v/>
+      </c>
+      <c r="C35" s="24">
+        <f>'SEO'!C11</f>
+        <v/>
+      </c>
+      <c r="D35" s="24">
+        <f>'SEO'!C30</f>
+        <v/>
+      </c>
+      <c r="E35" s="24">
+        <f>'SEO'!C54</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>'SEO'!C72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Ahrefs — referring domains</t>
+        </is>
+      </c>
+      <c r="B36" s="24">
+        <f>'SEO'!D6</f>
+        <v/>
+      </c>
+      <c r="C36" s="24">
+        <f>'SEO'!D11</f>
+        <v/>
+      </c>
+      <c r="D36" s="24">
+        <f>'SEO'!D30</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>'SEO'!D54</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>'SEO'!D72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>GA4 — engagement %</t>
+        </is>
+      </c>
+      <c r="B37" s="24">
+        <f>'SEO'!E6</f>
+        <v/>
+      </c>
+      <c r="C37" s="24">
+        <f>'SEO'!E11</f>
+        <v/>
+      </c>
+      <c r="D37" s="24">
+        <f>'SEO'!E30</f>
+        <v/>
+      </c>
+      <c r="E37" s="24">
+        <f>'SEO'!E54</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>'SEO'!E72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>GA4 — key events</t>
+        </is>
+      </c>
+      <c r="B38" s="24">
+        <f>'SEO'!F6</f>
+        <v/>
+      </c>
+      <c r="C38" s="24">
+        <f>'SEO'!F11</f>
+        <v/>
+      </c>
+      <c r="D38" s="24">
+        <f>'SEO'!F30</f>
+        <v/>
+      </c>
+      <c r="E38" s="24">
+        <f>'SEO'!F54</f>
+        <v/>
+      </c>
+      <c r="F38" s="24">
+        <f>'SEO'!F72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>GA4 — sessions</t>
+        </is>
+      </c>
+      <c r="B39" s="24">
+        <f>'SEO'!G6</f>
+        <v/>
+      </c>
+      <c r="C39" s="24">
+        <f>'SEO'!G11</f>
+        <v/>
+      </c>
+      <c r="D39" s="24">
+        <f>'SEO'!G30</f>
+        <v/>
+      </c>
+      <c r="E39" s="24">
+        <f>'SEO'!G54</f>
+        <v/>
+      </c>
+      <c r="F39" s="24">
+        <f>'SEO'!G72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>GA4 — users</t>
+        </is>
+      </c>
+      <c r="B40" s="24">
+        <f>'SEO'!H6</f>
+        <v/>
+      </c>
+      <c r="C40" s="24">
+        <f>'SEO'!H11</f>
+        <v/>
+      </c>
+      <c r="D40" s="24">
+        <f>'SEO'!H30</f>
+        <v/>
+      </c>
+      <c r="E40" s="24">
+        <f>'SEO'!H54</f>
+        <v/>
+      </c>
+      <c r="F40" s="24">
+        <f>'SEO'!H72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>GSC — clicks</t>
+        </is>
+      </c>
+      <c r="B41" s="24">
+        <f>'SEO'!I6</f>
+        <v/>
+      </c>
+      <c r="C41" s="24">
+        <f>'SEO'!I11</f>
+        <v/>
+      </c>
+      <c r="D41" s="24">
+        <f>'SEO'!I30</f>
+        <v/>
+      </c>
+      <c r="E41" s="24">
+        <f>'SEO'!I54</f>
+        <v/>
+      </c>
+      <c r="F41" s="24">
+        <f>'SEO'!I72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>GSC — CTR %</t>
+        </is>
+      </c>
+      <c r="B42" s="24">
+        <f>'SEO'!J6</f>
+        <v/>
+      </c>
+      <c r="C42" s="24">
+        <f>'SEO'!J11</f>
+        <v/>
+      </c>
+      <c r="D42" s="24">
+        <f>'SEO'!J30</f>
+        <v/>
+      </c>
+      <c r="E42" s="24">
+        <f>'SEO'!J54</f>
+        <v/>
+      </c>
+      <c r="F42" s="24">
+        <f>'SEO'!J72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>GSC — impressions</t>
+        </is>
+      </c>
+      <c r="B43" s="24">
+        <f>'SEO'!K6</f>
+        <v/>
+      </c>
+      <c r="C43" s="24">
+        <f>'SEO'!K11</f>
+        <v/>
+      </c>
+      <c r="D43" s="24">
+        <f>'SEO'!K30</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>'SEO'!K54</f>
+        <v/>
+      </c>
+      <c r="F43" s="24">
+        <f>'SEO'!K72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>GSC — vị trí TB</t>
+        </is>
+      </c>
+      <c r="B44" s="24">
+        <f>'SEO'!L6</f>
+        <v/>
+      </c>
+      <c r="C44" s="24">
+        <f>'SEO'!L11</f>
+        <v/>
+      </c>
+      <c r="D44" s="24">
+        <f>'SEO'!L30</f>
+        <v/>
+      </c>
+      <c r="E44" s="24">
+        <f>'SEO'!L54</f>
+        <v/>
+      </c>
+      <c r="F44" s="24">
+        <f>'SEO'!L72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>GSC — số truy vấn</t>
+        </is>
+      </c>
+      <c r="B45" s="24">
+        <f>'SEO'!M6</f>
+        <v/>
+      </c>
+      <c r="C45" s="24">
+        <f>'SEO'!M11</f>
+        <v/>
+      </c>
+      <c r="D45" s="24">
+        <f>'SEO'!M30</f>
+        <v/>
+      </c>
+      <c r="E45" s="24">
+        <f>'SEO'!M54</f>
+        <v/>
+      </c>
+      <c r="F45" s="24">
+        <f>'SEO'!M72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Sitemap — số URL</t>
+        </is>
+      </c>
+      <c r="B46" s="24">
+        <f>'SEO'!N6</f>
+        <v/>
+      </c>
+      <c r="C46" s="24">
+        <f>'SEO'!N11</f>
+        <v/>
+      </c>
+      <c r="D46" s="24">
+        <f>'SEO'!N30</f>
+        <v/>
+      </c>
+      <c r="E46" s="24">
+        <f>'SEO'!N54</f>
+        <v/>
+      </c>
+      <c r="F46" s="24">
+        <f>'SEO'!N72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>TTFB trung bình (ms)</t>
+        </is>
+      </c>
+      <c r="B47" s="24">
+        <f>'SEO'!O6</f>
+        <v/>
+      </c>
+      <c r="C47" s="24">
+        <f>'SEO'!O11</f>
+        <v/>
+      </c>
+      <c r="D47" s="24">
+        <f>'SEO'!O30</f>
+        <v/>
+      </c>
+      <c r="E47" s="24">
+        <f>'SEO'!O54</f>
+        <v/>
+      </c>
+      <c r="F47" s="24">
+        <f>'SEO'!O72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>KHÔNG CỘNG — Audit (lấy ngày quét cuối tháng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B51" s="24">
+        <f>'Audit'!B10</f>
+        <v/>
+      </c>
+      <c r="C51" s="24">
+        <f>'Audit'!B29</f>
+        <v/>
+      </c>
+      <c r="D51" s="24">
+        <f>'Audit'!B51</f>
+        <v/>
+      </c>
+      <c r="E51" s="24">
+        <f>'Audit'!B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>Crawlability</t>
+        </is>
+      </c>
+      <c r="B52" s="24">
+        <f>'Audit'!C10</f>
+        <v/>
+      </c>
+      <c r="C52" s="24">
+        <f>'Audit'!C29</f>
+        <v/>
+      </c>
+      <c r="D52" s="24">
+        <f>'Audit'!C51</f>
+        <v/>
+      </c>
+      <c r="E52" s="24">
+        <f>'Audit'!C69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Health score</t>
+        </is>
+      </c>
+      <c r="B53" s="24">
+        <f>'Audit'!D10</f>
+        <v/>
+      </c>
+      <c r="C53" s="24">
+        <f>'Audit'!D29</f>
+        <v/>
+      </c>
+      <c r="D53" s="24">
+        <f>'Audit'!D51</f>
+        <v/>
+      </c>
+      <c r="E53" s="24">
+        <f>'Audit'!D69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>On-page / Meta</t>
+        </is>
+      </c>
+      <c r="B54" s="24">
+        <f>'Audit'!E10</f>
+        <v/>
+      </c>
+      <c r="C54" s="24">
+        <f>'Audit'!E29</f>
+        <v/>
+      </c>
+      <c r="D54" s="24">
+        <f>'Audit'!E51</f>
+        <v/>
+      </c>
+      <c r="E54" s="24">
+        <f>'Audit'!E69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Số trang crawl</t>
+        </is>
+      </c>
+      <c r="B55" s="24">
+        <f>'Audit'!F10</f>
+        <v/>
+      </c>
+      <c r="C55" s="24">
+        <f>'Audit'!F29</f>
+        <v/>
+      </c>
+      <c r="D55" s="24">
+        <f>'Audit'!F51</f>
+        <v/>
+      </c>
+      <c r="E55" s="24">
+        <f>'Audit'!F69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Performance / TTFB</t>
+        </is>
+      </c>
+      <c r="B56" s="24">
+        <f>'Audit'!G10</f>
+        <v/>
+      </c>
+      <c r="C56" s="24">
+        <f>'Audit'!G29</f>
+        <v/>
+      </c>
+      <c r="D56" s="24">
+        <f>'Audit'!G51</f>
+        <v/>
+      </c>
+      <c r="E56" s="24">
+        <f>'Audit'!G69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Sitemap — số URL</t>
+        </is>
+      </c>
+      <c r="B57" s="24">
+        <f>'Audit'!H10</f>
+        <v/>
+      </c>
+      <c r="C57" s="24">
+        <f>'Audit'!H29</f>
+        <v/>
+      </c>
+      <c r="D57" s="24">
+        <f>'Audit'!H51</f>
+        <v/>
+      </c>
+      <c r="E57" s="24">
+        <f>'Audit'!H69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Structured data</t>
+        </is>
+      </c>
+      <c r="B58" s="24">
+        <f>'Audit'!I10</f>
+        <v/>
+      </c>
+      <c r="C58" s="24">
+        <f>'Audit'!I29</f>
+        <v/>
+      </c>
+      <c r="D58" s="24">
+        <f>'Audit'!I51</f>
+        <v/>
+      </c>
+      <c r="E58" s="24">
+        <f>'Audit'!I69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>TTFB trung bình (ms)</t>
+        </is>
+      </c>
+      <c r="B59" s="24">
+        <f>'Audit'!J10</f>
+        <v/>
+      </c>
+      <c r="C59" s="24">
+        <f>'Audit'!J29</f>
+        <v/>
+      </c>
+      <c r="D59" s="24">
+        <f>'Audit'!J51</f>
+        <v/>
+      </c>
+      <c r="E59" s="24">
+        <f>'Audit'!J69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>TTFB trung vị (ms)</t>
+        </is>
+      </c>
+      <c r="B60" s="24">
+        <f>'Audit'!K10</f>
+        <v/>
+      </c>
+      <c r="C60" s="24">
+        <f>'Audit'!K29</f>
+        <v/>
+      </c>
+      <c r="D60" s="24">
+        <f>'Audit'!K51</f>
+        <v/>
+      </c>
+      <c r="E60" s="24">
+        <f>'Audit'!K69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Tổng số từ</t>
+        </is>
+      </c>
+      <c r="B61" s="24">
+        <f>'Audit'!L10</f>
+        <v/>
+      </c>
+      <c r="C61" s="24">
+        <f>'Audit'!L29</f>
+        <v/>
+      </c>
+      <c r="D61" s="24">
+        <f>'Audit'!L51</f>
+        <v/>
+      </c>
+      <c r="E61" s="24">
+        <f>'Audit'!L69</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -1,286 +1,694 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Social — theo ngày" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Social — 28 ngày" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng hợp tháng" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Đọc trước" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Social — theo ngày" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Social — 28 ngày" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="SEO" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Audit" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Tổng hợp tháng" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="97">
+  <si>
+    <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xuất ngày 2026-10-25 · nguồn: data/rollup.json của ba repo báo cáo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File này là gì</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bản xuất phẳng của dữ liệu đã lưu trong ba báo cáo DX Living, để đọc bằng tay và dựng báo cáo tháng. KHÔNG phải nguồn sự thật.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguồn sự thật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data/YYYY-MM-DD.json trong mỗi repo — bất biến, mỗi ngày một file, không bao giờ sửa. File Excel này và dashboard cùng đọc từ data/rollup.json, nên không bao giờ lệch nhau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sửa file này thì sao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không ảnh hưởng gì tới báo cáo. Lần xuất sau sẽ ghi đè.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA LOẠI CHỈ SỐ — đọc kỹ trước khi cộng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số đo của đúng ngày đó. CỘNG DỒN ĐƯỢC. Hiện chỉ Social có (Facebook và Instagram), dựng lại từ chuỗi 28 giá trị lưu sẵn trong mỗi file ngày.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">window28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã là tổng của 28 ngày trước đó. KHÔNG ĐƯỢC CỘNG — hai ngày liền nhau chồng nhau 27 ngày, cộng lại là đếm trùng nhiều lần. Chỉ so đầu kỳ với cuối kỳ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giá trị tại thời điểm quét (điểm số, tốc độ, số follower). Không cộng — lấy giá trị cuối kỳ hoặc trung bình.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ô trống</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày đó không đo chỉ số này. Không suy ra, không điền 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày không quét</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không bao giờ được nội suy. Ví dụ không có bản quét 20/09/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta điều chỉnh số</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Với chuỗi day của Social, mỗi ngày giữ lần đọc MỚI NHẤT — Meta có sửa số về sau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÁC SHEET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social — theo ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112 dòng × 7 chỉ số · 2026-07-05 → 2026-10-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social — 28 ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68 dòng × 14 chỉ số · 2026-07-23 → 2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68 dòng × 14 chỉ số · 2026-06-30 → 2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65 dòng × 11 chỉ số · 2026-07-27 → 2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 112 ngày · 7 chỉ số</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grain →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — tương tác/ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — view 3 giây/ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — views/ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — lượt ghé/ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG — tương tác/ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG — reach/ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG — views/ngày</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 68 ngày · 14 chỉ số</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — followers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — tương tác (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — views (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB — lượt ghé (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG — followers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG — tương tác (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG — reach (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IG — views (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn — followers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn — impressions (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn — lượt xem trang (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedIn — reactions (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouTube — subscribers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouTube — views (28n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 68 ngày · 14 chỉ số</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahrefs — backlinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahrefs — referring domains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA4 — engagement %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA4 — key events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA4 — sessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GA4 — users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSC — clicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSC — CTR %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSC — impressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSC — vị trí TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSC — số truy vấn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sitemap — số URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTFB trung bình (ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 65 ngày · 11 chỉ số</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crawlability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-page / Meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số trang crawl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance / TTFB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structured data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTFB trung vị (ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng số từ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng hợp theo tháng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mọi ô dưới đây là CÔNG THỨC trỏ về các sheet dữ liệu — sửa dữ liệu thì số này tự đổi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chỉ chuỗi grain "day" mới được CỘNG (SUMIFS). window28 và state lấy GIÁ TRỊ NGÀY QUÉT CUỐI CÙNG của tháng (INDEX).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CỘNG ĐƯỢC — số theo ngày thật (Social)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chỉ số</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KHÔNG CỘNG — Social — 28 ngày (lấy ngày quét cuối tháng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KHÔNG CỘNG — SEO (lấy ngày quét cuối tháng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KHÔNG CỘNG — Audit (lấy ngày quét cuối tháng)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0.##"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0012161C"/>
-      <sz val="14"/>
+      <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006B727C"/>
-      <sz val="9"/>
+      <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
+      <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF12161C"/>
       <name val="Arial"/>
-      <sz val="10"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF6B727C"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="004A5260"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="8"/>
+      <color rgb="FF4A5260"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F5ED"/>
+        <fgColor rgb="FFE6F5ED"/>
+        <bgColor rgb="FFEEF1F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDF1E3"/>
+        <fgColor rgb="FFFDF1E3"/>
+        <bgColor rgb="FFEEF1F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF1F5"/>
+        <fgColor rgb="FFEEF1F5"/>
+        <bgColor rgb="FFE6F5ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3440"/>
+        <fgColor rgb="FF2C3440"/>
+        <bgColor rgb="FF333300"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00E6E9EE"/>
+        <color rgb="FFE6E9EE"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="25">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFDF1E3"/>
+      <rgbColor rgb="FFE6F5ED"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFEEF1F5"/>
+      <rgbColor rgb="FFE6E9EE"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF6B727C"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF12161C"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF4A5260"/>
+      <rgbColor rgb="FF2C3440"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -288,574 +696,366 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="104" customWidth="1" min="3" max="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="104"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>DX Living — dữ liệu báo cáo theo ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Xuất ngày 2026-10-22 · nguồn: data/rollup.json của ba repo báo cáo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>File này là gì</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Bản xuất phẳng của dữ liệu đã lưu trong ba báo cáo DX Living, để đọc bằng tay và dựng báo cáo tháng. KHÔNG phải nguồn sự thật.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Nguồn sự thật</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>data/YYYY-MM-DD.json trong mỗi repo — bất biến, mỗi ngày một file, không bao giờ sửa. File Excel này và dashboard cùng đọc từ data/rollup.json, nên không bao giờ lệch nhau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Sửa file này thì sao</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Không ảnh hưởng gì tới báo cáo. Lần xuất sau sẽ ghi đè.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>BA LOẠI CHỈ SỐ — đọc kỹ trước khi cộng</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Số đo của đúng ngày đó. CỘNG DỒN ĐƯỢC. Hiện chỉ Social có (Facebook và Instagram), dựng lại từ chuỗi 28 giá trị lưu sẵn trong mỗi file ngày.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Đã là tổng của 28 ngày trước đó. KHÔNG ĐƯỢC CỘNG — hai ngày liền nhau chồng nhau 27 ngày, cộng lại là đếm trùng nhiều lần. Chỉ so đầu kỳ với cuối kỳ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Giá trị tại thời điểm quét (điểm số, tốc độ, số follower). Không cộng — lấy giá trị cuối kỳ hoặc trung bình.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Ô trống</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Ngày đó không đo chỉ số này. Không suy ra, không điền 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Ngày không quét</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Không bao giờ được nội suy. Ví dụ không có bản quét 20/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Meta điều chỉnh số</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Với chuỗi day của Social, mỗi ngày giữ lần đọc MỚI NHẤT — Meta có sửa số về sau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>CÁC SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Social — theo ngày</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>109 dòng × 7 chỉ số · 2026-07-05 → 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Social — 28 ngày</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>67 dòng × 14 chỉ số · 2026-07-23 → 2026-10-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>SEO</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>67 dòng × 14 chỉ số · 2026-06-30 → 2026-10-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Audit</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>64 dòng × 11 chỉ số · 2026-07-27 → 2026-10-23</t>
-        </is>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H117"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Social — theo ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn: Social/data/rollup.json · 109 ngày · 7 chỉ số</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>grain →</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>FB — tương tác/ngày</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>FB — view 3 giây/ngày</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>FB — views/ngày</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>FB — lượt ghé/ngày</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>IG — tương tác/ngày</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>IG — reach/ngày</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>IG — views/ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="n">
         <v>46208</v>
       </c>
@@ -881,7 +1081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="n">
         <v>46209</v>
       </c>
@@ -907,7 +1107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="n">
         <v>46210</v>
       </c>
@@ -933,7 +1133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="n">
         <v>46211</v>
       </c>
@@ -959,7 +1159,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
         <v>46212</v>
       </c>
@@ -985,7 +1185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="n">
         <v>46213</v>
       </c>
@@ -1011,7 +1211,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="n">
         <v>46214</v>
       </c>
@@ -1037,7 +1237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="n">
         <v>46215</v>
       </c>
@@ -1063,7 +1263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="n">
         <v>46216</v>
       </c>
@@ -1089,7 +1289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
         <v>46217</v>
       </c>
@@ -1115,7 +1315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="n">
         <v>46218</v>
       </c>
@@ -1141,7 +1341,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="n">
         <v>46219</v>
       </c>
@@ -1167,7 +1367,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="n">
         <v>46220</v>
       </c>
@@ -1193,7 +1393,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="n">
         <v>46221</v>
       </c>
@@ -1219,7 +1419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
         <v>46222</v>
       </c>
@@ -1245,7 +1445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="n">
         <v>46223</v>
       </c>
@@ -1271,7 +1471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="n">
         <v>46224</v>
       </c>
@@ -1297,7 +1497,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
         <v>46225</v>
       </c>
@@ -1323,7 +1523,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="n">
         <v>46226</v>
       </c>
@@ -1349,7 +1549,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="n">
         <v>46227</v>
       </c>
@@ -1375,7 +1575,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="n">
         <v>46228</v>
       </c>
@@ -1401,7 +1601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="n">
         <v>46229</v>
       </c>
@@ -1427,7 +1627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="n">
         <v>46230</v>
       </c>
@@ -1453,7 +1653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="n">
         <v>46231</v>
       </c>
@@ -1479,7 +1679,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="n">
         <v>46232</v>
       </c>
@@ -1505,7 +1705,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="n">
         <v>46233</v>
       </c>
@@ -1531,7 +1731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="n">
         <v>46234</v>
       </c>
@@ -1557,7 +1757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="n">
         <v>46235</v>
       </c>
@@ -1583,7 +1783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="n">
         <v>46236</v>
       </c>
@@ -1609,7 +1809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="n">
         <v>46237</v>
       </c>
@@ -1635,7 +1835,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="n">
         <v>46238</v>
       </c>
@@ -1661,7 +1861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="n">
         <v>46239</v>
       </c>
@@ -1687,7 +1887,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="n">
         <v>46240</v>
       </c>
@@ -1713,7 +1913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="n">
         <v>46241</v>
       </c>
@@ -1739,7 +1939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="n">
         <v>46242</v>
       </c>
@@ -1765,7 +1965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="n">
         <v>46243</v>
       </c>
@@ -1791,7 +1991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="n">
         <v>46244</v>
       </c>
@@ -1817,7 +2017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="n">
         <v>46245</v>
       </c>
@@ -1843,7 +2043,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="n">
         <v>46246</v>
       </c>
@@ -1869,7 +2069,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="n">
         <v>46247</v>
       </c>
@@ -1895,7 +2095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="n">
         <v>46248</v>
       </c>
@@ -1921,7 +2121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="n">
         <v>46249</v>
       </c>
@@ -1947,7 +2147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="n">
         <v>46250</v>
       </c>
@@ -1973,7 +2173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="n">
         <v>46251</v>
       </c>
@@ -1999,7 +2199,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="n">
         <v>46252</v>
       </c>
@@ -2025,7 +2225,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="n">
         <v>46253</v>
       </c>
@@ -2051,7 +2251,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="n">
         <v>46254</v>
       </c>
@@ -2077,7 +2277,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="n">
         <v>46255</v>
       </c>
@@ -2103,7 +2303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="n">
         <v>46256</v>
       </c>
@@ -2129,7 +2329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="n">
         <v>46257</v>
       </c>
@@ -2155,7 +2355,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="n">
         <v>46258</v>
       </c>
@@ -2181,7 +2381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="n">
         <v>46259</v>
       </c>
@@ -2207,7 +2407,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="n">
         <v>46260</v>
       </c>
@@ -2233,7 +2433,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="n">
         <v>46261</v>
       </c>
@@ -2259,7 +2459,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="n">
         <v>46262</v>
       </c>
@@ -2285,7 +2485,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="n">
         <v>46263</v>
       </c>
@@ -2311,7 +2511,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="n">
         <v>46264</v>
       </c>
@@ -2337,7 +2537,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="n">
         <v>46265</v>
       </c>
@@ -2363,7 +2563,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="n">
         <v>46266</v>
       </c>
@@ -2389,7 +2589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="n">
         <v>46267</v>
       </c>
@@ -2415,7 +2615,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="n">
         <v>46268</v>
       </c>
@@ -2441,7 +2641,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="n">
         <v>46269</v>
       </c>
@@ -2467,7 +2667,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="n">
         <v>46270</v>
       </c>
@@ -2493,7 +2693,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="n">
         <v>46271</v>
       </c>
@@ -2519,7 +2719,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="n">
         <v>46272</v>
       </c>
@@ -2545,7 +2745,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="15" t="n">
         <v>46273</v>
       </c>
@@ -2571,7 +2771,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="n">
         <v>46274</v>
       </c>
@@ -2597,7 +2797,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="n">
         <v>46275</v>
       </c>
@@ -2623,7 +2823,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="15" t="n">
         <v>46276</v>
       </c>
@@ -2649,7 +2849,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="15" t="n">
         <v>46277</v>
       </c>
@@ -2675,7 +2875,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="15" t="n">
         <v>46278</v>
       </c>
@@ -2701,7 +2901,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="15" t="n">
         <v>46279</v>
       </c>
@@ -2727,7 +2927,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="15" t="n">
         <v>46280</v>
       </c>
@@ -2753,7 +2953,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="15" t="n">
         <v>46281</v>
       </c>
@@ -2779,7 +2979,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="n">
         <v>46282</v>
       </c>
@@ -2805,7 +3005,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="15" t="n">
         <v>46283</v>
       </c>
@@ -2831,7 +3031,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="15" t="n">
         <v>46284</v>
       </c>
@@ -2857,7 +3057,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="15" t="n">
         <v>46285</v>
       </c>
@@ -2883,7 +3083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="15" t="n">
         <v>46286</v>
       </c>
@@ -2909,7 +3109,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="15" t="n">
         <v>46287</v>
       </c>
@@ -2935,7 +3135,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="15" t="n">
         <v>46288</v>
       </c>
@@ -2961,7 +3161,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="15" t="n">
         <v>46289</v>
       </c>
@@ -2987,7 +3187,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="15" t="n">
         <v>46290</v>
       </c>
@@ -3013,7 +3213,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="15" t="n">
         <v>46291</v>
       </c>
@@ -3039,7 +3239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="15" t="n">
         <v>46292</v>
       </c>
@@ -3065,7 +3265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="15" t="n">
         <v>46293</v>
       </c>
@@ -3091,7 +3291,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="15" t="n">
         <v>46294</v>
       </c>
@@ -3117,7 +3317,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="15" t="n">
         <v>46295</v>
       </c>
@@ -3143,7 +3343,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15" t="n">
         <v>46296</v>
       </c>
@@ -3169,7 +3369,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="15" t="n">
         <v>46297</v>
       </c>
@@ -3195,7 +3395,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="15" t="n">
         <v>46298</v>
       </c>
@@ -3221,7 +3421,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="15" t="n">
         <v>46299</v>
       </c>
@@ -3247,7 +3447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="15" t="n">
         <v>46300</v>
       </c>
@@ -3273,7 +3473,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="15" t="n">
         <v>46301</v>
       </c>
@@ -3299,7 +3499,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="15" t="n">
         <v>46302</v>
       </c>
@@ -3325,7 +3525,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="15" t="n">
         <v>46303</v>
       </c>
@@ -3351,7 +3551,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="15" t="n">
         <v>46304</v>
       </c>
@@ -3377,7 +3577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="15" t="n">
         <v>46305</v>
       </c>
@@ -3403,7 +3603,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="15" t="n">
         <v>46306</v>
       </c>
@@ -3429,7 +3629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="15" t="n">
         <v>46307</v>
       </c>
@@ -3455,7 +3655,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="15" t="n">
         <v>46308</v>
       </c>
@@ -3481,7 +3681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="15" t="n">
         <v>46309</v>
       </c>
@@ -3500,12 +3700,12 @@
       <c r="F107" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="16" t="n"/>
+      <c r="G107" s="16"/>
       <c r="H107" s="16" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="15" t="n">
         <v>46310</v>
       </c>
@@ -3524,12 +3724,12 @@
       <c r="F108" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="G108" s="16" t="n"/>
+      <c r="G108" s="16"/>
       <c r="H108" s="16" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="15" t="n">
         <v>46311</v>
       </c>
@@ -3548,12 +3748,12 @@
       <c r="F109" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="G109" s="16" t="n"/>
+      <c r="G109" s="16"/>
       <c r="H109" s="16" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="15" t="n">
         <v>46312</v>
       </c>
@@ -3572,12 +3772,12 @@
       <c r="F110" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="16" t="n"/>
+      <c r="G110" s="16"/>
       <c r="H110" s="16" t="n">
         <v>128</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="15" t="n">
         <v>46313</v>
       </c>
@@ -3596,12 +3796,12 @@
       <c r="F111" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="G111" s="16" t="n"/>
+      <c r="G111" s="16"/>
       <c r="H111" s="16" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="15" t="n">
         <v>46314</v>
       </c>
@@ -3620,12 +3820,12 @@
       <c r="F112" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="G112" s="16" t="n"/>
+      <c r="G112" s="16"/>
       <c r="H112" s="16" t="n">
         <v>49</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="15" t="n">
         <v>46315</v>
       </c>
@@ -3644,12 +3844,12 @@
       <c r="F113" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="G113" s="16" t="n"/>
+      <c r="G113" s="16"/>
       <c r="H113" s="16" t="n">
         <v>52</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="15" t="n">
         <v>46316</v>
       </c>
@@ -3657,10 +3857,10 @@
         <v>5</v>
       </c>
       <c r="C114" s="16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D114" s="16" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E114" s="16" t="n">
         <v>45</v>
@@ -3668,218 +3868,216 @@
       <c r="F114" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="G114" s="16" t="n"/>
+      <c r="G114" s="16"/>
       <c r="H114" s="16" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="15" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B115" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C115" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D115" s="16" t="n">
+        <v>241</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="F115" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G115" s="16"/>
+      <c r="H115" s="16" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="15" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B116" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C116" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D116" s="16" t="n">
+        <v>160</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F116" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" s="16"/>
+      <c r="H116" s="16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="15" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B117" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" s="16"/>
+      <c r="H117" s="16" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="2" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Social — 28 ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn: Social/data/rollup.json · 67 ngày · 14 chỉ số</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>grain →</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="H4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="K4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="L4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="M4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="O4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>FB — followers</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>FB — tương tác (28n)</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>FB — views (28n)</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>FB — lượt ghé (28n)</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>IG — followers</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>IG — tương tác (28n)</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>IG — reach (28n)</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>IG — views (28n)</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn — followers</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn — impressions (28n)</t>
-        </is>
-      </c>
-      <c r="L5" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn — lượt xem trang (28n)</t>
-        </is>
-      </c>
-      <c r="M5" s="14" t="inlineStr">
-        <is>
-          <t>LinkedIn — reactions (28n)</t>
-        </is>
-      </c>
-      <c r="N5" s="14" t="inlineStr">
-        <is>
-          <t>YouTube — subscribers</t>
-        </is>
-      </c>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>YouTube — views (28n)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="n">
         <v>46226</v>
       </c>
@@ -3926,7 +4124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="n">
         <v>46230</v>
       </c>
@@ -3973,7 +4171,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="n">
         <v>46231</v>
       </c>
@@ -4020,7 +4218,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="n">
         <v>46232</v>
       </c>
@@ -4067,7 +4265,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
         <v>46233</v>
       </c>
@@ -4114,7 +4312,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="n">
         <v>46234</v>
       </c>
@@ -4161,7 +4359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="n">
         <v>46237</v>
       </c>
@@ -4208,7 +4406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="n">
         <v>46238</v>
       </c>
@@ -4255,7 +4453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="n">
         <v>46239</v>
       </c>
@@ -4302,7 +4500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
         <v>46240</v>
       </c>
@@ -4349,7 +4547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="n">
         <v>46241</v>
       </c>
@@ -4396,7 +4594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="n">
         <v>46244</v>
       </c>
@@ -4443,7 +4641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="n">
         <v>46245</v>
       </c>
@@ -4490,7 +4688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="n">
         <v>46246</v>
       </c>
@@ -4537,7 +4735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
         <v>46247</v>
       </c>
@@ -4584,7 +4782,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="n">
         <v>46248</v>
       </c>
@@ -4631,7 +4829,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="n">
         <v>46251</v>
       </c>
@@ -4678,7 +4876,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
         <v>46252</v>
       </c>
@@ -4725,7 +4923,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="n">
         <v>46253</v>
       </c>
@@ -4772,7 +4970,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="n">
         <v>46254</v>
       </c>
@@ -4819,7 +5017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="n">
         <v>46255</v>
       </c>
@@ -4866,7 +5064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="n">
         <v>46258</v>
       </c>
@@ -4913,7 +5111,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="n">
         <v>46259</v>
       </c>
@@ -4960,7 +5158,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="n">
         <v>46260</v>
       </c>
@@ -5007,7 +5205,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="n">
         <v>46261</v>
       </c>
@@ -5054,7 +5252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="n">
         <v>46262</v>
       </c>
@@ -5101,7 +5299,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="n">
         <v>46263</v>
       </c>
@@ -5148,7 +5346,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="n">
         <v>46268</v>
       </c>
@@ -5195,7 +5393,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="n">
         <v>46269</v>
       </c>
@@ -5242,7 +5440,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="n">
         <v>46272</v>
       </c>
@@ -5289,7 +5487,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="n">
         <v>46273</v>
       </c>
@@ -5336,7 +5534,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="n">
         <v>46274</v>
       </c>
@@ -5383,7 +5581,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="n">
         <v>46275</v>
       </c>
@@ -5430,7 +5628,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="n">
         <v>46276</v>
       </c>
@@ -5477,7 +5675,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="n">
         <v>46279</v>
       </c>
@@ -5524,7 +5722,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="n">
         <v>46280</v>
       </c>
@@ -5571,7 +5769,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="n">
         <v>46281</v>
       </c>
@@ -5618,7 +5816,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="n">
         <v>46282</v>
       </c>
@@ -5665,7 +5863,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="n">
         <v>46283</v>
       </c>
@@ -5712,7 +5910,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="n">
         <v>46284</v>
       </c>
@@ -5759,7 +5957,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="n">
         <v>46286</v>
       </c>
@@ -5806,7 +6004,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="n">
         <v>46287</v>
       </c>
@@ -5853,7 +6051,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="n">
         <v>46288</v>
       </c>
@@ -5900,7 +6098,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="n">
         <v>46289</v>
       </c>
@@ -5947,7 +6145,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="n">
         <v>46290</v>
       </c>
@@ -5994,7 +6192,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="n">
         <v>46291</v>
       </c>
@@ -6041,7 +6239,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="n">
         <v>46293</v>
       </c>
@@ -6088,7 +6286,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="n">
         <v>46294</v>
       </c>
@@ -6135,7 +6333,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="n">
         <v>46295</v>
       </c>
@@ -6182,7 +6380,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="n">
         <v>46296</v>
       </c>
@@ -6222,10 +6420,10 @@
       <c r="M55" s="16" t="n">
         <v>37</v>
       </c>
-      <c r="N55" s="16" t="n"/>
-      <c r="O55" s="16" t="n"/>
-    </row>
-    <row r="56">
+      <c r="N55" s="16"/>
+      <c r="O55" s="16"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="n">
         <v>46297</v>
       </c>
@@ -6272,7 +6470,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="n">
         <v>46298</v>
       </c>
@@ -6319,7 +6517,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="n">
         <v>46300</v>
       </c>
@@ -6366,7 +6564,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="n">
         <v>46301</v>
       </c>
@@ -6413,7 +6611,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="n">
         <v>46302</v>
       </c>
@@ -6460,7 +6658,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="n">
         <v>46303</v>
       </c>
@@ -6507,7 +6705,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="n">
         <v>46304</v>
       </c>
@@ -6554,7 +6752,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="n">
         <v>46307</v>
       </c>
@@ -6601,7 +6799,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="n">
         <v>46308</v>
       </c>
@@ -6648,7 +6846,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="n">
         <v>46309</v>
       </c>
@@ -6695,7 +6893,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="n">
         <v>46310</v>
       </c>
@@ -6742,7 +6940,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="n">
         <v>46311</v>
       </c>
@@ -6770,10 +6968,10 @@
       <c r="I67" s="16" t="n">
         <v>1823</v>
       </c>
-      <c r="J67" s="16" t="n"/>
-      <c r="K67" s="16" t="n"/>
-      <c r="L67" s="16" t="n"/>
-      <c r="M67" s="16" t="n"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
       <c r="N67" s="16" t="n">
         <v>7</v>
       </c>
@@ -6781,7 +6979,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="n">
         <v>46313</v>
       </c>
@@ -6828,7 +7026,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="n">
         <v>46315</v>
       </c>
@@ -6875,7 +7073,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="n">
         <v>46316</v>
       </c>
@@ -6922,7 +7120,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="15" t="n">
         <v>46317</v>
       </c>
@@ -6969,7 +7167,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="n">
         <v>46318</v>
       </c>
@@ -6997,10 +7195,10 @@
       <c r="I72" s="16" t="n">
         <v>1875</v>
       </c>
-      <c r="J72" s="16" t="n"/>
-      <c r="K72" s="16" t="n"/>
-      <c r="L72" s="16" t="n"/>
-      <c r="M72" s="16" t="n"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
       <c r="N72" s="16" t="n">
         <v>7</v>
       </c>
@@ -7008,225 +7206,190 @@
         <v>860</v>
       </c>
     </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="15" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B73" s="16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>172</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>4270</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>556</v>
+      </c>
+      <c r="F73" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="H73" s="16" t="n">
+        <v>336</v>
+      </c>
+      <c r="I73" s="16" t="n">
+        <v>1933</v>
+      </c>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+      <c r="N73" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O73" s="16" t="n">
+        <v>868</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="2" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SEO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn: SEO/data/rollup.json · 67 ngày · 14 chỉ số</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>grain →</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="H4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="I4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="K4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="L4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="M4" s="18" t="inlineStr">
-        <is>
-          <t>window28</t>
-        </is>
-      </c>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="O4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Ahrefs — trích dẫn AI</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Ahrefs — backlinks</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Ahrefs — referring domains</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>GA4 — engagement %</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>GA4 — key events</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>GA4 — sessions</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>GA4 — users</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>GSC — clicks</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>GSC — CTR %</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>GSC — impressions</t>
-        </is>
-      </c>
-      <c r="L5" s="14" t="inlineStr">
-        <is>
-          <t>GSC — vị trí TB</t>
-        </is>
-      </c>
-      <c r="M5" s="14" t="inlineStr">
-        <is>
-          <t>GSC — số truy vấn</t>
-        </is>
-      </c>
-      <c r="N5" s="14" t="inlineStr">
-        <is>
-          <t>Sitemap — số URL</t>
-        </is>
-      </c>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>TTFB trung bình (ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="n">
         <v>46203</v>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="16" t="n">
         <v>244</v>
       </c>
       <c r="E6" s="19" t="n">
         <v>18.9</v>
       </c>
-      <c r="F6" s="16" t="n"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="16" t="n">
         <v>322</v>
       </c>
@@ -7245,16 +7408,16 @@
       <c r="L6" s="19" t="n">
         <v>13.8</v>
       </c>
-      <c r="M6" s="16" t="n"/>
-      <c r="N6" s="16" t="n"/>
-      <c r="O6" s="16" t="n"/>
-    </row>
-    <row r="7">
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="n">
         <v>46230</v>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="16" t="n">
         <v>244</v>
       </c>
@@ -7267,7 +7430,7 @@
       <c r="G7" s="16" t="n">
         <v>442</v>
       </c>
-      <c r="H7" s="16" t="n"/>
+      <c r="H7" s="16"/>
       <c r="I7" s="16" t="n">
         <v>65</v>
       </c>
@@ -7280,11 +7443,11 @@
       <c r="L7" s="19" t="n">
         <v>23.2</v>
       </c>
-      <c r="M7" s="16" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="16" t="n"/>
-    </row>
-    <row r="8">
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="n">
         <v>46231</v>
       </c>
@@ -7306,7 +7469,7 @@
       <c r="G8" s="16" t="n">
         <v>435</v>
       </c>
-      <c r="H8" s="16" t="n"/>
+      <c r="H8" s="16"/>
       <c r="I8" s="16" t="n">
         <v>65</v>
       </c>
@@ -7319,11 +7482,11 @@
       <c r="L8" s="19" t="n">
         <v>23.7</v>
       </c>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16" t="n"/>
-    </row>
-    <row r="9">
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="n">
         <v>46232</v>
       </c>
@@ -7337,7 +7500,7 @@
         <v>339</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>64.09999999999999</v>
+        <v>64.1</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>42</v>
@@ -7345,7 +7508,7 @@
       <c r="G9" s="16" t="n">
         <v>421</v>
       </c>
-      <c r="H9" s="16" t="n"/>
+      <c r="H9" s="16"/>
       <c r="I9" s="16" t="n">
         <v>63</v>
       </c>
@@ -7361,10 +7524,10 @@
       <c r="M9" s="16" t="n">
         <v>113</v>
       </c>
-      <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16" t="n"/>
-    </row>
-    <row r="10">
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
         <v>46233</v>
       </c>
@@ -7378,7 +7541,7 @@
         <v>339</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>64.09999999999999</v>
+        <v>64.1</v>
       </c>
       <c r="F10" s="16" t="n">
         <v>42</v>
@@ -7386,7 +7549,7 @@
       <c r="G10" s="16" t="n">
         <v>421</v>
       </c>
-      <c r="H10" s="16" t="n"/>
+      <c r="H10" s="16"/>
       <c r="I10" s="16" t="n">
         <v>65</v>
       </c>
@@ -7402,10 +7565,10 @@
       <c r="M10" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16" t="n"/>
-    </row>
-    <row r="11">
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="n">
         <v>46234</v>
       </c>
@@ -7427,7 +7590,7 @@
       <c r="G11" s="16" t="n">
         <v>405</v>
       </c>
-      <c r="H11" s="16" t="n"/>
+      <c r="H11" s="16"/>
       <c r="I11" s="16" t="n">
         <v>67</v>
       </c>
@@ -7443,10 +7606,10 @@
       <c r="M11" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16" t="n"/>
-    </row>
-    <row r="12">
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="n">
         <v>46237</v>
       </c>
@@ -7468,7 +7631,7 @@
       <c r="G12" s="16" t="n">
         <v>381</v>
       </c>
-      <c r="H12" s="16" t="n"/>
+      <c r="H12" s="16"/>
       <c r="I12" s="16" t="n">
         <v>68</v>
       </c>
@@ -7484,10 +7647,10 @@
       <c r="M12" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16" t="n"/>
-    </row>
-    <row r="13">
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="n">
         <v>46241</v>
       </c>
@@ -7501,7 +7664,7 @@
         <v>366</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>67.59999999999999</v>
+        <v>67.6</v>
       </c>
       <c r="F13" s="16" t="n">
         <v>23</v>
@@ -7530,9 +7693,9 @@
       <c r="N13" s="16" t="n">
         <v>75</v>
       </c>
-      <c r="O13" s="16" t="n"/>
-    </row>
-    <row r="14">
+      <c r="O13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="n">
         <v>46244</v>
       </c>
@@ -7575,9 +7738,9 @@
       <c r="N14" s="16" t="n">
         <v>76</v>
       </c>
-      <c r="O14" s="16" t="n"/>
-    </row>
-    <row r="15">
+      <c r="O14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
         <v>46245</v>
       </c>
@@ -7591,7 +7754,7 @@
         <v>397</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>65.04000000000001</v>
+        <v>65.04</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>15</v>
@@ -7620,9 +7783,9 @@
       <c r="N15" s="16" t="n">
         <v>77</v>
       </c>
-      <c r="O15" s="16" t="n"/>
-    </row>
-    <row r="16">
+      <c r="O15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="n">
         <v>46246</v>
       </c>
@@ -7665,9 +7828,9 @@
       <c r="N16" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="O16" s="16" t="n"/>
-    </row>
-    <row r="17">
+      <c r="O16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="n">
         <v>46247</v>
       </c>
@@ -7710,9 +7873,9 @@
       <c r="N17" s="16" t="n">
         <v>79</v>
       </c>
-      <c r="O17" s="16" t="n"/>
-    </row>
-    <row r="18">
+      <c r="O17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="n">
         <v>46248</v>
       </c>
@@ -7726,7 +7889,7 @@
         <v>410</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>67.81999999999999</v>
+        <v>67.82</v>
       </c>
       <c r="F18" s="16" t="n">
         <v>13</v>
@@ -7755,9 +7918,9 @@
       <c r="N18" s="16" t="n">
         <v>79</v>
       </c>
-      <c r="O18" s="16" t="n"/>
-    </row>
-    <row r="19">
+      <c r="O18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="n">
         <v>46251</v>
       </c>
@@ -7800,9 +7963,9 @@
       <c r="N19" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="O19" s="16" t="n"/>
-    </row>
-    <row r="20">
+      <c r="O19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
         <v>46252</v>
       </c>
@@ -7845,9 +8008,9 @@
       <c r="N20" s="16" t="n">
         <v>82</v>
       </c>
-      <c r="O20" s="16" t="n"/>
-    </row>
-    <row r="21">
+      <c r="O20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="n">
         <v>46253</v>
       </c>
@@ -7872,17 +8035,17 @@
       <c r="H21" s="16" t="n">
         <v>56</v>
       </c>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
-      <c r="M21" s="16" t="n"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
       <c r="N21" s="16" t="n">
         <v>81</v>
       </c>
-      <c r="O21" s="16" t="n"/>
-    </row>
-    <row r="22">
+      <c r="O21" s="16"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="n">
         <v>46254</v>
       </c>
@@ -7925,9 +8088,9 @@
       <c r="N22" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="O22" s="16" t="n"/>
-    </row>
-    <row r="23">
+      <c r="O22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
         <v>46255</v>
       </c>
@@ -7970,9 +8133,9 @@
       <c r="N23" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="O23" s="16" t="n"/>
-    </row>
-    <row r="24">
+      <c r="O23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="n">
         <v>46258</v>
       </c>
@@ -8015,9 +8178,9 @@
       <c r="N24" s="16" t="n">
         <v>86</v>
       </c>
-      <c r="O24" s="16" t="n"/>
-    </row>
-    <row r="25">
+      <c r="O24" s="16"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="n">
         <v>46259</v>
       </c>
@@ -8060,9 +8223,9 @@
       <c r="N25" s="16" t="n">
         <v>86</v>
       </c>
-      <c r="O25" s="16" t="n"/>
-    </row>
-    <row r="26">
+      <c r="O25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="n">
         <v>46260</v>
       </c>
@@ -8105,9 +8268,9 @@
       <c r="N26" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="O26" s="16" t="n"/>
-    </row>
-    <row r="27">
+      <c r="O26" s="16"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="n">
         <v>46261</v>
       </c>
@@ -8150,9 +8313,9 @@
       <c r="N27" s="16" t="n">
         <v>91</v>
       </c>
-      <c r="O27" s="16" t="n"/>
-    </row>
-    <row r="28">
+      <c r="O27" s="16"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="n">
         <v>46262</v>
       </c>
@@ -8199,7 +8362,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="n">
         <v>46263</v>
       </c>
@@ -8246,7 +8409,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="n">
         <v>46265</v>
       </c>
@@ -8293,7 +8456,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="n">
         <v>46266</v>
       </c>
@@ -8340,7 +8503,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="n">
         <v>46268</v>
       </c>
@@ -8387,7 +8550,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="n">
         <v>46269</v>
       </c>
@@ -8434,7 +8597,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="n">
         <v>46270</v>
       </c>
@@ -8481,7 +8644,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="n">
         <v>46272</v>
       </c>
@@ -8528,7 +8691,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="n">
         <v>46273</v>
       </c>
@@ -8575,7 +8738,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="n">
         <v>46274</v>
       </c>
@@ -8622,7 +8785,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="n">
         <v>46275</v>
       </c>
@@ -8669,7 +8832,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="n">
         <v>46276</v>
       </c>
@@ -8716,7 +8879,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="n">
         <v>46279</v>
       </c>
@@ -8763,7 +8926,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="n">
         <v>46280</v>
       </c>
@@ -8810,7 +8973,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="n">
         <v>46281</v>
       </c>
@@ -8857,7 +9020,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="n">
         <v>46282</v>
       </c>
@@ -8904,7 +9067,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="n">
         <v>46283</v>
       </c>
@@ -8951,7 +9114,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="n">
         <v>46284</v>
       </c>
@@ -8998,7 +9161,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="n">
         <v>46286</v>
       </c>
@@ -9045,7 +9208,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="n">
         <v>46287</v>
       </c>
@@ -9092,7 +9255,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="n">
         <v>46288</v>
       </c>
@@ -9139,7 +9302,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="n">
         <v>46289</v>
       </c>
@@ -9186,7 +9349,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="n">
         <v>46290</v>
       </c>
@@ -9233,7 +9396,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="n">
         <v>46291</v>
       </c>
@@ -9280,7 +9443,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="n">
         <v>46293</v>
       </c>
@@ -9327,7 +9490,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="n">
         <v>46294</v>
       </c>
@@ -9374,7 +9537,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="n">
         <v>46295</v>
       </c>
@@ -9421,7 +9584,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="n">
         <v>46296</v>
       </c>
@@ -9434,15 +9597,15 @@
       <c r="D55" s="16" t="n">
         <v>882</v>
       </c>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="16" t="n"/>
-      <c r="M55" s="16" t="n"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
       <c r="N55" s="16" t="n">
         <v>119</v>
       </c>
@@ -9450,7 +9613,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="n">
         <v>46297</v>
       </c>
@@ -9497,7 +9660,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="n">
         <v>46298</v>
       </c>
@@ -9544,7 +9707,7 @@
         <v>326.9</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="n">
         <v>46300</v>
       </c>
@@ -9591,7 +9754,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="n">
         <v>46301</v>
       </c>
@@ -9638,7 +9801,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="n">
         <v>46302</v>
       </c>
@@ -9685,7 +9848,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="n">
         <v>46303</v>
       </c>
@@ -9732,7 +9895,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="n">
         <v>46304</v>
       </c>
@@ -9779,7 +9942,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="n">
         <v>46307</v>
       </c>
@@ -9826,7 +9989,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="n">
         <v>46308</v>
       </c>
@@ -9873,7 +10036,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="n">
         <v>46309</v>
       </c>
@@ -9920,7 +10083,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="n">
         <v>46310</v>
       </c>
@@ -9967,7 +10130,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="n">
         <v>46311</v>
       </c>
@@ -10014,7 +10177,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="n">
         <v>46313</v>
       </c>
@@ -10061,7 +10224,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="n">
         <v>46315</v>
       </c>
@@ -10108,7 +10271,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="n">
         <v>46316</v>
       </c>
@@ -10155,7 +10318,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="15" t="n">
         <v>46317</v>
       </c>
@@ -10202,7 +10365,7 @@
         <v>311.2</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="n">
         <v>46318</v>
       </c>
@@ -10249,180 +10412,168 @@
         <v>310.4</v>
       </c>
     </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="15" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B73" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>909</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>873</v>
+      </c>
+      <c r="E73" s="19" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="F73" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>699</v>
+      </c>
+      <c r="H73" s="16" t="n">
+        <v>439</v>
+      </c>
+      <c r="I73" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K73" s="16" t="n">
+        <v>1411</v>
+      </c>
+      <c r="L73" s="19" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M73" s="16" t="n">
+        <v>131</v>
+      </c>
+      <c r="N73" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="O73" s="19" t="n">
+        <v>314.4</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L70"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn: Audit/data/rollup.json · 64 ngày · 11 chỉ số</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>grain →</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="I4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="K4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Crawlability</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Health score</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>On-page / Meta</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>Số trang crawl</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Performance / TTFB</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>Sitemap — số URL</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>Structured data</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>TTFB trung bình (ms)</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>TTFB trung vị (ms)</t>
-        </is>
-      </c>
-      <c r="L5" s="14" t="inlineStr">
-        <is>
-          <t>Tổng số từ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="n">
         <v>46230</v>
       </c>
@@ -10450,11 +10601,11 @@
       <c r="I6" s="16" t="n">
         <v>72</v>
       </c>
-      <c r="J6" s="16" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="16" t="n"/>
-    </row>
-    <row r="7">
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="n">
         <v>46231</v>
       </c>
@@ -10482,11 +10633,11 @@
       <c r="I7" s="16" t="n">
         <v>74</v>
       </c>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-    </row>
-    <row r="8">
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="n">
         <v>46232</v>
       </c>
@@ -10514,11 +10665,11 @@
       <c r="I8" s="16" t="n">
         <v>74</v>
       </c>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-    </row>
-    <row r="9">
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="n">
         <v>46233</v>
       </c>
@@ -10546,11 +10697,11 @@
       <c r="I9" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-    </row>
-    <row r="10">
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
         <v>46234</v>
       </c>
@@ -10578,11 +10729,11 @@
       <c r="I10" s="16" t="n">
         <v>82</v>
       </c>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-    </row>
-    <row r="11">
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="n">
         <v>46237</v>
       </c>
@@ -10610,11 +10761,11 @@
       <c r="I11" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-    </row>
-    <row r="12">
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="n">
         <v>46238</v>
       </c>
@@ -10642,11 +10793,11 @@
       <c r="I12" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-    </row>
-    <row r="13">
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="n">
         <v>46239</v>
       </c>
@@ -10674,11 +10825,11 @@
       <c r="I13" s="16" t="n">
         <v>81</v>
       </c>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
-    </row>
-    <row r="14">
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="n">
         <v>46241</v>
       </c>
@@ -10706,11 +10857,11 @@
       <c r="I14" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-    </row>
-    <row r="15">
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
         <v>46244</v>
       </c>
@@ -10738,11 +10889,11 @@
       <c r="I15" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="J15" s="16" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="16" t="n"/>
-    </row>
-    <row r="16">
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="n">
         <v>46245</v>
       </c>
@@ -10770,11 +10921,11 @@
       <c r="I16" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="J16" s="16" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="16" t="n"/>
-    </row>
-    <row r="17">
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="n">
         <v>46246</v>
       </c>
@@ -10805,10 +10956,10 @@
       <c r="J17" s="16" t="n">
         <v>697</v>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
-    </row>
-    <row r="18">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="n">
         <v>46247</v>
       </c>
@@ -10839,10 +10990,10 @@
       <c r="J18" s="16" t="n">
         <v>674</v>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
-    </row>
-    <row r="19">
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="n">
         <v>46248</v>
       </c>
@@ -10873,10 +11024,10 @@
       <c r="J19" s="16" t="n">
         <v>618</v>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
-    </row>
-    <row r="20">
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
         <v>46251</v>
       </c>
@@ -10907,10 +11058,10 @@
       <c r="J20" s="16" t="n">
         <v>671</v>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
-    </row>
-    <row r="21">
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="n">
         <v>46252</v>
       </c>
@@ -10941,10 +11092,10 @@
       <c r="J21" s="16" t="n">
         <v>761</v>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
-    </row>
-    <row r="22">
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="n">
         <v>46253</v>
       </c>
@@ -10975,10 +11126,10 @@
       <c r="J22" s="16" t="n">
         <v>755</v>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
-    </row>
-    <row r="23">
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
         <v>46254</v>
       </c>
@@ -11009,10 +11160,10 @@
       <c r="J23" s="16" t="n">
         <v>821</v>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
-    </row>
-    <row r="24">
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="n">
         <v>46255</v>
       </c>
@@ -11043,10 +11194,10 @@
       <c r="J24" s="16" t="n">
         <v>757</v>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
-    </row>
-    <row r="25">
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="n">
         <v>46258</v>
       </c>
@@ -11077,10 +11228,10 @@
       <c r="J25" s="16" t="n">
         <v>700</v>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
-    </row>
-    <row r="26">
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="n">
         <v>46259</v>
       </c>
@@ -11111,10 +11262,10 @@
       <c r="J26" s="16" t="n">
         <v>656</v>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
-    </row>
-    <row r="27">
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="n">
         <v>46260</v>
       </c>
@@ -11145,10 +11296,10 @@
       <c r="J27" s="16" t="n">
         <v>720</v>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
-    </row>
-    <row r="28">
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="n">
         <v>46261</v>
       </c>
@@ -11179,10 +11330,10 @@
       <c r="J28" s="16" t="n">
         <v>888</v>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
-    </row>
-    <row r="29">
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="n">
         <v>46262</v>
       </c>
@@ -11213,10 +11364,10 @@
       <c r="J29" s="16" t="n">
         <v>862</v>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
-    </row>
-    <row r="30">
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="n">
         <v>46268</v>
       </c>
@@ -11247,10 +11398,10 @@
       <c r="J30" s="16" t="n">
         <v>924</v>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
-    </row>
-    <row r="31">
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="n">
         <v>46269</v>
       </c>
@@ -11266,23 +11417,23 @@
       <c r="E31" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="F31" s="16" t="n"/>
+      <c r="F31" s="16"/>
       <c r="G31" s="16" t="n">
         <v>85</v>
       </c>
-      <c r="H31" s="16" t="n"/>
+      <c r="H31" s="16"/>
       <c r="I31" s="16" t="n">
         <v>96</v>
       </c>
       <c r="J31" s="16" t="n">
         <v>932</v>
       </c>
-      <c r="K31" s="16" t="n"/>
+      <c r="K31" s="16"/>
       <c r="L31" s="16" t="n">
         <v>204862</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="n">
         <v>46272</v>
       </c>
@@ -11304,19 +11455,19 @@
       <c r="G32" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="H32" s="16" t="n"/>
+      <c r="H32" s="16"/>
       <c r="I32" s="16" t="n">
         <v>96</v>
       </c>
       <c r="J32" s="16" t="n">
         <v>785</v>
       </c>
-      <c r="K32" s="16" t="n"/>
+      <c r="K32" s="16"/>
       <c r="L32" s="16" t="n">
         <v>210673</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="n">
         <v>46273</v>
       </c>
@@ -11338,19 +11489,19 @@
       <c r="G33" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="H33" s="16" t="n"/>
+      <c r="H33" s="16"/>
       <c r="I33" s="16" t="n">
         <v>95</v>
       </c>
       <c r="J33" s="16" t="n">
         <v>877</v>
       </c>
-      <c r="K33" s="16" t="n"/>
+      <c r="K33" s="16"/>
       <c r="L33" s="16" t="n">
         <v>213007</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="n">
         <v>46274</v>
       </c>
@@ -11372,7 +11523,7 @@
       <c r="G34" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="H34" s="16" t="n"/>
+      <c r="H34" s="16"/>
       <c r="I34" s="16" t="n">
         <v>94</v>
       </c>
@@ -11386,7 +11537,7 @@
         <v>215236</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="n">
         <v>46275</v>
       </c>
@@ -11424,7 +11575,7 @@
         <v>216434</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="n">
         <v>46276</v>
       </c>
@@ -11462,7 +11613,7 @@
         <v>219115</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="n">
         <v>46279</v>
       </c>
@@ -11500,7 +11651,7 @@
         <v>224048</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="n">
         <v>46280</v>
       </c>
@@ -11538,7 +11689,7 @@
         <v>218216</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="n">
         <v>46281</v>
       </c>
@@ -11576,7 +11727,7 @@
         <v>222873</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="n">
         <v>46282</v>
       </c>
@@ -11614,7 +11765,7 @@
         <v>222873</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="n">
         <v>46283</v>
       </c>
@@ -11652,7 +11803,7 @@
         <v>224773</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="n">
         <v>46284</v>
       </c>
@@ -11690,7 +11841,7 @@
         <v>229319</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="n">
         <v>46286</v>
       </c>
@@ -11728,7 +11879,7 @@
         <v>231563</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="n">
         <v>46287</v>
       </c>
@@ -11766,7 +11917,7 @@
         <v>234251</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="n">
         <v>46288</v>
       </c>
@@ -11804,7 +11955,7 @@
         <v>236840</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="n">
         <v>46289</v>
       </c>
@@ -11842,7 +11993,7 @@
         <v>239199</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="n">
         <v>46290</v>
       </c>
@@ -11880,7 +12031,7 @@
         <v>239208</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="n">
         <v>46291</v>
       </c>
@@ -11918,7 +12069,7 @@
         <v>239577</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="n">
         <v>46293</v>
       </c>
@@ -11956,7 +12107,7 @@
         <v>239577</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="n">
         <v>46294</v>
       </c>
@@ -11994,7 +12145,7 @@
         <v>241329</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="n">
         <v>46295</v>
       </c>
@@ -12032,7 +12183,7 @@
         <v>241329</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="n">
         <v>46296</v>
       </c>
@@ -12070,7 +12221,7 @@
         <v>241211</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="n">
         <v>46297</v>
       </c>
@@ -12108,7 +12259,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="n">
         <v>46298</v>
       </c>
@@ -12146,7 +12297,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="n">
         <v>46300</v>
       </c>
@@ -12184,7 +12335,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="n">
         <v>46301</v>
       </c>
@@ -12222,7 +12373,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="n">
         <v>46302</v>
       </c>
@@ -12260,7 +12411,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="n">
         <v>46303</v>
       </c>
@@ -12298,7 +12449,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="n">
         <v>46304</v>
       </c>
@@ -12336,7 +12487,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="n">
         <v>46307</v>
       </c>
@@ -12374,7 +12525,7 @@
         <v>241675</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="n">
         <v>46308</v>
       </c>
@@ -12412,7 +12563,7 @@
         <v>242620</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="n">
         <v>46309</v>
       </c>
@@ -12450,7 +12601,7 @@
         <v>241898</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="n">
         <v>46310</v>
       </c>
@@ -12488,7 +12639,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="n">
         <v>46311</v>
       </c>
@@ -12526,7 +12677,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="n">
         <v>46313</v>
       </c>
@@ -12564,7 +12715,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="n">
         <v>46315</v>
       </c>
@@ -12602,7 +12753,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="n">
         <v>46316</v>
       </c>
@@ -12640,7 +12791,7 @@
         <v>242263</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="n">
         <v>46317</v>
       </c>
@@ -12678,7 +12829,7 @@
         <v>243021</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="n">
         <v>46318</v>
       </c>
@@ -12716,1304 +12867,1202 @@
         <v>243401</v>
       </c>
     </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B70" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F70" s="16" t="n">
+        <v>118</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H70" s="16" t="n">
+        <v>119</v>
+      </c>
+      <c r="I70" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J70" s="19" t="n">
+        <v>314.4</v>
+      </c>
+      <c r="K70" s="16" t="n">
+        <v>249</v>
+      </c>
+      <c r="L70" s="16" t="n">
+        <v>243401</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tổng hợp theo tháng</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Mọi ô dưới đây là CÔNG THỨC trỏ về các sheet dữ liệu — sửa dữ liệu thì số này tự đổi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ chuỗi grain "day" mới được CỘNG (SUMIFS). window28 và state lấy GIÁ TRỊ NGÀY QUÉT CUỐI CÙNG của tháng (INDEX).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>CỘNG ĐƯỢC — số theo ngày thật (Social)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Chỉ số</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>FB — tương tác/ngày</t>
-        </is>
-      </c>
-      <c r="B7" s="16">
-        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v/>
-      </c>
-      <c r="C7" s="16">
-        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v/>
-      </c>
-      <c r="D7" s="16">
-        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v/>
-      </c>
-      <c r="E7" s="16">
-        <f>SUMIFS('Social — theo ngày'!B6:B114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>FB — view 3 giây/ngày</t>
-        </is>
-      </c>
-      <c r="B8" s="16">
-        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v/>
-      </c>
-      <c r="C8" s="16">
-        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v/>
-      </c>
-      <c r="D8" s="16">
-        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v/>
-      </c>
-      <c r="E8" s="16">
-        <f>SUMIFS('Social — theo ngày'!C6:C114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>FB — views/ngày</t>
-        </is>
-      </c>
-      <c r="B9" s="16">
-        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v/>
-      </c>
-      <c r="C9" s="16">
-        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v/>
-      </c>
-      <c r="D9" s="16">
-        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v/>
-      </c>
-      <c r="E9" s="16">
-        <f>SUMIFS('Social — theo ngày'!D6:D114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>FB — lượt ghé/ngày</t>
-        </is>
-      </c>
-      <c r="B10" s="16">
-        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v/>
-      </c>
-      <c r="C10" s="16">
-        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v/>
-      </c>
-      <c r="D10" s="16">
-        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v/>
-      </c>
-      <c r="E10" s="16">
-        <f>SUMIFS('Social — theo ngày'!E6:E114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>IG — tương tác/ngày</t>
-        </is>
-      </c>
-      <c r="B11" s="16">
-        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v/>
-      </c>
-      <c r="C11" s="16">
-        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v/>
-      </c>
-      <c r="D11" s="16">
-        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v/>
-      </c>
-      <c r="E11" s="16">
-        <f>SUMIFS('Social — theo ngày'!F6:F114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>IG — reach/ngày</t>
-        </is>
-      </c>
-      <c r="B12" s="16">
-        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v/>
-      </c>
-      <c r="C12" s="16">
-        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v/>
-      </c>
-      <c r="D12" s="16">
-        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v/>
-      </c>
-      <c r="E12" s="16">
-        <f>SUMIFS('Social — theo ngày'!G6:G114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>IG — views/ngày</t>
-        </is>
-      </c>
-      <c r="B13" s="16">
-        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,7,31))</f>
-        <v/>
-      </c>
-      <c r="C13" s="16">
-        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,8,31))</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,9,30))</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>SUMIFS('Social — theo ngày'!H6:H114,'Social — theo ngày'!$A$6:$A$114,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$114,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>KHÔNG CỘNG — Social — 28 ngày (lấy ngày quét cuối tháng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Chỉ số</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>FB — followers</t>
-        </is>
-      </c>
-      <c r="B17" s="24">
-        <f>'Social — 28 ngày'!B11</f>
-        <v/>
-      </c>
-      <c r="C17" s="24">
-        <f>'Social — 28 ngày'!B32</f>
-        <v/>
-      </c>
-      <c r="D17" s="24">
-        <f>'Social — 28 ngày'!B54</f>
-        <v/>
-      </c>
-      <c r="E17" s="24">
-        <f>'Social — 28 ngày'!B72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>FB — tương tác (28n)</t>
-        </is>
-      </c>
-      <c r="B18" s="24">
-        <f>'Social — 28 ngày'!C11</f>
-        <v/>
-      </c>
-      <c r="C18" s="24">
-        <f>'Social — 28 ngày'!C32</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>'Social — 28 ngày'!C54</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>'Social — 28 ngày'!C72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="inlineStr">
-        <is>
-          <t>FB — views (28n)</t>
-        </is>
-      </c>
-      <c r="B19" s="24">
-        <f>'Social — 28 ngày'!D11</f>
-        <v/>
-      </c>
-      <c r="C19" s="24">
-        <f>'Social — 28 ngày'!D32</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>'Social — 28 ngày'!D54</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>'Social — 28 ngày'!D72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>FB — lượt ghé (28n)</t>
-        </is>
-      </c>
-      <c r="B20" s="24">
-        <f>'Social — 28 ngày'!E11</f>
-        <v/>
-      </c>
-      <c r="C20" s="24">
-        <f>'Social — 28 ngày'!E32</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>'Social — 28 ngày'!E54</f>
-        <v/>
-      </c>
-      <c r="E20" s="24">
-        <f>'Social — 28 ngày'!E72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>IG — followers</t>
-        </is>
-      </c>
-      <c r="B21" s="24">
-        <f>'Social — 28 ngày'!F11</f>
-        <v/>
-      </c>
-      <c r="C21" s="24">
-        <f>'Social — 28 ngày'!F32</f>
-        <v/>
-      </c>
-      <c r="D21" s="24">
-        <f>'Social — 28 ngày'!F54</f>
-        <v/>
-      </c>
-      <c r="E21" s="24">
-        <f>'Social — 28 ngày'!F72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
-        <is>
-          <t>IG — tương tác (28n)</t>
-        </is>
-      </c>
-      <c r="B22" s="24">
-        <f>'Social — 28 ngày'!G11</f>
-        <v/>
-      </c>
-      <c r="C22" s="24">
-        <f>'Social — 28 ngày'!G32</f>
-        <v/>
-      </c>
-      <c r="D22" s="24">
-        <f>'Social — 28 ngày'!G54</f>
-        <v/>
-      </c>
-      <c r="E22" s="24">
-        <f>'Social — 28 ngày'!G72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>IG — reach (28n)</t>
-        </is>
-      </c>
-      <c r="B23" s="24">
-        <f>'Social — 28 ngày'!H11</f>
-        <v/>
-      </c>
-      <c r="C23" s="24">
-        <f>'Social — 28 ngày'!H32</f>
-        <v/>
-      </c>
-      <c r="D23" s="24">
-        <f>'Social — 28 ngày'!H54</f>
-        <v/>
-      </c>
-      <c r="E23" s="24">
-        <f>'Social — 28 ngày'!H72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>IG — views (28n)</t>
-        </is>
-      </c>
-      <c r="B24" s="24">
-        <f>'Social — 28 ngày'!I11</f>
-        <v/>
-      </c>
-      <c r="C24" s="24">
-        <f>'Social — 28 ngày'!I32</f>
-        <v/>
-      </c>
-      <c r="D24" s="24">
-        <f>'Social — 28 ngày'!I54</f>
-        <v/>
-      </c>
-      <c r="E24" s="24">
-        <f>'Social — 28 ngày'!I72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>LinkedIn — followers</t>
-        </is>
-      </c>
-      <c r="B25" s="24">
-        <f>'Social — 28 ngày'!J11</f>
-        <v/>
-      </c>
-      <c r="C25" s="24">
-        <f>'Social — 28 ngày'!J32</f>
-        <v/>
-      </c>
-      <c r="D25" s="24">
-        <f>'Social — 28 ngày'!J54</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>'Social — 28 ngày'!J72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>LinkedIn — impressions (28n)</t>
-        </is>
-      </c>
-      <c r="B26" s="24">
-        <f>'Social — 28 ngày'!K11</f>
-        <v/>
-      </c>
-      <c r="C26" s="24">
-        <f>'Social — 28 ngày'!K32</f>
-        <v/>
-      </c>
-      <c r="D26" s="24">
-        <f>'Social — 28 ngày'!K54</f>
-        <v/>
-      </c>
-      <c r="E26" s="24">
-        <f>'Social — 28 ngày'!K72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>LinkedIn — lượt xem trang (28n)</t>
-        </is>
-      </c>
-      <c r="B27" s="24">
-        <f>'Social — 28 ngày'!L11</f>
-        <v/>
-      </c>
-      <c r="C27" s="24">
-        <f>'Social — 28 ngày'!L32</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
-        <f>'Social — 28 ngày'!L54</f>
-        <v/>
-      </c>
-      <c r="E27" s="24">
-        <f>'Social — 28 ngày'!L72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>LinkedIn — reactions (28n)</t>
-        </is>
-      </c>
-      <c r="B28" s="24">
-        <f>'Social — 28 ngày'!M11</f>
-        <v/>
-      </c>
-      <c r="C28" s="24">
-        <f>'Social — 28 ngày'!M32</f>
-        <v/>
-      </c>
-      <c r="D28" s="24">
-        <f>'Social — 28 ngày'!M54</f>
-        <v/>
-      </c>
-      <c r="E28" s="24">
-        <f>'Social — 28 ngày'!M72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>YouTube — subscribers</t>
-        </is>
-      </c>
-      <c r="B29" s="24">
-        <f>'Social — 28 ngày'!N11</f>
-        <v/>
-      </c>
-      <c r="C29" s="24">
-        <f>'Social — 28 ngày'!N32</f>
-        <v/>
-      </c>
-      <c r="D29" s="24">
-        <f>'Social — 28 ngày'!N54</f>
-        <v/>
-      </c>
-      <c r="E29" s="24">
-        <f>'Social — 28 ngày'!N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>YouTube — views (28n)</t>
-        </is>
-      </c>
-      <c r="B30" s="24">
-        <f>'Social — 28 ngày'!O11</f>
-        <v/>
-      </c>
-      <c r="C30" s="24">
-        <f>'Social — 28 ngày'!O32</f>
-        <v/>
-      </c>
-      <c r="D30" s="24">
-        <f>'Social — 28 ngày'!O54</f>
-        <v/>
-      </c>
-      <c r="E30" s="24">
-        <f>'Social — 28 ngày'!O72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>KHÔNG CỘNG — SEO (lấy ngày quét cuối tháng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>Chỉ số</t>
-        </is>
-      </c>
-      <c r="B33" s="21" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>Ahrefs — trích dẫn AI</t>
-        </is>
-      </c>
-      <c r="B34" s="24">
-        <f>'SEO'!B6</f>
-        <v/>
-      </c>
-      <c r="C34" s="24">
-        <f>'SEO'!B11</f>
-        <v/>
-      </c>
-      <c r="D34" s="24">
-        <f>'SEO'!B30</f>
-        <v/>
-      </c>
-      <c r="E34" s="24">
-        <f>'SEO'!B54</f>
-        <v/>
-      </c>
-      <c r="F34" s="24">
-        <f>'SEO'!B72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
-        <is>
-          <t>Ahrefs — backlinks</t>
-        </is>
-      </c>
-      <c r="B35" s="24">
-        <f>'SEO'!C6</f>
-        <v/>
-      </c>
-      <c r="C35" s="24">
-        <f>'SEO'!C11</f>
-        <v/>
-      </c>
-      <c r="D35" s="24">
-        <f>'SEO'!C30</f>
-        <v/>
-      </c>
-      <c r="E35" s="24">
-        <f>'SEO'!C54</f>
-        <v/>
-      </c>
-      <c r="F35" s="24">
-        <f>'SEO'!C72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>Ahrefs — referring domains</t>
-        </is>
-      </c>
-      <c r="B36" s="24">
-        <f>'SEO'!D6</f>
-        <v/>
-      </c>
-      <c r="C36" s="24">
-        <f>'SEO'!D11</f>
-        <v/>
-      </c>
-      <c r="D36" s="24">
-        <f>'SEO'!D30</f>
-        <v/>
-      </c>
-      <c r="E36" s="24">
-        <f>'SEO'!D54</f>
-        <v/>
-      </c>
-      <c r="F36" s="24">
-        <f>'SEO'!D72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>GA4 — engagement %</t>
-        </is>
-      </c>
-      <c r="B37" s="24">
-        <f>'SEO'!E6</f>
-        <v/>
-      </c>
-      <c r="C37" s="24">
-        <f>'SEO'!E11</f>
-        <v/>
-      </c>
-      <c r="D37" s="24">
-        <f>'SEO'!E30</f>
-        <v/>
-      </c>
-      <c r="E37" s="24">
-        <f>'SEO'!E54</f>
-        <v/>
-      </c>
-      <c r="F37" s="24">
-        <f>'SEO'!E72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>GA4 — key events</t>
-        </is>
-      </c>
-      <c r="B38" s="24">
-        <f>'SEO'!F6</f>
-        <v/>
-      </c>
-      <c r="C38" s="24">
-        <f>'SEO'!F11</f>
-        <v/>
-      </c>
-      <c r="D38" s="24">
-        <f>'SEO'!F30</f>
-        <v/>
-      </c>
-      <c r="E38" s="24">
-        <f>'SEO'!F54</f>
-        <v/>
-      </c>
-      <c r="F38" s="24">
-        <f>'SEO'!F72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>GA4 — sessions</t>
-        </is>
-      </c>
-      <c r="B39" s="24">
-        <f>'SEO'!G6</f>
-        <v/>
-      </c>
-      <c r="C39" s="24">
-        <f>'SEO'!G11</f>
-        <v/>
-      </c>
-      <c r="D39" s="24">
-        <f>'SEO'!G30</f>
-        <v/>
-      </c>
-      <c r="E39" s="24">
-        <f>'SEO'!G54</f>
-        <v/>
-      </c>
-      <c r="F39" s="24">
-        <f>'SEO'!G72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>GA4 — users</t>
-        </is>
-      </c>
-      <c r="B40" s="24">
-        <f>'SEO'!H6</f>
-        <v/>
-      </c>
-      <c r="C40" s="24">
-        <f>'SEO'!H11</f>
-        <v/>
-      </c>
-      <c r="D40" s="24">
-        <f>'SEO'!H30</f>
-        <v/>
-      </c>
-      <c r="E40" s="24">
-        <f>'SEO'!H54</f>
-        <v/>
-      </c>
-      <c r="F40" s="24">
-        <f>'SEO'!H72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>GSC — clicks</t>
-        </is>
-      </c>
-      <c r="B41" s="24">
-        <f>'SEO'!I6</f>
-        <v/>
-      </c>
-      <c r="C41" s="24">
-        <f>'SEO'!I11</f>
-        <v/>
-      </c>
-      <c r="D41" s="24">
-        <f>'SEO'!I30</f>
-        <v/>
-      </c>
-      <c r="E41" s="24">
-        <f>'SEO'!I54</f>
-        <v/>
-      </c>
-      <c r="F41" s="24">
-        <f>'SEO'!I72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>GSC — CTR %</t>
-        </is>
-      </c>
-      <c r="B42" s="24">
-        <f>'SEO'!J6</f>
-        <v/>
-      </c>
-      <c r="C42" s="24">
-        <f>'SEO'!J11</f>
-        <v/>
-      </c>
-      <c r="D42" s="24">
-        <f>'SEO'!J30</f>
-        <v/>
-      </c>
-      <c r="E42" s="24">
-        <f>'SEO'!J54</f>
-        <v/>
-      </c>
-      <c r="F42" s="24">
-        <f>'SEO'!J72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
-        <is>
-          <t>GSC — impressions</t>
-        </is>
-      </c>
-      <c r="B43" s="24">
-        <f>'SEO'!K6</f>
-        <v/>
-      </c>
-      <c r="C43" s="24">
-        <f>'SEO'!K11</f>
-        <v/>
-      </c>
-      <c r="D43" s="24">
-        <f>'SEO'!K30</f>
-        <v/>
-      </c>
-      <c r="E43" s="24">
-        <f>'SEO'!K54</f>
-        <v/>
-      </c>
-      <c r="F43" s="24">
-        <f>'SEO'!K72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>GSC — vị trí TB</t>
-        </is>
-      </c>
-      <c r="B44" s="24">
-        <f>'SEO'!L6</f>
-        <v/>
-      </c>
-      <c r="C44" s="24">
-        <f>'SEO'!L11</f>
-        <v/>
-      </c>
-      <c r="D44" s="24">
-        <f>'SEO'!L30</f>
-        <v/>
-      </c>
-      <c r="E44" s="24">
-        <f>'SEO'!L54</f>
-        <v/>
-      </c>
-      <c r="F44" s="24">
-        <f>'SEO'!L72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="22" t="inlineStr">
-        <is>
-          <t>GSC — số truy vấn</t>
-        </is>
-      </c>
-      <c r="B45" s="24">
-        <f>'SEO'!M6</f>
-        <v/>
-      </c>
-      <c r="C45" s="24">
-        <f>'SEO'!M11</f>
-        <v/>
-      </c>
-      <c r="D45" s="24">
-        <f>'SEO'!M30</f>
-        <v/>
-      </c>
-      <c r="E45" s="24">
-        <f>'SEO'!M54</f>
-        <v/>
-      </c>
-      <c r="F45" s="24">
-        <f>'SEO'!M72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>Sitemap — số URL</t>
-        </is>
-      </c>
-      <c r="B46" s="24">
-        <f>'SEO'!N6</f>
-        <v/>
-      </c>
-      <c r="C46" s="24">
-        <f>'SEO'!N11</f>
-        <v/>
-      </c>
-      <c r="D46" s="24">
-        <f>'SEO'!N30</f>
-        <v/>
-      </c>
-      <c r="E46" s="24">
-        <f>'SEO'!N54</f>
-        <v/>
-      </c>
-      <c r="F46" s="24">
-        <f>'SEO'!N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>TTFB trung bình (ms)</t>
-        </is>
-      </c>
-      <c r="B47" s="24">
-        <f>'SEO'!O6</f>
-        <v/>
-      </c>
-      <c r="C47" s="24">
-        <f>'SEO'!O11</f>
-        <v/>
-      </c>
-      <c r="D47" s="24">
-        <f>'SEO'!O30</f>
-        <v/>
-      </c>
-      <c r="E47" s="24">
-        <f>'SEO'!O54</f>
-        <v/>
-      </c>
-      <c r="F47" s="24">
-        <f>'SEO'!O72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>KHÔNG CỘNG — Audit (lấy ngày quét cuối tháng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>Chỉ số</t>
-        </is>
-      </c>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="22" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="B51" s="24">
-        <f>'Audit'!B10</f>
-        <v/>
-      </c>
-      <c r="C51" s="24">
-        <f>'Audit'!B29</f>
-        <v/>
-      </c>
-      <c r="D51" s="24">
-        <f>'Audit'!B51</f>
-        <v/>
-      </c>
-      <c r="E51" s="24">
-        <f>'Audit'!B69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>Crawlability</t>
-        </is>
-      </c>
-      <c r="B52" s="24">
-        <f>'Audit'!C10</f>
-        <v/>
-      </c>
-      <c r="C52" s="24">
-        <f>'Audit'!C29</f>
-        <v/>
-      </c>
-      <c r="D52" s="24">
-        <f>'Audit'!C51</f>
-        <v/>
-      </c>
-      <c r="E52" s="24">
-        <f>'Audit'!C69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
-        <is>
-          <t>Health score</t>
-        </is>
-      </c>
-      <c r="B53" s="24">
-        <f>'Audit'!D10</f>
-        <v/>
-      </c>
-      <c r="C53" s="24">
-        <f>'Audit'!D29</f>
-        <v/>
-      </c>
-      <c r="D53" s="24">
-        <f>'Audit'!D51</f>
-        <v/>
-      </c>
-      <c r="E53" s="24">
-        <f>'Audit'!D69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
-        <is>
-          <t>On-page / Meta</t>
-        </is>
-      </c>
-      <c r="B54" s="24">
-        <f>'Audit'!E10</f>
-        <v/>
-      </c>
-      <c r="C54" s="24">
-        <f>'Audit'!E29</f>
-        <v/>
-      </c>
-      <c r="D54" s="24">
-        <f>'Audit'!E51</f>
-        <v/>
-      </c>
-      <c r="E54" s="24">
-        <f>'Audit'!E69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>Số trang crawl</t>
-        </is>
-      </c>
-      <c r="B55" s="24">
-        <f>'Audit'!F10</f>
-        <v/>
-      </c>
-      <c r="C55" s="24">
-        <f>'Audit'!F29</f>
-        <v/>
-      </c>
-      <c r="D55" s="24">
-        <f>'Audit'!F51</f>
-        <v/>
-      </c>
-      <c r="E55" s="24">
-        <f>'Audit'!F69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="22" t="inlineStr">
-        <is>
-          <t>Performance / TTFB</t>
-        </is>
-      </c>
-      <c r="B56" s="24">
-        <f>'Audit'!G10</f>
-        <v/>
-      </c>
-      <c r="C56" s="24">
-        <f>'Audit'!G29</f>
-        <v/>
-      </c>
-      <c r="D56" s="24">
-        <f>'Audit'!G51</f>
-        <v/>
-      </c>
-      <c r="E56" s="24">
-        <f>'Audit'!G69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>Sitemap — số URL</t>
-        </is>
-      </c>
-      <c r="B57" s="24">
-        <f>'Audit'!H10</f>
-        <v/>
-      </c>
-      <c r="C57" s="24">
-        <f>'Audit'!H29</f>
-        <v/>
-      </c>
-      <c r="D57" s="24">
-        <f>'Audit'!H51</f>
-        <v/>
-      </c>
-      <c r="E57" s="24">
-        <f>'Audit'!H69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="22" t="inlineStr">
-        <is>
-          <t>Structured data</t>
-        </is>
-      </c>
-      <c r="B58" s="24">
-        <f>'Audit'!I10</f>
-        <v/>
-      </c>
-      <c r="C58" s="24">
-        <f>'Audit'!I29</f>
-        <v/>
-      </c>
-      <c r="D58" s="24">
-        <f>'Audit'!I51</f>
-        <v/>
-      </c>
-      <c r="E58" s="24">
-        <f>'Audit'!I69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="22" t="inlineStr">
-        <is>
-          <t>TTFB trung bình (ms)</t>
-        </is>
-      </c>
-      <c r="B59" s="24">
-        <f>'Audit'!J10</f>
-        <v/>
-      </c>
-      <c r="C59" s="24">
-        <f>'Audit'!J29</f>
-        <v/>
-      </c>
-      <c r="D59" s="24">
-        <f>'Audit'!J51</f>
-        <v/>
-      </c>
-      <c r="E59" s="24">
-        <f>'Audit'!J69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="22" t="inlineStr">
-        <is>
-          <t>TTFB trung vị (ms)</t>
-        </is>
-      </c>
-      <c r="B60" s="24">
-        <f>'Audit'!K10</f>
-        <v/>
-      </c>
-      <c r="C60" s="24">
-        <f>'Audit'!K29</f>
-        <v/>
-      </c>
-      <c r="D60" s="24">
-        <f>'Audit'!K51</f>
-        <v/>
-      </c>
-      <c r="E60" s="24">
-        <f>'Audit'!K69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="22" t="inlineStr">
-        <is>
-          <t>Tổng số từ</t>
-        </is>
-      </c>
-      <c r="B61" s="24">
-        <f>'Audit'!L10</f>
-        <v/>
-      </c>
-      <c r="C61" s="24">
-        <f>'Audit'!L29</f>
-        <v/>
-      </c>
-      <c r="D61" s="24">
-        <f>'Audit'!L51</f>
-        <v/>
-      </c>
-      <c r="E61" s="24">
-        <f>'Audit'!L69</f>
-        <v/>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v>125</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v>195</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>160</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v>147</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>354</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v>3579</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v>4978</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>4776</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v>189</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v>314</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>425</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>543</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v>51</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v>69</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>25</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v>275</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v>387</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>177</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <v>869</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <v>1161</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <v>2465</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!B11</f>
+        <v>115</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!B32</f>
+        <v>115</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!B54</f>
+        <v>116</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!B73</f>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!C11</f>
+        <v>130</v>
+      </c>
+      <c r="C18" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!C32</f>
+        <v>184</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!C54</f>
+        <v>141</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!C73</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!D11</f>
+        <v>3635</v>
+      </c>
+      <c r="C19" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!D32</f>
+        <v>4735</v>
+      </c>
+      <c r="D19" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!D54</f>
+        <v>4519</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!D73</f>
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!E11</f>
+        <v>171</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!E32</f>
+        <v>280</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!E54</f>
+        <v>422</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!E73</f>
+        <v>556</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!F11</f>
+        <v>33</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!F32</f>
+        <v>47</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!F54</f>
+        <v>49</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!F73</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!G11</f>
+        <v>49</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!G32</f>
+        <v>68</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!G54</f>
+        <v>20</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!G73</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!H11</f>
+        <v>192</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!H32</f>
+        <v>275</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!H54</f>
+        <v>87</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!H73</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!I11</f>
+        <v>855</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!I32</f>
+        <v>1039</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!I54</f>
+        <v>2258</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!I73</f>
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!J11</f>
+        <v>55</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!J32</f>
+        <v>100</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!J54</f>
+        <v>102</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!J73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!K11</f>
+        <v>1351</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!K32</f>
+        <v>1691</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!K54</f>
+        <v>1193</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!K73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!L11</f>
+        <v>39</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!L32</f>
+        <v>127</v>
+      </c>
+      <c r="D27" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!L54</f>
+        <v>24</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!L73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!M11</f>
+        <v>56</v>
+      </c>
+      <c r="C28" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!M32</f>
+        <v>86</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!M54</f>
+        <v>36</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!M73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!N11</f>
+        <v>4</v>
+      </c>
+      <c r="C29" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!N32</f>
+        <v>4</v>
+      </c>
+      <c r="D29" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!N54</f>
+        <v>4</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!N73</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!O11</f>
+        <v>28</v>
+      </c>
+      <c r="C30" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!O32</f>
+        <v>59</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!O54</f>
+        <v>634</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <f aca="false">'Social — 28 ngày'!O73</f>
+        <v>868</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="24" t="n">
+        <f aca="false">SEO!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <f aca="false">SEO!B11</f>
+        <v>14</v>
+      </c>
+      <c r="D34" s="24" t="n">
+        <f aca="false">SEO!B30</f>
+        <v>21</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <f aca="false">SEO!B54</f>
+        <v>16</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <f aca="false">SEO!B73</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="24" t="n">
+        <f aca="false">SEO!C6</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="24" t="n">
+        <f aca="false">SEO!C11</f>
+        <v>346</v>
+      </c>
+      <c r="D35" s="24" t="n">
+        <f aca="false">SEO!C30</f>
+        <v>364</v>
+      </c>
+      <c r="E35" s="24" t="n">
+        <f aca="false">SEO!C54</f>
+        <v>918</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <f aca="false">SEO!C73</f>
+        <v>909</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="24" t="n">
+        <f aca="false">SEO!D6</f>
+        <v>244</v>
+      </c>
+      <c r="C36" s="24" t="n">
+        <f aca="false">SEO!D11</f>
+        <v>341</v>
+      </c>
+      <c r="D36" s="24" t="n">
+        <f aca="false">SEO!D30</f>
+        <v>349</v>
+      </c>
+      <c r="E36" s="24" t="n">
+        <f aca="false">SEO!D54</f>
+        <v>882</v>
+      </c>
+      <c r="F36" s="24" t="n">
+        <f aca="false">SEO!D73</f>
+        <v>873</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <f aca="false">SEO!E6</f>
+        <v>18.9</v>
+      </c>
+      <c r="C37" s="24" t="n">
+        <f aca="false">SEO!E11</f>
+        <v>66.7</v>
+      </c>
+      <c r="D37" s="24" t="n">
+        <f aca="false">SEO!E30</f>
+        <v>42.93</v>
+      </c>
+      <c r="E37" s="24" t="n">
+        <f aca="false">SEO!E54</f>
+        <v>33.99</v>
+      </c>
+      <c r="F37" s="24" t="n">
+        <f aca="false">SEO!E73</f>
+        <v>39.77</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="24" t="n">
+        <f aca="false">SEO!F6</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="24" t="n">
+        <f aca="false">SEO!F11</f>
+        <v>42</v>
+      </c>
+      <c r="D38" s="24" t="n">
+        <f aca="false">SEO!F30</f>
+        <v>7</v>
+      </c>
+      <c r="E38" s="24" t="n">
+        <f aca="false">SEO!F54</f>
+        <v>4</v>
+      </c>
+      <c r="F38" s="24" t="n">
+        <f aca="false">SEO!F73</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="24" t="n">
+        <f aca="false">SEO!G6</f>
+        <v>322</v>
+      </c>
+      <c r="C39" s="24" t="n">
+        <f aca="false">SEO!G11</f>
+        <v>405</v>
+      </c>
+      <c r="D39" s="24" t="n">
+        <f aca="false">SEO!G30</f>
+        <v>375</v>
+      </c>
+      <c r="E39" s="24" t="n">
+        <f aca="false">SEO!G54</f>
+        <v>559</v>
+      </c>
+      <c r="F39" s="24" t="n">
+        <f aca="false">SEO!G73</f>
+        <v>699</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="24" t="n">
+        <f aca="false">SEO!H6</f>
+        <v>205</v>
+      </c>
+      <c r="C40" s="24" t="n">
+        <f aca="false">SEO!H11</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="24" t="n">
+        <f aca="false">SEO!H30</f>
+        <v>204</v>
+      </c>
+      <c r="E40" s="24" t="n">
+        <f aca="false">SEO!H54</f>
+        <v>394</v>
+      </c>
+      <c r="F40" s="24" t="n">
+        <f aca="false">SEO!H73</f>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="24" t="n">
+        <f aca="false">SEO!I6</f>
+        <v>47</v>
+      </c>
+      <c r="C41" s="24" t="n">
+        <f aca="false">SEO!I11</f>
+        <v>67</v>
+      </c>
+      <c r="D41" s="24" t="n">
+        <f aca="false">SEO!I30</f>
+        <v>67</v>
+      </c>
+      <c r="E41" s="24" t="n">
+        <f aca="false">SEO!I54</f>
+        <v>30</v>
+      </c>
+      <c r="F41" s="24" t="n">
+        <f aca="false">SEO!I73</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" s="24" t="n">
+        <f aca="false">SEO!J6</f>
+        <v>8</v>
+      </c>
+      <c r="C42" s="24" t="n">
+        <f aca="false">SEO!J11</f>
+        <v>6.5</v>
+      </c>
+      <c r="D42" s="24" t="n">
+        <f aca="false">SEO!J30</f>
+        <v>3.8</v>
+      </c>
+      <c r="E42" s="24" t="n">
+        <f aca="false">SEO!J54</f>
+        <v>2.8</v>
+      </c>
+      <c r="F42" s="24" t="n">
+        <f aca="false">SEO!J73</f>
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="24" t="n">
+        <f aca="false">SEO!K6</f>
+        <v>587</v>
+      </c>
+      <c r="C43" s="24" t="n">
+        <f aca="false">SEO!K11</f>
+        <v>1032</v>
+      </c>
+      <c r="D43" s="24" t="n">
+        <f aca="false">SEO!K30</f>
+        <v>1757</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <f aca="false">SEO!K54</f>
+        <v>1056</v>
+      </c>
+      <c r="F43" s="24" t="n">
+        <f aca="false">SEO!K73</f>
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" s="24" t="n">
+        <f aca="false">SEO!L6</f>
+        <v>13.8</v>
+      </c>
+      <c r="C44" s="24" t="n">
+        <f aca="false">SEO!L11</f>
+        <v>24.1</v>
+      </c>
+      <c r="D44" s="24" t="n">
+        <f aca="false">SEO!L30</f>
+        <v>29.4</v>
+      </c>
+      <c r="E44" s="24" t="n">
+        <f aca="false">SEO!L54</f>
+        <v>25.8</v>
+      </c>
+      <c r="F44" s="24" t="n">
+        <f aca="false">SEO!L73</f>
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <f aca="false">SEO!M6</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="24" t="n">
+        <f aca="false">SEO!M11</f>
+        <v>92</v>
+      </c>
+      <c r="D45" s="24" t="n">
+        <f aca="false">SEO!M30</f>
+        <v>151</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <f aca="false">SEO!M54</f>
+        <v>80</v>
+      </c>
+      <c r="F45" s="24" t="n">
+        <f aca="false">SEO!M73</f>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="24" t="n">
+        <f aca="false">SEO!N6</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="24" t="n">
+        <f aca="false">SEO!N11</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="24" t="n">
+        <f aca="false">SEO!N30</f>
+        <v>95</v>
+      </c>
+      <c r="E46" s="24" t="n">
+        <f aca="false">SEO!N54</f>
+        <v>119</v>
+      </c>
+      <c r="F46" s="24" t="n">
+        <f aca="false">SEO!N73</f>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="24" t="n">
+        <f aca="false">SEO!O6</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="24" t="n">
+        <f aca="false">SEO!O11</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="24" t="n">
+        <f aca="false">SEO!O30</f>
+        <v>1022</v>
+      </c>
+      <c r="E47" s="24" t="n">
+        <f aca="false">SEO!O54</f>
+        <v>342</v>
+      </c>
+      <c r="F47" s="24" t="n">
+        <f aca="false">SEO!O73</f>
+        <v>314.4</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="24" t="n">
+        <f aca="false">Audit!B10</f>
+        <v>77</v>
+      </c>
+      <c r="C51" s="24" t="n">
+        <f aca="false">Audit!B29</f>
+        <v>88</v>
+      </c>
+      <c r="D51" s="24" t="n">
+        <f aca="false">Audit!B51</f>
+        <v>93</v>
+      </c>
+      <c r="E51" s="24" t="n">
+        <f aca="false">Audit!B70</f>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="24" t="n">
+        <f aca="false">Audit!C10</f>
+        <v>89</v>
+      </c>
+      <c r="C52" s="24" t="n">
+        <f aca="false">Audit!C29</f>
+        <v>97</v>
+      </c>
+      <c r="D52" s="24" t="n">
+        <f aca="false">Audit!C51</f>
+        <v>98</v>
+      </c>
+      <c r="E52" s="24" t="n">
+        <f aca="false">Audit!C70</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="24" t="n">
+        <f aca="false">Audit!D10</f>
+        <v>84</v>
+      </c>
+      <c r="C53" s="24" t="n">
+        <f aca="false">Audit!D29</f>
+        <v>92</v>
+      </c>
+      <c r="D53" s="24" t="n">
+        <f aca="false">Audit!D51</f>
+        <v>95</v>
+      </c>
+      <c r="E53" s="24" t="n">
+        <f aca="false">Audit!D70</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="24" t="n">
+        <f aca="false">Audit!E10</f>
+        <v>76</v>
+      </c>
+      <c r="C54" s="24" t="n">
+        <f aca="false">Audit!E29</f>
+        <v>91</v>
+      </c>
+      <c r="D54" s="24" t="n">
+        <f aca="false">Audit!E51</f>
+        <v>92</v>
+      </c>
+      <c r="E54" s="24" t="n">
+        <f aca="false">Audit!E70</f>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="24" t="n">
+        <f aca="false">Audit!F10</f>
+        <v>68</v>
+      </c>
+      <c r="C55" s="24" t="n">
+        <f aca="false">Audit!F29</f>
+        <v>91</v>
+      </c>
+      <c r="D55" s="24" t="n">
+        <f aca="false">Audit!F51</f>
+        <v>118</v>
+      </c>
+      <c r="E55" s="24" t="n">
+        <f aca="false">Audit!F70</f>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="24" t="n">
+        <f aca="false">Audit!G10</f>
+        <v>91</v>
+      </c>
+      <c r="C56" s="24" t="n">
+        <f aca="false">Audit!G29</f>
+        <v>88</v>
+      </c>
+      <c r="D56" s="24" t="n">
+        <f aca="false">Audit!G51</f>
+        <v>98</v>
+      </c>
+      <c r="E56" s="24" t="n">
+        <f aca="false">Audit!G70</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B57" s="24" t="n">
+        <f aca="false">Audit!H10</f>
+        <v>67</v>
+      </c>
+      <c r="C57" s="24" t="n">
+        <f aca="false">Audit!H29</f>
+        <v>92</v>
+      </c>
+      <c r="D57" s="24" t="n">
+        <f aca="false">Audit!H51</f>
+        <v>119</v>
+      </c>
+      <c r="E57" s="24" t="n">
+        <f aca="false">Audit!H70</f>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="24" t="n">
+        <f aca="false">Audit!I10</f>
+        <v>82</v>
+      </c>
+      <c r="C58" s="24" t="n">
+        <f aca="false">Audit!I29</f>
+        <v>96</v>
+      </c>
+      <c r="D58" s="24" t="n">
+        <f aca="false">Audit!I51</f>
+        <v>92</v>
+      </c>
+      <c r="E58" s="24" t="n">
+        <f aca="false">Audit!I70</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" s="24" t="n">
+        <f aca="false">Audit!J10</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="24" t="n">
+        <f aca="false">Audit!J29</f>
+        <v>862</v>
+      </c>
+      <c r="D59" s="24" t="n">
+        <f aca="false">Audit!J51</f>
+        <v>342</v>
+      </c>
+      <c r="E59" s="24" t="n">
+        <f aca="false">Audit!J70</f>
+        <v>314.4</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="24" t="n">
+        <f aca="false">Audit!K10</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="24" t="n">
+        <f aca="false">Audit!K29</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="24" t="n">
+        <f aca="false">Audit!K51</f>
+        <v>276</v>
+      </c>
+      <c r="E60" s="24" t="n">
+        <f aca="false">Audit!K70</f>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B61" s="24" t="n">
+        <f aca="false">Audit!L10</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="24" t="n">
+        <f aca="false">Audit!L29</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="24" t="n">
+        <f aca="false">Audit!L51</f>
+        <v>241329</v>
+      </c>
+      <c r="E61" s="24" t="n">
+        <f aca="false">Audit!L70</f>
+        <v>243401</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -7234,10 +7234,18 @@
       <c r="I73" s="16" t="n">
         <v>1933</v>
       </c>
-      <c r="J73" s="16"/>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+      <c r="J73" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="K73" s="16" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L73" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="M73" s="16" t="n">
+        <v>38</v>
+      </c>
       <c r="N73" s="16" t="n">
         <v>7</v>
       </c>
@@ -13320,7 +13328,7 @@
       </c>
       <c r="E25" s="24" t="n">
         <f aca="false">'Social — 28 ngày'!J73</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13341,7 +13349,7 @@
       </c>
       <c r="E26" s="24" t="n">
         <f aca="false">'Social — 28 ngày'!K73</f>
-        <v>0</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13362,7 +13370,7 @@
       </c>
       <c r="E27" s="24" t="n">
         <f aca="false">'Social — 28 ngày'!L73</f>
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13383,7 +13391,7 @@
       </c>
       <c r="E28" s="24" t="n">
         <f aca="false">'Social — 28 ngày'!M73</f>
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-25 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-26 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">112 dòng × 7 chỉ số · 2026-07-05 → 2026-10-24</t>
+    <t xml:space="preserve">113 dòng × 7 chỉ số · 2026-07-05 → 2026-10-25</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">68 dòng × 14 chỉ số · 2026-07-23 → 2026-10-26</t>
+    <t xml:space="preserve">69 dòng × 14 chỉ số · 2026-07-23 → 2026-10-27</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">68 dòng × 14 chỉ số · 2026-06-30 → 2026-10-26</t>
+    <t xml:space="preserve">69 dòng × 14 chỉ số · 2026-06-30 → 2026-10-27</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">65 dòng × 11 chỉ số · 2026-07-27 → 2026-10-26</t>
+    <t xml:space="preserve">66 dòng × 11 chỉ số · 2026-07-27 → 2026-10-27</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 112 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 113 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 68 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 69 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 68 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 69 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 65 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 66 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3943,6 +3943,30 @@
       <c r="G117" s="16"/>
       <c r="H117" s="16" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="15" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B118" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D118" s="16" t="n">
+        <v>103</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="F118" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="16"/>
+      <c r="H118" s="16" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3961,7 +3985,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7250,6 +7274,53 @@
         <v>7</v>
       </c>
       <c r="O73" s="16" t="n">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="15" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B74" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>173</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>4308</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>598</v>
+      </c>
+      <c r="F74" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G74" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="H74" s="16" t="n">
+        <v>337</v>
+      </c>
+      <c r="I74" s="16" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J74" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="K74" s="16" t="n">
+        <v>1262</v>
+      </c>
+      <c r="L74" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="M74" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="N74" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>868</v>
       </c>
     </row>
@@ -7269,7 +7340,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10465,6 +10536,53 @@
       </c>
       <c r="O73" s="19" t="n">
         <v>314.4</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="15" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B74" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>906</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>870</v>
+      </c>
+      <c r="E74" s="19" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="F74" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G74" s="16" t="n">
+        <v>689</v>
+      </c>
+      <c r="H74" s="16" t="n">
+        <v>436</v>
+      </c>
+      <c r="I74" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="J74" s="19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K74" s="16" t="n">
+        <v>1424</v>
+      </c>
+      <c r="L74" s="19" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M74" s="16" t="n">
+        <v>132</v>
+      </c>
+      <c r="N74" s="16" t="n">
+        <v>121</v>
+      </c>
+      <c r="O74" s="19" t="n">
+        <v>325.5</v>
       </c>
     </row>
   </sheetData>
@@ -10483,7 +10601,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -12911,6 +13029,44 @@
       </c>
       <c r="L70" s="16" t="n">
         <v>243401</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="15" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B71" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F71" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H71" s="16" t="n">
+        <v>121</v>
+      </c>
+      <c r="I71" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="K71" s="19" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="L71" s="16" t="n">
+        <v>247309</v>
       </c>
     </row>
   </sheetData>
@@ -12978,20 +13134,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>147</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12999,20 +13155,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>419</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13020,20 +13176,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>3768</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>3871</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13041,20 +13197,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>543</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>589</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13062,19 +13218,19 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>60</v>
       </c>
     </row>
@@ -13083,19 +13239,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -13104,20 +13260,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H117,'Social — theo ngày'!$A$6:$A$117,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$117,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1688</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1744</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13159,8 +13315,8 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B73</f>
-        <v>116</v>
+        <f aca="false">'Social — 28 ngày'!B74</f>
+        <v>117</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13180,8 +13336,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C73</f>
-        <v>172</v>
+        <f aca="false">'Social — 28 ngày'!C74</f>
+        <v>173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13201,8 +13357,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D73</f>
-        <v>4270</v>
+        <f aca="false">'Social — 28 ngày'!D74</f>
+        <v>4308</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13222,8 +13378,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E73</f>
-        <v>556</v>
+        <f aca="false">'Social — 28 ngày'!E74</f>
+        <v>598</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13243,7 +13399,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F73</f>
+        <f aca="false">'Social — 28 ngày'!F74</f>
         <v>49</v>
       </c>
     </row>
@@ -13264,7 +13420,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G73</f>
+        <f aca="false">'Social — 28 ngày'!G74</f>
         <v>68</v>
       </c>
     </row>
@@ -13285,8 +13441,8 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H73</f>
-        <v>336</v>
+        <f aca="false">'Social — 28 ngày'!H74</f>
+        <v>337</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13306,8 +13462,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I73</f>
-        <v>1933</v>
+        <f aca="false">'Social — 28 ngày'!I74</f>
+        <v>1981</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13327,7 +13483,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J73</f>
+        <f aca="false">'Social — 28 ngày'!J74</f>
         <v>140</v>
       </c>
     </row>
@@ -13348,8 +13504,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K73</f>
-        <v>1275</v>
+        <f aca="false">'Social — 28 ngày'!K74</f>
+        <v>1262</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13369,7 +13525,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L73</f>
+        <f aca="false">'Social — 28 ngày'!L74</f>
         <v>82</v>
       </c>
     </row>
@@ -13390,7 +13546,7 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M73</f>
+        <f aca="false">'Social — 28 ngày'!M74</f>
         <v>38</v>
       </c>
     </row>
@@ -13411,7 +13567,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N73</f>
+        <f aca="false">'Social — 28 ngày'!N74</f>
         <v>7</v>
       </c>
     </row>
@@ -13432,7 +13588,7 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O73</f>
+        <f aca="false">'Social — 28 ngày'!O74</f>
         <v>868</v>
       </c>
     </row>
@@ -13482,8 +13638,8 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B73</f>
-        <v>26</v>
+        <f aca="false">SEO!B74</f>
+        <v>29</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13507,8 +13663,8 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C73</f>
-        <v>909</v>
+        <f aca="false">SEO!C74</f>
+        <v>906</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13532,8 +13688,8 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D73</f>
-        <v>873</v>
+        <f aca="false">SEO!D74</f>
+        <v>870</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13557,8 +13713,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E73</f>
-        <v>39.77</v>
+        <f aca="false">SEO!E74</f>
+        <v>39.04</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13582,7 +13738,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F73</f>
+        <f aca="false">SEO!F74</f>
         <v>8</v>
       </c>
     </row>
@@ -13607,8 +13763,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G73</f>
-        <v>699</v>
+        <f aca="false">SEO!G74</f>
+        <v>689</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13632,8 +13788,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H73</f>
-        <v>439</v>
+        <f aca="false">SEO!H74</f>
+        <v>436</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13657,8 +13813,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I73</f>
-        <v>24</v>
+        <f aca="false">SEO!I74</f>
+        <v>23</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13682,8 +13838,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J73</f>
-        <v>1.7</v>
+        <f aca="false">SEO!J74</f>
+        <v>1.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13707,8 +13863,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K73</f>
-        <v>1411</v>
+        <f aca="false">SEO!K74</f>
+        <v>1424</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13732,7 +13888,7 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L73</f>
+        <f aca="false">SEO!L74</f>
         <v>20.4</v>
       </c>
     </row>
@@ -13757,8 +13913,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M73</f>
-        <v>131</v>
+        <f aca="false">SEO!M74</f>
+        <v>132</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13782,8 +13938,8 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N73</f>
-        <v>119</v>
+        <f aca="false">SEO!N74</f>
+        <v>121</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13807,8 +13963,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O73</f>
-        <v>314.4</v>
+        <f aca="false">SEO!O74</f>
+        <v>325.5</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13850,8 +14006,8 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B70</f>
-        <v>93</v>
+        <f aca="false">Audit!B71</f>
+        <v>94</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13871,7 +14027,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C70</f>
+        <f aca="false">Audit!C71</f>
         <v>98</v>
       </c>
     </row>
@@ -13892,7 +14048,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D70</f>
+        <f aca="false">Audit!D71</f>
         <v>97</v>
       </c>
     </row>
@@ -13913,7 +14069,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E70</f>
+        <f aca="false">Audit!E71</f>
         <v>93</v>
       </c>
     </row>
@@ -13934,8 +14090,8 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F70</f>
-        <v>118</v>
+        <f aca="false">Audit!F71</f>
+        <v>120</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13955,7 +14111,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G70</f>
+        <f aca="false">Audit!G71</f>
         <v>98</v>
       </c>
     </row>
@@ -13976,8 +14132,8 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H70</f>
-        <v>119</v>
+        <f aca="false">Audit!H71</f>
+        <v>121</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13997,7 +14153,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I70</f>
+        <f aca="false">Audit!I71</f>
         <v>98</v>
       </c>
     </row>
@@ -14018,8 +14174,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J70</f>
-        <v>314.4</v>
+        <f aca="false">Audit!J71</f>
+        <v>325.5</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14039,8 +14195,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K70</f>
-        <v>249</v>
+        <f aca="false">Audit!K71</f>
+        <v>262.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14060,8 +14216,8 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L70</f>
-        <v>243401</v>
+        <f aca="false">Audit!L71</f>
+        <v>247309</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-26 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-27 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">113 dòng × 7 chỉ số · 2026-07-05 → 2026-10-25</t>
+    <t xml:space="preserve">114 dòng × 7 chỉ số · 2026-07-05 → 2026-10-26</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">69 dòng × 14 chỉ số · 2026-07-23 → 2026-10-27</t>
+    <t xml:space="preserve">70 dòng × 14 chỉ số · 2026-07-23 → 2026-10-28</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">69 dòng × 14 chỉ số · 2026-06-30 → 2026-10-27</t>
+    <t xml:space="preserve">70 dòng × 14 chỉ số · 2026-06-30 → 2026-10-28</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">66 dòng × 11 chỉ số · 2026-07-27 → 2026-10-27</t>
+    <t xml:space="preserve">67 dòng × 11 chỉ số · 2026-07-27 → 2026-10-28</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 113 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 114 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 69 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 70 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 69 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 70 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 66 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 67 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3967,6 +3967,30 @@
       <c r="G118" s="16"/>
       <c r="H118" s="16" t="n">
         <v>56</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="15" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B119" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C119" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" s="16" t="n">
+        <v>127</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="F119" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" s="16"/>
+      <c r="H119" s="16" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3985,7 +4009,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7322,6 +7346,53 @@
       </c>
       <c r="O74" s="16" t="n">
         <v>868</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="15" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B75" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>171</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>4255</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>609</v>
+      </c>
+      <c r="F75" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G75" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="H75" s="16" t="n">
+        <v>337</v>
+      </c>
+      <c r="I75" s="16" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J75" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="K75" s="16" t="n">
+        <v>1256</v>
+      </c>
+      <c r="L75" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="M75" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="N75" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O75" s="16" t="n">
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -7340,7 +7411,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10583,6 +10654,53 @@
       </c>
       <c r="O74" s="19" t="n">
         <v>325.5</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="15" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B75" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>906</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>870</v>
+      </c>
+      <c r="E75" s="19" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="F75" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" s="16" t="n">
+        <v>698</v>
+      </c>
+      <c r="H75" s="16" t="n">
+        <v>439</v>
+      </c>
+      <c r="I75" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J75" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K75" s="16" t="n">
+        <v>1501</v>
+      </c>
+      <c r="L75" s="19" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M75" s="16" t="n">
+        <v>138</v>
+      </c>
+      <c r="N75" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="O75" s="19" t="n">
+        <v>318.4</v>
       </c>
     </row>
   </sheetData>
@@ -10601,7 +10719,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -13067,6 +13185,44 @@
       </c>
       <c r="L71" s="16" t="n">
         <v>247309</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="15" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>121</v>
+      </c>
+      <c r="G72" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="H72" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="I72" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J72" s="19" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="K72" s="16" t="n">
+        <v>257</v>
+      </c>
+      <c r="L72" s="16" t="n">
+        <v>249426</v>
       </c>
     </row>
   </sheetData>
@@ -13134,20 +13290,20 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>148</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>152</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13155,20 +13311,20 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>432</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>433</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13176,20 +13332,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>3871</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>3998</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13197,20 +13353,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>589</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>606</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13218,20 +13374,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>60</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13239,19 +13395,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -13260,20 +13416,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H118,'Social — theo ngày'!$A$6:$A$118,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$118,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1744</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1761</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13315,7 +13471,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B74</f>
+        <f aca="false">'Social — 28 ngày'!B75</f>
         <v>117</v>
       </c>
     </row>
@@ -13336,8 +13492,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C74</f>
-        <v>173</v>
+        <f aca="false">'Social — 28 ngày'!C75</f>
+        <v>171</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13357,8 +13513,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D74</f>
-        <v>4308</v>
+        <f aca="false">'Social — 28 ngày'!D75</f>
+        <v>4255</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13378,8 +13534,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E74</f>
-        <v>598</v>
+        <f aca="false">'Social — 28 ngày'!E75</f>
+        <v>609</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13399,7 +13555,7 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F74</f>
+        <f aca="false">'Social — 28 ngày'!F75</f>
         <v>49</v>
       </c>
     </row>
@@ -13420,7 +13576,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G74</f>
+        <f aca="false">'Social — 28 ngày'!G75</f>
         <v>68</v>
       </c>
     </row>
@@ -13441,7 +13597,7 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H74</f>
+        <f aca="false">'Social — 28 ngày'!H75</f>
         <v>337</v>
       </c>
     </row>
@@ -13462,8 +13618,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I74</f>
-        <v>1981</v>
+        <f aca="false">'Social — 28 ngày'!I75</f>
+        <v>1968</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13483,8 +13639,8 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J74</f>
-        <v>140</v>
+        <f aca="false">'Social — 28 ngày'!J75</f>
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13504,8 +13660,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K74</f>
-        <v>1262</v>
+        <f aca="false">'Social — 28 ngày'!K75</f>
+        <v>1256</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13525,7 +13681,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L74</f>
+        <f aca="false">'Social — 28 ngày'!L75</f>
         <v>82</v>
       </c>
     </row>
@@ -13546,7 +13702,7 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M74</f>
+        <f aca="false">'Social — 28 ngày'!M75</f>
         <v>38</v>
       </c>
     </row>
@@ -13567,7 +13723,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N74</f>
+        <f aca="false">'Social — 28 ngày'!N75</f>
         <v>7</v>
       </c>
     </row>
@@ -13588,8 +13744,8 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O74</f>
-        <v>868</v>
+        <f aca="false">'Social — 28 ngày'!O75</f>
+        <v>869</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13638,7 +13794,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B74</f>
+        <f aca="false">SEO!B75</f>
         <v>29</v>
       </c>
     </row>
@@ -13663,7 +13819,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C74</f>
+        <f aca="false">SEO!C75</f>
         <v>906</v>
       </c>
     </row>
@@ -13688,7 +13844,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D74</f>
+        <f aca="false">SEO!D75</f>
         <v>870</v>
       </c>
     </row>
@@ -13713,8 +13869,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E74</f>
-        <v>39.04</v>
+        <f aca="false">SEO!E75</f>
+        <v>39.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13738,8 +13894,8 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F74</f>
-        <v>8</v>
+        <f aca="false">SEO!F75</f>
+        <v>7</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13763,8 +13919,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G74</f>
-        <v>689</v>
+        <f aca="false">SEO!G75</f>
+        <v>698</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13788,8 +13944,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H74</f>
-        <v>436</v>
+        <f aca="false">SEO!H75</f>
+        <v>439</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13813,8 +13969,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I74</f>
-        <v>23</v>
+        <f aca="false">SEO!I75</f>
+        <v>22</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13838,8 +13994,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J74</f>
-        <v>1.6</v>
+        <f aca="false">SEO!J75</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13863,8 +14019,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K74</f>
-        <v>1424</v>
+        <f aca="false">SEO!K75</f>
+        <v>1501</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13888,8 +14044,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L74</f>
-        <v>20.4</v>
+        <f aca="false">SEO!L75</f>
+        <v>20.9</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13913,8 +14069,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M74</f>
-        <v>132</v>
+        <f aca="false">SEO!M75</f>
+        <v>138</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13938,8 +14094,8 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N74</f>
-        <v>121</v>
+        <f aca="false">SEO!N75</f>
+        <v>122</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13963,8 +14119,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O74</f>
-        <v>325.5</v>
+        <f aca="false">SEO!O75</f>
+        <v>318.4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14006,7 +14162,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B71</f>
+        <f aca="false">Audit!B72</f>
         <v>94</v>
       </c>
     </row>
@@ -14027,7 +14183,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C71</f>
+        <f aca="false">Audit!C72</f>
         <v>98</v>
       </c>
     </row>
@@ -14048,7 +14204,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D71</f>
+        <f aca="false">Audit!D72</f>
         <v>97</v>
       </c>
     </row>
@@ -14069,7 +14225,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E71</f>
+        <f aca="false">Audit!E72</f>
         <v>93</v>
       </c>
     </row>
@@ -14090,8 +14246,8 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F71</f>
-        <v>120</v>
+        <f aca="false">Audit!F72</f>
+        <v>121</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14111,8 +14267,8 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G71</f>
-        <v>98</v>
+        <f aca="false">Audit!G72</f>
+        <v>99</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14132,8 +14288,8 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H71</f>
-        <v>121</v>
+        <f aca="false">Audit!H72</f>
+        <v>122</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14153,7 +14309,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I71</f>
+        <f aca="false">Audit!I72</f>
         <v>98</v>
       </c>
     </row>
@@ -14174,8 +14330,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J71</f>
-        <v>325.5</v>
+        <f aca="false">Audit!J72</f>
+        <v>318.4</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14195,8 +14351,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K71</f>
-        <v>262.5</v>
+        <f aca="false">Audit!K72</f>
+        <v>257</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14216,8 +14372,8 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L71</f>
-        <v>247309</v>
+        <f aca="false">Audit!L72</f>
+        <v>249426</v>
       </c>
     </row>
   </sheetData>

--- a/dxl-metrics.xlsx
+++ b/dxl-metrics.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">DX Living — dữ liệu báo cáo theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất ngày 2026-10-27 · nguồn: data/rollup.json của ba repo báo cáo</t>
+    <t xml:space="preserve">Xuất ngày 2026-10-29 · nguồn: data/rollup.json của ba repo báo cáo</t>
   </si>
   <si>
     <t xml:space="preserve">File này là gì</t>
@@ -96,31 +96,31 @@
     <t xml:space="preserve">Social — theo ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">114 dòng × 7 chỉ số · 2026-07-05 → 2026-10-26</t>
+    <t xml:space="preserve">115 dòng × 7 chỉ số · 2026-07-05 → 2026-10-27</t>
   </si>
   <si>
     <t xml:space="preserve">Social — 28 ngày</t>
   </si>
   <si>
-    <t xml:space="preserve">70 dòng × 14 chỉ số · 2026-07-23 → 2026-10-28</t>
+    <t xml:space="preserve">71 dòng × 14 chỉ số · 2026-07-23 → 2026-10-29</t>
   </si>
   <si>
     <t xml:space="preserve">SEO</t>
   </si>
   <si>
-    <t xml:space="preserve">70 dòng × 14 chỉ số · 2026-06-30 → 2026-10-28</t>
+    <t xml:space="preserve">71 dòng × 14 chỉ số · 2026-06-30 → 2026-10-29</t>
   </si>
   <si>
     <t xml:space="preserve">Audit</t>
   </si>
   <si>
-    <t xml:space="preserve">67 dòng × 11 chỉ số · 2026-07-27 → 2026-10-28</t>
+    <t xml:space="preserve">68 dòng × 11 chỉ số · 2026-07-27 → 2026-10-29</t>
   </si>
   <si>
     <t xml:space="preserve">Số theo NGÀY THẬT — cộng dồn được. Dựng lại từ chuỗi 28 giá trị trong mỗi file ngày, giữ lần đọc mới nhất cho mỗi ngày.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 114 ngày · 7 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 115 ngày · 7 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">grain →</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Ảnh chụp cửa sổ 28 ngày và chỉ số trạng thái — KHÔNG cộng dồn. Chỉ so đầu kỳ với cuối kỳ.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 70 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Social/data/rollup.json · 71 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">FB — followers</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">GSC/GA4 là cửa sổ 28 ngày trượt; Ahrefs, TTFB, sitemap là trạng thái. KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 70 ngày · 14 chỉ số</t>
+    <t xml:space="preserve">Nguồn: SEO/data/rollup.json · 71 ngày · 14 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Ahrefs — trích dẫn AI</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">Mỗi dòng là một lần crawl tại thời điểm. Điểm số và tốc độ — KHÔNG cộng dồn.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 67 ngày · 11 chỉ số</t>
+    <t xml:space="preserve">Nguồn: Audit/data/rollup.json · 68 ngày · 11 chỉ số</t>
   </si>
   <si>
     <t xml:space="preserve">Content</t>
@@ -981,7 +981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -3991,6 +3991,30 @@
       <c r="G119" s="16"/>
       <c r="H119" s="16" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="15" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="F120" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="16"/>
+      <c r="H120" s="16" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4009,7 +4033,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7392,6 +7416,53 @@
         <v>7</v>
       </c>
       <c r="O75" s="16" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="15" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B76" s="16" t="n">
+        <v>117</v>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>167</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>4199</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>653</v>
+      </c>
+      <c r="F76" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="G76" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="H76" s="16" t="n">
+        <v>337</v>
+      </c>
+      <c r="I76" s="16" t="n">
+        <v>1916</v>
+      </c>
+      <c r="J76" s="16" t="n">
+        <v>141</v>
+      </c>
+      <c r="K76" s="16" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L76" s="16" t="n">
+        <v>82</v>
+      </c>
+      <c r="M76" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="N76" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>869</v>
       </c>
     </row>
@@ -7411,7 +7482,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -10701,6 +10772,53 @@
       </c>
       <c r="O75" s="19" t="n">
         <v>318.4</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="15" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B76" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>906</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>870</v>
+      </c>
+      <c r="E76" s="19" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="F76" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G76" s="16" t="n">
+        <v>683</v>
+      </c>
+      <c r="H76" s="16" t="n">
+        <v>434</v>
+      </c>
+      <c r="I76" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="J76" s="19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K76" s="16" t="n">
+        <v>1580</v>
+      </c>
+      <c r="L76" s="19" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M76" s="16" t="n">
+        <v>139</v>
+      </c>
+      <c r="N76" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="O76" s="19" t="n">
+        <v>318.2</v>
       </c>
     </row>
   </sheetData>
@@ -10719,7 +10837,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -13222,6 +13340,44 @@
         <v>257</v>
       </c>
       <c r="L72" s="16" t="n">
+        <v>249426</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="15" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B73" s="16" t="n">
+        <v>94</v>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>93</v>
+      </c>
+      <c r="F73" s="16" t="n">
+        <v>121</v>
+      </c>
+      <c r="G73" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="H73" s="16" t="n">
+        <v>122</v>
+      </c>
+      <c r="I73" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v>318.2</v>
+      </c>
+      <c r="K73" s="16" t="n">
+        <v>258</v>
+      </c>
+      <c r="L73" s="16" t="n">
         <v>249426</v>
       </c>
     </row>
@@ -13290,19 +13446,19 @@
         <v>34</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>125</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>195</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>160</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!B6:B119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!B6:B120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>152</v>
       </c>
     </row>
@@ -13311,19 +13467,19 @@
         <v>35</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>106</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>147</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!C6:C119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!C6:C120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>433</v>
       </c>
     </row>
@@ -13332,20 +13488,20 @@
         <v>36</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>3579</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>4978</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>4776</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!D6:D119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>3998</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!D6:D120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>4037</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13353,20 +13509,20 @@
         <v>37</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>189</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>314</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>425</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!E6:E119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>606</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!E6:E120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>650</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13374,20 +13530,20 @@
         <v>38</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>51</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>69</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>25</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!F6:F119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>63</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!F6:F120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>64</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13395,19 +13551,19 @@
         <v>39</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>275</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>387</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>177</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!G6:G119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!G6:G120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,10,31))</f>
         <v>85</v>
       </c>
     </row>
@@ -13416,20 +13572,20 @@
         <v>40</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,7,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,7,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,7,31))</f>
         <v>869</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,8,31))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,8,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,8,31))</f>
         <v>1161</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,9,30))</f>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,9,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,9,30))</f>
         <v>2465</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">SUMIFS('Social — theo ngày'!H6:H119,'Social — theo ngày'!$A$6:$A$119,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$119,"&lt;="&amp;DATE(2026,10,31))</f>
-        <v>1761</v>
+        <f aca="false">SUMIFS('Social — theo ngày'!H6:H120,'Social — theo ngày'!$A$6:$A$120,"&gt;="&amp;DATE(2026,10,1),'Social — theo ngày'!$A$6:$A$120,"&lt;="&amp;DATE(2026,10,31))</f>
+        <v>1769</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13471,7 +13627,7 @@
         <v>116</v>
       </c>
       <c r="E17" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!B75</f>
+        <f aca="false">'Social — 28 ngày'!B76</f>
         <v>117</v>
       </c>
     </row>
@@ -13492,8 +13648,8 @@
         <v>141</v>
       </c>
       <c r="E18" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!C75</f>
-        <v>171</v>
+        <f aca="false">'Social — 28 ngày'!C76</f>
+        <v>167</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13513,8 +13669,8 @@
         <v>4519</v>
       </c>
       <c r="E19" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!D75</f>
-        <v>4255</v>
+        <f aca="false">'Social — 28 ngày'!D76</f>
+        <v>4199</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13534,8 +13690,8 @@
         <v>422</v>
       </c>
       <c r="E20" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!E75</f>
-        <v>609</v>
+        <f aca="false">'Social — 28 ngày'!E76</f>
+        <v>653</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13555,8 +13711,8 @@
         <v>49</v>
       </c>
       <c r="E21" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!F75</f>
-        <v>49</v>
+        <f aca="false">'Social — 28 ngày'!F76</f>
+        <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13576,8 +13732,8 @@
         <v>20</v>
       </c>
       <c r="E22" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!G75</f>
-        <v>68</v>
+        <f aca="false">'Social — 28 ngày'!G76</f>
+        <v>66</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13597,7 +13753,7 @@
         <v>87</v>
       </c>
       <c r="E23" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!H75</f>
+        <f aca="false">'Social — 28 ngày'!H76</f>
         <v>337</v>
       </c>
     </row>
@@ -13618,8 +13774,8 @@
         <v>2258</v>
       </c>
       <c r="E24" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!I75</f>
-        <v>1968</v>
+        <f aca="false">'Social — 28 ngày'!I76</f>
+        <v>1916</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13639,7 +13795,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!J75</f>
+        <f aca="false">'Social — 28 ngày'!J76</f>
         <v>141</v>
       </c>
     </row>
@@ -13660,8 +13816,8 @@
         <v>1193</v>
       </c>
       <c r="E26" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!K75</f>
-        <v>1256</v>
+        <f aca="false">'Social — 28 ngày'!K76</f>
+        <v>1268</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13681,7 +13837,7 @@
         <v>24</v>
       </c>
       <c r="E27" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!L75</f>
+        <f aca="false">'Social — 28 ngày'!L76</f>
         <v>82</v>
       </c>
     </row>
@@ -13702,8 +13858,8 @@
         <v>36</v>
       </c>
       <c r="E28" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!M75</f>
-        <v>38</v>
+        <f aca="false">'Social — 28 ngày'!M76</f>
+        <v>39</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13723,7 +13879,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!N75</f>
+        <f aca="false">'Social — 28 ngày'!N76</f>
         <v>7</v>
       </c>
     </row>
@@ -13744,7 +13900,7 @@
         <v>634</v>
       </c>
       <c r="E30" s="24" t="n">
-        <f aca="false">'Social — 28 ngày'!O75</f>
+        <f aca="false">'Social — 28 ngày'!O76</f>
         <v>869</v>
       </c>
     </row>
@@ -13794,7 +13950,7 @@
         <v>16</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">SEO!B75</f>
+        <f aca="false">SEO!B76</f>
         <v>29</v>
       </c>
     </row>
@@ -13819,7 +13975,7 @@
         <v>918</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">SEO!C75</f>
+        <f aca="false">SEO!C76</f>
         <v>906</v>
       </c>
     </row>
@@ -13844,7 +14000,7 @@
         <v>882</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">SEO!D75</f>
+        <f aca="false">SEO!D76</f>
         <v>870</v>
       </c>
     </row>
@@ -13869,8 +14025,8 @@
         <v>33.99</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">SEO!E75</f>
-        <v>39.4</v>
+        <f aca="false">SEO!E76</f>
+        <v>39.09</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13894,8 +14050,8 @@
         <v>4</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">SEO!F75</f>
-        <v>7</v>
+        <f aca="false">SEO!F76</f>
+        <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13919,8 +14075,8 @@
         <v>559</v>
       </c>
       <c r="F39" s="24" t="n">
-        <f aca="false">SEO!G75</f>
-        <v>698</v>
+        <f aca="false">SEO!G76</f>
+        <v>683</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13944,8 +14100,8 @@
         <v>394</v>
       </c>
       <c r="F40" s="24" t="n">
-        <f aca="false">SEO!H75</f>
-        <v>439</v>
+        <f aca="false">SEO!H76</f>
+        <v>434</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13969,8 +14125,8 @@
         <v>30</v>
       </c>
       <c r="F41" s="24" t="n">
-        <f aca="false">SEO!I75</f>
-        <v>22</v>
+        <f aca="false">SEO!I76</f>
+        <v>21</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13994,8 +14150,8 @@
         <v>2.8</v>
       </c>
       <c r="F42" s="24" t="n">
-        <f aca="false">SEO!J75</f>
-        <v>1.5</v>
+        <f aca="false">SEO!J76</f>
+        <v>1.3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14019,8 +14175,8 @@
         <v>1056</v>
       </c>
       <c r="F43" s="24" t="n">
-        <f aca="false">SEO!K75</f>
-        <v>1501</v>
+        <f aca="false">SEO!K76</f>
+        <v>1580</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14044,8 +14200,8 @@
         <v>25.8</v>
       </c>
       <c r="F44" s="24" t="n">
-        <f aca="false">SEO!L75</f>
-        <v>20.9</v>
+        <f aca="false">SEO!L76</f>
+        <v>21.1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14069,8 +14225,8 @@
         <v>80</v>
       </c>
       <c r="F45" s="24" t="n">
-        <f aca="false">SEO!M75</f>
-        <v>138</v>
+        <f aca="false">SEO!M76</f>
+        <v>139</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14094,7 +14250,7 @@
         <v>119</v>
       </c>
       <c r="F46" s="24" t="n">
-        <f aca="false">SEO!N75</f>
+        <f aca="false">SEO!N76</f>
         <v>122</v>
       </c>
     </row>
@@ -14119,8 +14275,8 @@
         <v>342</v>
       </c>
       <c r="F47" s="24" t="n">
-        <f aca="false">SEO!O75</f>
-        <v>318.4</v>
+        <f aca="false">SEO!O76</f>
+        <v>318.2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14162,7 +14318,7 @@
         <v>93</v>
       </c>
       <c r="E51" s="24" t="n">
-        <f aca="false">Audit!B72</f>
+        <f aca="false">Audit!B73</f>
         <v>94</v>
       </c>
     </row>
@@ -14183,7 +14339,7 @@
         <v>98</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">Audit!C72</f>
+        <f aca="false">Audit!C73</f>
         <v>98</v>
       </c>
     </row>
@@ -14204,7 +14360,7 @@
         <v>95</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">Audit!D72</f>
+        <f aca="false">Audit!D73</f>
         <v>97</v>
       </c>
     </row>
@@ -14225,7 +14381,7 @@
         <v>92</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">Audit!E72</f>
+        <f aca="false">Audit!E73</f>
         <v>93</v>
       </c>
     </row>
@@ -14246,7 +14402,7 @@
         <v>118</v>
       </c>
       <c r="E55" s="24" t="n">
-        <f aca="false">Audit!F72</f>
+        <f aca="false">Audit!F73</f>
         <v>121</v>
       </c>
     </row>
@@ -14267,7 +14423,7 @@
         <v>98</v>
       </c>
       <c r="E56" s="24" t="n">
-        <f aca="false">Audit!G72</f>
+        <f aca="false">Audit!G73</f>
         <v>99</v>
       </c>
     </row>
@@ -14288,7 +14444,7 @@
         <v>119</v>
       </c>
       <c r="E57" s="24" t="n">
-        <f aca="false">Audit!H72</f>
+        <f aca="false">Audit!H73</f>
         <v>122</v>
       </c>
     </row>
@@ -14309,7 +14465,7 @@
         <v>92</v>
       </c>
       <c r="E58" s="24" t="n">
-        <f aca="false">Audit!I72</f>
+        <f aca="false">Audit!I73</f>
         <v>98</v>
       </c>
     </row>
@@ -14330,8 +14486,8 @@
         <v>342</v>
       </c>
       <c r="E59" s="24" t="n">
-        <f aca="false">Audit!J72</f>
-        <v>318.4</v>
+        <f aca="false">Audit!J73</f>
+        <v>318.2</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14351,8 +14507,8 @@
         <v>276</v>
       </c>
       <c r="E60" s="24" t="n">
-        <f aca="false">Audit!K72</f>
-        <v>257</v>
+        <f aca="false">Audit!K73</f>
+        <v>258</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14372,7 +14528,7 @@
         <v>241329</v>
       </c>
       <c r="E61" s="24" t="n">
-        <f aca="false">Audit!L72</f>
+        <f aca="false">Audit!L73</f>
         <v>249426</v>
       </c>
     </row>
